--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -44,7 +44,7 @@
       <color rgb="00898781"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -54,6 +54,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="002F3E4E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00EEEAF8"/>
       </patternFill>
     </fill>
   </fills>
@@ -69,21 +74,31 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -449,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M6"/>
+  <dimension ref="A1:M63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -535,49 +550,57 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>表格</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>0138</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ZETRIX</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>21920900</v>
-      </c>
-      <c r="G2" s="5" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H2" t="n">
-        <v>28.04</v>
-      </c>
-      <c r="I2" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="K2" s="2" t="n">
-        <v>0.272</v>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" s="7" t="inlineStr"/>
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>信号</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>4324</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>HENGYUAN</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>0.0074</v>
+      </c>
+      <c r="F2" s="5" t="n">
+        <v>1857400</v>
+      </c>
+      <c r="G2" s="6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="I2" s="7" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="n">
+        <v>3.755</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>3.202</v>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>🎯 SAR 转多</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr">
+        <is>
+          <t>SAR转多信号，RSI 63.3未超买，现价高于50日均线约27%，技术面信号偏可靠。</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -587,42 +610,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0138</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GIIB</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>0.715</v>
-      </c>
-      <c r="E3" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="4" t="n">
-        <v>19396300</v>
-      </c>
-      <c r="G3" s="5" t="n">
-        <v>0.77</v>
+          <t>ZETRIX</t>
+        </is>
+      </c>
+      <c r="D3" s="9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E3" s="10" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F3" s="11" t="n">
+        <v>63221000</v>
+      </c>
+      <c r="G3" s="12" t="n">
+        <v>0.18</v>
       </c>
       <c r="H3" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I3" s="9" t="inlineStr">
+        <v>29.97</v>
+      </c>
+      <c r="I3" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>0.642</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>0.548</v>
+      <c r="J3" s="9" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="K3" s="9" t="n">
+        <v>0.272</v>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="7" t="inlineStr"/>
+      <c r="M3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -632,42 +655,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>KINERGY</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0.0133</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>1848300</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.21</v>
+          <t>TANCO</t>
+        </is>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>0.155</v>
+      </c>
+      <c r="E4" s="10" t="n">
+        <v>0.0333</v>
+      </c>
+      <c r="F4" s="11" t="n">
+        <v>7718700</v>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>0.54</v>
       </c>
       <c r="H4" t="n">
-        <v>31.09</v>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>0.391</v>
-      </c>
-      <c r="K4" s="2" t="n">
-        <v>0.404</v>
+        <v>44</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="K4" s="9" t="n">
+        <v>0.18</v>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="7" t="inlineStr"/>
+      <c r="M4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -677,42 +700,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>VS</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E5" s="8" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>1152200</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.01</v>
+          <t>GIIB</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.006999999999999999</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>6527900</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.26</v>
       </c>
       <c r="H5" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="n">
-        <v>0.314</v>
-      </c>
-      <c r="K5" s="2" t="n">
-        <v>0.265</v>
+        <v>78.51000000000001</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="K5" s="9" t="n">
+        <v>0.555</v>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="7" t="inlineStr"/>
+      <c r="M5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -722,45 +745,2587 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>4723</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>JAKS</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>6340900</v>
+      </c>
+      <c r="G6" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K6" s="9" t="n">
+        <v>0.146</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" s="14" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>0362</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ASM</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>6071500</v>
+      </c>
+      <c r="G7" s="12" t="n">
+        <v>12.06</v>
+      </c>
+      <c r="H7" t="n">
+        <v>69.77</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0.128</v>
+      </c>
+      <c r="K7" s="9" t="n">
+        <v>0.129</v>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" s="14" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>0270</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NATGATE</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0244</v>
+      </c>
+      <c r="F8" s="11" t="n">
+        <v>5314200</v>
+      </c>
+      <c r="G8" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H8" t="n">
+        <v>55.32</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>1.963</v>
+      </c>
+      <c r="K8" s="9" t="n">
+        <v>1.786</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4456</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>DNEX</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0241</v>
+      </c>
+      <c r="F9" s="11" t="n">
+        <v>4795500</v>
+      </c>
+      <c r="G9" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H9" t="n">
+        <v>32.88</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="K9" s="9" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" s="14" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>7113</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TOPGLOV</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.0114</v>
+      </c>
+      <c r="F10" s="11" t="n">
+        <v>4385900</v>
+      </c>
+      <c r="G10" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H10" t="n">
+        <v>61.17</v>
+      </c>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="K10" s="9" t="n">
+        <v>0.757</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7215</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NIHSIN</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="11" t="n">
+        <v>4082700</v>
+      </c>
+      <c r="G11" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H11" t="n">
+        <v>74.87</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="K11" s="9" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" s="14" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0193</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>KINERGY</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.0133</v>
+      </c>
+      <c r="F12" s="11" t="n">
+        <v>4047100</v>
+      </c>
+      <c r="G12" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H12" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K12" s="9" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" s="14" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3174</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>L&amp;G</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>0.185</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.0278</v>
+      </c>
+      <c r="F13" s="11" t="n">
+        <v>3657600</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H13" t="n">
+        <v>48.36</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.187</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" s="14" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>5311</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CEB</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="11" t="n">
+        <v>3611000</v>
+      </c>
+      <c r="G14" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H14" t="n">
+        <v>38.24</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="K14" s="9" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" s="14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0050</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>WTS</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.0286</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>3174700</v>
+      </c>
+      <c r="G15" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H15" t="n">
+        <v>56.21</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="K15" s="9" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>7106</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>SUPERMX</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.0345</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>3103900</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H16" t="n">
+        <v>58.64</v>
+      </c>
+      <c r="I16" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" s="14" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>6963</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>VS</t>
+        </is>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>2661200</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="H17" t="n">
+        <v>60.54</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" s="14" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0457</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PENTECH</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>2562300</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>41.29</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" s="14" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0339</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CBHB</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="F19" s="11" t="n">
+        <v>2454700</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H19" t="n">
+        <v>37.19</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>1.014</v>
+      </c>
+      <c r="K19" s="9" t="n">
+        <v>0.977</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" s="14" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>5199</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HIBISCS</t>
+        </is>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E20" s="10" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="F20" s="11" t="n">
+        <v>2271900</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H20" t="n">
+        <v>65.53</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>2.201</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" s="14" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1651</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>MRCB</t>
+        </is>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F21" s="11" t="n">
+        <v>2111600</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H21" t="n">
+        <v>34.07</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="K21" s="9" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" s="14" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>5238</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AAGB</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>-0.0115</v>
+      </c>
+      <c r="F22" s="11" t="n">
+        <v>2067400</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H22" t="n">
+        <v>25.47</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" s="14" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>5151</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>HEXTAR</t>
         </is>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D23" s="9" t="n">
         <v>0.775</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E23" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="4" t="n">
-        <v>690000</v>
-      </c>
-      <c r="G6" s="5" t="n">
+      <c r="F23" s="11" t="n">
+        <v>2048700</v>
+      </c>
+      <c r="G23" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H23" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K23" s="9" t="n">
+        <v>0.776</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" s="14" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0198</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>GDB</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="11" t="n">
+        <v>1943200</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="H24" t="n">
+        <v>78.48</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.443</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.436</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" s="14" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>5161</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>JCY</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="E25" s="10" t="n">
+        <v>0.0092</v>
+      </c>
+      <c r="F25" s="11" t="n">
+        <v>1895500</v>
+      </c>
+      <c r="G25" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H25" t="n">
+        <v>47.37</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" s="14" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5210</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ARMADA</t>
+        </is>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="E26" s="10" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="F26" s="11" t="n">
+        <v>1818500</v>
+      </c>
+      <c r="G26" s="12" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="H26" t="n">
+        <v>57.39</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="K26" s="9" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" s="14" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5183</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PCHEM</t>
+        </is>
+      </c>
+      <c r="D27" s="9" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.0423</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>1779800</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H27" t="n">
+        <v>60.11</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="n">
+        <v>4.411</v>
+      </c>
+      <c r="K27" s="9" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" s="14" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0479</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>RPLANET</t>
+        </is>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" s="11" t="n">
+        <v>1750600</v>
+      </c>
+      <c r="G28" s="12" t="n"/>
+      <c r="I28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" s="14" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>3182</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>GENTING</t>
+        </is>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E29" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" s="11" t="n">
+        <v>1687000</v>
+      </c>
+      <c r="G29" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H29" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="n">
+        <v>1.591</v>
+      </c>
+      <c r="K29" s="9" t="n">
+        <v>1.884</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" s="14" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>7204</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>D&amp;O</t>
+        </is>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="E30" s="10" t="n">
+        <v>0.0233</v>
+      </c>
+      <c r="F30" s="11" t="n">
+        <v>1678300</v>
+      </c>
+      <c r="G30" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H30" t="n">
+        <v>40.39</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J30" s="9" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" s="14" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0248</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>YEWLEE</t>
+        </is>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.007900000000000001</v>
+      </c>
+      <c r="F31" s="11" t="n">
+        <v>1644800</v>
+      </c>
+      <c r="G31" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H31" t="n">
+        <v>63.35</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J31" s="9" t="n">
+        <v>0.623</v>
+      </c>
+      <c r="K31" s="9" t="n">
+        <v>0.618</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>5216</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>DATASONIC</t>
+        </is>
+      </c>
+      <c r="D32" s="9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F32" s="11" t="n">
+        <v>1643700</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>43.03</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J32" s="9" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="K32" s="9" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" s="14" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>5184</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CYPARK</t>
+        </is>
+      </c>
+      <c r="D33" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="11" t="n">
+        <v>1517000</v>
+      </c>
+      <c r="G33" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H33" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J33" s="9" t="n">
+        <v>0.736</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" s="14" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0476</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>SLG</t>
+        </is>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="11" t="n">
+        <v>1512600</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" s="14" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0262</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>SUNVIEW</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="E35" s="15" t="n">
+        <v>-0.0238</v>
+      </c>
+      <c r="F35" s="11" t="n">
+        <v>1494600</v>
+      </c>
+      <c r="G35" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H35" t="n">
+        <v>54.72</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J35" s="9" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K35" s="9" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" s="14" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0181</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>AEMULUS</t>
+        </is>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>-0.0114</v>
+      </c>
+      <c r="F36" s="11" t="n">
+        <v>1465200</v>
+      </c>
+      <c r="G36" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H36" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J36" s="9" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K36" s="9" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" s="14" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>5099</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CAPITALA</t>
+        </is>
+      </c>
+      <c r="D37" s="9" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0244</v>
+      </c>
+      <c r="F37" s="11" t="n">
+        <v>1439500</v>
+      </c>
+      <c r="G37" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H37" t="n">
+        <v>32.99</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>0.225</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" s="14" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0453</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>EIPOWER</t>
+        </is>
+      </c>
+      <c r="D38" s="9" t="n">
+        <v>0.805</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.019</v>
+      </c>
+      <c r="F38" s="11" t="n">
+        <v>1419500</v>
+      </c>
+      <c r="G38" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H38" t="n">
+        <v>38.5</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J38" s="9" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="K38" s="9" t="n">
+        <v>0.856</v>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" s="14" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0024</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>JAG</t>
+        </is>
+      </c>
+      <c r="D39" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>-0.0263</v>
+      </c>
+      <c r="F39" s="11" t="n">
+        <v>1191200</v>
+      </c>
+      <c r="G39" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H39" t="n">
+        <v>48.52</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" s="14" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0368</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>OXB</t>
+        </is>
+      </c>
+      <c r="D40" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F40" s="11" t="n">
+        <v>1179600</v>
+      </c>
+      <c r="G40" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H40" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J40" s="9" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="K40" s="9" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" s="14" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0382</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>FOODIE</t>
+        </is>
+      </c>
+      <c r="D41" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0169</v>
+      </c>
+      <c r="F41" s="11" t="n">
+        <v>1159200</v>
+      </c>
+      <c r="G41" s="12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="H41" t="n">
+        <v>49.66</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" s="14" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0166</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>INARI</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F42" s="11" t="n">
+        <v>1158900</v>
+      </c>
+      <c r="G42" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H42" t="n">
+        <v>40.13</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J42" s="9" t="n">
+        <v>2.597</v>
+      </c>
+      <c r="K42" s="9" t="n">
+        <v>2.558</v>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" s="14" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D43" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E43" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="11" t="n">
+        <v>1153500</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H43" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J43" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K43" s="9" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" s="14" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>5301</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CTOS</t>
+        </is>
+      </c>
+      <c r="D44" s="9" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>-0.0132</v>
+      </c>
+      <c r="F44" s="11" t="n">
+        <v>1150100</v>
+      </c>
+      <c r="G44" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H44" t="n">
+        <v>27.63</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>0.478</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>0.589</v>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" s="14" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0292</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>JTGROUP</t>
+        </is>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>-0.0224</v>
+      </c>
+      <c r="F45" s="11" t="n">
+        <v>1083600</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="H45" t="n">
+        <v>58.28</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J45" s="9" t="n">
+        <v>1.247</v>
+      </c>
+      <c r="K45" s="9" t="n">
+        <v>1.108</v>
+      </c>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" s="14" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0477</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ECOSYS</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="11" t="n">
+        <v>1081100</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" s="14" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>5398</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>GAMUDA</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="F47" s="11" t="n">
+        <v>992600</v>
+      </c>
+      <c r="G47" s="12" t="n">
         <v>0.04</v>
       </c>
-      <c r="H6" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
+      <c r="H47" t="n">
+        <v>46.66</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="n">
+        <v>4.871</v>
+      </c>
+      <c r="K47" s="9" t="n">
+        <v>4.756</v>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" s="14" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0208</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GREATEC</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="F48" s="11" t="n">
+        <v>982700</v>
+      </c>
+      <c r="G48" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H48" t="n">
+        <v>43.71</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J48" s="9" t="n">
+        <v>2.595</v>
+      </c>
+      <c r="K48" s="9" t="n">
+        <v>2.606</v>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" s="14" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>5168</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>HARTA</t>
+        </is>
+      </c>
+      <c r="D49" s="9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0377</v>
+      </c>
+      <c r="F49" s="11" t="n">
+        <v>979300</v>
+      </c>
+      <c r="G49" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H49" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J49" s="9" t="n">
+        <v>1.082</v>
+      </c>
+      <c r="K49" s="9" t="n">
+        <v>1.053</v>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" s="14" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>7121</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>XL</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <v>-0.0061</v>
+      </c>
+      <c r="F50" s="11" t="n">
+        <v>937500</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H50" t="n">
+        <v>54.27</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
         <is>
           <t>多头</t>
         </is>
       </c>
-      <c r="J6" s="2" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>0.776</v>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" s="7" t="inlineStr"/>
+      <c r="J50" s="9" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="K50" s="9" t="n">
+        <v>0.8139999999999999</v>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" s="14" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D51" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="11" t="n">
+        <v>807500</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H51" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J51" s="9" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="K51" s="9" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" s="14" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>0455</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>BUSCAP</t>
+        </is>
+      </c>
+      <c r="D52" s="9" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>-0.0692</v>
+      </c>
+      <c r="F52" s="11" t="n">
+        <v>773600</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H52" t="n">
+        <v>46.84</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="K52" s="9" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" s="14" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>4715</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>GENM</t>
+        </is>
+      </c>
+      <c r="D53" s="9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="E53" s="15" t="n">
+        <v>-0.0086</v>
+      </c>
+      <c r="F53" s="11" t="n">
+        <v>756000</v>
+      </c>
+      <c r="G53" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H53" t="n">
+        <v>19.71</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J53" s="9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>1.516</v>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" s="14" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D54" s="9" t="n">
+        <v>0.725</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>-0.0136</v>
+      </c>
+      <c r="F54" s="11" t="n">
+        <v>745600</v>
+      </c>
+      <c r="G54" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H54" t="n">
+        <v>48.8</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K54" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" s="14" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0083</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>NOTION</t>
+        </is>
+      </c>
+      <c r="D55" s="9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>-0.0182</v>
+      </c>
+      <c r="F55" s="11" t="n">
+        <v>708300</v>
+      </c>
+      <c r="G55" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H55" t="n">
+        <v>36.41</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J55" s="9" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="K55" s="9" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" s="14" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="E56" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="11" t="n">
+        <v>683300</v>
+      </c>
+      <c r="G56" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H56" t="n">
+        <v>50.44</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>1.264</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" s="14" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>4677</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>YTL</t>
+        </is>
+      </c>
+      <c r="D57" s="9" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>665100</v>
+      </c>
+      <c r="G57" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H57" t="n">
+        <v>38.59</v>
+      </c>
+      <c r="I57" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J57" s="9" t="n">
+        <v>2.117</v>
+      </c>
+      <c r="K57" s="9" t="n">
+        <v>2.234</v>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" s="14" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>-0.0187</v>
+      </c>
+      <c r="F58" s="11" t="n">
+        <v>661900</v>
+      </c>
+      <c r="G58" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H58" t="n">
+        <v>39.04</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J58" s="9" t="n">
+        <v>1.129</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" s="14" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D59" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.04650000000000001</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>659400</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H59" t="n">
+        <v>43.94</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n">
+        <v>1.367</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>1.444</v>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" s="14" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>639500</v>
+      </c>
+      <c r="G60" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H60" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J60" s="9" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="K60" s="9" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" s="14" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D61" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>-0.008500000000000001</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>600700</v>
+      </c>
+      <c r="G61" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H61" t="n">
+        <v>34.76</v>
+      </c>
+      <c r="I61" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J61" s="9" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="K61" s="9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" s="14" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0236</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>RAMSSOL</t>
+        </is>
+      </c>
+      <c r="D62" s="9" t="n">
+        <v>0.755</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>-0.0131</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>551000</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>45.88</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n">
+        <v>0.768</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>0.771</v>
+      </c>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" s="14" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D63" s="9" t="n">
+        <v>0.515</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>-0.009599999999999999</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>543200</v>
+      </c>
+      <c r="G63" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H63" t="n">
+        <v>43.43</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J63" s="9" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="K63" s="9" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" s="14" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M6"/>
+  <autoFilter ref="A1:M63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$88</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M63"/>
+  <dimension ref="A1:M88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0074</v>
+        <v>0.0173</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>1857400</v>
+        <v>2528700</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.25</v>
+        <v>0.34</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.3</v>
+        <v>64.12</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.755</v>
+        <v>3.759</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.202</v>
+        <v>3.203</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 63.3未超买，现价高于50日均线约27%，技术面信号偏可靠。</t>
+          <t>SAR转多信号可靠，RSI 64.12偏高但未超买，现价4.12高于50日均线3.203约28.6%，多头动能较强。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>63221000</v>
+        <v>72599300</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H3" t="n">
-        <v>29.97</v>
+        <v>28.04</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.272</v>
@@ -655,39 +655,39 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>6963</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>VS</t>
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E4" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.32</v>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>7718700</v>
+        <v>15243900</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.54</v>
+        <v>0.18</v>
       </c>
       <c r="H4" t="n">
-        <v>44</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.38</v>
+      </c>
+      <c r="I4" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.154</v>
+        <v>0.313</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.18</v>
+        <v>0.264</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -700,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>6527900</v>
+        <v>11519300</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.26</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>78.51000000000001</v>
+        <v>44</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.649</v>
+        <v>0.154</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.555</v>
+        <v>0.18</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.165</v>
+        <v>0.41</v>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.0294</v>
+        <v>-0.012</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>6340900</v>
+        <v>8590400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.1</v>
+        <v>0.24</v>
       </c>
       <c r="H6" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.83</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.16</v>
+        <v>0.457</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.146</v>
+        <v>0.476</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.14</v>
+        <v>0.465</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>0.12</v>
+        <v>0.0109</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>6071500</v>
+        <v>8255900</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>12.06</v>
+        <v>0.23</v>
       </c>
       <c r="H7" t="n">
-        <v>69.77</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.128</v>
+        <v>0.412</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.129</v>
+        <v>0.309</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2</v>
+        <v>0.165</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0244</v>
+        <v>-0.0294</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>5314200</v>
+        <v>7412300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.19</v>
+        <v>0.12</v>
       </c>
       <c r="H8" t="n">
-        <v>55.32</v>
+        <v>53.64</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1.963</v>
+        <v>0.16</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1.786</v>
+        <v>0.146</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.405</v>
+        <v>1.99</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0241</v>
+        <v>-0.0293</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>4795500</v>
+        <v>7301200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.13</v>
+        <v>0.26</v>
       </c>
       <c r="H9" t="n">
-        <v>32.88</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.66</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.457</v>
+        <v>1.962</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.476</v>
+        <v>1.786</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.0114</v>
+        <v>0.71</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.006999999999999999</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>4385900</v>
+        <v>7119800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H10" t="n">
-        <v>61.17</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.85</v>
+        <v>0.649</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.757</v>
+        <v>0.555</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0</v>
+        <v>0.14</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.12</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>4082700</v>
+        <v>6749800</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.11</v>
+        <v>13.41</v>
       </c>
       <c r="H11" t="n">
-        <v>74.87</v>
+        <v>69.77</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.411</v>
+        <v>0.128</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.309</v>
+        <v>0.129</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0133</v>
+        <v>0.005</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>4047100</v>
+        <v>6128500</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.46</v>
+        <v>16.84</v>
       </c>
       <c r="H12" t="n">
-        <v>18.34</v>
+        <v>47.02</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.39</v>
+        <v>0.005</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.404</v>
+        <v>0.006</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.185</v>
+        <v>0.895</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>0.0278</v>
+        <v>0.017</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>3657600</v>
+        <v>5649400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.17</v>
+        <v>0.08</v>
       </c>
       <c r="H13" t="n">
-        <v>48.36</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.84</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.187</v>
+        <v>0.851</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.186</v>
+        <v>0.757</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E14" s="15" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>3611000</v>
+        <v>4968500</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>38.24</v>
+        <v>18.34</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.287</v>
+        <v>0.39</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.279</v>
+        <v>0.404</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,39 +1150,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.0286</v>
+        <v>0.445</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.023</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>3174700</v>
+        <v>4316700</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.59</v>
+        <v>0.22</v>
       </c>
       <c r="H15" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>57.51</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.163</v>
+        <v>0.429</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.165</v>
+        <v>0.381</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>-0.0265</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>4299700</v>
+      </c>
+      <c r="G16" s="12" t="n">
         <v>0.45</v>
       </c>
-      <c r="E16" s="10" t="n">
-        <v>0.0345</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>3103900</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0.16</v>
-      </c>
       <c r="H16" t="n">
-        <v>58.64</v>
+        <v>37.19</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.429</v>
+        <v>1.014</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.381</v>
+        <v>0.977</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6963</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>VS</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>2661200</v>
+        <v>4177600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>0.03</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="n">
-        <v>60.54</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.314</v>
+        <v>0.159</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.265</v>
+        <v>0.157</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,28 +1285,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.315</v>
+        <v>0.18</v>
       </c>
       <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>2562300</v>
+        <v>3778300</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.25</v>
+        <v>0.18</v>
       </c>
       <c r="H18" t="n">
-        <v>41.29</v>
+        <v>44.11</v>
       </c>
       <c r="I18" s="16" t="inlineStr">
         <is>
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.338</v>
+        <v>0.186</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.336</v>
+        <v>0.186</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1330,28 +1330,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>-0.0265</v>
+        <v>0.265</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>2454700</v>
+        <v>3761000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19</v>
+        <v>40.68</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.014</v>
+        <v>0.287</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.977</v>
+        <v>0.28</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,28 +1375,28 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E20" s="10" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.82</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>2271900</v>
+        <v>3637000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.64</v>
+        <v>0.23</v>
       </c>
       <c r="H20" t="n">
-        <v>65.53</v>
+        <v>54.27</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1404,10 +1404,10 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>2.28</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>2.201</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1420,28 +1420,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.02</v>
+        <v>0.425</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>2111600</v>
+        <v>3619400</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.26</v>
+        <v>0.22</v>
       </c>
       <c r="H21" t="n">
-        <v>34.07</v>
+        <v>24.81</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1449,10 +1449,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.269</v>
+        <v>0.484</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.294</v>
+        <v>0.63</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,28 +1465,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.0115</v>
+        <v>0.205</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>2067400</v>
+        <v>3569200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
       <c r="H22" t="n">
-        <v>25.47</v>
+        <v>28.46</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1494,10 +1494,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.484</v>
+        <v>0.225</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.63</v>
+        <v>0.272</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1510,28 +1510,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>2048700</v>
+        <v>3194800</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.13</v>
+        <v>0.59</v>
       </c>
       <c r="H23" t="n">
-        <v>50.42</v>
+        <v>56.21</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.774</v>
+        <v>0.163</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.776</v>
+        <v>0.165</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,40 +1555,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.505</v>
+        <v>0.26</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>1943200</v>
-      </c>
-      <c r="G24" s="12" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="H24" t="n">
-        <v>78.48</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>0.436</v>
-      </c>
+        <v>3159000</v>
+      </c>
+      <c r="G24" s="12" t="n"/>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1600,39 +1591,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.55</v>
+        <v>0.345</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>0.0092</v>
+        <v>0.0147</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>1895500</v>
+        <v>3080000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.09</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.39</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.336</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.545</v>
+        <v>0.343</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1645,28 +1636,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E26" s="10" t="n">
-        <v>0.0147</v>
+        <v>2.42</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>1818500</v>
+        <v>3075200</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.41</v>
+        <v>0.87</v>
       </c>
       <c r="H26" t="n">
-        <v>57.39</v>
+        <v>63.94</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1674,10 +1665,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.336</v>
+        <v>2.278</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.343</v>
+        <v>2.201</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1690,39 +1681,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.0423</v>
+        <v>1.35</v>
+      </c>
+      <c r="E27" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>1779800</v>
+        <v>2966700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.36</v>
+        <v>0.22</v>
       </c>
       <c r="H27" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.69</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>4.411</v>
+        <v>1.591</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>4.44</v>
+        <v>1.884</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1735,31 +1726,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0</v>
+        <v>0.44</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>1750600</v>
-      </c>
-      <c r="G28" s="12" t="n"/>
+        <v>2883900</v>
+      </c>
+      <c r="G28" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H28" t="n">
+        <v>40.39</v>
+      </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.468</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1771,28 +1771,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E29" s="17" t="n">
-        <v>0</v>
+        <v>0.255</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>1687000</v>
+        <v>2659700</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.13</v>
+        <v>0.32</v>
       </c>
       <c r="H29" t="n">
-        <v>18.69</v>
+        <v>34.07</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1800,10 +1800,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>1.591</v>
+        <v>0.269</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>1.884</v>
+        <v>0.294</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1816,39 +1816,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E30" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.775</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>1678300</v>
+        <v>2630000</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>0.17</v>
       </c>
       <c r="H30" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.496</v>
+        <v>0.774</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.468</v>
+        <v>0.776</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1861,39 +1861,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>4.8</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>-0.0062</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>1644800</v>
+        <v>2627600</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.16</v>
+        <v>0.11</v>
       </c>
       <c r="H31" t="n">
-        <v>63.35</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.66</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.623</v>
+        <v>4.871</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.618</v>
+        <v>4.756</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1906,28 +1906,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>-0.0182</v>
+        <v>0.555</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>1643700</v>
+        <v>2621100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.2</v>
+        <v>0.13</v>
       </c>
       <c r="H32" t="n">
-        <v>43.03</v>
+        <v>48.37</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.285</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.283</v>
+        <v>0.545</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1951,40 +1951,33 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.73</v>
+        <v>0.225</v>
       </c>
       <c r="E33" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>1517000</v>
+        <v>2581400</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0.12</v>
       </c>
-      <c r="H33" t="n">
-        <v>49.2</v>
-      </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J33" s="9" t="n">
-        <v>0.736</v>
-      </c>
-      <c r="K33" s="9" t="n">
-        <v>0.724</v>
-      </c>
+      <c r="J33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -1996,33 +1989,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>0</v>
+        <v>0.32</v>
+      </c>
+      <c r="E34" s="10" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>1512600</v>
+        <v>2574400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="H34" t="n">
+        <v>43.38</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J34" s="9" t="n"/>
-      <c r="K34" s="9" t="n"/>
+      <c r="J34" s="9" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="K34" s="9" t="n">
+        <v>0.336</v>
+      </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
     </row>
@@ -2034,39 +2034,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.41</v>
+        <v>0.765</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>-0.0238</v>
+        <v>-0.0377</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>1494600</v>
+        <v>2542700</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.12</v>
+        <v>0.54</v>
       </c>
       <c r="H35" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.34</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.4</v>
+        <v>0.837</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.382</v>
+        <v>0.619</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>-0.0114</v>
+        <v>4.66</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0379</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>1465200</v>
+        <v>2382100</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.21</v>
+        <v>0.48</v>
       </c>
       <c r="H36" t="n">
-        <v>52.42</v>
+        <v>59.54</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.429</v>
+        <v>4.409</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.418</v>
+        <v>4.439</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,39 +2124,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <v>0.0244</v>
+        <v>0.5</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>1439500</v>
+        <v>2065700</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
       <c r="H37" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.41</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.225</v>
+        <v>0.443</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.272</v>
+        <v>0.436</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.805</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.019</v>
+        <v>0.865</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1419500</v>
+        <v>1934100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.22</v>
+        <v>0.09</v>
       </c>
       <c r="H38" t="n">
-        <v>38.5</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.89</v>
+        <v>0.868</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.856</v>
+        <v>0.869</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,40 +2214,33 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>-0.0263</v>
+        <v>0.725</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1191200</v>
+        <v>1926500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H39" t="n">
-        <v>48.52</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J39" s="9" t="n">
-        <v>0.372</v>
-      </c>
-      <c r="K39" s="9" t="n">
-        <v>0.37</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2259,39 +2252,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.575</v>
+        <v>0.41</v>
       </c>
       <c r="E40" s="15" t="n">
-        <v>-0.0086</v>
+        <v>-0.0238</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1179600</v>
+        <v>1923200</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H40" t="n">
-        <v>60.37</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.72</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.535</v>
+        <v>0.4</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.482</v>
+        <v>0.382</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2297,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.3</v>
+        <v>2.47</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.0169</v>
+        <v>0.004099999999999999</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1159200</v>
+        <v>1852200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.02</v>
+        <v>0.1</v>
       </c>
       <c r="H41" t="n">
-        <v>49.66</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.83</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.294</v>
+        <v>2.6</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.329</v>
+        <v>2.559</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,28 +2342,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.8</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1158900</v>
+        <v>1851100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.06</v>
+        <v>0.29</v>
       </c>
       <c r="H42" t="n">
-        <v>40.13</v>
+        <v>37.71</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2378,10 +2371,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>2.597</v>
+        <v>0.889</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>2.558</v>
+        <v>0.856</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E43" s="17" t="n">
-        <v>0</v>
+        <v>2.05</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>-0.0097</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1153500</v>
+        <v>1845100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.31</v>
+        <v>0.17</v>
       </c>
       <c r="H43" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.59</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.276</v>
+        <v>2.117</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.268</v>
+        <v>2.234</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,28 +2432,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.375</v>
+        <v>0.435</v>
       </c>
       <c r="E44" s="15" t="n">
-        <v>-0.0132</v>
+        <v>-0.0114</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1150100</v>
+        <v>1841900</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.11</v>
+        <v>0.27</v>
       </c>
       <c r="H44" t="n">
-        <v>27.63</v>
+        <v>52.42</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2468,10 +2461,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.478</v>
+        <v>0.429</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.589</v>
+        <v>0.418</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2484,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.0224</v>
+        <v>0.74</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.0137</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1083600</v>
+        <v>1761400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.31</v>
+        <v>0.14</v>
       </c>
       <c r="H45" t="n">
-        <v>58.28</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.62</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>1.247</v>
+        <v>0.737</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>1.108</v>
+        <v>0.724</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2529,33 +2522,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0</v>
+        <v>0.27</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1081100</v>
+        <v>1663700</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.03</v>
+        <v>0.2</v>
+      </c>
+      <c r="H46" t="n">
+        <v>43.03</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J46" s="9" t="n"/>
-      <c r="K46" s="9" t="n"/>
+      <c r="J46" s="9" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="K46" s="9" t="n">
+        <v>0.283</v>
+      </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
     </row>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0062</v>
+        <v>-0.0299</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>992600</v>
+        <v>1657500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.04</v>
+        <v>0.47</v>
       </c>
       <c r="H47" t="n">
-        <v>46.66</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.31</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>4.871</v>
+        <v>1.246</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>4.756</v>
+        <v>1.107</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>-0.0195</v>
+        <v>0.64</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>982700</v>
+        <v>1644800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H48" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.35</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.595</v>
+        <v>0.623</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.606</v>
+        <v>0.618</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0377</v>
+        <v>0.38</v>
+      </c>
+      <c r="E49" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>979300</v>
+        <v>1614100</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="H49" t="n">
-        <v>53.32</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.08</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>1.082</v>
+        <v>0.479</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>1.053</v>
+        <v>0.589</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.82</v>
+        <v>6.95</v>
       </c>
       <c r="E50" s="15" t="n">
-        <v>-0.0061</v>
+        <v>-0.01</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>937500</v>
+        <v>1579200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.06</v>
+        <v>0.33</v>
       </c>
       <c r="H50" t="n">
-        <v>54.27</v>
+        <v>60.48</v>
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>6.798</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>6.823</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>807500</v>
+        <v>1545100</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="H51" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>19.71</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.803</v>
+        <v>1.32</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.777</v>
+        <v>1.516</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>-0.0692</v>
+        <v>0.23</v>
+      </c>
+      <c r="E52" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>773600</v>
+        <v>1454400</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.16</v>
+        <v>1.08</v>
       </c>
       <c r="H52" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.835</v>
+        <v>0.23</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.619</v>
+        <v>0.238</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.15</v>
+        <v>2.55</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.0086</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>756000</v>
+        <v>1453200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.15</v>
+        <v>0.26</v>
       </c>
       <c r="H53" t="n">
-        <v>19.71</v>
+        <v>45.87</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.32</v>
+        <v>2.598</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>1.516</v>
+        <v>2.607</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.0136</v>
+        <v>1.1</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0377</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>745600</v>
+        <v>1424100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.25</v>
+        <v>0.16</v>
       </c>
       <c r="H54" t="n">
-        <v>48.8</v>
+        <v>53.32</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.741</v>
+        <v>1.082</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.707</v>
+        <v>1.053</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>-0.0182</v>
+        <v>0.305</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>708300</v>
+        <v>1424000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.08</v>
+        <v>1.25</v>
       </c>
       <c r="H55" t="n">
-        <v>36.41</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.614</v>
+        <v>0.295</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.617</v>
+        <v>0.329</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,40 +2972,38 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E56" s="17" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.0143</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>683300</v>
+        <v>1318200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.27</v>
+        <v>0.24</v>
       </c>
       <c r="H56" t="n">
-        <v>50.44</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>1.264</v>
-      </c>
-      <c r="K56" s="9" t="n">
-        <v>1.183</v>
-      </c>
+        <v>0.333</v>
+      </c>
+      <c r="K56" s="9" t="n"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
     </row>
@@ -3017,28 +3015,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
         <v>2.05</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>-0.0097</v>
+        <v>-0.0049</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>665100</v>
+        <v>1316500</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.06</v>
+        <v>3.94</v>
       </c>
       <c r="H57" t="n">
-        <v>38.59</v>
+        <v>40.07</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3046,10 +3044,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.117</v>
+        <v>2.076</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.234</v>
+        <v>2.082</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3060,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.05</v>
+        <v>0.755</v>
       </c>
       <c r="E58" s="15" t="n">
-        <v>-0.0187</v>
+        <v>-0.0131</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>661900</v>
+        <v>1256000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.2</v>
+        <v>0.16</v>
       </c>
       <c r="H58" t="n">
-        <v>39.04</v>
+        <v>45.88</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3091,10 +3089,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.129</v>
+        <v>0.768</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.11</v>
+        <v>0.771</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,39 +3105,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0.04650000000000001</v>
+        <v>0.375</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>659400</v>
+        <v>1246200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.36</v>
+        <v>0.18</v>
       </c>
       <c r="H59" t="n">
-        <v>43.94</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.367</v>
+        <v>0.373</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.444</v>
+        <v>0.37</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,28 +3150,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>3.39</v>
+        <v>0.3</v>
       </c>
       <c r="E60" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0345</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>639500</v>
+        <v>1230300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="H60" t="n">
-        <v>88.61</v>
+        <v>38.77</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3181,10 +3179,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>3.003</v>
+        <v>0.317</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.546</v>
+        <v>0.361</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3195,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.58</v>
+        <v>0.575</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.0086</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>600700</v>
+        <v>1227500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H61" t="n">
-        <v>34.76</v>
+        <v>60.37</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3226,10 +3224,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.652</v>
+        <v>0.535</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.482</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,28 +3240,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>-0.0131</v>
+        <v>0.25</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>551000</v>
+        <v>1188500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H62" t="n">
-        <v>45.88</v>
+        <v>41.23</v>
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
@@ -3271,10 +3269,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.768</v>
+        <v>0.266</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.771</v>
+        <v>0.286</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,28 +3285,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.515</v>
+        <v>0.545</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0091</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>543200</v>
+        <v>1157300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H63" t="n">
-        <v>43.43</v>
+        <v>37.01</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3316,16 +3314,1141 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.548</v>
+        <v>0.614</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.523</v>
+        <v>0.617</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
     </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0450</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>MFGROUP</t>
+        </is>
+      </c>
+      <c r="D64" s="9" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>1153500</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="H64" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J64" s="9" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K64" s="9" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" s="14" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1295</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>PBBANK</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.0042</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>1125600</v>
+      </c>
+      <c r="G65" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H65" t="n">
+        <v>48.77</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="n">
+        <v>4.727</v>
+      </c>
+      <c r="K65" s="9" t="n">
+        <v>4.818</v>
+      </c>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" s="14" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0275</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>OPPSTAR</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="E66" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>1120900</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H66" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n">
+        <v>0.652</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0.6850000000000001</v>
+      </c>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" s="14" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0321</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>SDCG</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="11" t="n">
+        <v>1108900</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H67" t="n">
+        <v>68.73</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="n">
+        <v>0.803</v>
+      </c>
+      <c r="K67" s="9" t="n">
+        <v>0.777</v>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" s="14" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>6742</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>YTLPOWR</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="n">
+        <v>5.21</v>
+      </c>
+      <c r="E68" s="15" t="n">
+        <v>-0.0151</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>1037400</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H68" t="n">
+        <v>39.47</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="n">
+        <v>5.433</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>5.506</v>
+      </c>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" s="14" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>5176</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>SUNREIT</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="F69" s="11" t="n">
+        <v>1002800</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H69" t="n">
+        <v>46.51</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J69" s="9" t="n">
+        <v>2.039</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>2.065</v>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" s="14" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>8907</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="D70" s="9" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="11" t="n">
+        <v>911200</v>
+      </c>
+      <c r="G70" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H70" t="n">
+        <v>32.27</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>1.666</v>
+      </c>
+      <c r="K70" s="9" t="n">
+        <v>1.746</v>
+      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" s="14" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>4197</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SIME</t>
+        </is>
+      </c>
+      <c r="D71" s="9" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="E71" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F71" s="11" t="n">
+        <v>874800</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H71" t="n">
+        <v>46.38</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J71" s="9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>2.408</v>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" s="14" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D72" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>-0.0068</v>
+      </c>
+      <c r="F72" s="11" t="n">
+        <v>873000</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H72" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="I72" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J72" s="9" t="n">
+        <v>0.741</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" s="14" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>5141</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>DAYANG</t>
+        </is>
+      </c>
+      <c r="D73" s="9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="E73" s="10" t="n">
+        <v>0.0388</v>
+      </c>
+      <c r="F73" s="11" t="n">
+        <v>838500</v>
+      </c>
+      <c r="G73" s="12" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H73" t="n">
+        <v>42.22</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J73" s="9" t="n">
+        <v>1.366</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>1.443</v>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" s="14" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>5352</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>MTTSL</t>
+        </is>
+      </c>
+      <c r="D74" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>-0.007800000000000001</v>
+      </c>
+      <c r="F74" s="11" t="n">
+        <v>817500</v>
+      </c>
+      <c r="G74" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H74" t="n">
+        <v>58.78</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.225</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.204</v>
+      </c>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" s="14" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>7153</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>KOSSAN</t>
+        </is>
+      </c>
+      <c r="D75" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F75" s="11" t="n">
+        <v>802000</v>
+      </c>
+      <c r="G75" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H75" t="n">
+        <v>52.08</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>1.172</v>
+      </c>
+      <c r="K75" s="9" t="n">
+        <v>1.147</v>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" s="14" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D76" s="9" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F76" s="11" t="n">
+        <v>785000</v>
+      </c>
+      <c r="G76" s="12" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H76" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="I76" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J76" s="9" t="n">
+        <v>1.265</v>
+      </c>
+      <c r="K76" s="9" t="n">
+        <v>1.183</v>
+      </c>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" s="14" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F77" s="11" t="n">
+        <v>784000</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H77" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J77" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K77" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" s="14" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0390</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>ISF</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.0061</v>
+      </c>
+      <c r="F78" s="11" t="n">
+        <v>739000</v>
+      </c>
+      <c r="G78" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H78" t="n">
+        <v>51.41</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J78" s="9" t="n">
+        <v>0.825</v>
+      </c>
+      <c r="K78" s="9" t="n">
+        <v>0.796</v>
+      </c>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" s="14" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0273</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>VLB</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="F79" s="11" t="n">
+        <v>724000</v>
+      </c>
+      <c r="G79" s="12" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="H79" t="n">
+        <v>48.54</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J79" s="9" t="n">
+        <v>0.907</v>
+      </c>
+      <c r="K79" s="9" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" s="14" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D80" s="9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F80" s="11" t="n">
+        <v>696200</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H80" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J80" s="9" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="K80" s="9" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" s="14" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F81" s="11" t="n">
+        <v>673700</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H81" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J81" s="9" t="n">
+        <v>7.097</v>
+      </c>
+      <c r="K81" s="9" t="n">
+        <v>7.521</v>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" s="14" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F82" s="11" t="n">
+        <v>663700</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H82" t="n">
+        <v>44.39</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" s="14" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n">
+        <v>6.32</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>-0.009399999999999999</v>
+      </c>
+      <c r="F83" s="11" t="n">
+        <v>623300</v>
+      </c>
+      <c r="G83" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H83" t="n">
+        <v>52.62</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>6.258</v>
+      </c>
+      <c r="K83" s="9" t="n">
+        <v>5.979</v>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" s="14" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>-0.008100000000000001</v>
+      </c>
+      <c r="F84" s="11" t="n">
+        <v>612400</v>
+      </c>
+      <c r="G84" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H84" t="n">
+        <v>44.65</v>
+      </c>
+      <c r="I84" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="n">
+        <v>3.801</v>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>3.732</v>
+      </c>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" s="14" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F85" s="11" t="n">
+        <v>586500</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H85" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" s="14" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.0146</v>
+      </c>
+      <c r="F86" s="11" t="n">
+        <v>575300</v>
+      </c>
+      <c r="G86" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H86" t="n">
+        <v>60.35</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="n">
+        <v>1.948</v>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" s="14" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F87" s="11" t="n">
+        <v>541200</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H87" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" s="14" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D88" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>-0.0052</v>
+      </c>
+      <c r="F88" s="11" t="n">
+        <v>540800</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H88" t="n">
+        <v>62.71</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M63"/>
+  <autoFilter ref="A1:M88"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$88</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.12</v>
+        <v>4.07</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0173</v>
+        <v>0.0049</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>2528700</v>
+        <v>3231900</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.34</v>
+        <v>0.43</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.12</v>
+        <v>63.09</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.759</v>
+        <v>3.755</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.203</v>
+        <v>3.202</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号可靠，RSI 64.12偏高但未超买，现价4.12高于50日均线3.203约28.6%，多头动能较强。</t>
+          <t>SAR转多信号，RSI 63.09未超买，现价高于50日均线约27%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>72599300</v>
+        <v>95156500</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H3" t="n">
-        <v>28.04</v>
+        <v>29.97</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.272</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.32</v>
+        <v>0.325</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0303</v>
+        <v>-0.0152</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>15243900</v>
+        <v>17688600</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.18</v>
+        <v>0.21</v>
       </c>
       <c r="H4" t="n">
-        <v>56.38</v>
+        <v>58.39</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.313</v>
+        <v>0.314</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.264</v>
+        <v>0.265</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -715,10 +715,10 @@
         <v>0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>11519300</v>
+        <v>13554300</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.95</v>
       </c>
       <c r="H5" t="n">
         <v>44</v>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.012</v>
+        <v>0.415</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>8590400</v>
+        <v>9982700</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H6" t="n">
-        <v>33.83</v>
+        <v>34.84</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -805,10 +805,10 @@
         <v>0.0109</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>8255900</v>
+        <v>9737300</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.23</v>
+        <v>0.27</v>
       </c>
       <c r="H7" t="n">
         <v>75.68000000000001</v>
@@ -835,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.165</v>
+        <v>2.01</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0294</v>
+        <v>-0.0195</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>7412300</v>
+        <v>8555200</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.12</v>
+        <v>0.3</v>
       </c>
       <c r="H8" t="n">
-        <v>53.64</v>
+        <v>56.01</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.16</v>
+        <v>1.964</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.146</v>
+        <v>1.786</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0293</v>
+        <v>0.715</v>
+      </c>
+      <c r="E9" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>7301200</v>
+        <v>8248400</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.26</v>
+        <v>0.33</v>
       </c>
       <c r="H9" t="n">
-        <v>54.66</v>
+        <v>81.19</v>
       </c>
       <c r="I9" s="13" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>1.962</v>
+        <v>0.649</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>1.786</v>
+        <v>0.555</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.006999999999999999</v>
+        <v>0.135</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.08</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>7119800</v>
+        <v>8181900</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.29</v>
+        <v>16.25</v>
       </c>
       <c r="H10" t="n">
-        <v>78.51000000000001</v>
+        <v>64.23</v>
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.649</v>
+        <v>0.127</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.555</v>
+        <v>0.129</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.12</v>
+        <v>0.165</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>6749800</v>
+        <v>8023100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>13.41</v>
+        <v>0.13</v>
       </c>
       <c r="H11" t="n">
-        <v>69.77</v>
+        <v>53.64</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.128</v>
+        <v>0.16</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.129</v>
+        <v>0.146</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.885</v>
+      </c>
+      <c r="E12" s="10" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>6128500</v>
+        <v>7620700</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>16.84</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.49</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.005</v>
+        <v>0.85</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.006</v>
+        <v>0.757</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,39 +1060,39 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E13" s="10" t="n">
-        <v>0.017</v>
+        <v>1.12</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>5649400</v>
+        <v>7304200</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.08</v>
+        <v>1.47</v>
       </c>
       <c r="H13" t="n">
-        <v>61.84</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.28</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.851</v>
+        <v>1.317</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.757</v>
+        <v>1.515</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1105,28 +1105,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E14" s="15" t="n">
-        <v>-0.0133</v>
+        <v>0.18</v>
+      </c>
+      <c r="E14" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>4968500</v>
+        <v>6996200</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H14" t="n">
-        <v>18.34</v>
+        <v>44.11</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.39</v>
+        <v>0.186</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.404</v>
+        <v>0.186</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.023</v>
+        <v>0.37</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>4316700</v>
+        <v>6316900</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.22</v>
+        <v>0.71</v>
       </c>
       <c r="H15" t="n">
-        <v>57.51</v>
+        <v>18.34</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.429</v>
+        <v>0.39</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.381</v>
+        <v>0.404</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.0265</v>
+        <v>0.005</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>4299700</v>
+        <v>6228500</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.45</v>
+        <v>17.12</v>
       </c>
       <c r="H16" t="n">
-        <v>37.19</v>
+        <v>47.02</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.014</v>
+        <v>0.005</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.977</v>
+        <v>0.006</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>BENALEC</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.17</v>
+        <v>0.065</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.0833</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>4177600</v>
+        <v>6160300</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>1.35</v>
+        <v>7.67</v>
       </c>
       <c r="H17" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.159</v>
+        <v>0.063</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.157</v>
+        <v>0.066</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,40 +1285,31 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.18</v>
+        <v>0.275</v>
       </c>
       <c r="E18" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>3778300</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="H18" t="n">
-        <v>44.11</v>
-      </c>
+        <v>5911600</v>
+      </c>
+      <c r="G18" s="12" t="n"/>
       <c r="I18" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="K18" s="9" t="n">
-        <v>0.186</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n"/>
+      <c r="K18" s="9" t="n"/>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1330,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E19" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.92</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>-0.0265</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>3761000</v>
+        <v>5774000</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.35</v>
+        <v>0.6</v>
       </c>
       <c r="H19" t="n">
-        <v>40.68</v>
+        <v>37.19</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1359,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.287</v>
+        <v>1.014</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.28</v>
+        <v>0.977</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1390,10 +1381,10 @@
         <v>-0.0061</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>3637000</v>
+        <v>5734000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.23</v>
+        <v>0.36</v>
       </c>
       <c r="H20" t="n">
         <v>54.27</v>
@@ -1420,28 +1411,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>-0.023</v>
+        <v>0.44</v>
+      </c>
+      <c r="E21" s="10" t="n">
+        <v>0.0115</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>3619400</v>
+        <v>5453600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="H21" t="n">
-        <v>24.81</v>
+        <v>56.32</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1449,10 +1440,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.484</v>
+        <v>0.428</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.63</v>
+        <v>0.381</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1465,40 +1456,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>0.09</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>3569200</v>
+        <v>5426900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="H22" t="n">
-        <v>28.46</v>
+        <v>0.21</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J22" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.272</v>
-      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1510,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>-0.0286</v>
+        <v>0.19</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>3194800</v>
+        <v>5357600</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.59</v>
+        <v>0.25</v>
       </c>
       <c r="H23" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.79</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.163</v>
+        <v>0.21</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.165</v>
+        <v>0.23</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1555,31 +1539,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>3159000</v>
-      </c>
-      <c r="G24" s="12" t="n"/>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="n"/>
-      <c r="K24" s="9" t="n"/>
+        <v>5136300</v>
+      </c>
+      <c r="G24" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H24" t="n">
+        <v>48.33</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="K24" s="9" t="n">
+        <v>0.156</v>
+      </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1591,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E25" s="10" t="n">
-        <v>0.0147</v>
+        <v>0.43</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>-0.0115</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>3080000</v>
+        <v>4525800</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.27</v>
       </c>
       <c r="H25" t="n">
-        <v>57.39</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>25.47</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.336</v>
+        <v>0.484</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.343</v>
+        <v>0.63</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1636,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.775</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>3075200</v>
+        <v>4445000</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.87</v>
+        <v>0.29</v>
       </c>
       <c r="H26" t="n">
-        <v>63.94</v>
+        <v>50.42</v>
       </c>
       <c r="I26" s="13" t="inlineStr">
         <is>
@@ -1665,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>2.278</v>
+        <v>0.774</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>2.201</v>
+        <v>0.776</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1681,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="E27" s="10" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="F27" s="11" t="n">
+        <v>4177600</v>
+      </c>
+      <c r="G27" s="12" t="n">
         <v>1.35</v>
       </c>
-      <c r="E27" s="17" t="n">
-        <v>0</v>
-      </c>
-      <c r="F27" s="11" t="n">
-        <v>2966700</v>
-      </c>
-      <c r="G27" s="12" t="n">
-        <v>0.22</v>
-      </c>
       <c r="H27" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>1.591</v>
+        <v>0.159</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>1.884</v>
+        <v>0.157</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1726,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E28" s="10" t="n">
-        <v>0.0233</v>
+        <v>1.35</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>2883900</v>
+        <v>4095200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="H28" t="n">
-        <v>40.39</v>
+        <v>18.69</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1755,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.496</v>
+        <v>1.591</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.468</v>
+        <v>1.884</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1771,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.02</v>
+        <v>4.77</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>-0.0124</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>2659700</v>
+        <v>4031500</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.32</v>
+        <v>0.17</v>
       </c>
       <c r="H29" t="n">
-        <v>34.07</v>
+        <v>45.1</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1800,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.269</v>
+        <v>4.868</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.294</v>
+        <v>4.755</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1816,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.775</v>
+        <v>0.205</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>2630000</v>
+        <v>4026300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.17</v>
+        <v>0.36</v>
       </c>
       <c r="H30" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.46</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.774</v>
+        <v>0.225</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.776</v>
+        <v>0.272</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1861,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="E31" s="15" t="n">
-        <v>-0.0062</v>
+        <v>0.305</v>
+      </c>
+      <c r="E31" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>2627600</v>
+        <v>3851000</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="H31" t="n">
-        <v>46.66</v>
+        <v>47.4</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1890,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>4.871</v>
+        <v>0.307</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>4.756</v>
+        <v>0.302</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1906,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0183</v>
+        <v>2.4</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>2621100</v>
+        <v>3824600</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.13</v>
+        <v>1.08</v>
       </c>
       <c r="H32" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.98</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.276</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.545</v>
+        <v>2.2</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1951,33 +1944,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0</v>
+        <v>0.265</v>
+      </c>
+      <c r="E33" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>2581400</v>
+        <v>3771000</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.12</v>
+        <v>0.35</v>
+      </c>
+      <c r="H33" t="n">
+        <v>40.68</v>
       </c>
       <c r="I33" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J33" s="9" t="n"/>
-      <c r="K33" s="9" t="n"/>
+      <c r="J33" s="9" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="K33" s="9" t="n">
+        <v>0.28</v>
+      </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
     </row>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0159</v>
+        <v>0.0233</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>2574400</v>
+        <v>3750200</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.25</v>
+        <v>0.39</v>
       </c>
       <c r="H34" t="n">
-        <v>43.38</v>
+        <v>40.39</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.339</v>
+        <v>0.496</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.336</v>
+        <v>0.468</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,39 +2034,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.765</v>
+        <v>0.17</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>-0.0377</v>
+        <v>-0.0286</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>2542700</v>
+        <v>3606500</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.54</v>
+        <v>0.67</v>
       </c>
       <c r="H35" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="I35" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.21</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.837</v>
+        <v>0.163</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.619</v>
+        <v>0.165</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <v>0.0379</v>
+        <v>0.865</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>2382100</v>
+        <v>3590200</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.48</v>
+        <v>0.17</v>
       </c>
       <c r="H36" t="n">
-        <v>59.54</v>
+        <v>46.51</v>
       </c>
       <c r="I36" s="13" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>4.409</v>
+        <v>0.868</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>4.439</v>
+        <v>0.869</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,40 +2124,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.225</v>
+      </c>
+      <c r="E37" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>2065700</v>
+        <v>3443400</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="H37" t="n">
-        <v>75.41</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>0.443</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>0.436</v>
-      </c>
+        <v>0.16</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2169,28 +2162,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0312</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>OFB</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.165</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0313</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>1934100</v>
+        <v>3353800</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.09</v>
+        <v>53.46</v>
       </c>
       <c r="H38" t="n">
-        <v>46.51</v>
+        <v>78.33</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2198,10 +2191,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.868</v>
+        <v>0.137</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.869</v>
+        <v>0.138</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,33 +2207,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.725</v>
+        <v>0.555</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.0183</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>1926500</v>
+        <v>3349400</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
+      </c>
+      <c r="H39" t="n">
+        <v>48.37</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J39" s="9" t="n"/>
-      <c r="K39" s="9" t="n"/>
+      <c r="J39" s="9" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K39" s="9" t="n">
+        <v>0.545</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
     </row>
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-0.0238</v>
+        <v>0.635</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>1923200</v>
+        <v>3250900</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>54.72</v>
+        <v>60.81</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.4</v>
+        <v>0.623</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.382</v>
+        <v>0.617</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,28 +2297,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.47</v>
+        <v>0.26</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.004099999999999999</v>
+        <v>0.04</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>1852200</v>
+        <v>3244900</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.1</v>
+        <v>0.39</v>
       </c>
       <c r="H41" t="n">
-        <v>41.83</v>
+        <v>38.73</v>
       </c>
       <c r="I41" s="16" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.6</v>
+        <v>0.27</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.559</v>
+        <v>0.294</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.34</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>1851100</v>
+        <v>3177000</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.29</v>
+        <v>0.71</v>
       </c>
       <c r="H42" t="n">
-        <v>37.71</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.95</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.889</v>
+        <v>0.336</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.856</v>
+        <v>0.343</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,28 +2387,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.05</v>
+        <v>0.41</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>-0.0097</v>
+        <v>-0.0238</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>1845100</v>
+        <v>2921700</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.17</v>
+        <v>0.24</v>
       </c>
       <c r="H43" t="n">
-        <v>38.59</v>
+        <v>54.72</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.117</v>
+        <v>0.4</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.234</v>
+        <v>0.382</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,28 +2432,28 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>-0.0114</v>
+        <v>4.65</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0356</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>1841900</v>
+        <v>2696200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.27</v>
+        <v>0.55</v>
       </c>
       <c r="H44" t="n">
-        <v>52.42</v>
+        <v>59.24</v>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.429</v>
+        <v>4.408</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.418</v>
+        <v>4.439</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,28 +2477,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="E45" s="10" t="n">
-        <v>0.0137</v>
+        <v>0.735</v>
+      </c>
+      <c r="E45" s="15" t="n">
+        <v>-0.0755</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>1761400</v>
+        <v>2683100</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.14</v>
+        <v>0.57</v>
       </c>
       <c r="H45" t="n">
-        <v>50.62</v>
+        <v>46.56</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.737</v>
+        <v>0.834</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.724</v>
+        <v>0.618</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>-0.0182</v>
+        <v>0.32</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>1663700</v>
+        <v>2682800</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H46" t="n">
-        <v>43.03</v>
+        <v>43.38</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.285</v>
+        <v>0.339</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.283</v>
+        <v>0.336</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="E47" s="15" t="n">
-        <v>-0.0299</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>1657500</v>
+        <v>2645000</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.47</v>
+        <v>0.38</v>
       </c>
       <c r="H47" t="n">
-        <v>57.31</v>
+        <v>58.78</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.246</v>
+        <v>1.225</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.107</v>
+        <v>1.204</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.007900000000000001</v>
+        <v>2.06</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>1644800</v>
+        <v>2428600</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="H48" t="n">
-        <v>63.35</v>
+        <v>39.55</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.623</v>
+        <v>2.118</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.618</v>
+        <v>2.234</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="E49" s="17" t="n">
-        <v>0</v>
+        <v>2.5</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>1614100</v>
+        <v>2392700</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H49" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.88</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.479</v>
+        <v>2.603</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.589</v>
+        <v>2.559</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <v>-0.01</v>
+        <v>0.755</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0342</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>1579200</v>
+        <v>2312200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H50" t="n">
-        <v>60.48</v>
-      </c>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.59</v>
+      </c>
+      <c r="I50" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>6.798</v>
+        <v>0.738</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>6.823</v>
+        <v>0.725</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>-0.0086</v>
+        <v>0.44</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>1545100</v>
+        <v>2304500</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.31</v>
+        <v>0.34</v>
       </c>
       <c r="H51" t="n">
-        <v>19.71</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.62</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>1.32</v>
+        <v>0.429</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>1.516</v>
+        <v>0.418</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E52" s="17" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>-0.0263</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>1454400</v>
+        <v>2289500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>1.08</v>
+        <v>0.21</v>
       </c>
       <c r="H52" t="n">
-        <v>48.11</v>
+        <v>27.19</v>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.23</v>
+        <v>0.478</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.238</v>
+        <v>0.589</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>2.55</v>
+        <v>1.29</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0373</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>1453200</v>
+        <v>2164300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.26</v>
+        <v>0.62</v>
       </c>
       <c r="H53" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.37</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>2.598</v>
+        <v>1.245</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>2.607</v>
+        <v>1.107</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>1.1</v>
+        <v>0.795</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0377</v>
+        <v>0.0063</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>1424100</v>
+        <v>2150300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H54" t="n">
-        <v>53.32</v>
+        <v>36.9</v>
       </c>
       <c r="I54" s="16" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>1.082</v>
+        <v>0.889</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>1.053</v>
+        <v>0.856</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E55" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.5</v>
+      </c>
+      <c r="E55" s="15" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>1424000</v>
+        <v>2092400</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>1.25</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>51.87</v>
+        <v>75.41</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.295</v>
+        <v>0.443</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.329</v>
+        <v>0.436</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,37 +2972,32 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>-0.0143</v>
+        <v>0.725</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>1318200</v>
+        <v>2034300</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H56" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J56" s="9" t="n">
-        <v>0.333</v>
-      </c>
+        <v>0.05</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n"/>
       <c r="K56" s="9" t="n"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3015,28 +3010,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.05</v>
+        <v>0.545</v>
       </c>
       <c r="E57" s="15" t="n">
-        <v>-0.0049</v>
+        <v>-0.0091</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1316500</v>
+        <v>1890400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>3.94</v>
+        <v>0.21</v>
       </c>
       <c r="H57" t="n">
-        <v>40.07</v>
+        <v>37.01</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3044,10 +3039,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.076</v>
+        <v>0.614</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.082</v>
+        <v>0.617</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3060,28 +3055,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>-0.0131</v>
+        <v>1.09</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1256000</v>
+        <v>1888200</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="H58" t="n">
-        <v>45.88</v>
+        <v>51.98</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3089,10 +3084,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.768</v>
+        <v>1.081</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.771</v>
+        <v>1.053</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3105,40 +3100,38 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.375</v>
+        <v>0.23</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>-0.0132</v>
+        <v>-0.0417</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1246200</v>
+        <v>1852000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H59" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>14.67</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.373</v>
-      </c>
-      <c r="K59" s="9" t="n">
-        <v>0.37</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="K59" s="9" t="n"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
     </row>
@@ -3150,39 +3143,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0345</v>
+        <v>2.57</v>
+      </c>
+      <c r="E60" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1230300</v>
+        <v>1843200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.19</v>
+        <v>0.33</v>
       </c>
       <c r="H60" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.317</v>
+        <v>2.6</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.361</v>
+        <v>2.607</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3195,28 +3188,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>-0.0086</v>
+        <v>2.02</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1227500</v>
+        <v>1780300</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="H61" t="n">
-        <v>60.37</v>
+        <v>44.06</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3224,10 +3217,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.535</v>
+        <v>2.038</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.482</v>
+        <v>2.065</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3240,28 +3233,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.27</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1188500</v>
+        <v>1772900</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H62" t="n">
-        <v>41.23</v>
+        <v>43.03</v>
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
@@ -3269,10 +3262,10 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.266</v>
+        <v>0.285</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.286</v>
+        <v>0.283</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3285,28 +3278,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.545</v>
+        <v>5.26</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>-0.0091</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1157300</v>
+        <v>1767100</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>0.13</v>
       </c>
       <c r="H63" t="n">
-        <v>37.01</v>
+        <v>41.18</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3314,10 +3307,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.614</v>
+        <v>5.438</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.617</v>
+        <v>5.507</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3330,39 +3323,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E64" s="17" t="n">
-        <v>0</v>
+        <v>6.96</v>
+      </c>
+      <c r="E64" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1153500</v>
+        <v>1731900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1.31</v>
+        <v>0.37</v>
       </c>
       <c r="H64" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>61.22</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.276</v>
+        <v>6.799</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.268</v>
+        <v>6.823</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3375,28 +3368,28 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>4.73</v>
+        <v>0.305</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.0339</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1125600</v>
+        <v>1672000</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.05</v>
+        <v>1.47</v>
       </c>
       <c r="H65" t="n">
-        <v>48.77</v>
+        <v>51.87</v>
       </c>
       <c r="I65" s="13" t="inlineStr">
         <is>
@@ -3404,10 +3397,10 @@
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>4.727</v>
+        <v>0.295</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>4.818</v>
+        <v>0.329</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3420,39 +3413,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E66" s="17" t="n">
-        <v>0</v>
+        <v>2.13</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1120900</v>
+        <v>1560600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="H66" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.88</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.652</v>
+        <v>2.108</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>2.107</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3465,28 +3458,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.825</v>
+        <v>0.23</v>
       </c>
       <c r="E67" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1108900</v>
+        <v>1542300</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.21</v>
+        <v>1.14</v>
       </c>
       <c r="H67" t="n">
-        <v>68.73</v>
+        <v>48.11</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3494,10 +3487,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.803</v>
+        <v>0.23</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.777</v>
+        <v>0.238</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3510,40 +3503,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>5.21</v>
+        <v>0.345</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>-0.0151</v>
+        <v>-0.0143</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1037400</v>
+        <v>1533700</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.08</v>
+        <v>0.27</v>
       </c>
       <c r="H68" t="n">
-        <v>39.47</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.7</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>5.433</v>
-      </c>
-      <c r="K68" s="9" t="n">
-        <v>5.506</v>
-      </c>
+        <v>0.333</v>
+      </c>
+      <c r="K68" s="9" t="n"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
     </row>
@@ -3555,39 +3546,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.005</v>
+        <v>0.825</v>
+      </c>
+      <c r="E69" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1002800</v>
+        <v>1508500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="H69" t="n">
-        <v>46.51</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2.039</v>
+        <v>0.803</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.065</v>
+        <v>0.777</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3600,28 +3591,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>2.4</v>
+      </c>
+      <c r="E70" s="15" t="n">
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>911200</v>
+        <v>1466900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.15</v>
+        <v>0.13</v>
       </c>
       <c r="H70" t="n">
-        <v>32.27</v>
+        <v>45.1</v>
       </c>
       <c r="I70" s="16" t="inlineStr">
         <is>
@@ -3629,10 +3620,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>1.666</v>
+        <v>2.439</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>1.746</v>
+        <v>2.408</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3645,39 +3636,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E71" s="17" t="n">
-        <v>0</v>
+        <v>4.73</v>
+      </c>
+      <c r="E71" s="10" t="n">
+        <v>0.0042</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>874800</v>
+        <v>1460400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>46.38</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.77</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>2.44</v>
+        <v>4.727</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>2.408</v>
+        <v>4.818</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3690,28 +3681,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0068</v>
+        <v>1.55</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>873000</v>
+        <v>1430600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H72" t="n">
-        <v>49.59</v>
+        <v>33.77</v>
       </c>
       <c r="I72" s="16" t="inlineStr">
         <is>
@@ -3719,10 +3710,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.741</v>
+        <v>1.667</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.707</v>
+        <v>1.747</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,28 +3726,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="E73" s="10" t="n">
-        <v>0.0388</v>
+        <v>2.05</v>
+      </c>
+      <c r="E73" s="15" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>838500</v>
+        <v>1420400</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.46</v>
+        <v>4.25</v>
       </c>
       <c r="H73" t="n">
-        <v>42.22</v>
+        <v>40.07</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3764,10 +3755,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>1.366</v>
+        <v>2.076</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>1.443</v>
+        <v>2.082</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3780,28 +3771,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.3</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>817500</v>
+        <v>1396500</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="H74" t="n">
-        <v>58.78</v>
+        <v>38.77</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3809,10 +3800,10 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.225</v>
+        <v>0.317</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.204</v>
+        <v>0.361</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3825,28 +3816,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.755</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>802000</v>
+        <v>1362000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H75" t="n">
-        <v>52.08</v>
+        <v>45.88</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3854,10 +3845,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>1.172</v>
+        <v>0.768</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>1.147</v>
+        <v>0.771</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3870,28 +3861,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E76" s="10" t="n">
-        <v>0.008</v>
+        <v>0.585</v>
+      </c>
+      <c r="E76" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>785000</v>
+        <v>1359400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.3</v>
+        <v>0.16</v>
       </c>
       <c r="H76" t="n">
-        <v>51.3</v>
+        <v>35.4</v>
       </c>
       <c r="I76" s="16" t="inlineStr">
         <is>
@@ -3899,10 +3890,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>1.265</v>
+        <v>0.652</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>1.183</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3915,39 +3906,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>1.06</v>
+        <v>0.375</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>-0.009300000000000001</v>
+        <v>-0.0132</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>784000</v>
+        <v>1346200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="H77" t="n">
-        <v>40.12</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>1.13</v>
+        <v>0.373</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>1.11</v>
+        <v>0.37</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3960,28 +3951,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.825</v>
+        <v>1.17</v>
       </c>
       <c r="E78" s="10" t="n">
-        <v>0.0061</v>
+        <v>0.0086</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>739000</v>
+        <v>1329000</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="H78" t="n">
-        <v>51.41</v>
+        <v>50.61</v>
       </c>
       <c r="I78" s="16" t="inlineStr">
         <is>
@@ -3989,10 +3980,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.825</v>
+        <v>1.171</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.796</v>
+        <v>1.147</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,28 +3996,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.895</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.017</v>
+        <v>0.58</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>724000</v>
+        <v>1253100</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.38</v>
+        <v>0.26</v>
       </c>
       <c r="H79" t="n">
-        <v>48.54</v>
+        <v>61.45</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4034,10 +4025,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.907</v>
+        <v>0.536</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.889</v>
+        <v>0.482</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4050,39 +4041,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>3.39</v>
+        <v>0.835</v>
       </c>
       <c r="E80" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0183</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>696200</v>
+        <v>1246100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.22</v>
+        <v>0.32</v>
       </c>
       <c r="H80" t="n">
-        <v>88.61</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.21</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>3.003</v>
+        <v>0.826</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.546</v>
+        <v>0.796</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4095,28 +4086,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>-0.0058</v>
+        <v>7.15</v>
+      </c>
+      <c r="E81" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>673700</v>
+        <v>1227400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H81" t="n">
-        <v>39.13</v>
+        <v>33.23</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4124,10 +4115,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>7.097</v>
+        <v>7.387</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>7.521</v>
+        <v>7.637</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4140,28 +4131,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E82" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>663700</v>
+        <v>1194000</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H82" t="n">
-        <v>44.39</v>
+        <v>41.23</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4169,10 +4160,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.549</v>
+        <v>0.266</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.523</v>
+        <v>0.286</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4185,28 +4176,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>6.32</v>
+        <v>1.16</v>
       </c>
       <c r="E83" s="15" t="n">
-        <v>-0.009399999999999999</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>623300</v>
+        <v>1161500</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.1</v>
+        <v>2.19</v>
       </c>
       <c r="H83" t="n">
-        <v>52.62</v>
+        <v>37.8</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4214,10 +4205,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>6.258</v>
+        <v>1.182</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>5.979</v>
+        <v>1.205</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4230,28 +4221,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>3.67</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>-0.008100000000000001</v>
+        <v>0.92</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>612400</v>
+        <v>1161300</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="H84" t="n">
-        <v>44.65</v>
+        <v>28.81</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4259,10 +4250,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>3.801</v>
+        <v>0.953</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>3.732</v>
+        <v>1.036</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4275,28 +4266,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.275</v>
+      </c>
+      <c r="E85" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>586500</v>
+        <v>1153500</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.08</v>
+        <v>1.31</v>
       </c>
       <c r="H85" t="n">
-        <v>39.83</v>
+        <v>50.42</v>
       </c>
       <c r="I85" s="16" t="inlineStr">
         <is>
@@ -4304,10 +4295,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.213</v>
+        <v>0.276</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.298</v>
+        <v>0.268</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4320,28 +4311,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>-0.0146</v>
+        <v>0.235</v>
+      </c>
+      <c r="E86" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>575300</v>
+        <v>1130200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.09</v>
+        <v>0.54</v>
       </c>
       <c r="H86" t="n">
-        <v>60.35</v>
+        <v>46.77</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4349,10 +4340,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.948</v>
+        <v>0.239</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.957</v>
+        <v>0.241</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4365,28 +4356,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.63</v>
+        <v>0.89</v>
       </c>
       <c r="E87" s="10" t="n">
-        <v>0.008</v>
+        <v>0.0114</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>541200</v>
+        <v>1114200</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.1</v>
+        <v>0.59</v>
       </c>
       <c r="H87" t="n">
-        <v>38.08</v>
+        <v>47.64</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4394,10 +4385,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.721</v>
+        <v>0.907</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4410,45 +4401,1170 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.965</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>-0.0052</v>
+        <v>1.31</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.0155</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>540800</v>
+        <v>1071100</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.1</v>
+        <v>0.59</v>
       </c>
       <c r="H88" t="n">
-        <v>62.71</v>
-      </c>
-      <c r="I88" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.37</v>
+      </c>
+      <c r="I88" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.363</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.889</v>
+        <v>1.443</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>7692</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>MYTECH</t>
+        </is>
+      </c>
+      <c r="D89" s="9" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="E89" s="15" t="n">
+        <v>-0.0208</v>
+      </c>
+      <c r="F89" s="11" t="n">
+        <v>1050000</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="H89" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" s="14" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>7277</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>DIALOG</t>
+        </is>
+      </c>
+      <c r="D90" s="9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>-0.0097</v>
+      </c>
+      <c r="F90" s="11" t="n">
+        <v>964800</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H90" t="n">
+        <v>61.78</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="n">
+        <v>1.949</v>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>1.957</v>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" s="14" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>0146</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>JFTECH</t>
+        </is>
+      </c>
+      <c r="D91" s="9" t="n">
+        <v>0.735</v>
+      </c>
+      <c r="E91" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F91" s="11" t="n">
+        <v>944500</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H91" t="n">
+        <v>50.4</v>
+      </c>
+      <c r="I91" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>0.707</v>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" s="14" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>5327</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>MEGAFB</t>
+        </is>
+      </c>
+      <c r="D92" s="9" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E92" s="10" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="F92" s="11" t="n">
+        <v>903900</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H92" t="n">
+        <v>88.61</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="n">
+        <v>3.003</v>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>2.546</v>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" s="14" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0240</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>CORAZA</t>
+        </is>
+      </c>
+      <c r="D93" s="9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F93" s="11" t="n">
+        <v>902300</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="H93" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="n">
+        <v>1.266</v>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>1.184</v>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" s="14" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>0217</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>PWRWELL</t>
+        </is>
+      </c>
+      <c r="D94" s="9" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>-0.009300000000000001</v>
+      </c>
+      <c r="F94" s="11" t="n">
+        <v>898100</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="H94" t="n">
+        <v>40.12</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" s="14" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>8869</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>PMETAL</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>-0.0058</v>
+      </c>
+      <c r="F95" s="11" t="n">
+        <v>888700</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H95" t="n">
+        <v>39.13</v>
+      </c>
+      <c r="I95" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="n">
+        <v>7.097</v>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>7.521</v>
+      </c>
+      <c r="L95" t="inlineStr"/>
+      <c r="M95" s="14" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>0127</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>JHM</t>
+        </is>
+      </c>
+      <c r="D96" s="9" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="E96" s="10" t="n">
+        <v>0.009599999999999999</v>
+      </c>
+      <c r="F96" s="11" t="n">
+        <v>811200</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H96" t="n">
+        <v>45.59</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="L96" t="inlineStr"/>
+      <c r="M96" s="14" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D97" s="9" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F97" s="11" t="n">
+        <v>795300</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H97" t="n">
+        <v>45.03</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="n">
+        <v>3.801</v>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>3.732</v>
+      </c>
+      <c r="L97" t="inlineStr"/>
+      <c r="M97" s="14" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>1066</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>RHBBANK</t>
+        </is>
+      </c>
+      <c r="D98" s="9" t="n">
+        <v>7.35</v>
+      </c>
+      <c r="E98" s="15" t="n">
+        <v>-0.0054</v>
+      </c>
+      <c r="F98" s="11" t="n">
+        <v>789400</v>
+      </c>
+      <c r="G98" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H98" t="n">
+        <v>41.41</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="n">
+        <v>7.421</v>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>7.843</v>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" s="14" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>MRDIY</t>
+        </is>
+      </c>
+      <c r="D99" s="9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="E99" s="10" t="n">
+        <v>0.0172</v>
+      </c>
+      <c r="F99" s="11" t="n">
+        <v>740400</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H99" t="n">
+        <v>39.83</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="n">
+        <v>1.213</v>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>1.298</v>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" s="14" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>5356</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>STRATUS</t>
+        </is>
+      </c>
+      <c r="D100" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.0215</v>
+      </c>
+      <c r="F100" s="11" t="n">
+        <v>728700</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H100" t="n">
+        <v>34.84</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>2.841</v>
+      </c>
+      <c r="L100" t="inlineStr"/>
+      <c r="M100" s="14" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D101" s="9" t="n">
+        <v>6.39</v>
+      </c>
+      <c r="E101" s="10" t="n">
+        <v>0.0016</v>
+      </c>
+      <c r="F101" s="11" t="n">
+        <v>720300</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H101" t="n">
+        <v>53.83</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="n">
+        <v>6.264</v>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>5.981</v>
+      </c>
+      <c r="L101" t="inlineStr"/>
+      <c r="M101" s="14" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>0246</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>CNERGEN</t>
+        </is>
+      </c>
+      <c r="D102" s="9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0.009000000000000001</v>
+      </c>
+      <c r="F102" s="11" t="n">
+        <v>719300</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H102" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="I102" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" s="14" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D103" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E103" s="10" t="n">
+        <v>0.006</v>
+      </c>
+      <c r="F103" s="11" t="n">
+        <v>700000</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="H103" t="n">
+        <v>34.08</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J103" s="9" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="K103" s="9" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" s="14" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1961</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>IOICORP</t>
+        </is>
+      </c>
+      <c r="D104" s="9" t="n">
+        <v>4.47</v>
+      </c>
+      <c r="E104" s="15" t="n">
+        <v>-0.0022</v>
+      </c>
+      <c r="F104" s="11" t="n">
+        <v>681400</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H104" t="n">
+        <v>38.22</v>
+      </c>
+      <c r="I104" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J104" s="9" t="n">
+        <v>4.568</v>
+      </c>
+      <c r="K104" s="9" t="n">
+        <v>4.641</v>
+      </c>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" s="14" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>0318</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>ELRIDGE</t>
+        </is>
+      </c>
+      <c r="D105" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F105" s="11" t="n">
+        <v>663400</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H105" t="n">
+        <v>60.66</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J105" s="9" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="K105" s="9" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="L105" t="inlineStr"/>
+      <c r="M105" s="14" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>6888</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>AXIATA</t>
+        </is>
+      </c>
+      <c r="D106" s="9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.0186</v>
+      </c>
+      <c r="F106" s="11" t="n">
+        <v>635300</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H106" t="n">
+        <v>50.6</v>
+      </c>
+      <c r="I106" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J106" s="9" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="K106" s="9" t="n">
+        <v>1.678</v>
+      </c>
+      <c r="L106" t="inlineStr"/>
+      <c r="M106" s="14" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D107" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="F107" s="11" t="n">
+        <v>618800</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H107" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I107" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J107" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="K107" s="9" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L107" t="inlineStr"/>
+      <c r="M107" s="14" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D108" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="F108" s="11" t="n">
+        <v>607300</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H108" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J108" s="9" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="K108" s="9" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="L108" t="inlineStr"/>
+      <c r="M108" s="14" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D109" s="9" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.0102</v>
+      </c>
+      <c r="F109" s="11" t="n">
+        <v>592000</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H109" t="n">
+        <v>45.96</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J109" s="9" t="n">
+        <v>2.063</v>
+      </c>
+      <c r="K109" s="9" t="n">
+        <v>1.992</v>
+      </c>
+      <c r="L109" t="inlineStr"/>
+      <c r="M109" s="14" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D110" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="F110" s="11" t="n">
+        <v>584300</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H110" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="I110" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J110" s="9" t="n">
+        <v>0.722</v>
+      </c>
+      <c r="K110" s="9" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L110" t="inlineStr"/>
+      <c r="M110" s="14" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D111" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="11" t="n">
+        <v>571400</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H111" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I111" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J111" s="9" t="n">
+        <v>2.491</v>
+      </c>
+      <c r="K111" s="9" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="L111" t="inlineStr"/>
+      <c r="M111" s="14" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D112" s="9" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.0052</v>
+      </c>
+      <c r="F112" s="11" t="n">
+        <v>553900</v>
+      </c>
+      <c r="G112" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H112" t="n">
+        <v>41.12</v>
+      </c>
+      <c r="I112" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J112" s="9" t="n">
+        <v>5.838</v>
+      </c>
+      <c r="K112" s="9" t="n">
+        <v>6.106</v>
+      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" s="14" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D113" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E113" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F113" s="11" t="n">
+        <v>515400</v>
+      </c>
+      <c r="G113" s="12" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="H113" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J113" s="9" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="K113" s="9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L113" t="inlineStr"/>
+      <c r="M113" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M88"/>
+  <autoFilter ref="A1:M113"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$139</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.07</v>
+        <v>4.08</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0049</v>
+        <v>0.0074</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3231900</v>
+        <v>3710000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.43</v>
+        <v>0.49</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.09</v>
+        <v>63.3</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 63.09未超买，现价高于50日均线约27%，技术面信号可靠性较高。</t>
+          <t>SAR转多信号可靠，RSI 63.3未超买，现价高于50日均线约27%，技术面偏强。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>95156500</v>
+        <v>108811500</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H3" t="n">
         <v>29.97</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.325</v>
+        <v>0.32</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0152</v>
+        <v>-0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>17688600</v>
+        <v>51675100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.21</v>
+        <v>0.62</v>
       </c>
       <c r="H4" t="n">
-        <v>58.39</v>
+        <v>56.38</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -684,10 +684,10 @@
         </is>
       </c>
       <c r="J4" s="9" t="n">
-        <v>0.314</v>
+        <v>0.313</v>
       </c>
       <c r="K4" s="9" t="n">
-        <v>0.265</v>
+        <v>0.264</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" s="14" t="inlineStr"/>
@@ -715,10 +715,10 @@
         <v>0.0333</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>13554300</v>
+        <v>18133400</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.95</v>
+        <v>1.27</v>
       </c>
       <c r="H5" t="n">
         <v>44</v>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <v>0</v>
+        <v>0.47</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.0217</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>9982700</v>
+        <v>13830500</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.28</v>
+        <v>0.38</v>
       </c>
       <c r="H6" t="n">
-        <v>34.84</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.43000000000001</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.458</v>
+        <v>0.412</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.477</v>
+        <v>0.309</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.465</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0109</v>
+        <v>1.97</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-0.039</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>9737300</v>
+        <v>12214500</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.27</v>
+        <v>0.43</v>
       </c>
       <c r="H7" t="n">
-        <v>75.68000000000001</v>
+        <v>53.38</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.412</v>
+        <v>1.96</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.309</v>
+        <v>1.785</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0195</v>
+        <v>0.425</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>8555200</v>
+        <v>11703500</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="H8" t="n">
-        <v>56.01</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.49</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1.964</v>
+        <v>0.459</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1.786</v>
+        <v>0.477</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.715</v>
+        <v>0.18</v>
       </c>
       <c r="E9" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>8248400</v>
+        <v>10196200</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H9" t="n">
-        <v>81.19</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.649</v>
+        <v>0.186</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.555</v>
+        <v>0.186</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,39 +925,39 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.08</v>
+        <v>1.12</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>8181900</v>
+        <v>10021300</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>16.25</v>
+        <v>2.02</v>
       </c>
       <c r="H10" t="n">
-        <v>64.23</v>
-      </c>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.28</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.127</v>
+        <v>1.317</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.129</v>
+        <v>1.515</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,28 +970,28 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0294</v>
+        <v>0.885</v>
+      </c>
+      <c r="E11" s="10" t="n">
+        <v>0.005699999999999999</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>8023100</v>
+        <v>9932100</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>0.13</v>
       </c>
       <c r="H11" t="n">
-        <v>53.64</v>
+        <v>60.49</v>
       </c>
       <c r="I11" s="13" t="inlineStr">
         <is>
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.16</v>
+        <v>0.85</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.146</v>
+        <v>0.757</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E12" s="10" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.005</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>7620700</v>
+        <v>9844000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.1</v>
+        <v>27.05</v>
       </c>
       <c r="H12" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.85</v>
+        <v>0.005</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.757</v>
+        <v>0.006</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,40 +1060,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0345</v>
+        <v>0.265</v>
+      </c>
+      <c r="E13" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>7304200</v>
-      </c>
-      <c r="G13" s="12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="H13" t="n">
-        <v>18.28</v>
-      </c>
+        <v>9387600</v>
+      </c>
+      <c r="G13" s="12" t="n"/>
       <c r="I13" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="n">
-        <v>1.317</v>
-      </c>
-      <c r="K13" s="9" t="n">
-        <v>1.515</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
     </row>
@@ -1105,28 +1096,28 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>BENALEC</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E14" s="17" t="n">
-        <v>0</v>
+        <v>0.065</v>
+      </c>
+      <c r="E14" s="10" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>6996200</v>
+        <v>9275700</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.33</v>
+        <v>11.55</v>
       </c>
       <c r="H14" t="n">
-        <v>44.11</v>
+        <v>55.37</v>
       </c>
       <c r="I14" s="16" t="inlineStr">
         <is>
@@ -1134,10 +1125,10 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.186</v>
+        <v>0.063</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.186</v>
+        <v>0.066</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,39 +1141,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.006999999999999999</v>
+      </c>
+      <c r="F15" s="11" t="n">
+        <v>9045300</v>
+      </c>
+      <c r="G15" s="12" t="n">
         <v>0.37</v>
       </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.0133</v>
-      </c>
-      <c r="F15" s="11" t="n">
-        <v>6316900</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0.71</v>
-      </c>
       <c r="H15" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="I15" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>81.81</v>
+      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.39</v>
+        <v>0.65</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.404</v>
+        <v>0.555</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,28 +1186,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.91</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>6228500</v>
+        <v>8363800</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>17.12</v>
+        <v>0.87</v>
       </c>
       <c r="H16" t="n">
-        <v>47.02</v>
+        <v>36.24</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1224,10 +1215,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.005</v>
+        <v>1.013</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.006</v>
+        <v>0.977</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>BENALEC</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.065</v>
+        <v>0.13</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.04</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>6160300</v>
+        <v>8302600</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>7.67</v>
+        <v>16.49</v>
       </c>
       <c r="H17" t="n">
-        <v>55.37</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.063</v>
+        <v>0.127</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.066</v>
+        <v>0.129</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1285,31 +1276,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E18" s="17" t="n">
-        <v>0</v>
+        <v>0.16</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>-0.0588</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>5911600</v>
-      </c>
-      <c r="G18" s="12" t="n"/>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="9" t="n"/>
+        <v>8122000</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H18" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0.159</v>
+      </c>
+      <c r="K18" s="9" t="n">
+        <v>0.145</v>
+      </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
     </row>
@@ -1321,28 +1321,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>-0.0265</v>
+        <v>0.305</v>
+      </c>
+      <c r="E19" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>5774000</v>
+        <v>7756500</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H19" t="n">
-        <v>37.19</v>
+        <v>47.4</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1350,10 +1350,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>1.014</v>
+        <v>0.307</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.977</v>
+        <v>0.302</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1381,10 +1381,10 @@
         <v>-0.0061</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>5734000</v>
+        <v>7630000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="H20" t="n">
         <v>54.27</v>
@@ -1420,19 +1420,19 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E21" s="10" t="n">
-        <v>0.0115</v>
+        <v>0.435</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>5453600</v>
+        <v>7223500</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.27</v>
+        <v>0.36</v>
       </c>
       <c r="H21" t="n">
-        <v>56.32</v>
+        <v>55.05</v>
       </c>
       <c r="I21" s="16" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
         <v>-0.0526</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>5426900</v>
+        <v>6782900</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="I22" s="16" t="inlineStr">
         <is>
@@ -1494,28 +1494,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.19</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.365</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>-0.0267</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>5357600</v>
+        <v>6347400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.25</v>
+        <v>0.72</v>
       </c>
       <c r="H23" t="n">
-        <v>33.79</v>
+        <v>16.27</v>
       </c>
       <c r="I23" s="16" t="inlineStr">
         <is>
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.21</v>
+        <v>0.39</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.23</v>
+        <v>0.404</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1539,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>-0.0313</v>
+        <v>0.19</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5136300</v>
+        <v>5974400</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.14</v>
+        <v>0.28</v>
       </c>
       <c r="H24" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.79</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.156</v>
+        <v>0.21</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.156</v>
+        <v>0.23</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>-0.0115</v>
+        <v>0.775</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>4525800</v>
+        <v>5764100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.27</v>
+        <v>0.37</v>
       </c>
       <c r="H25" t="n">
-        <v>25.47</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.484</v>
+        <v>0.774</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.63</v>
+        <v>0.776</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1629,39 +1629,39 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E26" s="17" t="n">
-        <v>0</v>
+        <v>4.78</v>
+      </c>
+      <c r="E26" s="15" t="n">
+        <v>-0.0104</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>4445000</v>
+        <v>5753600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.29</v>
+        <v>0.24</v>
       </c>
       <c r="H26" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.61</v>
+      </c>
+      <c r="I26" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>0.774</v>
+        <v>4.869</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>0.776</v>
+        <v>4.755</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E27" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.15</v>
+      </c>
+      <c r="E27" s="15" t="n">
+        <v>-0.0625</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>4177600</v>
+        <v>5640000</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>1.35</v>
+        <v>0.16</v>
       </c>
       <c r="H27" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.46</v>
+      </c>
+      <c r="I27" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.159</v>
+        <v>0.155</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.157</v>
+        <v>0.156</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E28" s="15" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4095200</v>
+        <v>4816700</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="H28" t="n">
-        <v>18.69</v>
+        <v>24.81</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>1.591</v>
+        <v>0.484</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>1.884</v>
+        <v>0.63</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>4.77</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>-0.0124</v>
+        <v>0.255</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4031500</v>
+        <v>4691800</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.17</v>
+        <v>0.57</v>
       </c>
       <c r="H29" t="n">
-        <v>45.1</v>
+        <v>34.07</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>4.868</v>
+        <v>0.269</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>4.755</v>
+        <v>0.294</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,40 +1809,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.205</v>
+        <v>0.225</v>
       </c>
       <c r="E30" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4026300</v>
+        <v>4659300</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H30" t="n">
-        <v>28.46</v>
+        <v>0.21</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="K30" s="9" t="n">
-        <v>0.272</v>
-      </c>
+      <c r="J30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1854,28 +1847,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.305</v>
+        <v>1.35</v>
       </c>
       <c r="E31" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>3851000</v>
+        <v>4558900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H31" t="n">
-        <v>47.4</v>
+        <v>18.69</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1883,10 +1876,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.307</v>
+        <v>1.591</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.302</v>
+        <v>1.884</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1892,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>-0.0123</v>
+        <v>0.445</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0349</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>3824600</v>
+        <v>4346400</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>1.08</v>
+        <v>0.45</v>
       </c>
       <c r="H32" t="n">
-        <v>61.98</v>
-      </c>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.38</v>
+      </c>
+      <c r="I32" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>2.276</v>
+        <v>0.496</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>2.2</v>
+        <v>0.468</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1944,39 +1937,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E33" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.865</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>3771000</v>
+        <v>4301600</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.35</v>
+        <v>0.21</v>
       </c>
       <c r="H33" t="n">
-        <v>40.68</v>
-      </c>
-      <c r="I33" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.287</v>
+        <v>0.868</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.28</v>
+        <v>0.869</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1982,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.44</v>
+        <v>0.17</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.0625</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>3750200</v>
+        <v>4237600</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.39</v>
+        <v>1.37</v>
       </c>
       <c r="H34" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.496</v>
+        <v>0.159</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.468</v>
+        <v>0.157</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2027,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.17</v>
+        <v>2.39</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>-0.0286</v>
+        <v>-0.0165</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>3606500</v>
+        <v>4116600</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.67</v>
+        <v>1.17</v>
       </c>
       <c r="H35" t="n">
-        <v>56.21</v>
+        <v>61.04</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2056,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.163</v>
+        <v>2.275</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.165</v>
+        <v>2.2</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2072,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E36" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.205</v>
+      </c>
+      <c r="E36" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>3590200</v>
+        <v>4111400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.17</v>
+        <v>0.37</v>
       </c>
       <c r="H36" t="n">
-        <v>46.51</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.46</v>
+      </c>
+      <c r="I36" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.868</v>
+        <v>0.225</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.869</v>
+        <v>0.272</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,33 +2117,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E37" s="17" t="n">
-        <v>0</v>
+        <v>2.06</v>
+      </c>
+      <c r="E37" s="15" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>3443400</v>
+        <v>4008500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="I37" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
+        <v>0.36</v>
+      </c>
+      <c r="H37" t="n">
+        <v>39.55</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n">
+        <v>2.118</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>2.234</v>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2162,28 +2162,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0312</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OFB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0313</v>
+        <v>0.635</v>
+      </c>
+      <c r="E38" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3353800</v>
+        <v>3928100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>53.46</v>
+        <v>0.37</v>
       </c>
       <c r="H38" t="n">
-        <v>78.33</v>
+        <v>60.81</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.137</v>
+        <v>0.623</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.138</v>
+        <v>0.617</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,28 +2207,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.555</v>
+        <v>0.265</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.0192</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3349400</v>
+        <v>3859000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.16</v>
+        <v>0.36</v>
       </c>
       <c r="H39" t="n">
-        <v>48.37</v>
+        <v>40.68</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.287</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.545</v>
+        <v>0.28</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,28 +2252,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>0.41</v>
+      </c>
+      <c r="E40" s="15" t="n">
+        <v>-0.0238</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3250900</v>
+        <v>3764300</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>0.31</v>
       </c>
       <c r="H40" t="n">
-        <v>60.81</v>
+        <v>54.72</v>
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.623</v>
+        <v>0.4</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.617</v>
+        <v>0.382</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,39 +2297,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0312</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>OFB</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.04</v>
+        <v>0.16</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3244900</v>
+        <v>3643200</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.39</v>
+        <v>58.07</v>
       </c>
       <c r="H41" t="n">
-        <v>38.73</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.15000000000001</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.27</v>
+        <v>0.136</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.294</v>
+        <v>0.138</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,28 +2342,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E42" s="17" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E42" s="15" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3177000</v>
+        <v>3626900</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="H42" t="n">
-        <v>52.95</v>
+        <v>56.21</v>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
@@ -2371,10 +2371,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.336</v>
+        <v>0.163</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.343</v>
+        <v>0.165</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>-0.0238</v>
+        <v>0.55</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.0092</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>2921700</v>
+        <v>3626600</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.24</v>
+        <v>0.17</v>
       </c>
       <c r="H43" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.37</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.4</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.382</v>
+        <v>0.545</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.33</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>2696200</v>
+        <v>3532200</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="H44" t="n">
-        <v>59.24</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.21</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>4.408</v>
+        <v>0.35</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>4.439</v>
+        <v>0.329</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,28 +2477,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E45" s="15" t="n">
-        <v>-0.0755</v>
+        <v>0.32</v>
+      </c>
+      <c r="E45" s="10" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>2683100</v>
+        <v>3420900</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.57</v>
+        <v>0.33</v>
       </c>
       <c r="H45" t="n">
-        <v>46.56</v>
+        <v>43.38</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.834</v>
+        <v>0.339</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.618</v>
+        <v>0.336</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E46" s="10" t="n">
-        <v>0.0159</v>
+        <v>1.27</v>
+      </c>
+      <c r="E46" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>2682800</v>
+        <v>3291300</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.26</v>
+        <v>0.48</v>
       </c>
       <c r="H46" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="I46" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.78</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.339</v>
+        <v>1.225</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.336</v>
+        <v>1.204</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.34</v>
+      </c>
+      <c r="E47" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>2645000</v>
+        <v>3237500</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.38</v>
+        <v>0.72</v>
       </c>
       <c r="H47" t="n">
-        <v>58.78</v>
+        <v>52.95</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>1.225</v>
+        <v>0.336</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>1.204</v>
+        <v>0.343</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.06</v>
+        <v>0.73</v>
       </c>
       <c r="E48" s="15" t="n">
-        <v>-0.0048</v>
+        <v>-0.0818</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>2428600</v>
+        <v>3186300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.22</v>
+        <v>0.68</v>
       </c>
       <c r="H48" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.27</v>
+      </c>
+      <c r="I48" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.118</v>
+        <v>0.834</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.234</v>
+        <v>0.618</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.5</v>
+        <v>4.62</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>0.0163</v>
+        <v>0.029</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>2392700</v>
+        <v>3104900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.13</v>
+        <v>0.63</v>
       </c>
       <c r="H49" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.34</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.603</v>
+        <v>4.406</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.559</v>
+        <v>4.438</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.755</v>
+        <v>0.745</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0342</v>
+        <v>0.0205</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>2312200</v>
+        <v>3088200</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.18</v>
+        <v>0.24</v>
       </c>
       <c r="H50" t="n">
-        <v>52.59</v>
+        <v>51.29</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.738</v>
+        <v>0.737</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.725</v>
+        <v>0.724</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E51" s="17" t="n">
-        <v>0</v>
+        <v>0.25</v>
+      </c>
+      <c r="E51" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>2304500</v>
+        <v>3068900</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.34</v>
+        <v>0.5</v>
       </c>
       <c r="H51" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.23</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.429</v>
+        <v>0.266</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.418</v>
+        <v>0.286</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E52" s="15" t="n">
-        <v>-0.0263</v>
+        <v>2.5</v>
+      </c>
+      <c r="E52" s="10" t="n">
+        <v>0.0163</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>2289500</v>
+        <v>3062100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.21</v>
+        <v>0.16</v>
       </c>
       <c r="H52" t="n">
-        <v>27.19</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.88</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.478</v>
+        <v>2.603</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.589</v>
+        <v>2.559</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,40 +2837,38 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>1.29</v>
+        <v>0.22</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.0373</v>
+        <v>-0.0833</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2164300</v>
+        <v>2972200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.62</v>
+        <v>1.11</v>
       </c>
       <c r="H53" t="n">
-        <v>56.37</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>13.47</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>1.245</v>
-      </c>
-      <c r="K53" s="9" t="n">
-        <v>1.107</v>
-      </c>
+        <v>0.259</v>
+      </c>
+      <c r="K53" s="9" t="n"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
     </row>
@@ -2882,39 +2880,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.795</v>
+        <v>0.295</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.0172</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2150300</v>
+        <v>2714400</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="H54" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>36.34</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.889</v>
+        <v>0.316</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.856</v>
+        <v>0.361</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2925,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.5</v>
+        <v>0.785</v>
       </c>
       <c r="E55" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.0063</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2092400</v>
+        <v>2472600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.38</v>
       </c>
       <c r="H55" t="n">
-        <v>75.41</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.61</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.443</v>
+        <v>0.888</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.436</v>
+        <v>0.856</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,33 +2970,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.435</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.0114</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2034300</v>
+        <v>2463200</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I56" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J56" s="9" t="n"/>
-      <c r="K56" s="9" t="n"/>
+        <v>0.36</v>
+      </c>
+      <c r="H56" t="n">
+        <v>52.42</v>
+      </c>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J56" s="9" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="K56" s="9" t="n">
+        <v>0.418</v>
+      </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
     </row>
@@ -3010,28 +3015,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.545</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>-0.0091</v>
+        <v>1.09</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0283</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>1890400</v>
+        <v>2437900</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.21</v>
+        <v>0.27</v>
       </c>
       <c r="H57" t="n">
-        <v>37.01</v>
+        <v>51.98</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3039,10 +3044,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.614</v>
+        <v>1.081</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.617</v>
+        <v>1.053</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3055,40 +3060,33 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.0283</v>
+        <v>0.72</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>1888200</v>
+        <v>2429900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="H58" t="n">
-        <v>51.98</v>
+        <v>0.06</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J58" s="9" t="n">
-        <v>1.081</v>
-      </c>
-      <c r="K58" s="9" t="n">
-        <v>1.053</v>
-      </c>
+      <c r="J58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3100,38 +3098,40 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.23</v>
+        <v>1.29</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>-0.0417</v>
+        <v>-0.0373</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>1852000</v>
+        <v>2373000</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="H59" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.37</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K59" s="9" t="n"/>
+        <v>1.245</v>
+      </c>
+      <c r="K59" s="9" t="n">
+        <v>1.107</v>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
     </row>
@@ -3143,39 +3143,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E60" s="17" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>1843200</v>
+        <v>2359100</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.33</v>
+        <v>0.22</v>
       </c>
       <c r="H60" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>27.63</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.6</v>
+        <v>0.478</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>2.607</v>
+        <v>0.589</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3188,28 +3188,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+        <v>5.26</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>1780300</v>
+        <v>2337500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.48</v>
+        <v>0.18</v>
       </c>
       <c r="H61" t="n">
-        <v>44.06</v>
+        <v>41.18</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>2.038</v>
+        <v>5.438</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>2.065</v>
+        <v>5.507</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3233,39 +3233,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>-0.0182</v>
+        <v>2.13</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.004699999999999999</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>1772900</v>
+        <v>2259700</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="H62" t="n">
-        <v>43.03</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.88</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.285</v>
+        <v>2.108</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>0.283</v>
+        <v>2.107</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3278,28 +3278,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>5.26</v>
+        <v>2.4</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>1767100</v>
+        <v>2248200</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.13</v>
+        <v>0.2</v>
       </c>
       <c r="H63" t="n">
-        <v>41.18</v>
+        <v>45.1</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>5.438</v>
+        <v>2.439</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>5.507</v>
+        <v>2.408</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3323,39 +3323,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>6.96</v>
+        <v>2.55</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>1731900</v>
+        <v>2207700</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="H64" t="n">
-        <v>61.22</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.87</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>6.799</v>
+        <v>2.598</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>6.823</v>
+        <v>2.607</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3368,39 +3368,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.305</v>
+        <v>2.03</v>
       </c>
       <c r="E65" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.005</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>1672000</v>
+        <v>2181100</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>1.47</v>
+        <v>0.59</v>
       </c>
       <c r="H65" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.295</v>
+        <v>2.039</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.329</v>
+        <v>2.065</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3413,28 +3413,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.5</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>1560600</v>
+        <v>2130400</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.14</v>
+        <v>0.7</v>
       </c>
       <c r="H66" t="n">
-        <v>54.88</v>
+        <v>75.41</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>2.108</v>
+        <v>0.443</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>2.107</v>
+        <v>0.436</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3458,39 +3458,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>7.13</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>1542300</v>
+        <v>2071700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.14</v>
+        <v>0.13</v>
       </c>
       <c r="H67" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.55</v>
+      </c>
+      <c r="I67" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.23</v>
+        <v>7.385</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.238</v>
+        <v>7.637</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3503,38 +3503,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.345</v>
+        <v>0.545</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>-0.0143</v>
+        <v>-0.0091</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>1533700</v>
+        <v>2051200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.27</v>
+        <v>0.23</v>
       </c>
       <c r="H68" t="n">
-        <v>54.7</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.01</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="K68" s="9" t="n"/>
+        <v>0.614</v>
+      </c>
+      <c r="K68" s="9" t="n">
+        <v>0.617</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
     </row>
@@ -3546,28 +3548,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E69" s="17" t="n">
-        <v>0</v>
+        <v>4.47</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1508500</v>
+        <v>1958600</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="H69" t="n">
-        <v>68.73</v>
+        <v>38.22</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3575,10 +3577,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.803</v>
+        <v>4.568</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>0.777</v>
+        <v>4.641</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3591,39 +3593,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E70" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>0.305</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1466900</v>
+        <v>1953700</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.13</v>
+        <v>1.72</v>
       </c>
       <c r="H70" t="n">
-        <v>45.1</v>
-      </c>
-      <c r="I70" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>2.439</v>
+        <v>0.295</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>2.408</v>
+        <v>0.329</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3636,39 +3638,39 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="E71" s="10" t="n">
-        <v>0.0042</v>
+        <v>0.755</v>
+      </c>
+      <c r="E71" s="15" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1460400</v>
+        <v>1913100</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H71" t="n">
-        <v>48.77</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>4.727</v>
+        <v>0.768</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>4.818</v>
+        <v>0.771</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3681,40 +3683,38 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.34</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1430600</v>
+        <v>1894000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.24</v>
+        <v>0.34</v>
       </c>
       <c r="H72" t="n">
-        <v>33.77</v>
-      </c>
-      <c r="I72" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.16</v>
+      </c>
+      <c r="I72" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>1.667</v>
-      </c>
-      <c r="K72" s="9" t="n">
-        <v>1.747</v>
-      </c>
+        <v>0.333</v>
+      </c>
+      <c r="K72" s="9" t="n"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -3726,28 +3726,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>2.05</v>
+        <v>0.265</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.0049</v>
+        <v>-0.0364</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1420400</v>
+        <v>1876500</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>4.25</v>
+        <v>0.23</v>
       </c>
       <c r="H73" t="n">
-        <v>40.07</v>
+        <v>41.24</v>
       </c>
       <c r="I73" s="16" t="inlineStr">
         <is>
@@ -3755,10 +3755,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>2.076</v>
+        <v>0.284</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>2.082</v>
+        <v>0.283</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3771,39 +3771,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.3</v>
+        <v>0.59</v>
       </c>
       <c r="E74" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1396500</v>
+        <v>1876200</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H74" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.56</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.317</v>
+        <v>0.653</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.361</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3816,39 +3816,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.755</v>
+        <v>6.92</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>-0.0131</v>
+        <v>-0.0142</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1362000</v>
+        <v>1835200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.17</v>
+        <v>0.39</v>
       </c>
       <c r="H75" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.35</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.768</v>
+        <v>6.795</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.771</v>
+        <v>6.823</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3861,39 +3861,39 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.585</v>
+        <v>4.71</v>
       </c>
       <c r="E76" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1359400</v>
+        <v>1824400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.16</v>
+        <v>0.08</v>
       </c>
       <c r="H76" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I76" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.79</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.652</v>
+        <v>4.725</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>4.818</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3906,28 +3906,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>MYTECH</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.375</v>
+        <v>0.235</v>
       </c>
       <c r="E77" s="15" t="n">
-        <v>-0.0132</v>
+        <v>-0.0208</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1346200</v>
+        <v>1712300</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.19</v>
+        <v>15.14</v>
       </c>
       <c r="H77" t="n">
-        <v>54.17</v>
+        <v>46.35</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.373</v>
+        <v>0.236</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.37</v>
+        <v>0.25</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,39 +3951,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.0086</v>
+        <v>0.825</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1329000</v>
+        <v>1707400</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="H78" t="n">
-        <v>50.61</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>1.171</v>
+        <v>0.803</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>1.147</v>
+        <v>0.777</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3996,28 +3996,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.58</v>
+        <v>1.16</v>
       </c>
       <c r="E79" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1253100</v>
+        <v>1643300</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="H79" t="n">
-        <v>61.45</v>
+        <v>49.06</v>
       </c>
       <c r="I79" s="16" t="inlineStr">
         <is>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.536</v>
+        <v>1.17</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.482</v>
+        <v>1.147</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,39 +4041,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.23</v>
+      </c>
+      <c r="E80" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1246100</v>
+        <v>1602600</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.32</v>
+        <v>1.18</v>
       </c>
       <c r="H80" t="n">
-        <v>53.21</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.826</v>
+        <v>0.23</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.796</v>
+        <v>0.238</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,28 +4086,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>7.15</v>
-      </c>
-      <c r="E81" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1227400</v>
+        <v>1600100</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="H81" t="n">
-        <v>33.23</v>
+        <v>50.82</v>
       </c>
       <c r="I81" s="16" t="inlineStr">
         <is>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>7.387</v>
+        <v>0.865</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>7.637</v>
+        <v>0.86</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,28 +4131,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.25</v>
+        <v>1.55</v>
       </c>
       <c r="E82" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1194000</v>
+        <v>1599500</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.2</v>
+        <v>0.26</v>
       </c>
       <c r="H82" t="n">
-        <v>41.23</v>
+        <v>33.77</v>
       </c>
       <c r="I82" s="16" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.266</v>
+        <v>1.667</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.286</v>
+        <v>1.747</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4176,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>3.39</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.003</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1161500</v>
+        <v>1594900</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>2.19</v>
+        <v>0.5</v>
       </c>
       <c r="H83" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="I83" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.61</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.182</v>
+        <v>3.003</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.205</v>
+        <v>2.546</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,28 +4221,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E84" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>6.9</v>
+      </c>
+      <c r="E84" s="15" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1161300</v>
+        <v>1556500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.27</v>
+        <v>0.14</v>
       </c>
       <c r="H84" t="n">
-        <v>28.81</v>
+        <v>39.13</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.953</v>
+        <v>7.097</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>1.036</v>
+        <v>7.521</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,39 +4266,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E85" s="17" t="n">
-        <v>0</v>
+        <v>1.63</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1153500</v>
+        <v>1475800</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1.31</v>
+        <v>0.19</v>
       </c>
       <c r="H85" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.3</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.276</v>
+        <v>1.625</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.268</v>
+        <v>1.678</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,28 +4311,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E86" s="17" t="n">
-        <v>0</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1130200</v>
+        <v>1455000</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H86" t="n">
-        <v>46.77</v>
+        <v>48.93</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.239</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.241</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,28 +4356,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.0114</v>
+        <v>2.05</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1114200</v>
+        <v>1420400</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.59</v>
+        <v>4.25</v>
       </c>
       <c r="H87" t="n">
-        <v>47.64</v>
+        <v>40.07</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>0.907</v>
+        <v>2.076</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>0.889</v>
+        <v>2.082</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4416,10 +4416,10 @@
         <v>0.0155</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1071100</v>
+        <v>1418700</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.59</v>
+        <v>0.78</v>
       </c>
       <c r="H88" t="n">
         <v>36.37</v>
@@ -4446,28 +4446,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MYTECH</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.235</v>
+        <v>0.375</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>-0.0208</v>
+        <v>-0.0132</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1050000</v>
+        <v>1346200</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>9.279999999999999</v>
+        <v>0.19</v>
       </c>
       <c r="H89" t="n">
-        <v>46.35</v>
+        <v>54.17</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.236</v>
+        <v>0.373</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.25</v>
+        <v>0.37</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>-0.0097</v>
+        <v>0.58</v>
+      </c>
+      <c r="E90" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>964800</v>
+        <v>1345900</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.15</v>
+        <v>0.28</v>
       </c>
       <c r="H90" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.45</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>1.949</v>
+        <v>0.536</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>1.957</v>
+        <v>0.482</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,28 +4536,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.735</v>
+        <v>2.7</v>
       </c>
       <c r="E91" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>944500</v>
+        <v>1323600</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.32</v>
+        <v>0.11</v>
       </c>
       <c r="H91" t="n">
-        <v>50.4</v>
+        <v>46.45</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.742</v>
+        <v>2.741</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.707</v>
+        <v>2.747</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>3.39</v>
+        <v>0.825</v>
       </c>
       <c r="E92" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0061</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>903900</v>
+        <v>1312400</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H92" t="n">
-        <v>88.61</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.41</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>3.003</v>
+        <v>0.825</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>2.546</v>
+        <v>0.796</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,28 +4626,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0.016</v>
+        <v>1.16</v>
+      </c>
+      <c r="E93" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>902300</v>
+        <v>1307000</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.35</v>
+        <v>0.17</v>
       </c>
       <c r="H93" t="n">
-        <v>52.13</v>
+        <v>35.09</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.266</v>
+        <v>1.211</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.184</v>
+        <v>1.297</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>-0.009300000000000001</v>
+        <v>0.92</v>
+      </c>
+      <c r="E94" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>898100</v>
+        <v>1279200</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="H94" t="n">
-        <v>40.12</v>
+        <v>28.81</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.13</v>
+        <v>0.953</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.11</v>
+        <v>1.036</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4716,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>-0.0058</v>
+        <v>0.35</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.0294</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>888700</v>
+        <v>1252700</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.08</v>
+        <v>2.04</v>
       </c>
       <c r="H95" t="n">
-        <v>39.13</v>
+        <v>62.49</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>7.097</v>
+        <v>0.336</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>7.521</v>
+        <v>0.326</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,28 +4761,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E96" s="10" t="n">
-        <v>0.009599999999999999</v>
+        <v>1.16</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>811200</v>
+        <v>1237500</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.16</v>
+        <v>2.33</v>
       </c>
       <c r="H96" t="n">
-        <v>45.59</v>
+        <v>37.8</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.549</v>
+        <v>1.182</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.524</v>
+        <v>1.205</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>3.68</v>
+        <v>0.955</v>
       </c>
       <c r="E97" s="15" t="n">
-        <v>-0.0054</v>
+        <v>-0.0155</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>795300</v>
+        <v>1230600</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.24</v>
+        <v>0.23</v>
       </c>
       <c r="H97" t="n">
-        <v>45.03</v>
-      </c>
-      <c r="I97" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.75</v>
+      </c>
+      <c r="I97" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>3.801</v>
+        <v>0.9389999999999999</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>3.732</v>
+        <v>0.889</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,28 +4851,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>7.35</v>
+        <v>2.04</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>-0.0054</v>
+        <v>-0.0097</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>789400</v>
+        <v>1214800</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.19</v>
       </c>
       <c r="H98" t="n">
-        <v>41.41</v>
+        <v>61.78</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>7.421</v>
+        <v>1.949</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>7.843</v>
+        <v>1.957</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E99" s="10" t="n">
-        <v>0.0172</v>
+        <v>7.34</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>740400</v>
+        <v>1200600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="H99" t="n">
-        <v>39.83</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.97</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>1.213</v>
+        <v>7.42</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>1.298</v>
+        <v>7.843</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0.0215</v>
+        <v>0.235</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>728700</v>
+        <v>1180200</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.13</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H100" t="n">
-        <v>34.84</v>
-      </c>
-      <c r="I100" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.77</v>
+      </c>
+      <c r="I100" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>2.659</v>
+        <v>0.239</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>2.841</v>
+        <v>0.241</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,28 +4986,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>6.39</v>
+        <v>0.27</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>0.0016</v>
+        <v>0.0189</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>720300</v>
+        <v>1166900</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="H101" t="n">
-        <v>53.83</v>
+        <v>36.06</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>6.264</v>
+        <v>0.3</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>5.981</v>
+        <v>0.326</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.275</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>719300</v>
+        <v>1153500</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.15</v>
+        <v>1.31</v>
       </c>
       <c r="H102" t="n">
-        <v>57.31</v>
+        <v>50.42</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>1.08</v>
+        <v>0.276</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.952</v>
+        <v>0.268</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E103" s="10" t="n">
-        <v>0.006</v>
+        <v>0.26</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>700000</v>
+        <v>1151300</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.23</v>
+        <v>0.61</v>
       </c>
       <c r="H103" t="n">
-        <v>34.08</v>
+        <v>49.74</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.874</v>
+        <v>0.263</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.243</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,39 +5121,39 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E104" s="15" t="n">
-        <v>-0.0022</v>
+        <v>0.89</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.0114</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>681400</v>
+        <v>1114200</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.08</v>
+        <v>0.59</v>
       </c>
       <c r="H104" t="n">
-        <v>38.22</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.64</v>
+      </c>
+      <c r="I104" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>4.568</v>
+        <v>0.907</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>4.641</v>
+        <v>0.889</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>-0.0103</v>
+        <v>2.36</v>
+      </c>
+      <c r="E105" s="10" t="n">
+        <v>0.0129</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>663400</v>
+        <v>1077500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.13</v>
+        <v>0.19</v>
       </c>
       <c r="H105" t="n">
-        <v>60.66</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.69</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.657</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.889</v>
+        <v>2.84</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,39 +5211,39 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0.0186</v>
+        <v>2.6</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>635300</v>
+        <v>1034500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.08</v>
+        <v>6.34</v>
       </c>
       <c r="H106" t="n">
-        <v>50.6</v>
-      </c>
-      <c r="I106" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.25</v>
+      </c>
+      <c r="I106" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.626</v>
+        <v>2.682</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.678</v>
+        <v>2.787</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>0.965</v>
+        <v>1.06</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>618800</v>
+        <v>1032500</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.16</v>
+        <v>0.31</v>
       </c>
       <c r="H107" t="n">
-        <v>42.4</v>
+        <v>40.12</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.025</v>
+        <v>1.13</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>0.967</v>
+        <v>1.11</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,39 +5301,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.73</v>
+        <v>0.46</v>
       </c>
       <c r="E108" s="10" t="n">
-        <v>0.0139</v>
+        <v>0.011</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>607300</v>
+        <v>1010700</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="H108" t="n">
-        <v>50.16</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>35.5</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.739</v>
+        <v>0.484</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.542</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,28 +5346,28 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0.0102</v>
+        <v>0.73</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>592000</v>
+        <v>984300</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H109" t="n">
-        <v>45.96</v>
+        <v>49.59</v>
       </c>
       <c r="I109" s="16" t="inlineStr">
         <is>
@@ -5375,10 +5375,10 @@
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>2.063</v>
+        <v>0.741</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.992</v>
+        <v>0.707</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.635</v>
+        <v>0.505</v>
       </c>
       <c r="E110" s="10" t="n">
-        <v>0.016</v>
+        <v>0.0202</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>584300</v>
+        <v>968700</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.11</v>
+        <v>0.26</v>
       </c>
       <c r="H110" t="n">
-        <v>38.84</v>
+        <v>32.86</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.722</v>
+        <v>0.555</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.591</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E111" s="10" t="n">
+        <v>0.008</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>571400</v>
+        <v>966800</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="H111" t="n">
-        <v>33.86</v>
+        <v>51.3</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>2.491</v>
+        <v>1.265</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>2.659</v>
+        <v>1.183</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,39 +5481,39 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="E112" s="10" t="n">
-        <v>0.0052</v>
+        <v>1.11</v>
+      </c>
+      <c r="E112" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>553900</v>
+        <v>944000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="H112" t="n">
-        <v>41.12</v>
-      </c>
-      <c r="I112" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>56.45</v>
+      </c>
+      <c r="I112" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>5.838</v>
+        <v>1.079</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>6.106</v>
+        <v>0.952</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,45 +5526,1215 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>2.91</v>
-      </c>
-      <c r="E113" s="17" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E113" s="15" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>515400</v>
+        <v>932700</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.45</v>
+        <v>0.18</v>
       </c>
       <c r="H113" t="n">
-        <v>57.47</v>
-      </c>
-      <c r="I113" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.43</v>
+      </c>
+      <c r="I113" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>2.793</v>
+        <v>0.548</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>2.84</v>
+        <v>0.523</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
     </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>0245</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>MNHLDG</t>
+        </is>
+      </c>
+      <c r="D114" s="9" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>-0.0135</v>
+      </c>
+      <c r="F114" s="11" t="n">
+        <v>930500</v>
+      </c>
+      <c r="G114" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H114" t="n">
+        <v>43.89</v>
+      </c>
+      <c r="I114" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J114" s="9" t="n">
+        <v>3.799</v>
+      </c>
+      <c r="K114" s="9" t="n">
+        <v>3.731</v>
+      </c>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" s="14" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>0388</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>SEMICO</t>
+        </is>
+      </c>
+      <c r="D115" s="9" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E115" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F115" s="11" t="n">
+        <v>904500</v>
+      </c>
+      <c r="G115" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H115" t="n">
+        <v>63.68</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J115" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="K115" s="9" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" s="14" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>0338</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>KOPI</t>
+        </is>
+      </c>
+      <c r="D116" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E116" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F116" s="11" t="n">
+        <v>894000</v>
+      </c>
+      <c r="G116" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H116" t="n">
+        <v>32.09</v>
+      </c>
+      <c r="I116" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J116" s="9" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="K116" s="9" t="n">
+        <v>0.9360000000000001</v>
+      </c>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" s="14" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>0459</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>SUM</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F117" s="11" t="n">
+        <v>888500</v>
+      </c>
+      <c r="G117" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H117" t="n">
+        <v>38.08</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="n">
+        <v>0.721</v>
+      </c>
+      <c r="K117" s="9" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="L117" t="inlineStr"/>
+      <c r="M117" s="14" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>5285</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>SDG</t>
+        </is>
+      </c>
+      <c r="D118" s="9" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.0017</v>
+      </c>
+      <c r="F118" s="11" t="n">
+        <v>824100</v>
+      </c>
+      <c r="G118" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H118" t="n">
+        <v>39.64</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J118" s="9" t="n">
+        <v>5.836</v>
+      </c>
+      <c r="K118" s="9" t="n">
+        <v>6.105</v>
+      </c>
+      <c r="L118" t="inlineStr"/>
+      <c r="M118" s="14" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>0375</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>THMY</t>
+        </is>
+      </c>
+      <c r="D119" s="9" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="E119" s="10" t="n">
+        <v>0.0305</v>
+      </c>
+      <c r="F119" s="11" t="n">
+        <v>786200</v>
+      </c>
+      <c r="G119" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H119" t="n">
+        <v>48.43</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J119" s="9" t="n">
+        <v>2.067</v>
+      </c>
+      <c r="K119" s="9" t="n">
+        <v>1.993</v>
+      </c>
+      <c r="L119" t="inlineStr"/>
+      <c r="M119" s="14" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>5286</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>MI</t>
+        </is>
+      </c>
+      <c r="D120" s="9" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="E120" s="15" t="n">
+        <v>-0.0031</v>
+      </c>
+      <c r="F120" s="11" t="n">
+        <v>779700</v>
+      </c>
+      <c r="G120" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H120" t="n">
+        <v>53.32</v>
+      </c>
+      <c r="I120" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J120" s="9" t="n">
+        <v>6.262</v>
+      </c>
+      <c r="K120" s="9" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" s="14" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>7081</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>PHARMA</t>
+        </is>
+      </c>
+      <c r="D121" s="9" t="n">
+        <v>0.785</v>
+      </c>
+      <c r="E121" s="15" t="n">
+        <v>-0.0309</v>
+      </c>
+      <c r="F121" s="11" t="n">
+        <v>751100</v>
+      </c>
+      <c r="G121" s="12" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H121" t="n">
+        <v>23.21</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J121" s="9" t="n">
+        <v>0.889</v>
+      </c>
+      <c r="K121" s="9" t="n">
+        <v>1.048</v>
+      </c>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" s="14" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2852</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CMSB</t>
+        </is>
+      </c>
+      <c r="D122" s="9" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="E122" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F122" s="11" t="n">
+        <v>748800</v>
+      </c>
+      <c r="G122" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H122" t="n">
+        <v>30.9</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J122" s="9" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="K122" s="9" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="L122" t="inlineStr"/>
+      <c r="M122" s="14" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>0310</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>UUE</t>
+        </is>
+      </c>
+      <c r="D123" s="9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="E123" s="10" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="F123" s="11" t="n">
+        <v>721100</v>
+      </c>
+      <c r="G123" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H123" t="n">
+        <v>50.16</v>
+      </c>
+      <c r="I123" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J123" s="9" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="K123" s="9" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" s="14" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>0296</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>HEGROUP</t>
+        </is>
+      </c>
+      <c r="D124" s="9" t="n">
+        <v>0.965</v>
+      </c>
+      <c r="E124" s="15" t="n">
+        <v>-0.035</v>
+      </c>
+      <c r="F124" s="11" t="n">
+        <v>679200</v>
+      </c>
+      <c r="G124" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H124" t="n">
+        <v>42.4</v>
+      </c>
+      <c r="I124" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J124" s="9" t="n">
+        <v>1.025</v>
+      </c>
+      <c r="K124" s="9" t="n">
+        <v>0.967</v>
+      </c>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" s="14" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>5272</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>RANHILL</t>
+        </is>
+      </c>
+      <c r="D125" s="9" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>-0.0254</v>
+      </c>
+      <c r="F125" s="11" t="n">
+        <v>653500</v>
+      </c>
+      <c r="G125" s="12" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="H125" t="n">
+        <v>46.76</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J125" s="9" t="n">
+        <v>3.151</v>
+      </c>
+      <c r="K125" s="9" t="n">
+        <v>2.942</v>
+      </c>
+      <c r="L125" t="inlineStr"/>
+      <c r="M125" s="14" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>5878</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>KPJ</t>
+        </is>
+      </c>
+      <c r="D126" s="9" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" s="11" t="n">
+        <v>642500</v>
+      </c>
+      <c r="G126" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H126" t="n">
+        <v>33.86</v>
+      </c>
+      <c r="I126" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J126" s="9" t="n">
+        <v>2.491</v>
+      </c>
+      <c r="K126" s="9" t="n">
+        <v>2.659</v>
+      </c>
+      <c r="L126" t="inlineStr"/>
+      <c r="M126" s="14" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>1171</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>MBSB</t>
+        </is>
+      </c>
+      <c r="D127" s="9" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" s="11" t="n">
+        <v>637200</v>
+      </c>
+      <c r="G127" s="12" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="H127" t="n">
+        <v>29.82</v>
+      </c>
+      <c r="I127" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J127" s="9" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="K127" s="9" t="n">
+        <v>0.5629999999999999</v>
+      </c>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" s="14" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>5323</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>JPG</t>
+        </is>
+      </c>
+      <c r="D128" s="9" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" s="11" t="n">
+        <v>635800</v>
+      </c>
+      <c r="G128" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H128" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="I128" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J128" s="9" t="n">
+        <v>1.755</v>
+      </c>
+      <c r="K128" s="9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" s="14" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D129" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="E129" s="10" t="n">
+        <v>0.008699999999999999</v>
+      </c>
+      <c r="F129" s="11" t="n">
+        <v>633600</v>
+      </c>
+      <c r="G129" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H129" t="n">
+        <v>53.52</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J129" s="9" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="K129" s="9" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" s="14" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>0097</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>VITROX</t>
+        </is>
+      </c>
+      <c r="D130" s="9" t="n">
+        <v>10.34</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>-0.0227</v>
+      </c>
+      <c r="F130" s="11" t="n">
+        <v>622400</v>
+      </c>
+      <c r="G130" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H130" t="n">
+        <v>50.64</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J130" s="9" t="n">
+        <v>10.434</v>
+      </c>
+      <c r="K130" s="9" t="n">
+        <v>9.846</v>
+      </c>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" s="14" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>1155</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>MAYBANK</t>
+        </is>
+      </c>
+      <c r="D131" s="9" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E131" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" s="11" t="n">
+        <v>618700</v>
+      </c>
+      <c r="G131" s="12" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="H131" t="n">
+        <v>46.44</v>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J131" s="9" t="n">
+        <v>9.988</v>
+      </c>
+      <c r="K131" s="9" t="n">
+        <v>10.116</v>
+      </c>
+      <c r="L131" t="inlineStr"/>
+      <c r="M131" s="14" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>0045</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>SSB8</t>
+        </is>
+      </c>
+      <c r="D132" s="9" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" s="11" t="n">
+        <v>581400</v>
+      </c>
+      <c r="G132" s="12" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="H132" t="n">
+        <v>45.21</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J132" s="9" t="n">
+        <v>0.634</v>
+      </c>
+      <c r="K132" s="9" t="n">
+        <v>0.621</v>
+      </c>
+      <c r="L132" t="inlineStr"/>
+      <c r="M132" s="14" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D133" s="9" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="E133" s="15" t="n">
+        <v>-0.0121</v>
+      </c>
+      <c r="F133" s="11" t="n">
+        <v>573300</v>
+      </c>
+      <c r="G133" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H133" t="n">
+        <v>39.52</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J133" s="9" t="n">
+        <v>3.332</v>
+      </c>
+      <c r="K133" s="9" t="n">
+        <v>3.561</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" s="14" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D134" s="9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>-0.0074</v>
+      </c>
+      <c r="F134" s="11" t="n">
+        <v>573000</v>
+      </c>
+      <c r="G134" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H134" t="n">
+        <v>46.18</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J134" s="9" t="n">
+        <v>2.779</v>
+      </c>
+      <c r="K134" s="9" t="n">
+        <v>2.684</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" s="14" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D135" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E135" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F135" s="11" t="n">
+        <v>570200</v>
+      </c>
+      <c r="G135" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H135" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J135" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="K135" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L135" t="inlineStr"/>
+      <c r="M135" s="14" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D136" s="9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="E136" s="15" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="F136" s="11" t="n">
+        <v>551200</v>
+      </c>
+      <c r="G136" s="12" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="H136" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J136" s="9" t="n">
+        <v>2.791</v>
+      </c>
+      <c r="K136" s="9" t="n">
+        <v>2.839</v>
+      </c>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" s="14" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D137" s="9" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="E137" s="15" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="F137" s="11" t="n">
+        <v>547200</v>
+      </c>
+      <c r="G137" s="12" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H137" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J137" s="9" t="n">
+        <v>13.055</v>
+      </c>
+      <c r="K137" s="9" t="n">
+        <v>13.334</v>
+      </c>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" s="14" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>5292</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>UWC</t>
+        </is>
+      </c>
+      <c r="D138" s="9" t="n">
+        <v>7.08</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>539700</v>
+      </c>
+      <c r="G138" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H138" t="n">
+        <v>47.02</v>
+      </c>
+      <c r="I138" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J138" s="9" t="n">
+        <v>7.281</v>
+      </c>
+      <c r="K138" s="9" t="n">
+        <v>6.934</v>
+      </c>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" s="14" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D139" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F139" s="11" t="n">
+        <v>520100</v>
+      </c>
+      <c r="G139" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H139" t="n">
+        <v>55</v>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J139" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K139" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M113"/>
+  <autoFilter ref="A1:M139"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$152</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.08</v>
+        <v>4.11</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0074</v>
+        <v>0.0148</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3710000</v>
+        <v>3934500</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.49</v>
+        <v>0.52</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.3</v>
+        <v>63.92</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.755</v>
+        <v>3.758</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>3.202</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号可靠，RSI 63.3未超买，现价高于50日均线约27%，技术面偏强。</t>
+          <t>SAR转多信号可靠，RSI 63.92未超买，现价高于50日均线约28%，多头动能偏强。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.065</v>
+        <v>0.06</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>108811500</v>
+        <v>115423300</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H3" t="n">
-        <v>29.97</v>
+        <v>28.04</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.272</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.32</v>
+        <v>0.315</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0303</v>
+        <v>-0.0455</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>51675100</v>
+        <v>52780700</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="H4" t="n">
-        <v>56.38</v>
+        <v>54.51</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0.0333</v>
+        <v>0.15</v>
+      </c>
+      <c r="E5" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>18133400</v>
+        <v>20749600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="n">
-        <v>44</v>
+        <v>37.79</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.47</v>
+        <v>0.485</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>0.0217</v>
+        <v>0.05429999999999999</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>13830500</v>
+        <v>20366000</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>76.43000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.412</v>
+        <v>0.414</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.309</v>
+        <v>0.31</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>-0.039</v>
+        <v>0.91</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0341</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>12214500</v>
+        <v>18414700</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="H7" t="n">
-        <v>53.38</v>
+        <v>63.71</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>1.96</v>
+        <v>0.852</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>1.785</v>
+        <v>0.758</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0241</v>
+        <v>1.98</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0341</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>11703500</v>
+        <v>13812700</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.33</v>
+        <v>0.49</v>
       </c>
       <c r="H8" t="n">
-        <v>38.49</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.01</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.459</v>
+        <v>1.961</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.477</v>
+        <v>1.786</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0241</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>10196200</v>
+        <v>12575000</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.48</v>
+        <v>0.35</v>
       </c>
       <c r="H9" t="n">
-        <v>44.11</v>
+        <v>38.49</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.186</v>
+        <v>0.459</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.186</v>
+        <v>0.477</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0345</v>
+        <v>0.455</v>
+      </c>
+      <c r="E10" s="10" t="n">
+        <v>0.046</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>10021300</v>
+        <v>12397000</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>2.02</v>
+        <v>0.62</v>
       </c>
       <c r="H10" t="n">
-        <v>18.28</v>
+        <v>59.71</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.317</v>
+        <v>0.43</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>1.515</v>
+        <v>0.381</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.885</v>
-      </c>
-      <c r="E11" s="10" t="n">
-        <v>0.005699999999999999</v>
+        <v>0.895</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0529</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>9932100</v>
+        <v>12083100</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.13</v>
+        <v>1.26</v>
       </c>
       <c r="H11" t="n">
-        <v>60.49</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.91</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.85</v>
+        <v>1.011</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.757</v>
+        <v>0.977</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>0.155</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>9844000</v>
+        <v>11647400</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>27.05</v>
+        <v>0.32</v>
       </c>
       <c r="H12" t="n">
-        <v>47.02</v>
+        <v>48.33</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.005</v>
+        <v>0.156</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.006</v>
+        <v>0.156</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,31 +1060,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.265</v>
+        <v>0.305</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>9387600</v>
-      </c>
-      <c r="G13" s="12" t="n"/>
+        <v>11306900</v>
+      </c>
+      <c r="G13" s="12" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="H13" t="n">
+        <v>47.4</v>
+      </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K13" s="9" t="n">
+        <v>0.302</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
     </row>
@@ -1096,39 +1105,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>BENALEC</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.065</v>
+        <v>0.735</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.028</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>9275700</v>
+        <v>11192600</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>11.55</v>
+        <v>0.45</v>
       </c>
       <c r="H14" t="n">
-        <v>55.37</v>
-      </c>
-      <c r="I14" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>83.44</v>
+      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.063</v>
+        <v>0.651</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.066</v>
+        <v>0.555</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1141,39 +1150,39 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.006999999999999999</v>
+        <v>1.11</v>
+      </c>
+      <c r="E15" s="15" t="n">
+        <v>-0.0431</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>9045300</v>
+        <v>10498600</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>0.37</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>81.81</v>
-      </c>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>17.85</v>
+      </c>
+      <c r="I15" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>0.65</v>
+        <v>1.316</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>0.555</v>
+        <v>1.515</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1186,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.03700000000000001</v>
+        <v>0.005</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>8363800</v>
+        <v>10304000</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>0.87</v>
+        <v>28.32</v>
       </c>
       <c r="H16" t="n">
-        <v>36.24</v>
+        <v>47.02</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1215,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>1.013</v>
+        <v>0.005</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.977</v>
+        <v>0.006</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1231,39 +1240,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="E17" s="10" t="n">
-        <v>0.04</v>
+        <v>0.18</v>
+      </c>
+      <c r="E17" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>8302600</v>
+        <v>10255200</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>16.49</v>
+        <v>0.49</v>
       </c>
       <c r="H17" t="n">
-        <v>56.19</v>
-      </c>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I17" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>0.127</v>
+        <v>0.186</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>0.129</v>
+        <v>0.186</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,39 +1285,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>BENALEC</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>-0.0588</v>
+        <v>0.065</v>
+      </c>
+      <c r="E18" s="10" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>8122000</v>
+        <v>10139400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.13</v>
+        <v>12.63</v>
       </c>
       <c r="H18" t="n">
-        <v>51.35</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.159</v>
+        <v>0.063</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.145</v>
+        <v>0.066</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,28 +1330,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E19" s="17" t="n">
-        <v>0</v>
+        <v>0.37</v>
+      </c>
+      <c r="E19" s="15" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>7756500</v>
+        <v>10124400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.4</v>
+        <v>1.14</v>
       </c>
       <c r="H19" t="n">
-        <v>47.4</v>
+        <v>18.34</v>
       </c>
       <c r="I19" s="16" t="inlineStr">
         <is>
@@ -1350,10 +1359,10 @@
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.307</v>
+        <v>0.39</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.302</v>
+        <v>0.404</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,40 +1375,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E20" s="15" t="n">
-        <v>-0.0061</v>
+        <v>0.265</v>
+      </c>
+      <c r="E20" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>7630000</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="H20" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n">
-        <v>0.8169999999999999</v>
-      </c>
-      <c r="K20" s="9" t="n">
-        <v>0.8139999999999999</v>
-      </c>
+        <v>9932300</v>
+      </c>
+      <c r="G20" s="12" t="n"/>
+      <c r="I20" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n"/>
+      <c r="K20" s="9" t="n"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>0.82</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>7223500</v>
+        <v>9071000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="H21" t="n">
-        <v>55.05</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.428</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.381</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,33 +1456,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.0526</v>
+        <v>0.135</v>
+      </c>
+      <c r="E22" s="10" t="n">
+        <v>0.08</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>6782900</v>
+        <v>8521100</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+        <v>16.93</v>
+      </c>
+      <c r="H22" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.129</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1494,39 +1501,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.365</v>
+        <v>0.165</v>
       </c>
       <c r="E23" s="15" t="n">
-        <v>-0.0267</v>
+        <v>-0.0294</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>6347400</v>
+        <v>8308500</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.72</v>
+        <v>0.13</v>
       </c>
       <c r="H23" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.64</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.39</v>
+        <v>0.16</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.404</v>
+        <v>0.146</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,39 +1546,39 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.19</v>
+        <v>0.775</v>
       </c>
       <c r="E24" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>5974400</v>
+        <v>7349700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.28</v>
+        <v>0.47</v>
       </c>
       <c r="H24" t="n">
-        <v>33.79</v>
-      </c>
-      <c r="I24" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.21</v>
+        <v>0.774</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.23</v>
+        <v>0.776</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1584,40 +1591,33 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E25" s="17" t="n">
-        <v>0</v>
+        <v>0.09</v>
+      </c>
+      <c r="E25" s="15" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>5764100</v>
+        <v>6789100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="H25" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K25" s="9" t="n">
-        <v>0.776</v>
-      </c>
+        <v>0.27</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1638,19 +1638,19 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.78</v>
+        <v>4.77</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>-0.0104</v>
+        <v>-0.0124</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>5753600</v>
+        <v>6742600</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.24</v>
+        <v>0.28</v>
       </c>
       <c r="H26" t="n">
-        <v>45.61</v>
+        <v>45.1</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.869</v>
+        <v>4.868</v>
       </c>
       <c r="K26" s="9" t="n">
         <v>4.755</v>
@@ -1674,39 +1674,39 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.15</v>
+        <v>0.865</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.0625</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>5640000</v>
+        <v>6698700</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.16</v>
+        <v>0.33</v>
       </c>
       <c r="H27" t="n">
-        <v>41.46</v>
-      </c>
-      <c r="I27" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.155</v>
+        <v>0.868</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.156</v>
+        <v>0.869</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E28" s="15" t="n">
-        <v>-0.023</v>
+        <v>0.19</v>
+      </c>
+      <c r="E28" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>4816700</v>
+        <v>6673200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.29</v>
+        <v>0.31</v>
       </c>
       <c r="H28" t="n">
-        <v>24.81</v>
+        <v>33.79</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.484</v>
+        <v>0.21</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.63</v>
+        <v>0.23</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E29" s="10" t="n">
-        <v>0.02</v>
+        <v>2.06</v>
+      </c>
+      <c r="E29" s="15" t="n">
+        <v>-0.0048</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>4691800</v>
+        <v>6225300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.57</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>34.07</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>39.55</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.269</v>
+        <v>2.118</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.294</v>
+        <v>2.234</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,33 +1809,40 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0</v>
+        <v>0.325</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>-0.0441</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>4659300</v>
+        <v>5998000</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.21</v>
+        <v>0.76</v>
+      </c>
+      <c r="H30" t="n">
+        <v>41.68</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J30" s="9" t="n"/>
-      <c r="K30" s="9" t="n"/>
+      <c r="J30" s="9" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K30" s="9" t="n">
+        <v>0.329</v>
+      </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
     </row>
@@ -1847,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E31" s="17" t="n">
-        <v>0</v>
+        <v>1.14</v>
+      </c>
+      <c r="E31" s="10" t="n">
+        <v>0.0755</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>4558900</v>
+        <v>5989400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.34</v>
+        <v>0.67</v>
       </c>
       <c r="H31" t="n">
-        <v>18.69</v>
-      </c>
-      <c r="I31" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.03</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.591</v>
+        <v>1.086</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.884</v>
+        <v>1.053</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1892,28 +1899,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.445</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0349</v>
+        <v>0.425</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>4346400</v>
+        <v>5534800</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.45</v>
+        <v>0.33</v>
       </c>
       <c r="H32" t="n">
-        <v>41.38</v>
+        <v>24.81</v>
       </c>
       <c r="I32" s="16" t="inlineStr">
         <is>
@@ -1921,10 +1928,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.496</v>
+        <v>0.484</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.468</v>
+        <v>0.63</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1937,28 +1944,28 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E33" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.635</v>
+      </c>
+      <c r="E33" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>4301600</v>
+        <v>5219300</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.21</v>
+        <v>0.5</v>
       </c>
       <c r="H33" t="n">
-        <v>46.51</v>
+        <v>60.81</v>
       </c>
       <c r="I33" s="13" t="inlineStr">
         <is>
@@ -1966,10 +1973,10 @@
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.868</v>
+        <v>0.623</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.869</v>
+        <v>0.617</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1982,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E34" s="10" t="n">
-        <v>0.0625</v>
+        <v>1.35</v>
+      </c>
+      <c r="E34" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4237600</v>
+        <v>4909400</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>1.37</v>
+        <v>0.37</v>
       </c>
       <c r="H34" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.69</v>
+      </c>
+      <c r="I34" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.159</v>
+        <v>1.591</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.157</v>
+        <v>1.884</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2027,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>2.39</v>
+        <v>0.41</v>
       </c>
       <c r="E35" s="15" t="n">
-        <v>-0.0165</v>
+        <v>-0.0238</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4116600</v>
+        <v>4763900</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>1.17</v>
+        <v>0.39</v>
       </c>
       <c r="H35" t="n">
-        <v>61.04</v>
+        <v>54.72</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2056,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>2.275</v>
+        <v>0.4</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>2.2</v>
+        <v>0.382</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2072,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.205</v>
+        <v>0.25</v>
       </c>
       <c r="E36" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4111400</v>
+        <v>4710300</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.37</v>
+        <v>0.57</v>
       </c>
       <c r="H36" t="n">
-        <v>28.46</v>
+        <v>28.65</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2101,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.225</v>
+        <v>0.269</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.272</v>
+        <v>0.294</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2117,40 +2124,33 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="E37" s="15" t="n">
-        <v>-0.0048</v>
+        <v>0.23</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4008500</v>
+        <v>4670500</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="H37" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J37" s="9" t="n">
-        <v>2.118</v>
-      </c>
-      <c r="K37" s="9" t="n">
-        <v>2.234</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="I37" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2162,25 +2162,25 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E38" s="17" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>3928100</v>
+        <v>4612100</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.37</v>
+        <v>1.49</v>
       </c>
       <c r="H38" t="n">
         <v>60.81</v>
@@ -2191,10 +2191,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.623</v>
+        <v>0.159</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.617</v>
+        <v>0.157</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,28 +2207,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.265</v>
+        <v>0.44</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.0233</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>3859000</v>
+        <v>4468000</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.36</v>
+        <v>0.46</v>
       </c>
       <c r="H39" t="n">
-        <v>40.68</v>
+        <v>40.39</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.287</v>
+        <v>0.496</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.28</v>
+        <v>0.468</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,39 +2252,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E40" s="15" t="n">
-        <v>-0.0238</v>
+        <v>0.26</v>
+      </c>
+      <c r="E40" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>3764300</v>
+        <v>4419000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="H40" t="n">
-        <v>54.72</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.24</v>
+      </c>
+      <c r="I40" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.4</v>
+        <v>0.287</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.382</v>
+        <v>0.279</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,28 +2297,28 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0312</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>OFB</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E41" s="17" t="n">
-        <v>0</v>
+        <v>2.41</v>
+      </c>
+      <c r="E41" s="15" t="n">
+        <v>-0.008199999999999999</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>3643200</v>
+        <v>4279400</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>58.07</v>
+        <v>1.21</v>
       </c>
       <c r="H41" t="n">
-        <v>76.15000000000001</v>
+        <v>62.94</v>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
@@ -2326,10 +2326,10 @@
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>0.136</v>
+        <v>2.277</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>0.138</v>
+        <v>2.2</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E42" s="15" t="n">
-        <v>-0.0286</v>
+        <v>0.21</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <v>0.0244</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>3626900</v>
+        <v>4122400</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.67</v>
+        <v>0.37</v>
       </c>
       <c r="H42" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.99</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.163</v>
+        <v>0.225</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.165</v>
+        <v>0.272</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,39 +2387,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="E43" s="10" t="n">
-        <v>0.0092</v>
+        <v>1.27</v>
+      </c>
+      <c r="E43" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3626600</v>
+        <v>3707900</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.17</v>
+        <v>0.54</v>
       </c>
       <c r="H43" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="I43" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.78</v>
+      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>0.5669999999999999</v>
+        <v>1.225</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>0.545</v>
+        <v>1.204</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="E44" s="15" t="n">
-        <v>-0.0294</v>
+        <v>4.64</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0334</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3532200</v>
+        <v>3704700</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="H44" t="n">
-        <v>43.21</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.94</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>0.35</v>
+        <v>4.407</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>0.329</v>
+        <v>4.439</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,28 +2477,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.32</v>
+        <v>0.555</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.0159</v>
+        <v>0.0183</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3420900</v>
+        <v>3657200</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.33</v>
+        <v>0.18</v>
       </c>
       <c r="H45" t="n">
-        <v>43.38</v>
+        <v>48.37</v>
       </c>
       <c r="I45" s="16" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.339</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.336</v>
+        <v>0.545</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>0312</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>OFB</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E46" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.16</v>
+      </c>
+      <c r="E46" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3291300</v>
+        <v>3654100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.48</v>
+        <v>58.24</v>
       </c>
       <c r="H46" t="n">
-        <v>58.78</v>
+        <v>76.15000000000001</v>
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>1.225</v>
+        <v>0.136</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>1.204</v>
+        <v>0.138</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,28 +2567,28 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E47" s="17" t="n">
-        <v>0</v>
+        <v>0.17</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3237500</v>
+        <v>3626900</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.72</v>
+        <v>0.67</v>
       </c>
       <c r="H47" t="n">
-        <v>52.95</v>
+        <v>56.21</v>
       </c>
       <c r="I47" s="13" t="inlineStr">
         <is>
@@ -2596,10 +2596,10 @@
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.336</v>
+        <v>0.163</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.343</v>
+        <v>0.165</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E48" s="15" t="n">
-        <v>-0.0818</v>
+        <v>2.49</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3186300</v>
+        <v>3463300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.68</v>
+        <v>0.18</v>
       </c>
       <c r="H48" t="n">
-        <v>46.27</v>
+        <v>43.21</v>
       </c>
       <c r="I48" s="16" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.834</v>
+        <v>2.602</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.618</v>
+        <v>2.559</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>4.62</v>
+        <v>0.32</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>0.029</v>
+        <v>0.0159</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3104900</v>
+        <v>3426900</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="H49" t="n">
-        <v>58.34</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.38</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>4.406</v>
+        <v>0.339</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>4.438</v>
+        <v>0.336</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.745</v>
+        <v>0.735</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0205</v>
+        <v>0.0068</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3088200</v>
+        <v>3345500</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H50" t="n">
-        <v>51.29</v>
+        <v>49.92</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.737</v>
+        <v>0.736</v>
       </c>
       <c r="K50" s="9" t="n">
         <v>0.724</v>
@@ -2747,28 +2747,28 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E51" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.73</v>
+      </c>
+      <c r="E51" s="15" t="n">
+        <v>-0.0818</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3068900</v>
+        <v>3329800</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="H51" t="n">
-        <v>41.23</v>
+        <v>46.27</v>
       </c>
       <c r="I51" s="16" t="inlineStr">
         <is>
@@ -2776,10 +2776,10 @@
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.266</v>
+        <v>0.834</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.286</v>
+        <v>0.618</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="E52" s="10" t="n">
-        <v>0.0163</v>
+        <v>0.335</v>
+      </c>
+      <c r="E52" s="15" t="n">
+        <v>-0.0147</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3062100</v>
+        <v>3245100</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.16</v>
+        <v>0.73</v>
       </c>
       <c r="H52" t="n">
-        <v>43.88</v>
-      </c>
-      <c r="I52" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.96</v>
+      </c>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.603</v>
+        <v>0.335</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.559</v>
+        <v>0.343</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2846,19 +2846,19 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="E53" s="15" t="n">
-        <v>-0.0833</v>
+        <v>-0.0417</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>2972200</v>
+        <v>3231200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="H53" t="n">
-        <v>13.47</v>
+        <v>14.67</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.259</v>
+        <v>0.26</v>
       </c>
       <c r="K53" s="9" t="n"/>
       <c r="L53" t="inlineStr"/>
@@ -2880,39 +2880,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.295</v>
-      </c>
-      <c r="E54" s="10" t="n">
-        <v>0.0172</v>
+        <v>7.13</v>
+      </c>
+      <c r="E54" s="15" t="n">
+        <v>-0.0028</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>2714400</v>
+        <v>3115300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="H54" t="n">
-        <v>36.34</v>
-      </c>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.55</v>
+      </c>
+      <c r="I54" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.316</v>
+        <v>7.385</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.361</v>
+        <v>7.637</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2925,39 +2925,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E55" s="15" t="n">
-        <v>-0.0063</v>
+        <v>0.105</v>
+      </c>
+      <c r="E55" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>2472600</v>
+        <v>3112900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.38</v>
+        <v>0.68</v>
       </c>
       <c r="H55" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="I55" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.33</v>
+      </c>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.888</v>
+        <v>0.098</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.856</v>
+        <v>0.083</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2970,39 +2970,39 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.435</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>-0.0114</v>
+        <v>0.25</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>2463200</v>
+        <v>3068900</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.36</v>
+        <v>0.5</v>
       </c>
       <c r="H56" t="n">
-        <v>52.42</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.23</v>
+      </c>
+      <c r="I56" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.429</v>
+        <v>0.266</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.418</v>
+        <v>0.286</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3015,28 +3015,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.0283</v>
+        <v>2.41</v>
+      </c>
+      <c r="E57" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2437900</v>
+        <v>2932600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="H57" t="n">
-        <v>51.98</v>
+        <v>46.38</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>1.081</v>
+        <v>2.44</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>1.053</v>
+        <v>2.408</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3060,33 +3060,40 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>0</v>
+        <v>1.19</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2429900</v>
+        <v>2890100</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.06</v>
+        <v>0.45</v>
+      </c>
+      <c r="H58" t="n">
+        <v>53.45</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="J58" s="9" t="n">
+        <v>1.173</v>
+      </c>
+      <c r="K58" s="9" t="n">
+        <v>1.147</v>
+      </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
     </row>
@@ -3098,28 +3105,28 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>1.29</v>
+        <v>0.43</v>
       </c>
       <c r="E59" s="15" t="n">
-        <v>-0.0373</v>
+        <v>-0.0227</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2373000</v>
+        <v>2817500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.67</v>
+        <v>0.41</v>
       </c>
       <c r="H59" t="n">
-        <v>56.37</v>
+        <v>51.27</v>
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
@@ -3127,10 +3134,10 @@
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>1.245</v>
+        <v>0.428</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>1.107</v>
+        <v>0.418</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3143,28 +3150,28 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>-0.0132</v>
+        <v>0.3</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2359100</v>
+        <v>2757900</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.22</v>
+        <v>0.43</v>
       </c>
       <c r="H60" t="n">
-        <v>27.63</v>
+        <v>38.77</v>
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
@@ -3172,10 +3179,10 @@
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.478</v>
+        <v>0.317</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.589</v>
+        <v>0.361</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3188,28 +3195,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>5.26</v>
+        <v>0.785</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0063</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2337500</v>
+        <v>2743400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.18</v>
+        <v>0.43</v>
       </c>
       <c r="H61" t="n">
-        <v>41.18</v>
+        <v>35.61</v>
       </c>
       <c r="I61" s="16" t="inlineStr">
         <is>
@@ -3217,10 +3224,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>5.438</v>
+        <v>0.888</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>5.507</v>
+        <v>0.856</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3233,40 +3240,33 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>0.715</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2259700</v>
+        <v>2713500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H62" t="n">
-        <v>54.88</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J62" s="9" t="n">
-        <v>2.108</v>
-      </c>
-      <c r="K62" s="9" t="n">
-        <v>2.107</v>
-      </c>
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I62" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J62" s="9" t="n"/>
+      <c r="K62" s="9" t="n"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
     </row>
@@ -3278,28 +3278,28 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="E63" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>2.57</v>
+      </c>
+      <c r="E63" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2248200</v>
+        <v>2642100</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.2</v>
+        <v>0.47</v>
       </c>
       <c r="H63" t="n">
-        <v>45.1</v>
+        <v>47.43</v>
       </c>
       <c r="I63" s="16" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.439</v>
+        <v>2.6</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.408</v>
+        <v>2.607</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3323,39 +3323,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>2.55</v>
+        <v>7.48</v>
       </c>
       <c r="E64" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0027</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2207700</v>
+        <v>2613800</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.4</v>
+        <v>0.97</v>
       </c>
       <c r="H64" t="n">
-        <v>45.87</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.22</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>2.598</v>
+        <v>7.55</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>2.607</v>
+        <v>7.72</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3368,39 +3368,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.005</v>
+        <v>0.375</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2181100</v>
+        <v>2549700</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.59</v>
+        <v>0.24</v>
       </c>
       <c r="H65" t="n">
-        <v>46.51</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>27.63</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.039</v>
+        <v>0.478</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>2.065</v>
+        <v>0.589</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3413,28 +3413,28 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.5</v>
+        <v>1.28</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2130400</v>
+        <v>2516200</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.7</v>
+        <v>0.72</v>
       </c>
       <c r="H66" t="n">
-        <v>75.41</v>
+        <v>55.46</v>
       </c>
       <c r="I66" s="13" t="inlineStr">
         <is>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.443</v>
+        <v>1.244</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.436</v>
+        <v>1.107</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3458,39 +3458,39 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>7.13</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>-0.0028</v>
+        <v>0.625</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2071700</v>
+        <v>2494400</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.13</v>
+        <v>0.72</v>
       </c>
       <c r="H67" t="n">
-        <v>32.55</v>
-      </c>
-      <c r="I67" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.68</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>7.385</v>
+        <v>0.62</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>7.637</v>
+        <v>0.61</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3503,39 +3503,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>0.545</v>
+        <v>6.94</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>-0.0091</v>
+        <v>-0.0114</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2051200</v>
+        <v>2490500</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.23</v>
+        <v>0.53</v>
       </c>
       <c r="H68" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="I68" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.75</v>
+      </c>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>0.614</v>
+        <v>6.797</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>0.617</v>
+        <v>6.823</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3548,28 +3548,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E69" s="15" t="n">
-        <v>-0.0022</v>
+        <v>2.14</v>
+      </c>
+      <c r="E69" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>1958600</v>
+        <v>2480800</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H69" t="n">
-        <v>38.22</v>
+        <v>56.48</v>
       </c>
       <c r="I69" s="13" t="inlineStr">
         <is>
@@ -3577,10 +3577,10 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>4.568</v>
+        <v>2.109</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>4.641</v>
+        <v>2.107</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3593,28 +3593,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.305</v>
+        <v>4.72</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.0021</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>1953700</v>
+        <v>2452600</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1.72</v>
+        <v>0.11</v>
       </c>
       <c r="H70" t="n">
-        <v>51.87</v>
+        <v>47.8</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.295</v>
+        <v>4.726</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.329</v>
+        <v>4.818</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3638,28 +3638,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.755</v>
+        <v>5.26</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.0131</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>1913100</v>
+        <v>2445500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.24</v>
+        <v>0.19</v>
       </c>
       <c r="H71" t="n">
-        <v>45.88</v>
+        <v>41.18</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3667,10 +3667,10 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.768</v>
+        <v>5.438</v>
       </c>
       <c r="K71" s="9" t="n">
-        <v>0.771</v>
+        <v>5.507</v>
       </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
@@ -3683,28 +3683,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0286</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>1894000</v>
+        <v>2387000</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.34</v>
+        <v>1.31</v>
       </c>
       <c r="H72" t="n">
-        <v>53.16</v>
+        <v>48.93</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3712,9 +3712,11 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="K72" s="9" t="n"/>
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="K72" s="9" t="n">
+        <v>0.5620000000000001</v>
+      </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
     </row>
@@ -3726,39 +3728,39 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.265</v>
+        <v>0.495</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.0364</v>
+        <v>-0.0198</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>1876500</v>
+        <v>2334900</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.23</v>
+        <v>0.77</v>
       </c>
       <c r="H73" t="n">
-        <v>41.24</v>
-      </c>
-      <c r="I73" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.58</v>
+      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.284</v>
+        <v>0.442</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.283</v>
+        <v>0.436</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3771,40 +3773,38 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.34</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>1876200</v>
+        <v>2302100</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.22</v>
+        <v>0.41</v>
       </c>
       <c r="H74" t="n">
-        <v>36.56</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.16</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.653</v>
-      </c>
-      <c r="K74" s="9" t="n">
-        <v>0.6850000000000001</v>
-      </c>
+        <v>0.333</v>
+      </c>
+      <c r="K74" s="9" t="n"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3816,39 +3816,39 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>6.92</v>
+        <v>0.54</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>-0.0142</v>
+        <v>-0.0182</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>1835200</v>
+        <v>2247200</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.39</v>
+        <v>0.25</v>
       </c>
       <c r="H75" t="n">
-        <v>58.35</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.41</v>
+      </c>
+      <c r="I75" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>6.795</v>
+        <v>0.614</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>6.823</v>
+        <v>0.617</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3861,28 +3861,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E76" s="17" t="n">
-        <v>0</v>
+        <v>4.47</v>
+      </c>
+      <c r="E76" s="15" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>1824400</v>
+        <v>2246200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.08</v>
+        <v>0.26</v>
       </c>
       <c r="H76" t="n">
-        <v>46.79</v>
+        <v>38.22</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>4.725</v>
+        <v>4.568</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>4.818</v>
+        <v>4.641</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3906,39 +3906,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MYTECH</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>-0.0208</v>
+        <v>2.03</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>1712300</v>
+        <v>2203200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>15.14</v>
+        <v>0.6</v>
       </c>
       <c r="H77" t="n">
-        <v>46.35</v>
-      </c>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I77" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.236</v>
+        <v>2.039</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.25</v>
+        <v>2.065</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,39 +3951,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E78" s="17" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E78" s="15" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>1707400</v>
+        <v>2162700</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H78" t="n">
-        <v>68.73</v>
-      </c>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I78" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.803</v>
+        <v>0.768</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.777</v>
+        <v>0.771</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3996,39 +3996,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0</v>
+        <v>0.31</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.0508</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>1643300</v>
+        <v>2142900</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0.25</v>
+        <v>1.88</v>
       </c>
       <c r="H79" t="n">
-        <v>49.06</v>
-      </c>
-      <c r="I79" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.89</v>
+      </c>
+      <c r="I79" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.17</v>
+        <v>0.295</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>1.147</v>
+        <v>0.329</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,39 +4041,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.23</v>
+        <v>0.585</v>
       </c>
       <c r="E80" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>1602600</v>
+        <v>2096700</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>1.18</v>
+        <v>0.25</v>
       </c>
       <c r="H80" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.4</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.23</v>
+        <v>0.652</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.238</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,39 +4086,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E81" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>3.39</v>
+      </c>
+      <c r="E81" s="10" t="n">
+        <v>0.003</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>1600100</v>
+        <v>2037400</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="H81" t="n">
-        <v>50.82</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.61</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.865</v>
+        <v>3.003</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.86</v>
+        <v>2.546</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,39 +4131,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="E82" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.375</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1599500</v>
+        <v>1982500</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H82" t="n">
-        <v>33.77</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.17</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>1.667</v>
+        <v>0.373</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>1.747</v>
+        <v>0.37</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,28 +4176,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>3.39</v>
+        <v>1.63</v>
       </c>
       <c r="E83" s="10" t="n">
-        <v>0.003</v>
+        <v>0.0124</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1594900</v>
+        <v>1973200</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="H83" t="n">
-        <v>88.61</v>
+        <v>49.3</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>3.003</v>
+        <v>1.625</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>2.546</v>
+        <v>1.678</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,28 +4221,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>6.9</v>
+        <v>0.27</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>-0.0058</v>
+        <v>-0.0182</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1556500</v>
+        <v>1957500</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.14</v>
+        <v>0.24</v>
       </c>
       <c r="H84" t="n">
-        <v>39.13</v>
+        <v>43.03</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>7.097</v>
+        <v>0.285</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>7.521</v>
+        <v>0.283</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,28 +4266,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MYTECH</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E85" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.23</v>
+      </c>
+      <c r="E85" s="15" t="n">
+        <v>-0.0417</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1475800</v>
+        <v>1898900</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.19</v>
+        <v>16.79</v>
       </c>
       <c r="H85" t="n">
-        <v>49.3</v>
+        <v>43</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>1.625</v>
+        <v>0.235</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1.678</v>
+        <v>0.25</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,39 +4311,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>1.52</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.013</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1455000</v>
+        <v>1870400</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.8</v>
+        <v>0.31</v>
       </c>
       <c r="H86" t="n">
-        <v>48.93</v>
-      </c>
-      <c r="I86" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.88</v>
+      </c>
+      <c r="I86" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>1.664</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>1.746</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,28 +4356,28 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>2.05</v>
+        <v>6.9</v>
       </c>
       <c r="E87" s="15" t="n">
-        <v>-0.0049</v>
+        <v>-0.0058</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1420400</v>
+        <v>1785300</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>4.25</v>
+        <v>0.16</v>
       </c>
       <c r="H87" t="n">
-        <v>40.07</v>
+        <v>39.13</v>
       </c>
       <c r="I87" s="16" t="inlineStr">
         <is>
@@ -4385,10 +4385,10 @@
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>2.076</v>
+        <v>7.097</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>2.082</v>
+        <v>7.521</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,39 +4401,39 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0155</v>
+        <v>0.825</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1418700</v>
+        <v>1707400</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.78</v>
+        <v>0.32</v>
       </c>
       <c r="H88" t="n">
-        <v>36.37</v>
-      </c>
-      <c r="I88" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>68.73</v>
+      </c>
+      <c r="I88" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>1.363</v>
+        <v>0.803</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>1.443</v>
+        <v>0.777</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.375</v>
+        <v>0.865</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>-0.0132</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1346200</v>
+        <v>1678100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.19</v>
+        <v>0.57</v>
       </c>
       <c r="H89" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I89" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.82</v>
+      </c>
+      <c r="I89" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.373</v>
+        <v>0.865</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.37</v>
+        <v>0.86</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.58</v>
+        <v>0.23</v>
       </c>
       <c r="E90" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1345900</v>
+        <v>1602600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.28</v>
+        <v>1.18</v>
       </c>
       <c r="H90" t="n">
-        <v>61.45</v>
-      </c>
-      <c r="I90" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I90" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.536</v>
+        <v>0.23</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.482</v>
+        <v>0.238</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,28 +4536,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E91" s="17" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E91" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1323600</v>
+        <v>1598400</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.11</v>
+        <v>0.87</v>
       </c>
       <c r="H91" t="n">
-        <v>46.45</v>
+        <v>34.14</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>2.741</v>
+        <v>1.362</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>2.747</v>
+        <v>1.443</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E92" s="10" t="n">
-        <v>0.0061</v>
+        <v>2.05</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1312400</v>
+        <v>1588800</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="H92" t="n">
-        <v>51.41</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.29</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.825</v>
+        <v>1.95</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.796</v>
+        <v>1.957</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,28 +4626,28 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E93" s="17" t="n">
-        <v>0</v>
+        <v>0.625</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.008100000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1307000</v>
+        <v>1579200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.17</v>
+        <v>0.47</v>
       </c>
       <c r="H93" t="n">
-        <v>35.09</v>
+        <v>47.24</v>
       </c>
       <c r="I93" s="16" t="inlineStr">
         <is>
@@ -4655,10 +4655,10 @@
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.211</v>
+        <v>0.635</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.297</v>
+        <v>0.621</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,39 +4671,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E94" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.965</v>
+      </c>
+      <c r="E94" s="15" t="n">
+        <v>-0.0052</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1279200</v>
+        <v>1567100</v>
       </c>
       <c r="G94" s="12" t="n">
         <v>0.3</v>
       </c>
       <c r="H94" t="n">
-        <v>28.81</v>
-      </c>
-      <c r="I94" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.71</v>
+      </c>
+      <c r="I94" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.953</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.036</v>
+        <v>0.889</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4716,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.0294</v>
+        <v>0.265</v>
+      </c>
+      <c r="E95" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1252700</v>
+        <v>1552300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>2.04</v>
+        <v>0.23</v>
       </c>
       <c r="H95" t="n">
-        <v>62.49</v>
+        <v>33.64</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.336</v>
+        <v>0.3</v>
       </c>
       <c r="K95" s="9" t="n">
         <v>0.326</v>
@@ -4761,28 +4761,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
         <v>1.16</v>
       </c>
-      <c r="E96" s="15" t="n">
-        <v>-0.008500000000000001</v>
+      <c r="E96" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1237500</v>
+        <v>1486400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>2.33</v>
+        <v>0.2</v>
       </c>
       <c r="H96" t="n">
-        <v>37.8</v>
+        <v>35.09</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.182</v>
+        <v>1.211</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.205</v>
+        <v>1.297</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,39 +4806,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.955</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>-0.0155</v>
+        <v>0.82</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1230600</v>
+        <v>1480300</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.23</v>
+        <v>0.38</v>
       </c>
       <c r="H97" t="n">
-        <v>58.75</v>
-      </c>
-      <c r="I97" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.46</v>
+      </c>
+      <c r="I97" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.9389999999999999</v>
+        <v>0.825</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.889</v>
+        <v>0.795</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>2.04</v>
+        <v>2.05</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>-0.0097</v>
+        <v>-0.0049</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1214800</v>
+        <v>1480000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.19</v>
+        <v>4.43</v>
       </c>
       <c r="H98" t="n">
-        <v>61.78</v>
-      </c>
-      <c r="I98" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.07</v>
+      </c>
+      <c r="I98" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.949</v>
+        <v>2.076</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.957</v>
+        <v>2.082</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>-0.0068</v>
+        <v>0.58</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1200600</v>
+        <v>1440700</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="H99" t="n">
-        <v>40.97</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>61.45</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>7.42</v>
+        <v>0.536</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>7.843</v>
+        <v>0.482</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0</v>
+        <v>7.34</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1180200</v>
+        <v>1440300</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="H100" t="n">
-        <v>46.77</v>
+        <v>40.97</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.239</v>
+        <v>7.42</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.241</v>
+        <v>7.843</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.27</v>
+        <v>5.75</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>0.0189</v>
+        <v>0.0035</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1166900</v>
+        <v>1433400</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="H101" t="n">
-        <v>36.06</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.39</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.3</v>
+        <v>5.837</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>0.326</v>
+        <v>6.105</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E102" s="17" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E102" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1153500</v>
+        <v>1432100</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>1.31</v>
+        <v>0.33</v>
       </c>
       <c r="H102" t="n">
-        <v>50.42</v>
+        <v>28.81</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.276</v>
+        <v>0.953</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.268</v>
+        <v>1.036</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.26</v>
+        <v>1.05</v>
       </c>
       <c r="E103" s="15" t="n">
-        <v>-0.0189</v>
+        <v>-0.0187</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1151300</v>
+        <v>1384300</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.61</v>
+        <v>0.41</v>
       </c>
       <c r="H103" t="n">
-        <v>49.74</v>
+        <v>39.04</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.263</v>
+        <v>1.129</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.243</v>
+        <v>1.11</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="E104" s="10" t="n">
-        <v>0.0114</v>
+        <v>2.7</v>
+      </c>
+      <c r="E104" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1114200</v>
+        <v>1324500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.59</v>
+        <v>0.12</v>
       </c>
       <c r="H104" t="n">
-        <v>47.64</v>
+        <v>46.45</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.907</v>
+        <v>2.741</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.889</v>
+        <v>2.747</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,28 +5166,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>2.36</v>
+        <v>0.35</v>
       </c>
       <c r="E105" s="10" t="n">
-        <v>0.0129</v>
+        <v>0.0294</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1077500</v>
+        <v>1302700</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.19</v>
+        <v>2.12</v>
       </c>
       <c r="H105" t="n">
-        <v>33.69</v>
+        <v>62.49</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>2.657</v>
+        <v>0.336</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>2.84</v>
+        <v>0.326</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E106" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1034500</v>
+        <v>1287500</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>6.34</v>
+        <v>2.42</v>
       </c>
       <c r="H106" t="n">
-        <v>39.25</v>
+        <v>37.8</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>2.682</v>
+        <v>1.182</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>2.787</v>
+        <v>1.205</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="E107" s="15" t="n">
-        <v>-0.009300000000000001</v>
+        <v>2.34</v>
+      </c>
+      <c r="E107" s="10" t="n">
+        <v>0.0043</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1032500</v>
+        <v>1239000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="H107" t="n">
-        <v>40.12</v>
+        <v>32.5</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>1.13</v>
+        <v>2.655</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>1.11</v>
+        <v>2.84</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,39 +5301,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0.011</v>
+        <v>0.26</v>
+      </c>
+      <c r="E108" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1010700</v>
+        <v>1202300</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.14</v>
+        <v>0.64</v>
       </c>
       <c r="H108" t="n">
-        <v>35.5</v>
-      </c>
-      <c r="I108" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.74</v>
+      </c>
+      <c r="I108" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.484</v>
+        <v>0.263</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.542</v>
+        <v>0.243</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>-0.0068</v>
+        <v>0.235</v>
+      </c>
+      <c r="E109" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>984300</v>
+        <v>1184700</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.33</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H109" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.77</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.741</v>
+        <v>0.239</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.707</v>
+        <v>0.241</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E110" s="10" t="n">
-        <v>0.0202</v>
+        <v>3.64</v>
+      </c>
+      <c r="E110" s="15" t="n">
+        <v>-0.0162</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>968700</v>
+        <v>1156500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.26</v>
+        <v>0.35</v>
       </c>
       <c r="H110" t="n">
-        <v>32.86</v>
+        <v>43.52</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>0.555</v>
+        <v>3.798</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>0.591</v>
+        <v>3.731</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="E111" s="10" t="n">
-        <v>0.008</v>
+        <v>0.275</v>
+      </c>
+      <c r="E111" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>966800</v>
+        <v>1153500</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>0.38</v>
+        <v>1.31</v>
       </c>
       <c r="H111" t="n">
-        <v>51.3</v>
+        <v>50.42</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>1.265</v>
+        <v>0.276</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>1.183</v>
+        <v>0.268</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E112" s="17" t="n">
-        <v>0</v>
+        <v>0.875</v>
+      </c>
+      <c r="E112" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>944000</v>
+        <v>1145000</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.2</v>
+        <v>0.6</v>
       </c>
       <c r="H112" t="n">
-        <v>56.45</v>
+        <v>44.95</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.079</v>
+        <v>0.905</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.952</v>
+        <v>0.888</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,39 +5526,39 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.515</v>
+        <v>0.785</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.0309</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>932700</v>
+        <v>1095300</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.18</v>
+        <v>0.49</v>
       </c>
       <c r="H113" t="n">
-        <v>43.43</v>
-      </c>
-      <c r="I113" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>23.21</v>
+      </c>
+      <c r="I113" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.548</v>
+        <v>0.889</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>0.523</v>
+        <v>1.048</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E114" s="15" t="n">
-        <v>-0.0135</v>
+        <v>1.11</v>
+      </c>
+      <c r="E114" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>930500</v>
+        <v>1064500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.28</v>
+        <v>0.22</v>
       </c>
       <c r="H114" t="n">
-        <v>43.89</v>
+        <v>56.45</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>3.799</v>
+        <v>1.079</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>3.731</v>
+        <v>0.952</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,39 +5616,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.625</v>
+        <v>2.6</v>
       </c>
       <c r="E115" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>904500</v>
+        <v>1054500</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>0.26</v>
+        <v>6.46</v>
       </c>
       <c r="H115" t="n">
-        <v>63.68</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.25</v>
+      </c>
+      <c r="I115" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.62</v>
+        <v>2.682</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.61</v>
+        <v>2.787</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,28 +5661,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E116" s="17" t="n">
-        <v>0</v>
+        <v>0.505</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0202</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>894000</v>
+        <v>1051600</v>
       </c>
       <c r="G116" s="12" t="n">
         <v>0.29</v>
       </c>
       <c r="H116" t="n">
-        <v>32.09</v>
+        <v>32.86</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.874</v>
+        <v>0.555</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.591</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,28 +5706,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="E117" s="10" t="n">
-        <v>0.008</v>
+        <v>0.83</v>
+      </c>
+      <c r="E117" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>888500</v>
+        <v>1023000</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.17</v>
+        <v>0.34</v>
       </c>
       <c r="H117" t="n">
-        <v>38.08</v>
+        <v>32.09</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.721</v>
+        <v>0.874</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>5.74</v>
-      </c>
-      <c r="E118" s="10" t="n">
-        <v>0.0017</v>
+        <v>0.455</v>
+      </c>
+      <c r="E118" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>824100</v>
+        <v>1022500</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.11</v>
+        <v>0.14</v>
       </c>
       <c r="H118" t="n">
-        <v>39.64</v>
+        <v>33.01</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>5.836</v>
+        <v>0.484</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>6.105</v>
+        <v>0.542</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,28 +5796,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E119" s="10" t="n">
-        <v>0.0305</v>
+        <v>0.73</v>
+      </c>
+      <c r="E119" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>786200</v>
+        <v>1014500</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.29</v>
+        <v>0.34</v>
       </c>
       <c r="H119" t="n">
-        <v>48.43</v>
+        <v>49.59</v>
       </c>
       <c r="I119" s="16" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>2.067</v>
+        <v>0.741</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>1.993</v>
+        <v>0.707</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,28 +5841,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="E120" s="15" t="n">
-        <v>-0.0031</v>
+        <v>1.25</v>
+      </c>
+      <c r="E120" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>779700</v>
+        <v>981900</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.13</v>
+        <v>0.38</v>
       </c>
       <c r="H120" t="n">
-        <v>53.32</v>
+        <v>50.44</v>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>6.262</v>
+        <v>1.264</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>5.98</v>
+        <v>1.183</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,39 +5886,39 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E121" s="15" t="n">
-        <v>-0.0309</v>
+        <v>0.52</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>751100</v>
+        <v>943700</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="H121" t="n">
-        <v>23.21</v>
-      </c>
-      <c r="I121" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.39</v>
+      </c>
+      <c r="I121" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.889</v>
+        <v>0.549</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>1.048</v>
+        <v>0.523</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,39 +5931,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E122" s="17" t="n">
-        <v>0</v>
+        <v>0.62</v>
+      </c>
+      <c r="E122" s="15" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>748800</v>
+        <v>933100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.21</v>
+        <v>0.18</v>
       </c>
       <c r="H122" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I122" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.83</v>
+      </c>
+      <c r="I122" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.895</v>
+        <v>0.721</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.96</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5991,10 +5991,10 @@
         <v>0.0139</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>721100</v>
+        <v>899100</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="H123" t="n">
         <v>50.16</v>
@@ -6030,19 +6030,19 @@
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.965</v>
+        <v>0.96</v>
       </c>
       <c r="E124" s="15" t="n">
-        <v>-0.035</v>
+        <v>-0.04</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>679200</v>
+        <v>875400</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="H124" t="n">
-        <v>42.4</v>
+        <v>41.8</v>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.025</v>
+        <v>1.024</v>
       </c>
       <c r="K124" s="9" t="n">
         <v>0.967</v>
@@ -6066,39 +6066,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>-0.0254</v>
+        <v>0.86</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>653500</v>
+        <v>857500</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.44</v>
+        <v>0.24</v>
       </c>
       <c r="H125" t="n">
-        <v>46.76</v>
-      </c>
-      <c r="I125" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.9</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>3.151</v>
+        <v>0.895</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>2.942</v>
+        <v>0.96</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,28 +6111,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0</v>
+        <v>6.35</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>642500</v>
+        <v>836500</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="H126" t="n">
-        <v>33.86</v>
+        <v>53.14</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>2.491</v>
+        <v>6.261</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>2.659</v>
+        <v>5.98</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,28 +6156,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E127" s="10" t="n">
+        <v>0.0152</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>637200</v>
+        <v>817300</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H127" t="n">
-        <v>29.82</v>
+        <v>46.6</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.531</v>
+        <v>2.064</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.992</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,28 +6201,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>0</v>
+        <v>3.09</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>635800</v>
+        <v>793000</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="H128" t="n">
-        <v>40.91</v>
+        <v>48.16</v>
       </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>1.755</v>
+        <v>3.153</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>1.86</v>
+        <v>2.942</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,39 +6246,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E129" s="10" t="n">
-        <v>0.008699999999999999</v>
+        <v>1.38</v>
+      </c>
+      <c r="E129" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>633600</v>
+        <v>775500</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.1</v>
+        <v>0.37</v>
       </c>
       <c r="H129" t="n">
-        <v>53.52</v>
-      </c>
-      <c r="I129" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.08</v>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.574</v>
+        <v>1.366</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.482</v>
+        <v>1.344</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6291,28 +6291,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="E130" s="15" t="n">
-        <v>-0.0227</v>
+        <v>0.505</v>
+      </c>
+      <c r="E130" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>622400</v>
+        <v>743000</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.17</v>
+        <v>0.25</v>
       </c>
       <c r="H130" t="n">
-        <v>50.64</v>
+        <v>29.82</v>
       </c>
       <c r="I130" s="16" t="inlineStr">
         <is>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>10.434</v>
+        <v>0.531</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>9.846</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6336,39 +6336,39 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>9.970000000000001</v>
+        <v>2.38</v>
       </c>
       <c r="E131" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>618700</v>
+        <v>739100</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="H131" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="I131" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.86</v>
+      </c>
+      <c r="I131" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>9.988</v>
+        <v>2.491</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>10.116</v>
+        <v>2.659</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6381,28 +6381,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="E132" s="15" t="n">
+        <v>-0.0278</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>581400</v>
+        <v>731900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="H132" t="n">
-        <v>45.21</v>
+        <v>45.52</v>
       </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>0.634</v>
+        <v>7.273</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>0.621</v>
+        <v>6.933</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6426,39 +6426,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>3.26</v>
+        <v>2.42</v>
       </c>
       <c r="E133" s="15" t="n">
-        <v>-0.0121</v>
+        <v>-0.032</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>573300</v>
+        <v>727900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.1</v>
+        <v>0.26</v>
       </c>
       <c r="H133" t="n">
-        <v>39.52</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.89</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.332</v>
+        <v>2.53</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>3.561</v>
+        <v>2.653</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6471,39 +6471,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>-0.0074</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>573000</v>
+        <v>716000</v>
       </c>
       <c r="G134" s="12" t="n">
         <v>0.06</v>
       </c>
       <c r="H134" t="n">
-        <v>46.18</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.44</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>2.779</v>
+        <v>9.988</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>2.684</v>
+        <v>10.116</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6516,28 +6516,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E135" s="10" t="n">
-        <v>0.0072</v>
+        <v>1.27</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>570200</v>
+        <v>708700</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="H135" t="n">
-        <v>40.67</v>
+        <v>51.39</v>
       </c>
       <c r="I135" s="13" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.714</v>
+        <v>1.264</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.773</v>
+        <v>1.272</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6561,39 +6561,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.88</v>
+        <v>10.3</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>-0.0103</v>
+        <v>-0.0265</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>551200</v>
+        <v>707800</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.48</v>
+        <v>0.2</v>
       </c>
       <c r="H136" t="n">
-        <v>55.45</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.93</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.791</v>
+        <v>10.431</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.839</v>
+        <v>9.845000000000001</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6606,39 +6606,39 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>13.22</v>
+        <v>1.72</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>-0.0015</v>
+        <v>-0.0058</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>547200</v>
+        <v>703200</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="H137" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="I137" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I137" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>13.055</v>
+        <v>1.754</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>13.334</v>
+        <v>1.86</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6651,28 +6651,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>7.08</v>
+        <v>0.57</v>
       </c>
       <c r="E138" s="15" t="n">
-        <v>-0.0167</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>539700</v>
+        <v>667000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="H138" t="n">
-        <v>47.02</v>
+        <v>52.22</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>7.281</v>
+        <v>0.573</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>6.934</v>
+        <v>0.482</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6696,28 +6696,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0</v>
+        <v>3.25</v>
+      </c>
+      <c r="E139" s="15" t="n">
+        <v>-0.0152</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>520100</v>
+        <v>638300</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.49</v>
+        <v>0.12</v>
       </c>
       <c r="H139" t="n">
-        <v>55</v>
+        <v>38.86</v>
       </c>
       <c r="I139" s="13" t="inlineStr">
         <is>
@@ -6725,16 +6725,601 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.633</v>
+        <v>3.331</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.632</v>
+        <v>3.56</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
     </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>0128</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>FRONTKN</t>
+        </is>
+      </c>
+      <c r="D140" s="9" t="n">
+        <v>5.03</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>-0.007900000000000001</v>
+      </c>
+      <c r="F140" s="11" t="n">
+        <v>631400</v>
+      </c>
+      <c r="G140" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H140" t="n">
+        <v>48.7</v>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J140" s="9" t="n">
+        <v>5.059</v>
+      </c>
+      <c r="K140" s="9" t="n">
+        <v>5.041</v>
+      </c>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" s="14" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D141" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F141" s="11" t="n">
+        <v>625100</v>
+      </c>
+      <c r="G141" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H141" t="n">
+        <v>55</v>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J141" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K141" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" s="14" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>0225</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>SCGBHD</t>
+        </is>
+      </c>
+      <c r="D142" s="9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="E142" s="15" t="n">
+        <v>-0.0037</v>
+      </c>
+      <c r="F142" s="11" t="n">
+        <v>622900</v>
+      </c>
+      <c r="G142" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H142" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J142" s="9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="K142" s="9" t="n">
+        <v>2.684</v>
+      </c>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" s="14" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>5347</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>TENAGA</t>
+        </is>
+      </c>
+      <c r="D143" s="9" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="F143" s="11" t="n">
+        <v>612400</v>
+      </c>
+      <c r="G143" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H143" t="n">
+        <v>56.14</v>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J143" s="9" t="n">
+        <v>13.055</v>
+      </c>
+      <c r="K143" s="9" t="n">
+        <v>13.334</v>
+      </c>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" s="14" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D144" s="9" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="E144" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" s="11" t="n">
+        <v>606300</v>
+      </c>
+      <c r="G144" s="12" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="H144" t="n">
+        <v>57.47</v>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J144" s="9" t="n">
+        <v>2.793</v>
+      </c>
+      <c r="K144" s="9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" s="14" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="E145" s="10" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="F145" s="11" t="n">
+        <v>591300</v>
+      </c>
+      <c r="G145" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H145" t="n">
+        <v>42.21</v>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="K145" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="L145" t="inlineStr"/>
+      <c r="M145" s="14" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>5031</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>TIMECOM</t>
+        </is>
+      </c>
+      <c r="D146" s="9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>-0.0076</v>
+      </c>
+      <c r="F146" s="11" t="n">
+        <v>588900</v>
+      </c>
+      <c r="G146" s="12" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="H146" t="n">
+        <v>30.67</v>
+      </c>
+      <c r="I146" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J146" s="9" t="n">
+        <v>5.483</v>
+      </c>
+      <c r="K146" s="9" t="n">
+        <v>5.752</v>
+      </c>
+      <c r="L146" t="inlineStr"/>
+      <c r="M146" s="14" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>7293</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>YINSON</t>
+        </is>
+      </c>
+      <c r="D147" s="9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="E147" s="15" t="n">
+        <v>-0.004699999999999999</v>
+      </c>
+      <c r="F147" s="11" t="n">
+        <v>585400</v>
+      </c>
+      <c r="G147" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H147" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J147" s="9" t="n">
+        <v>2.111</v>
+      </c>
+      <c r="K147" s="9" t="n">
+        <v>2.075</v>
+      </c>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" s="14" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>5211</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SUNWAY</t>
+        </is>
+      </c>
+      <c r="D148" s="9" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="E148" s="15" t="n">
+        <v>-0.012</v>
+      </c>
+      <c r="F148" s="11" t="n">
+        <v>584900</v>
+      </c>
+      <c r="G148" s="12" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="H148" t="n">
+        <v>31.35</v>
+      </c>
+      <c r="I148" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J148" s="9" t="n">
+        <v>4.333</v>
+      </c>
+      <c r="K148" s="9" t="n">
+        <v>4.641</v>
+      </c>
+      <c r="L148" t="inlineStr"/>
+      <c r="M148" s="14" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>0215</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SLVEST</t>
+        </is>
+      </c>
+      <c r="D149" s="9" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="E149" s="15" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F149" s="11" t="n">
+        <v>561300</v>
+      </c>
+      <c r="G149" s="12" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H149" t="n">
+        <v>49.7</v>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J149" s="9" t="n">
+        <v>3.949</v>
+      </c>
+      <c r="K149" s="9" t="n">
+        <v>3.621</v>
+      </c>
+      <c r="L149" t="inlineStr"/>
+      <c r="M149" s="14" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>4863</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>TM</t>
+        </is>
+      </c>
+      <c r="D150" s="9" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="F150" s="11" t="n">
+        <v>555800</v>
+      </c>
+      <c r="G150" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H150" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J150" s="9" t="n">
+        <v>7.817</v>
+      </c>
+      <c r="K150" s="9" t="n">
+        <v>7.856</v>
+      </c>
+      <c r="L150" t="inlineStr"/>
+      <c r="M150" s="14" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>RCECAP</t>
+        </is>
+      </c>
+      <c r="D151" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F151" s="11" t="n">
+        <v>522300</v>
+      </c>
+      <c r="G151" s="12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H151" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J151" s="9" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="K151" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L151" t="inlineStr"/>
+      <c r="M151" s="14" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>DRBHCOM</t>
+        </is>
+      </c>
+      <c r="D152" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E152" s="10" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F152" s="11" t="n">
+        <v>516000</v>
+      </c>
+      <c r="G152" s="12" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="H152" t="n">
+        <v>33.16</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J152" s="9" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="K152" s="9" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M139"/>
+  <autoFilter ref="A1:M152"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$152</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$168</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M152"/>
+  <dimension ref="A1:M168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.11</v>
+        <v>4.13</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0148</v>
+        <v>0.0198</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>3934500</v>
+        <v>4277600</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.52</v>
+        <v>0.57</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>63.92</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.758</v>
+        <v>3.76</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.202</v>
+        <v>3.203</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号可靠，RSI 63.92未超买，现价高于50日均线约28%，多头动能偏强。</t>
+          <t>SAR转多信号，RSI 64.32未超买，现价高于50日均线约29%，技术面信号可靠性较高。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.2</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>115423300</v>
+        <v>120040200</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="H3" t="n">
         <v>28.04</v>
@@ -664,19 +664,19 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>0.315</v>
+        <v>0.32</v>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0455</v>
+        <v>-0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>52780700</v>
+        <v>53575100</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="H4" t="n">
-        <v>54.51</v>
+        <v>56.38</v>
       </c>
       <c r="I4" s="16" t="inlineStr">
         <is>
@@ -700,28 +700,28 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E5" s="17" t="n">
-        <v>0</v>
+        <v>0.485</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.05429999999999999</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>20749600</v>
+        <v>22258900</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>1.45</v>
+        <v>0.61</v>
       </c>
       <c r="H5" t="n">
-        <v>37.79</v>
+        <v>78.45</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.154</v>
+        <v>0.414</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.18</v>
+        <v>0.31</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>20366000</v>
+        <v>21284400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H6" t="n">
-        <v>78.45</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.33</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.414</v>
+        <v>0.156</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.31</v>
+        <v>0.156</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E7" s="10" t="n">
-        <v>0.0341</v>
+        <v>0.15</v>
+      </c>
+      <c r="E7" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>18414700</v>
+        <v>20818800</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>0.25</v>
+        <v>1.46</v>
       </c>
       <c r="H7" t="n">
-        <v>63.71</v>
+        <v>37.79</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.852</v>
+        <v>0.154</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.758</v>
+        <v>0.18</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,28 +835,28 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0341</v>
+        <v>0.905</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.0284</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>13812700</v>
+        <v>19843600</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="H8" t="n">
-        <v>54.01</v>
+        <v>63.11</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>1.961</v>
+        <v>0.852</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>1.786</v>
+        <v>0.757</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,28 +880,28 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4456</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DNEX</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0241</v>
+        <v>0.37</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>12575000</v>
+        <v>16295300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.35</v>
+        <v>1.84</v>
       </c>
       <c r="H9" t="n">
-        <v>38.49</v>
+        <v>18.34</v>
       </c>
       <c r="I9" s="16" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.459</v>
+        <v>0.39</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.477</v>
+        <v>0.404</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -925,28 +925,28 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0339</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>CBHB</t>
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E10" s="10" t="n">
-        <v>0.046</v>
+        <v>0.895</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0529</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>12397000</v>
+        <v>15314200</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>0.62</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="n">
-        <v>59.71</v>
+        <v>34.91</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>0.43</v>
+        <v>1.011</v>
       </c>
       <c r="K10" s="9" t="n">
-        <v>0.381</v>
+        <v>0.977</v>
       </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" s="14" t="inlineStr"/>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0339</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CBHB</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.895</v>
+        <v>1.99</v>
       </c>
       <c r="E11" s="15" t="n">
-        <v>-0.0529</v>
+        <v>-0.0293</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>12083100</v>
+        <v>14493200</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>1.26</v>
+        <v>0.51</v>
       </c>
       <c r="H11" t="n">
-        <v>34.91</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.66</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1.011</v>
+        <v>1.962</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.977</v>
+        <v>1.786</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,28 +1015,28 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0313</v>
+        <v>0.305</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>11647400</v>
+        <v>13562900</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.32</v>
+        <v>0.7</v>
       </c>
       <c r="H12" t="n">
-        <v>48.33</v>
+        <v>47.4</v>
       </c>
       <c r="I12" s="16" t="inlineStr">
         <is>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.156</v>
+        <v>0.307</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.156</v>
+        <v>0.302</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1060,28 +1060,28 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>DNEX</t>
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.305</v>
+        <v>0.415</v>
       </c>
       <c r="E13" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>11306900</v>
+        <v>13314300</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.58</v>
+        <v>0.37</v>
       </c>
       <c r="H13" t="n">
-        <v>47.4</v>
+        <v>34.84</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="J13" s="9" t="n">
-        <v>0.307</v>
+        <v>0.458</v>
       </c>
       <c r="K13" s="9" t="n">
-        <v>0.302</v>
+        <v>0.477</v>
       </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" s="14" t="inlineStr"/>
@@ -1114,19 +1114,19 @@
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.735</v>
+        <v>0.745</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.028</v>
+        <v>0.042</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>11192600</v>
+        <v>13079900</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.45</v>
+        <v>0.53</v>
       </c>
       <c r="H14" t="n">
-        <v>83.44</v>
+        <v>84.38</v>
       </c>
       <c r="I14" s="13" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.651</v>
+        <v>0.652</v>
       </c>
       <c r="K14" s="9" t="n">
         <v>0.555</v>
@@ -1159,19 +1159,19 @@
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="E15" s="15" t="n">
-        <v>-0.0431</v>
+        <v>-0.0345</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>10498600</v>
+        <v>12481100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.12</v>
+        <v>2.52</v>
       </c>
       <c r="H15" t="n">
-        <v>17.85</v>
+        <v>18.28</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.316</v>
+        <v>1.317</v>
       </c>
       <c r="K15" s="9" t="n">
         <v>1.515</v>
@@ -1195,28 +1195,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.005</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>0.455</v>
+      </c>
+      <c r="E16" s="10" t="n">
+        <v>0.046</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>10304000</v>
+        <v>12466900</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>28.32</v>
+        <v>0.62</v>
       </c>
       <c r="H16" t="n">
-        <v>47.02</v>
+        <v>59.71</v>
       </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
         </is>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.005</v>
+        <v>0.43</v>
       </c>
       <c r="K16" s="9" t="n">
-        <v>0.006</v>
+        <v>0.381</v>
       </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
@@ -1240,40 +1240,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.18</v>
+        <v>0.26</v>
       </c>
       <c r="E17" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>10255200</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="H17" t="n">
-        <v>44.11</v>
-      </c>
+        <v>12239800</v>
+      </c>
+      <c r="G17" s="12" t="n"/>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n">
-        <v>0.186</v>
-      </c>
-      <c r="K17" s="9" t="n">
-        <v>0.186</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n"/>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1300,10 +1291,10 @@
         <v>0.0833</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10139400</v>
+        <v>10739400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>12.63</v>
+        <v>13.38</v>
       </c>
       <c r="H18" t="n">
         <v>55.37</v>
@@ -1330,39 +1321,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.37</v>
+        <v>0.82</v>
       </c>
       <c r="E19" s="15" t="n">
-        <v>-0.0133</v>
+        <v>-0.0061</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10124400</v>
+        <v>10613100</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>1.14</v>
+        <v>0.66</v>
       </c>
       <c r="H19" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="I19" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.39</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.404</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1375,31 +1366,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.265</v>
+        <v>0.18</v>
       </c>
       <c r="E20" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>9932300</v>
-      </c>
-      <c r="G20" s="12" t="n"/>
+        <v>10384100</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="H20" t="n">
+        <v>44.11</v>
+      </c>
       <c r="I20" s="16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K20" s="9" t="n">
+        <v>0.186</v>
+      </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
     </row>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E21" s="15" t="n">
-        <v>-0.0061</v>
+        <v>0.005</v>
+      </c>
+      <c r="E21" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>9071000</v>
+        <v>10304000</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.57</v>
+        <v>28.32</v>
       </c>
       <c r="H21" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I21" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,28 +1456,28 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E22" s="10" t="n">
-        <v>0.08</v>
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>8521100</v>
+        <v>9326200</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>16.93</v>
+        <v>0.6</v>
       </c>
       <c r="H22" t="n">
-        <v>64.23</v>
+        <v>50.42</v>
       </c>
       <c r="I22" s="13" t="inlineStr">
         <is>
@@ -1485,10 +1485,10 @@
         </is>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.127</v>
+        <v>0.774</v>
       </c>
       <c r="K22" s="9" t="n">
-        <v>0.129</v>
+        <v>0.776</v>
       </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
@@ -1501,28 +1501,28 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E23" s="15" t="n">
-        <v>-0.0294</v>
+        <v>0.135</v>
+      </c>
+      <c r="E23" s="10" t="n">
+        <v>0.08</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8308500</v>
+        <v>8738400</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.13</v>
+        <v>17.36</v>
       </c>
       <c r="H23" t="n">
-        <v>53.64</v>
+        <v>64.23</v>
       </c>
       <c r="I23" s="13" t="inlineStr">
         <is>
@@ -1530,10 +1530,10 @@
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.16</v>
+        <v>0.127</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.146</v>
+        <v>0.129</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,28 +1546,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E24" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E24" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>7349700</v>
+        <v>8679500</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.47</v>
+        <v>0.42</v>
       </c>
       <c r="H24" t="n">
-        <v>50.42</v>
+        <v>46.51</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.774</v>
+        <v>0.868</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.776</v>
+        <v>0.869</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,33 +1591,40 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.09</v>
+        <v>0.165</v>
       </c>
       <c r="E25" s="15" t="n">
-        <v>-0.0526</v>
+        <v>-0.0294</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>6789100</v>
+        <v>8504100</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I25" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J25" s="9" t="n"/>
-      <c r="K25" s="9" t="n"/>
+        <v>0.14</v>
+      </c>
+      <c r="H25" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K25" s="9" t="n">
+        <v>0.146</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
     </row>
@@ -1638,19 +1645,19 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="E26" s="15" t="n">
-        <v>-0.0124</v>
+        <v>-0.0083</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>6742600</v>
+        <v>7697200</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="H26" t="n">
-        <v>45.1</v>
+        <v>46.13</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1658,10 +1665,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.868</v>
+        <v>4.87</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.755</v>
+        <v>4.756</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1674,28 +1681,28 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>YTL</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>0.865</v>
+        <v>2.06</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0048</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>6698700</v>
+        <v>7123800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.33</v>
+        <v>0.65</v>
       </c>
       <c r="H27" t="n">
-        <v>46.51</v>
+        <v>39.55</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1703,10 +1710,10 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>0.868</v>
+        <v>2.118</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>0.869</v>
+        <v>2.234</v>
       </c>
       <c r="L27" t="inlineStr"/>
       <c r="M27" s="14" t="inlineStr"/>
@@ -1719,40 +1726,33 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.19</v>
+        <v>0.095</v>
       </c>
       <c r="E28" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6673200</v>
+        <v>6909200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="H28" t="n">
-        <v>33.79</v>
+        <v>0.27</v>
       </c>
       <c r="I28" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J28" s="9" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="K28" s="9" t="n">
-        <v>0.23</v>
-      </c>
+      <c r="J28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>4677</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>YTL</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2.06</v>
+        <v>0.185</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.0048</v>
+        <v>-0.0263</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6225300</v>
+        <v>6904600</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.32</v>
       </c>
       <c r="H29" t="n">
-        <v>39.55</v>
-      </c>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.82</v>
+      </c>
+      <c r="I29" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>2.118</v>
+        <v>0.209</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>2.234</v>
+        <v>0.23</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1818,19 +1818,19 @@
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.325</v>
+        <v>0.335</v>
       </c>
       <c r="E30" s="15" t="n">
-        <v>-0.0441</v>
+        <v>-0.0147</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>5998000</v>
+        <v>6741800</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.76</v>
+        <v>0.86</v>
       </c>
       <c r="H30" t="n">
-        <v>41.68</v>
+        <v>44.85</v>
       </c>
       <c r="I30" s="16" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.349</v>
+        <v>0.35</v>
       </c>
       <c r="K30" s="9" t="n">
         <v>0.329</v>
@@ -1854,39 +1854,39 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.14</v>
+        <v>1.37</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>0.0755</v>
+        <v>0.0148</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>5989400</v>
+        <v>6645400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="H31" t="n">
-        <v>58.03</v>
-      </c>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.65</v>
+      </c>
+      <c r="I31" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.086</v>
+        <v>1.593</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.053</v>
+        <v>1.885</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,39 +1899,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="E32" s="15" t="n">
-        <v>-0.023</v>
+        <v>1.14</v>
+      </c>
+      <c r="E32" s="10" t="n">
+        <v>0.0755</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>5534800</v>
+        <v>6635900</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.33</v>
+        <v>0.75</v>
       </c>
       <c r="H32" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="I32" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.03</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>0.484</v>
+        <v>1.086</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>0.63</v>
+        <v>1.053</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         <v>0</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>5219300</v>
+        <v>6200500</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="H33" t="n">
         <v>60.81</v>
@@ -1989,28 +1989,28 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E34" s="17" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E34" s="15" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>4909400</v>
+        <v>6002300</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.37</v>
+        <v>0.36</v>
       </c>
       <c r="H34" t="n">
-        <v>18.69</v>
+        <v>24.81</v>
       </c>
       <c r="I34" s="16" t="inlineStr">
         <is>
@@ -2018,10 +2018,10 @@
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>1.591</v>
+        <v>0.484</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>1.884</v>
+        <v>0.63</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2049,10 +2049,10 @@
         <v>-0.0238</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>4763900</v>
+        <v>5863800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.39</v>
+        <v>0.48</v>
       </c>
       <c r="H35" t="n">
         <v>54.72</v>
@@ -2079,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E36" s="17" t="n">
-        <v>0</v>
+        <v>0.12</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <v>0.0435</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>4710300</v>
+        <v>5804400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.57</v>
+        <v>0.3</v>
       </c>
       <c r="H36" t="n">
-        <v>28.65</v>
+        <v>38.64</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.269</v>
+        <v>0.134</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.294</v>
+        <v>0.147</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,33 +2124,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.23</v>
+        <v>0.435</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.0116</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>4670500</v>
+        <v>5372000</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.22</v>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H37" t="n">
+        <v>39.37</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J37" s="9" t="n"/>
-      <c r="K37" s="9" t="n"/>
+      <c r="J37" s="9" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="K37" s="9" t="n">
+        <v>0.468</v>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
     </row>
@@ -2162,28 +2169,28 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0625</v>
+        <v>1.25</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>-0.0234</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>4612100</v>
+        <v>5156000</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>1.49</v>
+        <v>0.75</v>
       </c>
       <c r="H38" t="n">
-        <v>60.81</v>
+        <v>55.63</v>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
@@ -2191,10 +2198,10 @@
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.159</v>
+        <v>1.223</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.157</v>
+        <v>1.203</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2207,28 +2214,28 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <v>0.0233</v>
+        <v>0.26</v>
+      </c>
+      <c r="E39" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>4468000</v>
+        <v>5044600</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H39" t="n">
-        <v>40.39</v>
+        <v>38.24</v>
       </c>
       <c r="I39" s="16" t="inlineStr">
         <is>
@@ -2236,10 +2243,10 @@
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.496</v>
+        <v>0.287</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.468</v>
+        <v>0.279</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2252,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4419000</v>
+        <v>4744000</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.42</v>
+        <v>0.57</v>
       </c>
       <c r="H40" t="n">
-        <v>38.24</v>
+        <v>28.65</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2281,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.287</v>
+        <v>0.269</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.279</v>
+        <v>0.294</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2297,40 +2304,33 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E41" s="15" t="n">
-        <v>-0.008199999999999999</v>
+        <v>0.23</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4279400</v>
+        <v>4671000</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="H41" t="n">
-        <v>62.94</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="n">
-        <v>2.277</v>
-      </c>
-      <c r="K41" s="9" t="n">
-        <v>2.2</v>
-      </c>
+        <v>0.22</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2342,39 +2342,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.0244</v>
+        <v>0.0625</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4122400</v>
+        <v>4622100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.37</v>
+        <v>1.49</v>
       </c>
       <c r="H42" t="n">
-        <v>32.99</v>
-      </c>
-      <c r="I42" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.225</v>
+        <v>0.159</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.272</v>
+        <v>0.157</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2387,28 +2387,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>1.27</v>
+        <v>2.4</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>-0.0123</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>3707900</v>
+        <v>4427000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>0.54</v>
+        <v>1.25</v>
       </c>
       <c r="H43" t="n">
-        <v>58.78</v>
+        <v>61.98</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>1.225</v>
+        <v>2.276</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>1.204</v>
+        <v>2.2</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2432,39 +2432,39 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0334</v>
+        <v>0.205</v>
+      </c>
+      <c r="E44" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>3704700</v>
+        <v>4187000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.75</v>
+        <v>0.38</v>
       </c>
       <c r="H44" t="n">
-        <v>58.94</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.46</v>
+      </c>
+      <c r="I44" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J44" s="9" t="n">
-        <v>4.407</v>
+        <v>0.225</v>
       </c>
       <c r="K44" s="9" t="n">
-        <v>4.439</v>
+        <v>0.272</v>
       </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
@@ -2477,39 +2477,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.555</v>
+        <v>4.66</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.0379</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3657200</v>
+        <v>3927400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.18</v>
+        <v>0.8</v>
       </c>
       <c r="H45" t="n">
-        <v>48.37</v>
-      </c>
-      <c r="I45" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>59.54</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>4.409</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.545</v>
+        <v>4.439</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,39 +2522,39 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0312</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>OFB</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E46" s="17" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E46" s="10" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3654100</v>
+        <v>3884500</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>58.24</v>
+        <v>0.19</v>
       </c>
       <c r="H46" t="n">
-        <v>76.15000000000001</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.37</v>
+      </c>
+      <c r="I46" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.136</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.138</v>
+        <v>0.545</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E47" s="15" t="n">
-        <v>-0.0286</v>
+        <v>2.49</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3626900</v>
+        <v>3777400</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.67</v>
+        <v>0.2</v>
       </c>
       <c r="H47" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.21</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.163</v>
+        <v>2.602</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.165</v>
+        <v>2.559</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,39 +2612,39 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0312</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>OFB</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.16</v>
+      </c>
+      <c r="E48" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3463300</v>
+        <v>3664200</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.18</v>
+        <v>58.4</v>
       </c>
       <c r="H48" t="n">
-        <v>43.21</v>
-      </c>
-      <c r="I48" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.15000000000001</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>2.602</v>
+        <v>0.136</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>2.559</v>
+        <v>0.138</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="E49" s="10" t="n">
-        <v>0.0159</v>
+        <v>0.17</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <v>-0.0286</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3426900</v>
+        <v>3639200</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.33</v>
+        <v>0.67</v>
       </c>
       <c r="H49" t="n">
-        <v>43.38</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.21</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.339</v>
+        <v>0.163</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.336</v>
+        <v>0.165</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2711,19 +2711,19 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E50" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.73</v>
+      </c>
+      <c r="E50" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3345500</v>
+        <v>3590000</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.26</v>
+        <v>0.28</v>
       </c>
       <c r="H50" t="n">
-        <v>49.92</v>
+        <v>49.2</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E51" s="15" t="n">
-        <v>-0.0818</v>
+        <v>0.38</v>
+      </c>
+      <c r="E51" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3329800</v>
+        <v>3582300</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.71</v>
+        <v>0.33</v>
       </c>
       <c r="H51" t="n">
-        <v>46.27</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>28.08</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.834</v>
+        <v>0.479</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.618</v>
+        <v>0.589</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,39 +2792,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>0.335</v>
+        <v>2.4</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>-0.0147</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3245100</v>
+        <v>3534000</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.73</v>
+        <v>0.31</v>
       </c>
       <c r="H52" t="n">
-        <v>47.96</v>
-      </c>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.1</v>
+      </c>
+      <c r="I52" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>0.335</v>
+        <v>2.439</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>0.343</v>
+        <v>2.408</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,28 +2837,28 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E53" s="15" t="n">
-        <v>-0.0417</v>
+        <v>0.315</v>
+      </c>
+      <c r="E53" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3231200</v>
+        <v>3464300</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>1.21</v>
+        <v>0.34</v>
       </c>
       <c r="H53" t="n">
-        <v>14.67</v>
+        <v>41.29</v>
       </c>
       <c r="I53" s="16" t="inlineStr">
         <is>
@@ -2866,9 +2866,11 @@
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K53" s="9" t="n"/>
+        <v>0.338</v>
+      </c>
+      <c r="K53" s="9" t="n">
+        <v>0.336</v>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
     </row>
@@ -2880,39 +2882,39 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>7.13</v>
+        <v>0.43</v>
       </c>
       <c r="E54" s="15" t="n">
-        <v>-0.0028</v>
+        <v>-0.0227</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3115300</v>
+        <v>3450600</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.19</v>
+        <v>0.51</v>
       </c>
       <c r="H54" t="n">
-        <v>32.55</v>
-      </c>
-      <c r="I54" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.27</v>
+      </c>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>7.385</v>
+        <v>0.428</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>7.637</v>
+        <v>0.418</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2925,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.105</v>
+        <v>4.71</v>
       </c>
       <c r="E55" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3112900</v>
+        <v>3435900</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.68</v>
+        <v>0.16</v>
       </c>
       <c r="H55" t="n">
-        <v>62.33</v>
+        <v>46.79</v>
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
@@ -2954,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.098</v>
+        <v>4.725</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.083</v>
+        <v>4.818</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2970,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E56" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.735</v>
+      </c>
+      <c r="E56" s="15" t="n">
+        <v>-0.0755</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3068900</v>
+        <v>3425800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.5</v>
+        <v>0.73</v>
       </c>
       <c r="H56" t="n">
-        <v>41.23</v>
+        <v>46.56</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
@@ -2999,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.266</v>
+        <v>0.834</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.286</v>
+        <v>0.618</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3015,28 +3017,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="E57" s="17" t="n">
-        <v>0</v>
+        <v>0.775</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>2932600</v>
+        <v>3423800</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.26</v>
+        <v>0.53</v>
       </c>
       <c r="H57" t="n">
-        <v>46.38</v>
+        <v>34.71</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3044,10 +3046,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>2.44</v>
+        <v>0.887</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>2.408</v>
+        <v>0.856</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3060,39 +3062,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E58" s="10" t="n">
-        <v>0.0259</v>
+        <v>0.105</v>
+      </c>
+      <c r="E58" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>2890100</v>
+        <v>3412900</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.45</v>
+        <v>0.74</v>
       </c>
       <c r="H58" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="I58" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.33</v>
+      </c>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>1.173</v>
+        <v>0.098</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>1.147</v>
+        <v>0.083</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3105,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E59" s="15" t="n">
-        <v>-0.0227</v>
+        <v>0.125</v>
+      </c>
+      <c r="E59" s="10" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>2817500</v>
+        <v>3356700</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.41</v>
+        <v>0.32</v>
       </c>
       <c r="H59" t="n">
-        <v>51.27</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.38</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.428</v>
+        <v>0.125</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.418</v>
+        <v>0.104</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3150,39 +3152,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E60" s="10" t="n">
-        <v>0.0345</v>
+        <v>7.12</v>
+      </c>
+      <c r="E60" s="15" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>2757900</v>
+        <v>3333000</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.43</v>
+        <v>0.2</v>
       </c>
       <c r="H60" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.22</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.317</v>
+        <v>7.384</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.361</v>
+        <v>7.636</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3195,39 +3197,39 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.785</v>
-      </c>
-      <c r="E61" s="15" t="n">
-        <v>-0.0063</v>
+        <v>0.34</v>
+      </c>
+      <c r="E61" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>2743400</v>
+        <v>3268100</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.43</v>
+        <v>0.73</v>
       </c>
       <c r="H61" t="n">
-        <v>35.61</v>
-      </c>
-      <c r="I61" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.95</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.888</v>
+        <v>0.336</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.856</v>
+        <v>0.343</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3240,32 +3242,37 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.715</v>
+        <v>0.23</v>
       </c>
       <c r="E62" s="15" t="n">
-        <v>-0.0069</v>
+        <v>-0.0417</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>2713500</v>
+        <v>3248400</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.21</v>
+      </c>
+      <c r="H62" t="n">
+        <v>14.67</v>
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J62" s="9" t="n"/>
+      <c r="J62" s="9" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K62" s="9" t="n"/>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3278,39 +3285,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="E63" s="17" t="n">
-        <v>0</v>
+        <v>0.3</v>
+      </c>
+      <c r="E63" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>2642100</v>
+        <v>3116500</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.47</v>
+        <v>0.49</v>
       </c>
       <c r="H63" t="n">
-        <v>47.43</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.77</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>2.6</v>
+        <v>0.317</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>2.607</v>
+        <v>0.361</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3323,39 +3330,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>7.48</v>
-      </c>
-      <c r="E64" s="15" t="n">
-        <v>-0.0027</v>
+        <v>0.25</v>
+      </c>
+      <c r="E64" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>2613800</v>
+        <v>3080200</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.97</v>
+        <v>0.51</v>
       </c>
       <c r="H64" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.23</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>7.55</v>
+        <v>0.266</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>7.72</v>
+        <v>0.286</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3368,39 +3375,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E65" s="15" t="n">
-        <v>-0.0132</v>
+        <v>1.19</v>
+      </c>
+      <c r="E65" s="10" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>2549700</v>
+        <v>3006100</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.24</v>
+        <v>0.47</v>
       </c>
       <c r="H65" t="n">
-        <v>27.63</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.45</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.478</v>
+        <v>1.173</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.589</v>
+        <v>1.147</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3413,40 +3420,33 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>1.28</v>
+        <v>0.71</v>
       </c>
       <c r="E66" s="15" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0139</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2516200</v>
+        <v>2967000</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="H66" t="n">
-        <v>55.46</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J66" s="9" t="n">
-        <v>1.244</v>
-      </c>
-      <c r="K66" s="9" t="n">
-        <v>1.107</v>
-      </c>
+        <v>0.08</v>
+      </c>
+      <c r="I66" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
     </row>
@@ -3458,28 +3458,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E67" s="17" t="n">
-        <v>0</v>
+        <v>7.49</v>
+      </c>
+      <c r="E67" s="15" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2494400</v>
+        <v>2966900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.72</v>
+        <v>1.1</v>
       </c>
       <c r="H67" t="n">
-        <v>63.68</v>
+        <v>45.65</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3487,10 +3487,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.62</v>
+        <v>7.551</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>0.61</v>
+        <v>7.72</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3503,39 +3503,39 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>6.94</v>
+        <v>2.55</v>
       </c>
       <c r="E68" s="15" t="n">
-        <v>-0.0114</v>
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2490500</v>
+        <v>2933200</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H68" t="n">
-        <v>59.75</v>
-      </c>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.87</v>
+      </c>
+      <c r="I68" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>6.797</v>
+        <v>2.598</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>6.823</v>
+        <v>2.607</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3548,39 +3548,39 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E69" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>5.24</v>
+      </c>
+      <c r="E69" s="15" t="n">
+        <v>-0.0095</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2480800</v>
+        <v>2875800</v>
       </c>
       <c r="G69" s="12" t="n">
         <v>0.22</v>
       </c>
       <c r="H69" t="n">
-        <v>56.48</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.48</v>
+      </c>
+      <c r="I69" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>2.109</v>
+        <v>5.436</v>
       </c>
       <c r="K69" s="9" t="n">
-        <v>2.107</v>
+        <v>5.506</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
@@ -3593,28 +3593,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>4.72</v>
-      </c>
-      <c r="E70" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.825</v>
+      </c>
+      <c r="E70" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2452600</v>
+        <v>2859300</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.11</v>
+        <v>0.54</v>
       </c>
       <c r="H70" t="n">
-        <v>47.8</v>
+        <v>68.73</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3622,10 +3622,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>4.726</v>
+        <v>0.803</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>4.818</v>
+        <v>0.777</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3638,40 +3638,38 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>5.26</v>
+        <v>0.335</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0429</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2445500</v>
+        <v>2777400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.19</v>
+        <v>0.5</v>
       </c>
       <c r="H71" t="n">
-        <v>41.18</v>
-      </c>
-      <c r="I71" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.7</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>5.438</v>
-      </c>
-      <c r="K71" s="9" t="n">
-        <v>5.507</v>
-      </c>
+        <v>0.332</v>
+      </c>
+      <c r="K71" s="9" t="n"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
@@ -3683,28 +3681,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.13</v>
       </c>
       <c r="E72" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.004699999999999999</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2387000</v>
+        <v>2776800</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>1.31</v>
+        <v>0.25</v>
       </c>
       <c r="H72" t="n">
-        <v>48.93</v>
+        <v>54.88</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3712,10 +3710,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>2.108</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.107</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3728,28 +3726,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.495</v>
+        <v>6.89</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.0198</v>
+        <v>-0.0185</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2334900</v>
+        <v>2759300</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.77</v>
+        <v>0.58</v>
       </c>
       <c r="H73" t="n">
-        <v>72.58</v>
+        <v>56.38</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3757,10 +3755,10 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.442</v>
+        <v>6.792</v>
       </c>
       <c r="K73" s="9" t="n">
-        <v>0.436</v>
+        <v>6.822</v>
       </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
@@ -3773,28 +3771,28 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.34</v>
+        <v>1.27</v>
       </c>
       <c r="E74" s="15" t="n">
-        <v>-0.0286</v>
+        <v>-0.0522</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2302100</v>
+        <v>2614000</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.41</v>
+        <v>0.74</v>
       </c>
       <c r="H74" t="n">
-        <v>53.16</v>
+        <v>54.58</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -3802,9 +3800,11 @@
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.333</v>
-      </c>
-      <c r="K74" s="9" t="n"/>
+        <v>1.243</v>
+      </c>
+      <c r="K74" s="9" t="n">
+        <v>1.107</v>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
     </row>
@@ -3816,28 +3816,28 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="E75" s="15" t="n">
-        <v>-0.0182</v>
+        <v>2.03</v>
+      </c>
+      <c r="E75" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2247200</v>
+        <v>2583600</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.25</v>
+        <v>0.7</v>
       </c>
       <c r="H75" t="n">
-        <v>36.41</v>
+        <v>46.51</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
@@ -3845,10 +3845,10 @@
         </is>
       </c>
       <c r="J75" s="9" t="n">
-        <v>0.614</v>
+        <v>2.039</v>
       </c>
       <c r="K75" s="9" t="n">
-        <v>0.617</v>
+        <v>2.065</v>
       </c>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3861,28 +3861,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>4.47</v>
+        <v>0.62</v>
       </c>
       <c r="E76" s="15" t="n">
-        <v>-0.0022</v>
+        <v>-0.008</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2246200</v>
+        <v>2541200</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.26</v>
+        <v>0.73</v>
       </c>
       <c r="H76" t="n">
-        <v>38.22</v>
+        <v>54.69</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>4.568</v>
+        <v>0.619</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>4.641</v>
+        <v>0.609</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3906,39 +3906,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E77" s="10" t="n">
-        <v>0.005</v>
+        <v>4.47</v>
+      </c>
+      <c r="E77" s="15" t="n">
+        <v>-0.0022</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2203200</v>
+        <v>2531800</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.6</v>
+        <v>0.29</v>
       </c>
       <c r="H77" t="n">
-        <v>46.51</v>
-      </c>
-      <c r="I77" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>38.22</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.039</v>
+        <v>4.568</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>2.065</v>
+        <v>4.641</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,39 +3951,39 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E78" s="15" t="n">
-        <v>-0.0131</v>
+        <v>3.39</v>
+      </c>
+      <c r="E78" s="10" t="n">
+        <v>0.003</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2162700</v>
+        <v>2486800</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.28</v>
+        <v>0.78</v>
       </c>
       <c r="H78" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="I78" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.61</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>0.768</v>
+        <v>3.003</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>0.771</v>
+        <v>2.546</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3996,28 +3996,28 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.31</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="E79" s="10" t="n">
-        <v>0.0508</v>
+        <v>0.009000000000000001</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2142900</v>
+        <v>2429500</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="H79" t="n">
-        <v>53.89</v>
+        <v>48.93</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4025,10 +4025,10 @@
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.295</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.329</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,39 +4041,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E80" s="17" t="n">
-        <v>0</v>
+        <v>0.495</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>-0.0198</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2096700</v>
+        <v>2381300</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.25</v>
+        <v>0.78</v>
       </c>
       <c r="H80" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I80" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>72.58</v>
+      </c>
+      <c r="I80" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.652</v>
+        <v>0.442</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.436</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,39 +4086,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E81" s="10" t="n">
-        <v>0.003</v>
+        <v>0.54</v>
+      </c>
+      <c r="E81" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2037400</v>
+        <v>2278600</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.64</v>
+        <v>0.26</v>
       </c>
       <c r="H81" t="n">
-        <v>88.61</v>
-      </c>
-      <c r="I81" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.41</v>
+      </c>
+      <c r="I81" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>3.003</v>
+        <v>0.614</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>2.546</v>
+        <v>0.617</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,39 +4131,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E82" s="15" t="n">
-        <v>-0.0132</v>
+        <v>0.585</v>
+      </c>
+      <c r="E82" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>1982500</v>
+        <v>2211600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="H82" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="I82" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>35.4</v>
+      </c>
+      <c r="I82" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.373</v>
+        <v>0.652</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.37</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4176,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>MYTECH</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E83" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.235</v>
+      </c>
+      <c r="E83" s="15" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>1973200</v>
+        <v>2199100</v>
       </c>
       <c r="G83" s="12" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="H83" t="n">
+        <v>46.35</v>
+      </c>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J83" s="9" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K83" s="9" t="n">
         <v>0.25</v>
-      </c>
-      <c r="H83" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>1.625</v>
-      </c>
-      <c r="K83" s="9" t="n">
-        <v>1.678</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,28 +4221,28 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>0.27</v>
+        <v>6.9</v>
       </c>
       <c r="E84" s="15" t="n">
-        <v>-0.0182</v>
+        <v>-0.0058</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>1957500</v>
+        <v>2187000</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.24</v>
+        <v>0.2</v>
       </c>
       <c r="H84" t="n">
-        <v>43.03</v>
+        <v>39.13</v>
       </c>
       <c r="I84" s="16" t="inlineStr">
         <is>
@@ -4250,10 +4250,10 @@
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>0.285</v>
+        <v>7.097</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>0.283</v>
+        <v>7.521</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,39 +4266,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MYTECH</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.23</v>
+        <v>0.755</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.0417</v>
+        <v>-0.0131</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>1898900</v>
+        <v>2168700</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>16.79</v>
+        <v>0.28</v>
       </c>
       <c r="H85" t="n">
-        <v>43</v>
-      </c>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.88</v>
+      </c>
+      <c r="I85" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.235</v>
+        <v>0.768</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.25</v>
+        <v>0.771</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,39 +4311,39 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E86" s="15" t="n">
-        <v>-0.013</v>
+        <v>0.31</v>
+      </c>
+      <c r="E86" s="10" t="n">
+        <v>0.0508</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>1870400</v>
+        <v>2157900</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.31</v>
+        <v>1.9</v>
       </c>
       <c r="H86" t="n">
-        <v>30.88</v>
-      </c>
-      <c r="I86" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.89</v>
+      </c>
+      <c r="I86" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.664</v>
+        <v>0.295</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.746</v>
+        <v>0.329</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4356,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E87" s="15" t="n">
-        <v>-0.0058</v>
+        <v>1.63</v>
+      </c>
+      <c r="E87" s="10" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>1785300</v>
+        <v>2153500</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.16</v>
+        <v>0.27</v>
       </c>
       <c r="H87" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="I87" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>49.3</v>
+      </c>
+      <c r="I87" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>7.097</v>
+        <v>1.625</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>7.521</v>
+        <v>1.678</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E88" s="17" t="n">
-        <v>0</v>
+        <v>5.75</v>
+      </c>
+      <c r="E88" s="10" t="n">
+        <v>0.0035</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>1707400</v>
+        <v>2100200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="H88" t="n">
-        <v>68.73</v>
+        <v>40.39</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.803</v>
+        <v>5.837</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.777</v>
+        <v>6.105</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,39 +4446,39 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.865</v>
+        <v>7.34</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0068</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>1678100</v>
+        <v>2064000</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.57</v>
+        <v>0.19</v>
       </c>
       <c r="H89" t="n">
-        <v>50.82</v>
-      </c>
-      <c r="I89" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.97</v>
+      </c>
+      <c r="I89" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.865</v>
+        <v>7.42</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.86</v>
+        <v>7.843</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,28 +4491,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E90" s="17" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>1602600</v>
+        <v>2062500</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>1.18</v>
+        <v>0.29</v>
       </c>
       <c r="H90" t="n">
-        <v>48.11</v>
+        <v>54.17</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.23</v>
+        <v>0.373</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.238</v>
+        <v>0.37</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,28 +4536,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E91" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.27</v>
+      </c>
+      <c r="E91" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>1598400</v>
+        <v>2007500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.87</v>
+        <v>0.24</v>
       </c>
       <c r="H91" t="n">
-        <v>34.14</v>
+        <v>43.03</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>1.362</v>
+        <v>0.285</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>1.443</v>
+        <v>0.283</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>2.05</v>
+        <v>1.05</v>
       </c>
       <c r="E92" s="15" t="n">
-        <v>-0.0049</v>
+        <v>-0.0187</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>1588800</v>
+        <v>2006000</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.25</v>
+        <v>0.59</v>
       </c>
       <c r="H92" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="I92" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I92" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.95</v>
+        <v>1.129</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.957</v>
+        <v>1.11</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E93" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>2.05</v>
+      </c>
+      <c r="E93" s="15" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1579200</v>
+        <v>1937800</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.47</v>
+        <v>0.3</v>
       </c>
       <c r="H93" t="n">
-        <v>47.24</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.29</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>0.635</v>
+        <v>1.95</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>0.621</v>
+        <v>1.957</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,39 +4671,39 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>0.965</v>
+        <v>1.52</v>
       </c>
       <c r="E94" s="15" t="n">
-        <v>-0.0052</v>
+        <v>-0.013</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1567100</v>
+        <v>1932900</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.3</v>
+        <v>0.32</v>
       </c>
       <c r="H94" t="n">
-        <v>62.71</v>
-      </c>
-      <c r="I94" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.88</v>
+      </c>
+      <c r="I94" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.664</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>0.889</v>
+        <v>1.746</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4716,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E95" s="17" t="n">
-        <v>0</v>
+        <v>2.34</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.0043</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1552300</v>
+        <v>1872600</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.23</v>
+        <v>0.33</v>
       </c>
       <c r="H95" t="n">
-        <v>33.64</v>
+        <v>32.5</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.3</v>
+        <v>2.655</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.326</v>
+        <v>2.84</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0</v>
+        <v>0.96</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>-0.0103</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1486400</v>
+        <v>1807800</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.2</v>
+        <v>0.34</v>
       </c>
       <c r="H96" t="n">
-        <v>35.09</v>
-      </c>
-      <c r="I96" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.66</v>
+      </c>
+      <c r="I96" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>1.211</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>1.297</v>
+        <v>0.889</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E97" s="17" t="n">
-        <v>0</v>
+        <v>0.525</v>
+      </c>
+      <c r="E97" s="10" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1480300</v>
+        <v>1730100</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.38</v>
+        <v>0.47</v>
       </c>
       <c r="H97" t="n">
-        <v>50.46</v>
+        <v>39.27</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.825</v>
+        <v>0.556</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.795</v>
+        <v>0.592</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,28 +4851,28 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>2.05</v>
+        <v>1.15</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>-0.0049</v>
+        <v>-0.0086</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1480000</v>
+        <v>1685000</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>4.43</v>
+        <v>0.22</v>
       </c>
       <c r="H98" t="n">
-        <v>40.07</v>
+        <v>33.76</v>
       </c>
       <c r="I98" s="16" t="inlineStr">
         <is>
@@ -4880,10 +4880,10 @@
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>2.076</v>
+        <v>1.21</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>2.082</v>
+        <v>1.297</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,28 +4896,28 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E99" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E99" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1440700</v>
+        <v>1678100</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.3</v>
+        <v>0.57</v>
       </c>
       <c r="H99" t="n">
-        <v>61.45</v>
+        <v>50.82</v>
       </c>
       <c r="I99" s="16" t="inlineStr">
         <is>
@@ -4925,10 +4925,10 @@
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.536</v>
+        <v>0.865</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.482</v>
+        <v>0.86</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,39 +4941,39 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>7.34</v>
-      </c>
-      <c r="E100" s="15" t="n">
-        <v>-0.0068</v>
+        <v>0.265</v>
+      </c>
+      <c r="E100" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1440300</v>
+        <v>1662100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.13</v>
+        <v>0.25</v>
       </c>
       <c r="H100" t="n">
-        <v>40.97</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I100" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>7.42</v>
+        <v>0.3</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>7.843</v>
+        <v>0.326</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>5.75</v>
+        <v>1.31</v>
       </c>
       <c r="E101" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.0155</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1433400</v>
+        <v>1660600</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.19</v>
+        <v>0.91</v>
       </c>
       <c r="H101" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.37</v>
+      </c>
+      <c r="I101" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>5.837</v>
+        <v>1.363</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>6.105</v>
+        <v>1.443</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.92</v>
+        <v>0.625</v>
       </c>
       <c r="E102" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>0.008100000000000001</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1432100</v>
+        <v>1610600</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.33</v>
+        <v>0.48</v>
       </c>
       <c r="H102" t="n">
-        <v>28.81</v>
+        <v>47.24</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.953</v>
+        <v>0.635</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>1.036</v>
+        <v>0.621</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,39 +5076,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E103" s="15" t="n">
-        <v>-0.0187</v>
+        <v>0.23</v>
+      </c>
+      <c r="E103" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1384300</v>
+        <v>1602600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.41</v>
+        <v>1.18</v>
       </c>
       <c r="H103" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="I103" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I103" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>1.129</v>
+        <v>0.23</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>1.11</v>
+        <v>0.238</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E104" s="17" t="n">
-        <v>0</v>
+        <v>0.825</v>
+      </c>
+      <c r="E104" s="10" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1324500</v>
+        <v>1591300</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.12</v>
+        <v>0.41</v>
       </c>
       <c r="H104" t="n">
-        <v>46.45</v>
+        <v>51.41</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>2.741</v>
+        <v>0.825</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>2.747</v>
+        <v>0.796</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,28 +5166,28 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="E105" s="10" t="n">
-        <v>0.0294</v>
+        <v>2.68</v>
+      </c>
+      <c r="E105" s="15" t="n">
+        <v>-0.0074</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1302700</v>
+        <v>1557400</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>2.12</v>
+        <v>0.14</v>
       </c>
       <c r="H105" t="n">
-        <v>62.49</v>
+        <v>45</v>
       </c>
       <c r="I105" s="16" t="inlineStr">
         <is>
@@ -5195,10 +5195,10 @@
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.336</v>
+        <v>2.739</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.326</v>
+        <v>2.747</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E106" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.92</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.005500000000000001</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1287500</v>
+        <v>1497600</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>2.42</v>
+        <v>0.35</v>
       </c>
       <c r="H106" t="n">
-        <v>37.8</v>
+        <v>28.81</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.182</v>
+        <v>0.953</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.205</v>
+        <v>1.036</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E107" s="10" t="n">
-        <v>0.0043</v>
+        <v>2.05</v>
+      </c>
+      <c r="E107" s="15" t="n">
+        <v>-0.0049</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1239000</v>
+        <v>1480000</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>0.22</v>
+        <v>4.43</v>
       </c>
       <c r="H107" t="n">
-        <v>32.5</v>
+        <v>40.07</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.655</v>
+        <v>2.076</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.84</v>
+        <v>2.082</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E108" s="15" t="n">
-        <v>-0.0189</v>
+        <v>0.58</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1202300</v>
+        <v>1473800</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="H108" t="n">
-        <v>49.74</v>
+        <v>61.45</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.263</v>
+        <v>0.536</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.243</v>
+        <v>0.482</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E109" s="17" t="n">
-        <v>0</v>
+        <v>0.725</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.0069</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1184700</v>
+        <v>1461800</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="H109" t="n">
-        <v>46.77</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.36</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.239</v>
+        <v>0.738</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.241</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5400,19 +5400,19 @@
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="E110" s="15" t="n">
-        <v>-0.0162</v>
+        <v>-0.0135</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1156500</v>
+        <v>1413600</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="H110" t="n">
-        <v>43.52</v>
+        <v>43.89</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5420,7 +5420,7 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.798</v>
+        <v>3.799</v>
       </c>
       <c r="K110" s="9" t="n">
         <v>3.731</v>
@@ -5436,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>MUHIBAH</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E111" s="17" t="n">
-        <v>0</v>
+        <v>0.4</v>
+      </c>
+      <c r="E111" s="15" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1153500</v>
+        <v>1401300</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>1.31</v>
+        <v>2.59</v>
       </c>
       <c r="H111" t="n">
-        <v>50.42</v>
+        <v>14.63</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.276</v>
+        <v>0.428</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.268</v>
+        <v>0.449</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E112" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.27</v>
+      </c>
+      <c r="E112" s="10" t="n">
+        <v>0.016</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1145000</v>
+        <v>1354500</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.6</v>
+        <v>0.53</v>
       </c>
       <c r="H112" t="n">
-        <v>44.95</v>
+        <v>52.13</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.905</v>
+        <v>1.266</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>0.888</v>
+        <v>1.184</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5541,10 +5541,10 @@
         <v>-0.0309</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1095300</v>
+        <v>1349700</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.49</v>
+        <v>0.6</v>
       </c>
       <c r="H113" t="n">
         <v>23.21</v>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="E114" s="17" t="n">
-        <v>0</v>
+        <v>0.345</v>
+      </c>
+      <c r="E114" s="10" t="n">
+        <v>0.0147</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1064500</v>
+        <v>1341600</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>0.22</v>
+        <v>2.18</v>
       </c>
       <c r="H114" t="n">
-        <v>56.45</v>
+        <v>59.5</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>1.079</v>
+        <v>0.335</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.952</v>
+        <v>0.326</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E115" s="17" t="n">
-        <v>0</v>
+        <v>1.16</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>-0.008500000000000001</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1054500</v>
+        <v>1333600</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>6.46</v>
+        <v>2.51</v>
       </c>
       <c r="H115" t="n">
-        <v>39.25</v>
+        <v>37.8</v>
       </c>
       <c r="I115" s="16" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>2.682</v>
+        <v>1.182</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>2.787</v>
+        <v>1.205</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,28 +5661,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0202</v>
+        <v>0.26</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1051600</v>
+        <v>1202300</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.29</v>
+        <v>0.64</v>
       </c>
       <c r="H116" t="n">
-        <v>32.86</v>
+        <v>49.74</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.555</v>
+        <v>0.263</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.591</v>
+        <v>0.243</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,39 +5706,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.83</v>
+        <v>1.27</v>
       </c>
       <c r="E117" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1023000</v>
+        <v>1195200</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="H117" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="I117" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.39</v>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.874</v>
+        <v>1.264</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.272</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E118" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E118" s="15" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1022500</v>
+        <v>1194700</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.14</v>
+        <v>0.53</v>
       </c>
       <c r="H118" t="n">
-        <v>33.01</v>
+        <v>58.99</v>
       </c>
       <c r="I118" s="13" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.484</v>
+        <v>0.271</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.542</v>
+        <v>0.258</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,39 +5796,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E119" s="15" t="n">
-        <v>-0.0068</v>
+        <v>0.235</v>
+      </c>
+      <c r="E119" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1014500</v>
+        <v>1185200</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.34</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H119" t="n">
-        <v>49.59</v>
-      </c>
-      <c r="I119" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.77</v>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.741</v>
+        <v>0.239</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.707</v>
+        <v>0.241</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,28 +5841,28 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.25</v>
+        <v>0.275</v>
       </c>
       <c r="E120" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>981900</v>
+        <v>1153500</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.38</v>
+        <v>1.31</v>
       </c>
       <c r="H120" t="n">
-        <v>50.44</v>
+        <v>50.42</v>
       </c>
       <c r="I120" s="16" t="inlineStr">
         <is>
@@ -5870,10 +5870,10 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.264</v>
+        <v>0.276</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>1.183</v>
+        <v>0.268</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,28 +5886,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0</v>
+        <v>0.835</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0.006</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>943700</v>
+        <v>1150500</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.18</v>
+        <v>0.38</v>
       </c>
       <c r="H121" t="n">
-        <v>44.39</v>
+        <v>34.08</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.549</v>
+        <v>0.874</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.523</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,28 +5931,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.62</v>
+        <v>0.875</v>
       </c>
       <c r="E122" s="15" t="n">
-        <v>-0.008</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>933100</v>
+        <v>1145000</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.18</v>
+        <v>0.6</v>
       </c>
       <c r="H122" t="n">
-        <v>36.83</v>
+        <v>44.95</v>
       </c>
       <c r="I122" s="16" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.721</v>
+        <v>0.905</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.888</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5976,28 +5976,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>0.73</v>
+        <v>1.13</v>
       </c>
       <c r="E123" s="10" t="n">
-        <v>0.0139</v>
+        <v>0.018</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>899100</v>
+        <v>1140800</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.15</v>
+        <v>0.24</v>
       </c>
       <c r="H123" t="n">
-        <v>50.16</v>
+        <v>58.14</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>0.739</v>
+        <v>1.08</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.952</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6030,19 +6030,19 @@
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.96</v>
+        <v>0.985</v>
       </c>
       <c r="E124" s="15" t="n">
-        <v>-0.04</v>
+        <v>-0.015</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>875400</v>
+        <v>1120700</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.23</v>
+        <v>0.3</v>
       </c>
       <c r="H124" t="n">
-        <v>41.8</v>
+        <v>44.99</v>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.024</v>
+        <v>1.027</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.967</v>
+        <v>0.968</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,39 +6066,39 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E125" s="17" t="n">
-        <v>0</v>
+        <v>0.705</v>
+      </c>
+      <c r="E125" s="15" t="n">
+        <v>-0.0473</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>857500</v>
+        <v>1097000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.24</v>
+        <v>0.48</v>
       </c>
       <c r="H125" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I125" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.47</v>
+      </c>
+      <c r="I125" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.895</v>
+        <v>0.762</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.96</v>
+        <v>0.771</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,28 +6111,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>6.35</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>-0.004699999999999999</v>
+        <v>0.37</v>
+      </c>
+      <c r="E126" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>836500</v>
+        <v>1094300</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.14</v>
+        <v>0.44</v>
       </c>
       <c r="H126" t="n">
-        <v>53.14</v>
+        <v>42.72</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>6.261</v>
+        <v>0.384</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>5.98</v>
+        <v>0.389</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,28 +6156,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="E127" s="10" t="n">
-        <v>0.0152</v>
+        <v>0.625</v>
+      </c>
+      <c r="E127" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>817300</v>
+        <v>1081700</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.3</v>
+        <v>0.21</v>
       </c>
       <c r="H127" t="n">
-        <v>46.6</v>
+        <v>37.29</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>2.064</v>
+        <v>0.721</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>1.992</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,28 +6201,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>-0.019</v>
+        <v>2.6</v>
+      </c>
+      <c r="E128" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>793000</v>
+        <v>1064500</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.53</v>
+        <v>6.52</v>
       </c>
       <c r="H128" t="n">
-        <v>48.16</v>
+        <v>39.25</v>
       </c>
       <c r="I128" s="16" t="inlineStr">
         <is>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>3.153</v>
+        <v>2.682</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.942</v>
+        <v>2.787</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,39 +6246,39 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>1.38</v>
+        <v>0.735</v>
       </c>
       <c r="E129" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>775500</v>
+        <v>1034200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="H129" t="n">
-        <v>56.08</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.4</v>
+      </c>
+      <c r="I129" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>1.366</v>
+        <v>0.742</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>1.344</v>
+        <v>0.707</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6291,39 +6291,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.505</v>
+        <v>0.455</v>
       </c>
       <c r="E130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>743000</v>
+        <v>1023500</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="H130" t="n">
-        <v>29.82</v>
-      </c>
-      <c r="I130" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.01</v>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.531</v>
+        <v>0.484</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.542</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6336,28 +6336,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E131" s="17" t="n">
-        <v>0</v>
+        <v>0.515</v>
+      </c>
+      <c r="E131" s="15" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>739100</v>
+        <v>984000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="H131" t="n">
-        <v>33.86</v>
+        <v>43.43</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.491</v>
+        <v>0.548</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.659</v>
+        <v>0.523</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6381,39 +6381,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>7</v>
-      </c>
-      <c r="E132" s="15" t="n">
-        <v>-0.0278</v>
+        <v>1.38</v>
+      </c>
+      <c r="E132" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>731900</v>
+        <v>981500</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.16</v>
+        <v>0.47</v>
       </c>
       <c r="H132" t="n">
-        <v>45.52</v>
-      </c>
-      <c r="I132" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.08</v>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>7.273</v>
+        <v>1.366</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>6.933</v>
+        <v>1.344</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6426,39 +6426,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E133" s="15" t="n">
-        <v>-0.032</v>
+        <v>0.86</v>
+      </c>
+      <c r="E133" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>727900</v>
+        <v>947500</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="H133" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I133" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.9</v>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>2.53</v>
+        <v>0.895</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>2.653</v>
+        <v>0.96</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6471,39 +6471,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>0</v>
+        <v>10.32</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>-0.0246</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>716000</v>
+        <v>938500</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.06</v>
+        <v>0.26</v>
       </c>
       <c r="H134" t="n">
-        <v>46.44</v>
-      </c>
-      <c r="I134" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>50.28</v>
+      </c>
+      <c r="I134" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>9.988</v>
+        <v>10.433</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>10.116</v>
+        <v>9.846</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6516,39 +6516,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>0</v>
+        <v>7.08</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>-0.0167</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>708700</v>
+        <v>933400</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="H135" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="I135" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I135" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>1.264</v>
+        <v>7.281</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>1.272</v>
+        <v>6.934</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6561,28 +6561,28 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>10.3</v>
+        <v>2.42</v>
       </c>
       <c r="E136" s="15" t="n">
-        <v>-0.0265</v>
+        <v>-0.032</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>707800</v>
+        <v>904100</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.2</v>
+        <v>0.32</v>
       </c>
       <c r="H136" t="n">
-        <v>49.93</v>
+        <v>33.89</v>
       </c>
       <c r="I136" s="16" t="inlineStr">
         <is>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>10.431</v>
+        <v>2.53</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>9.845000000000001</v>
+        <v>2.653</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6606,28 +6606,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>1.72</v>
+        <v>2.7</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>-0.0058</v>
+        <v>-0.0074</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>703200</v>
+        <v>881600</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.16</v>
+        <v>0.1</v>
       </c>
       <c r="H137" t="n">
-        <v>39.48</v>
+        <v>46.18</v>
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>1.754</v>
+        <v>2.779</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>1.86</v>
+        <v>2.684</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6651,28 +6651,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E138" s="15" t="n">
+        <v>-0.0159</v>
+      </c>
+      <c r="F138" s="11" t="n">
+        <v>860200</v>
+      </c>
+      <c r="G138" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="E138" s="15" t="n">
-        <v>-0.008699999999999999</v>
-      </c>
-      <c r="F138" s="11" t="n">
-        <v>667000</v>
-      </c>
-      <c r="G138" s="12" t="n">
-        <v>0.11</v>
-      </c>
       <c r="H138" t="n">
-        <v>52.22</v>
+        <v>48.89</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.573</v>
+        <v>3.154</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.482</v>
+        <v>2.942</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6696,39 +6696,39 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E139" s="15" t="n">
-        <v>-0.0152</v>
+        <v>6.38</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>638300</v>
+        <v>859900</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.12</v>
+        <v>0.14</v>
       </c>
       <c r="H139" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="I139" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.68</v>
+      </c>
+      <c r="I139" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>3.331</v>
+        <v>6.263</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>3.56</v>
+        <v>5.98</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6741,39 +6741,39 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>5.03</v>
-      </c>
-      <c r="E140" s="15" t="n">
-        <v>-0.007900000000000001</v>
+        <v>3.96</v>
+      </c>
+      <c r="E140" s="10" t="n">
+        <v>0.0025</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>631400</v>
+        <v>855200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.16</v>
+        <v>0.09</v>
       </c>
       <c r="H140" t="n">
-        <v>48.7</v>
-      </c>
-      <c r="I140" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.42</v>
+      </c>
+      <c r="I140" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>5.059</v>
+        <v>3.956</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>5.041</v>
+        <v>3.622</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6786,39 +6786,39 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>0</v>
+        <v>2.02</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.0254</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>625100</v>
+        <v>825400</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.59</v>
+        <v>0.3</v>
       </c>
       <c r="H141" t="n">
-        <v>55</v>
-      </c>
-      <c r="I141" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.83</v>
+      </c>
+      <c r="I141" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>0.633</v>
+        <v>2.066</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>0.632</v>
+        <v>1.993</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6831,39 +6831,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>2.71</v>
+        <v>7.72</v>
       </c>
       <c r="E142" s="15" t="n">
-        <v>-0.0037</v>
+        <v>-0.0077</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>622900</v>
+        <v>822600</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="H142" t="n">
-        <v>46.72</v>
-      </c>
-      <c r="I142" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.32</v>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>2.78</v>
+        <v>7.814</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>2.684</v>
+        <v>7.856</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6876,39 +6876,39 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>13.22</v>
-      </c>
-      <c r="E143" s="15" t="n">
-        <v>-0.0015</v>
+        <v>2.38</v>
+      </c>
+      <c r="E143" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>612400</v>
+        <v>822100</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.09</v>
+        <v>0.2</v>
       </c>
       <c r="H143" t="n">
-        <v>56.14</v>
-      </c>
-      <c r="I143" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.86</v>
+      </c>
+      <c r="I143" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>13.055</v>
+        <v>2.491</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>13.334</v>
+        <v>2.659</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6921,28 +6921,28 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.91</v>
+        <v>2.11</v>
       </c>
       <c r="E144" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>606300</v>
+        <v>812300</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.53</v>
+        <v>0.39</v>
       </c>
       <c r="H144" t="n">
-        <v>57.47</v>
+        <v>51.3</v>
       </c>
       <c r="I144" s="13" t="inlineStr">
         <is>
@@ -6950,10 +6950,10 @@
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.793</v>
+        <v>2.112</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.84</v>
+        <v>2.075</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6966,28 +6966,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E145" s="10" t="n">
-        <v>0.0145</v>
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>591300</v>
+        <v>797200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.09</v>
+        <v>0.06</v>
       </c>
       <c r="H145" t="n">
-        <v>42.21</v>
+        <v>46.44</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>0.714</v>
+        <v>9.988</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>0.774</v>
+        <v>10.116</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7011,28 +7011,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>-0.0076</v>
+        <v>0.51</v>
+      </c>
+      <c r="E146" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>588900</v>
+        <v>775100</v>
       </c>
       <c r="G146" s="12" t="n">
         <v>0.26</v>
       </c>
       <c r="H146" t="n">
-        <v>30.67</v>
+        <v>33.54</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>5.483</v>
+        <v>0.532</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>5.752</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7056,39 +7056,39 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>2.1</v>
+        <v>5.24</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>-0.004699999999999999</v>
+        <v>-0.0095</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>585400</v>
+        <v>762800</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="H147" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="I147" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.31</v>
+      </c>
+      <c r="I147" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>2.111</v>
+        <v>5.482</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>2.075</v>
+        <v>5.752</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7116,10 +7116,10 @@
         <v>-0.012</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>584900</v>
+        <v>734200</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="H148" t="n">
         <v>31.35</v>
@@ -7146,39 +7146,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>3.89</v>
+        <v>5.02</v>
       </c>
       <c r="E149" s="15" t="n">
-        <v>-0.0152</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>561300</v>
+        <v>720200</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="H149" t="n">
-        <v>49.7</v>
-      </c>
-      <c r="I149" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.19</v>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>3.949</v>
+        <v>5.058</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>3.621</v>
+        <v>5.041</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7191,39 +7191,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>7.75</v>
+        <v>1.72</v>
       </c>
       <c r="E150" s="15" t="n">
-        <v>-0.0039</v>
+        <v>-0.0058</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>555800</v>
+        <v>711800</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.18</v>
+        <v>0.16</v>
       </c>
       <c r="H150" t="n">
-        <v>44.15</v>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.48</v>
+      </c>
+      <c r="I150" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>7.817</v>
+        <v>1.754</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>7.856</v>
+        <v>1.86</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7236,39 +7236,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>-0.0213</v>
+        <v>13.24</v>
+      </c>
+      <c r="E151" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>522300</v>
+        <v>703600</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>1.48</v>
+        <v>0.11</v>
       </c>
       <c r="H151" t="n">
-        <v>29.15</v>
-      </c>
-      <c r="I151" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.19</v>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>0.958</v>
+        <v>13.056</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>0.993</v>
+        <v>13.335</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7281,45 +7281,765 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E152" s="10" t="n">
-        <v>0.0184</v>
+        <v>1.22</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>-0.024</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>516000</v>
+        <v>703300</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.86</v>
+        <v>0.09</v>
       </c>
       <c r="H152" t="n">
-        <v>33.16</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.04</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>0.862</v>
+        <v>1.277</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>0.924</v>
+        <v>1.316</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
     </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>0120</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>VIS</t>
+        </is>
+      </c>
+      <c r="D153" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F153" s="11" t="n">
+        <v>679000</v>
+      </c>
+      <c r="G153" s="12" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="H153" t="n">
+        <v>52.91</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J153" s="9" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="K153" s="9" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" s="14" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>5249</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>IOIPG</t>
+        </is>
+      </c>
+      <c r="D154" s="9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="E154" s="15" t="n">
+        <v>-0.0152</v>
+      </c>
+      <c r="F154" s="11" t="n">
+        <v>676000</v>
+      </c>
+      <c r="G154" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H154" t="n">
+        <v>38.86</v>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J154" s="9" t="n">
+        <v>3.331</v>
+      </c>
+      <c r="K154" s="9" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" s="14" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>5330</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>TMK</t>
+        </is>
+      </c>
+      <c r="D155" s="9" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E155" s="15" t="n">
+        <v>-0.0034</v>
+      </c>
+      <c r="F155" s="11" t="n">
+        <v>669900</v>
+      </c>
+      <c r="G155" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H155" t="n">
+        <v>56.78</v>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J155" s="9" t="n">
+        <v>2.792</v>
+      </c>
+      <c r="K155" s="9" t="n">
+        <v>2.839</v>
+      </c>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" s="14" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>7233</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>DUFU</t>
+        </is>
+      </c>
+      <c r="D156" s="9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E156" s="15" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F156" s="11" t="n">
+        <v>655000</v>
+      </c>
+      <c r="G156" s="12" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H156" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="I156" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J156" s="9" t="n">
+        <v>2.986</v>
+      </c>
+      <c r="K156" s="9" t="n">
+        <v>2.859</v>
+      </c>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" s="14" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D157" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E157" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F157" s="11" t="n">
+        <v>625100</v>
+      </c>
+      <c r="G157" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H157" t="n">
+        <v>55</v>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J157" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K157" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" s="14" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>8664</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SPSETIA</t>
+        </is>
+      </c>
+      <c r="D158" s="9" t="n">
+        <v>0.695</v>
+      </c>
+      <c r="E158" s="10" t="n">
+        <v>0.0072</v>
+      </c>
+      <c r="F158" s="11" t="n">
+        <v>616000</v>
+      </c>
+      <c r="G158" s="12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H158" t="n">
+        <v>40.67</v>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J158" s="9" t="n">
+        <v>0.714</v>
+      </c>
+      <c r="K158" s="9" t="n">
+        <v>0.773</v>
+      </c>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" s="14" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>5317</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CPETECH</t>
+        </is>
+      </c>
+      <c r="D159" s="9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0.0236</v>
+      </c>
+      <c r="F159" s="11" t="n">
+        <v>614700</v>
+      </c>
+      <c r="G159" s="12" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="H159" t="n">
+        <v>52.17</v>
+      </c>
+      <c r="I159" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J159" s="9" t="n">
+        <v>1.283</v>
+      </c>
+      <c r="K159" s="9" t="n">
+        <v>1.238</v>
+      </c>
+      <c r="L159" t="inlineStr"/>
+      <c r="M159" s="14" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>RCECAP</t>
+        </is>
+      </c>
+      <c r="D160" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F160" s="11" t="n">
+        <v>609300</v>
+      </c>
+      <c r="G160" s="12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="H160" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="I160" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J160" s="9" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="K160" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L160" t="inlineStr"/>
+      <c r="M160" s="14" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>7161</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>KERJAYA</t>
+        </is>
+      </c>
+      <c r="D161" s="9" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="E161" s="10" t="n">
+        <v>0.0182</v>
+      </c>
+      <c r="F161" s="11" t="n">
+        <v>565800</v>
+      </c>
+      <c r="G161" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H161" t="n">
+        <v>50.52</v>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J161" s="9" t="n">
+        <v>3.374</v>
+      </c>
+      <c r="K161" s="9" t="n">
+        <v>3.229</v>
+      </c>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" s="14" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>DRBHCOM</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="n">
+        <v>0.835</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="F162" s="11" t="n">
+        <v>562700</v>
+      </c>
+      <c r="G162" s="12" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+      <c r="H162" t="n">
+        <v>35.3</v>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J162" s="9" t="n">
+        <v>0.863</v>
+      </c>
+      <c r="K162" s="9" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L162" t="inlineStr"/>
+      <c r="M162" s="14" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D163" s="9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>-0.0138</v>
+      </c>
+      <c r="F163" s="11" t="n">
+        <v>552500</v>
+      </c>
+      <c r="G163" s="12" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="H163" t="n">
+        <v>32.78</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J163" s="9" t="n">
+        <v>1.567</v>
+      </c>
+      <c r="K163" s="9" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="L163" t="inlineStr"/>
+      <c r="M163" s="14" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>FFB</t>
+        </is>
+      </c>
+      <c r="D164" s="9" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="E164" s="15" t="n">
+        <v>-0.0111</v>
+      </c>
+      <c r="F164" s="11" t="n">
+        <v>545200</v>
+      </c>
+      <c r="G164" s="12" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="H164" t="n">
+        <v>42.1</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J164" s="9" t="n">
+        <v>1.808</v>
+      </c>
+      <c r="K164" s="9" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="L164" t="inlineStr"/>
+      <c r="M164" s="14" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D165" s="9" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="E165" s="10" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="F165" s="11" t="n">
+        <v>523100</v>
+      </c>
+      <c r="G165" s="12" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H165" t="n">
+        <v>44.15</v>
+      </c>
+      <c r="I165" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J165" s="9" t="n">
+        <v>6.342</v>
+      </c>
+      <c r="K165" s="9" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" s="14" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D166" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="E166" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F166" s="11" t="n">
+        <v>514400</v>
+      </c>
+      <c r="G166" s="12" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="H166" t="n">
+        <v>53.58</v>
+      </c>
+      <c r="I166" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J166" s="9" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="K166" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" s="14" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>7160</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>PENTA</t>
+        </is>
+      </c>
+      <c r="D167" s="9" t="n">
+        <v>5.51</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0.005500000000000001</v>
+      </c>
+      <c r="F167" s="11" t="n">
+        <v>509100</v>
+      </c>
+      <c r="G167" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H167" t="n">
+        <v>51.35</v>
+      </c>
+      <c r="I167" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J167" s="9" t="n">
+        <v>5.486</v>
+      </c>
+      <c r="K167" s="9" t="n">
+        <v>5.379</v>
+      </c>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" s="14" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>3816</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>MISC</t>
+        </is>
+      </c>
+      <c r="D168" s="9" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="E168" s="10" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="F168" s="11" t="n">
+        <v>506300</v>
+      </c>
+      <c r="G168" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="H168" t="n">
+        <v>56.55</v>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J168" s="9" t="n">
+        <v>8.103</v>
+      </c>
+      <c r="K168" s="9" t="n">
+        <v>7.955</v>
+      </c>
+      <c r="L168" t="inlineStr"/>
+      <c r="M168" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M152"/>
+  <autoFilter ref="A1:M168"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$168</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$178</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M168"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.13</v>
+        <v>4.12</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0198</v>
+        <v>0.0173</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4277600</v>
+        <v>4459800</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.31999999999999</v>
+        <v>64.12</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.76</v>
+        <v>3.759</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>3.203</v>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号，RSI 64.32未超买，现价高于50日均线约29%，技术面信号可靠性较高。</t>
+          <t>SAR转多信号可靠，RSI 64.12偏高但未超买，现价4.12高于50日均线3.203约29%，多头动能较强。</t>
         </is>
       </c>
     </row>
@@ -619,19 +619,19 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>0.06</v>
+        <v>0.065</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>120040200</v>
+        <v>127358900</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.34</v>
+        <v>0.36</v>
       </c>
       <c r="H3" t="n">
-        <v>28.04</v>
+        <v>29.97</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
@@ -639,7 +639,7 @@
         </is>
       </c>
       <c r="J3" s="9" t="n">
-        <v>0.1</v>
+        <v>0.101</v>
       </c>
       <c r="K3" s="9" t="n">
         <v>0.272</v>
@@ -670,10 +670,10 @@
         <v>-0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>53575100</v>
+        <v>56081400</v>
       </c>
       <c r="G4" s="12" t="n">
-        <v>0.65</v>
+        <v>0.68</v>
       </c>
       <c r="H4" t="n">
         <v>56.38</v>
@@ -700,39 +700,39 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>0095</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>MAG</t>
         </is>
       </c>
       <c r="D5" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E5" s="10" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.155</v>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>22258900</v>
+        <v>26311500</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.61</v>
+        <v>0.72</v>
       </c>
       <c r="H5" t="n">
-        <v>78.45</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.33</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J5" s="9" t="n">
-        <v>0.414</v>
+        <v>0.156</v>
       </c>
       <c r="K5" s="9" t="n">
-        <v>0.31</v>
+        <v>0.156</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" s="14" t="inlineStr"/>
@@ -745,39 +745,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0095</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>MAG</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.155</v>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0313</v>
+        <v>0.485</v>
+      </c>
+      <c r="E6" s="10" t="n">
+        <v>0.05429999999999999</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>21284400</v>
+        <v>22420400</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.59</v>
+        <v>0.62</v>
       </c>
       <c r="H6" t="n">
-        <v>48.33</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.45</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.156</v>
+        <v>0.414</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.156</v>
+        <v>0.31</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -799,19 +799,19 @@
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <v>0</v>
+        <v>0.145</v>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>-0.0333</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>20818800</v>
+        <v>20915900</v>
       </c>
       <c r="G7" s="12" t="n">
         <v>1.46</v>
       </c>
       <c r="H7" t="n">
-        <v>37.79</v>
+        <v>34.01</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.154</v>
+        <v>0.153</v>
       </c>
       <c r="K7" s="9" t="n">
         <v>0.18</v>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.905</v>
-      </c>
-      <c r="E8" s="10" t="n">
-        <v>0.0284</v>
+        <v>0.37</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>19843600</v>
+        <v>20817300</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>0.27</v>
+        <v>2.35</v>
       </c>
       <c r="H8" t="n">
-        <v>63.11</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.34</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.852</v>
+        <v>0.39</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.757</v>
+        <v>0.404</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0133</v>
+        <v>0.91</v>
+      </c>
+      <c r="E9" s="10" t="n">
+        <v>0.0341</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>16295300</v>
+        <v>20464700</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>1.84</v>
+        <v>0.28</v>
       </c>
       <c r="H9" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="I9" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.71</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.39</v>
+        <v>0.852</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.404</v>
+        <v>0.758</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -934,19 +934,19 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>0.895</v>
+        <v>0.91</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0529</v>
+        <v>-0.03700000000000001</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>15314200</v>
+        <v>17083400</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="H10" t="n">
-        <v>34.91</v>
+        <v>36.24</v>
       </c>
       <c r="I10" s="16" t="inlineStr">
         <is>
@@ -954,7 +954,7 @@
         </is>
       </c>
       <c r="J10" s="9" t="n">
-        <v>1.011</v>
+        <v>1.013</v>
       </c>
       <c r="K10" s="9" t="n">
         <v>0.977</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0293</v>
+        <v>0.305</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>14493200</v>
+        <v>15474000</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.51</v>
+        <v>0.8</v>
       </c>
       <c r="H11" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.4</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>1.962</v>
+        <v>0.307</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>1.786</v>
+        <v>0.302</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <v>0</v>
+        <v>1.99</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.0293</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>13562900</v>
+        <v>15273200</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.7</v>
+        <v>0.54</v>
       </c>
       <c r="H12" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.66</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>0.307</v>
+        <v>1.962</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>0.302</v>
+        <v>1.786</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1075,10 +1075,10 @@
         <v>0</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>13314300</v>
+        <v>14102400</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="H13" t="n">
         <v>34.84</v>
@@ -1120,10 +1120,10 @@
         <v>0.042</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13079900</v>
+        <v>13480800</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H14" t="n">
         <v>84.38</v>
@@ -1150,28 +1150,28 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E15" s="15" t="n">
-        <v>-0.0345</v>
+        <v>0.45</v>
+      </c>
+      <c r="E15" s="10" t="n">
+        <v>0.0345</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>12481100</v>
+        <v>13360500</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>2.52</v>
+        <v>0.67</v>
       </c>
       <c r="H15" t="n">
-        <v>18.28</v>
+        <v>58.64</v>
       </c>
       <c r="I15" s="16" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="J15" s="9" t="n">
-        <v>1.317</v>
+        <v>0.429</v>
       </c>
       <c r="K15" s="9" t="n">
-        <v>1.515</v>
+        <v>0.381</v>
       </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
@@ -1195,40 +1195,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E16" s="10" t="n">
-        <v>0.046</v>
+        <v>0.255</v>
+      </c>
+      <c r="E16" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>12466900</v>
-      </c>
-      <c r="G16" s="12" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="H16" t="n">
-        <v>59.71</v>
-      </c>
+        <v>13202500</v>
+      </c>
+      <c r="G16" s="12" t="n"/>
       <c r="I16" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="K16" s="9" t="n">
-        <v>0.381</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1240,31 +1231,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E17" s="17" t="n">
-        <v>0</v>
+        <v>1.12</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>-0.0345</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12239800</v>
-      </c>
-      <c r="G17" s="12" t="n"/>
+        <v>12936200</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="H17" t="n">
+        <v>18.28</v>
+      </c>
       <c r="I17" s="16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>1.317</v>
+      </c>
+      <c r="K17" s="9" t="n">
+        <v>1.515</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
     </row>
@@ -1276,39 +1276,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>BENALEC</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E18" s="10" t="n">
-        <v>0.0833</v>
+        <v>0.82</v>
+      </c>
+      <c r="E18" s="15" t="n">
+        <v>-0.0061</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>10739400</v>
+        <v>11181200</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>13.38</v>
+        <v>0.7</v>
       </c>
       <c r="H18" t="n">
-        <v>55.37</v>
-      </c>
-      <c r="I18" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.27</v>
+      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.063</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.066</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1321,39 +1321,39 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>BENALEC</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E19" s="15" t="n">
-        <v>-0.0061</v>
+        <v>0.065</v>
+      </c>
+      <c r="E19" s="10" t="n">
+        <v>0.0833</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>10613100</v>
+        <v>11139400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>0.66</v>
+        <v>13.87</v>
       </c>
       <c r="H19" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>55.37</v>
+      </c>
+      <c r="I19" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J19" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="K19" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" s="14" t="inlineStr"/>
@@ -1366,39 +1366,39 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>8052</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>CGB</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E20" s="17" t="n">
-        <v>0</v>
+        <v>0.865</v>
+      </c>
+      <c r="E20" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>10384100</v>
+        <v>11038000</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="H20" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="I20" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.186</v>
+        <v>0.868</v>
       </c>
       <c r="K20" s="9" t="n">
-        <v>0.186</v>
+        <v>0.869</v>
       </c>
       <c r="L20" t="inlineStr"/>
       <c r="M20" s="14" t="inlineStr"/>
@@ -1411,39 +1411,39 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.005</v>
+        <v>0.775</v>
       </c>
       <c r="E21" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10304000</v>
+        <v>10558600</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>28.32</v>
+        <v>0.68</v>
       </c>
       <c r="H21" t="n">
-        <v>47.02</v>
-      </c>
-      <c r="I21" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>50.42</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.005</v>
+        <v>0.774</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.006</v>
+        <v>0.776</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,40 +1456,33 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E22" s="17" t="n">
-        <v>0</v>
+        <v>0.09</v>
+      </c>
+      <c r="E22" s="15" t="n">
+        <v>-0.0526</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>9326200</v>
+        <v>10557400</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="H22" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n">
-        <v>0.774</v>
-      </c>
-      <c r="K22" s="9" t="n">
-        <v>0.776</v>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="I22" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1501,39 +1494,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.135</v>
-      </c>
-      <c r="E23" s="10" t="n">
-        <v>0.08</v>
+        <v>0.18</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>8738400</v>
+        <v>10503900</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>17.36</v>
+        <v>0.5</v>
       </c>
       <c r="H23" t="n">
-        <v>64.23</v>
-      </c>
-      <c r="I23" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.11</v>
+      </c>
+      <c r="I23" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.127</v>
+        <v>0.186</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.129</v>
+        <v>0.186</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1546,28 +1539,28 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>8052</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CGB</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.865</v>
+        <v>0.165</v>
       </c>
       <c r="E24" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0294</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>8679500</v>
+        <v>10416700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.42</v>
+        <v>0.17</v>
       </c>
       <c r="H24" t="n">
-        <v>46.51</v>
+        <v>53.64</v>
       </c>
       <c r="I24" s="13" t="inlineStr">
         <is>
@@ -1575,10 +1568,10 @@
         </is>
       </c>
       <c r="J24" s="9" t="n">
-        <v>0.868</v>
+        <v>0.16</v>
       </c>
       <c r="K24" s="9" t="n">
-        <v>0.869</v>
+        <v>0.146</v>
       </c>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
@@ -1591,39 +1584,39 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E25" s="15" t="n">
-        <v>-0.0294</v>
+        <v>0.005</v>
+      </c>
+      <c r="E25" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>8504100</v>
+        <v>10304000</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>0.14</v>
+        <v>28.32</v>
       </c>
       <c r="H25" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I25" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.16</v>
+        <v>0.005</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.146</v>
+        <v>0.006</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1636,28 +1629,28 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>5243</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>VELESTO</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E26" s="15" t="n">
-        <v>-0.0083</v>
+        <v>0.19</v>
+      </c>
+      <c r="E26" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>7697200</v>
+        <v>9304900</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>0.32</v>
+        <v>0.44</v>
       </c>
       <c r="H26" t="n">
-        <v>46.13</v>
+        <v>33.79</v>
       </c>
       <c r="I26" s="16" t="inlineStr">
         <is>
@@ -1665,10 +1658,10 @@
         </is>
       </c>
       <c r="J26" s="9" t="n">
-        <v>4.87</v>
+        <v>0.21</v>
       </c>
       <c r="K26" s="9" t="n">
-        <v>4.756</v>
+        <v>0.23</v>
       </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" s="14" t="inlineStr"/>
@@ -1696,10 +1689,10 @@
         <v>-0.0048</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>7123800</v>
+        <v>9057800</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>0.65</v>
+        <v>0.82</v>
       </c>
       <c r="H27" t="n">
         <v>39.55</v>
@@ -1726,33 +1719,40 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="E28" s="17" t="n">
-        <v>0</v>
+        <v>0.135</v>
+      </c>
+      <c r="E28" s="10" t="n">
+        <v>0.08</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>6909200</v>
+        <v>8806900</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="I28" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J28" s="9" t="n"/>
-      <c r="K28" s="9" t="n"/>
+        <v>17.5</v>
+      </c>
+      <c r="H28" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>0.127</v>
+      </c>
+      <c r="K28" s="9" t="n">
+        <v>0.129</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
     </row>
@@ -1764,28 +1764,28 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5243</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VELESTO</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>0.185</v>
+        <v>4.79</v>
       </c>
       <c r="E29" s="15" t="n">
-        <v>-0.0263</v>
+        <v>-0.0083</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>6904600</v>
+        <v>8198000</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.32</v>
+        <v>0.34</v>
       </c>
       <c r="H29" t="n">
-        <v>31.82</v>
+        <v>46.13</v>
       </c>
       <c r="I29" s="16" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>0.209</v>
+        <v>4.87</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>0.23</v>
+        <v>4.756</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>7155</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SKPRES</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.335</v>
-      </c>
-      <c r="E30" s="15" t="n">
-        <v>-0.0147</v>
+        <v>0.635</v>
+      </c>
+      <c r="E30" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>6741800</v>
+        <v>7607100</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.86</v>
+        <v>0.72</v>
       </c>
       <c r="H30" t="n">
-        <v>44.85</v>
-      </c>
-      <c r="I30" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.35</v>
+        <v>0.623</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.329</v>
+        <v>0.617</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="E31" s="10" t="n">
-        <v>0.0148</v>
+        <v>0.425</v>
+      </c>
+      <c r="E31" s="15" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>6645400</v>
+        <v>7489900</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H31" t="n">
-        <v>21.65</v>
+        <v>24.81</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>1.593</v>
+        <v>0.484</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1.885</v>
+        <v>0.63</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1914,10 +1914,10 @@
         <v>0.0755</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>6635900</v>
+        <v>7274000</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.75</v>
+        <v>0.82</v>
       </c>
       <c r="H32" t="n">
         <v>58.03</v>
@@ -1944,39 +1944,39 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>SKPRES</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E33" s="17" t="n">
-        <v>0</v>
+        <v>0.33</v>
+      </c>
+      <c r="E33" s="15" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>6200500</v>
+        <v>7217300</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>0.59</v>
+        <v>0.92</v>
       </c>
       <c r="H33" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.21</v>
+      </c>
+      <c r="I33" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J33" s="9" t="n">
-        <v>0.623</v>
+        <v>0.35</v>
       </c>
       <c r="K33" s="9" t="n">
-        <v>0.617</v>
+        <v>0.329</v>
       </c>
       <c r="L33" t="inlineStr"/>
       <c r="M33" s="14" t="inlineStr"/>
@@ -1989,39 +1989,39 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>0262</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>SUNVIEW</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>0.425</v>
+        <v>0.41</v>
       </c>
       <c r="E34" s="15" t="n">
-        <v>-0.023</v>
+        <v>-0.0238</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6002300</v>
+        <v>6937100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>0.36</v>
+        <v>0.57</v>
       </c>
       <c r="H34" t="n">
-        <v>24.81</v>
-      </c>
-      <c r="I34" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.72</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J34" s="9" t="n">
-        <v>0.484</v>
+        <v>0.4</v>
       </c>
       <c r="K34" s="9" t="n">
-        <v>0.63</v>
+        <v>0.382</v>
       </c>
       <c r="L34" t="inlineStr"/>
       <c r="M34" s="14" t="inlineStr"/>
@@ -2034,28 +2034,28 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0262</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>SUNVIEW</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E35" s="15" t="n">
-        <v>-0.0238</v>
+        <v>0.055</v>
+      </c>
+      <c r="E35" s="10" t="n">
+        <v>0.1</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>5863800</v>
+        <v>6804800</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.48</v>
+        <v>0.88</v>
       </c>
       <c r="H35" t="n">
-        <v>54.72</v>
+        <v>58.62</v>
       </c>
       <c r="I35" s="13" t="inlineStr">
         <is>
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.4</v>
+        <v>0.049</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.382</v>
+        <v>0.047</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,28 +2079,28 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0175</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HHRG</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>0.12</v>
+        <v>1.37</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.0435</v>
+        <v>0.0148</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>5804400</v>
+        <v>6775400</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.3</v>
+        <v>0.51</v>
       </c>
       <c r="H36" t="n">
-        <v>38.64</v>
+        <v>21.65</v>
       </c>
       <c r="I36" s="16" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>0.134</v>
+        <v>1.593</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>0.147</v>
+        <v>1.885</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2124,28 +2124,28 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>0175</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>HHRG</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>0.435</v>
+        <v>0.12</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>0.0116</v>
+        <v>0.0435</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>5372000</v>
+        <v>6336900</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.33</v>
       </c>
       <c r="H37" t="n">
-        <v>39.37</v>
+        <v>38.64</v>
       </c>
       <c r="I37" s="16" t="inlineStr">
         <is>
@@ -2153,10 +2153,10 @@
         </is>
       </c>
       <c r="J37" s="9" t="n">
-        <v>0.495</v>
+        <v>0.134</v>
       </c>
       <c r="K37" s="9" t="n">
-        <v>0.468</v>
+        <v>0.147</v>
       </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" s="14" t="inlineStr"/>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E38" s="15" t="n">
-        <v>-0.0234</v>
+        <v>0.44</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <v>0.0233</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5156000</v>
+        <v>5746300</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.75</v>
+        <v>0.59</v>
       </c>
       <c r="H38" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.39</v>
+      </c>
+      <c r="I38" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.223</v>
+        <v>0.496</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>1.203</v>
+        <v>0.468</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E39" s="17" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="E39" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5044600</v>
+        <v>5582100</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.47</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="I39" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.78</v>
+      </c>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>0.287</v>
+        <v>1.225</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>0.279</v>
+        <v>1.204</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,28 +2259,28 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="E40" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>4744000</v>
+        <v>5080600</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.57</v>
+        <v>0.48</v>
       </c>
       <c r="H40" t="n">
-        <v>28.65</v>
+        <v>38.24</v>
       </c>
       <c r="I40" s="16" t="inlineStr">
         <is>
@@ -2288,10 +2288,10 @@
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.269</v>
+        <v>0.287</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.294</v>
+        <v>0.279</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,33 +2304,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>0.23</v>
+        <v>2.14</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>0.0222</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4671000</v>
+        <v>4986600</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I41" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J41" s="9" t="n"/>
-      <c r="K41" s="9" t="n"/>
+        <v>0.44</v>
+      </c>
+      <c r="H41" t="n">
+        <v>56.48</v>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J41" s="9" t="n">
+        <v>2.109</v>
+      </c>
+      <c r="K41" s="9" t="n">
+        <v>2.107</v>
+      </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
     </row>
@@ -2342,39 +2349,39 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.17</v>
+        <v>0.255</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.02</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4622100</v>
+        <v>4878200</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>1.49</v>
+        <v>0.59</v>
       </c>
       <c r="H42" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.07</v>
+      </c>
+      <c r="I42" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.159</v>
+        <v>0.269</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.157</v>
+        <v>0.294</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2396,19 +2403,19 @@
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="E43" s="15" t="n">
-        <v>-0.0123</v>
+        <v>-0.0165</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4427000</v>
+        <v>4795000</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="H43" t="n">
-        <v>61.98</v>
+        <v>61.04</v>
       </c>
       <c r="I43" s="13" t="inlineStr">
         <is>
@@ -2416,7 +2423,7 @@
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.276</v>
+        <v>2.275</v>
       </c>
       <c r="K43" s="9" t="n">
         <v>2.2</v>
@@ -2432,40 +2439,33 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E44" s="17" t="n">
-        <v>0</v>
+        <v>0.23</v>
+      </c>
+      <c r="E44" s="10" t="n">
+        <v>0.0222</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4187000</v>
+        <v>4671000</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="H44" t="n">
-        <v>28.46</v>
+        <v>0.22</v>
       </c>
       <c r="I44" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J44" s="9" t="n">
-        <v>0.225</v>
-      </c>
-      <c r="K44" s="9" t="n">
-        <v>0.272</v>
-      </c>
+      <c r="J44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2477,28 +2477,28 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>5183</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PCHEM</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>4.66</v>
+        <v>0.17</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.0379</v>
+        <v>0.0625</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>3927400</v>
+        <v>4622400</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0.8</v>
+        <v>1.49</v>
       </c>
       <c r="H45" t="n">
-        <v>59.54</v>
+        <v>60.81</v>
       </c>
       <c r="I45" s="13" t="inlineStr">
         <is>
@@ -2506,10 +2506,10 @@
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>4.409</v>
+        <v>0.159</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>4.439</v>
+        <v>0.157</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,28 +2522,28 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>0.555</v>
+        <v>2.51</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.0203</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>3884500</v>
+        <v>4615400</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="H46" t="n">
-        <v>48.37</v>
+        <v>44.53</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="J46" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>2.604</v>
       </c>
       <c r="K46" s="9" t="n">
-        <v>0.545</v>
+        <v>2.559</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0323</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>CREST</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>2.49</v>
+        <v>0.205</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.1389</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>3777400</v>
+        <v>4563100</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>0.2</v>
+        <v>5.69</v>
       </c>
       <c r="H47" t="n">
-        <v>43.21</v>
-      </c>
-      <c r="I47" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>67.34</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>2.602</v>
+        <v>0.173</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>2.559</v>
+        <v>0.177</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2612,28 +2612,28 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0312</t>
+          <t>5301</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>OFB</t>
+          <t>CTOS</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E48" s="17" t="n">
-        <v>0</v>
+        <v>0.375</v>
+      </c>
+      <c r="E48" s="15" t="n">
+        <v>-0.0132</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>3664200</v>
+        <v>4548300</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>58.4</v>
+        <v>0.42</v>
       </c>
       <c r="H48" t="n">
-        <v>76.15000000000001</v>
+        <v>27.63</v>
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
@@ -2641,10 +2641,10 @@
         </is>
       </c>
       <c r="J48" s="9" t="n">
-        <v>0.136</v>
+        <v>0.478</v>
       </c>
       <c r="K48" s="9" t="n">
-        <v>0.138</v>
+        <v>0.589</v>
       </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" s="14" t="inlineStr"/>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>0.17</v>
+        <v>2.39</v>
       </c>
       <c r="E49" s="15" t="n">
-        <v>-0.0286</v>
+        <v>-0.0083</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>3639200</v>
+        <v>4360300</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.67</v>
+        <v>0.38</v>
       </c>
       <c r="H49" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.89</v>
+      </c>
+      <c r="I49" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>0.163</v>
+        <v>2.438</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>0.165</v>
+        <v>2.408</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,28 +2702,28 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="E50" s="17" t="n">
-        <v>0</v>
+        <v>0.795</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>0.0063</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>3590000</v>
+        <v>4307800</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.28</v>
+        <v>0.67</v>
       </c>
       <c r="H50" t="n">
-        <v>49.2</v>
+        <v>36.9</v>
       </c>
       <c r="I50" s="16" t="inlineStr">
         <is>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.736</v>
+        <v>0.889</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.724</v>
+        <v>0.856</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CTOS</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.38</v>
+        <v>0.205</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>3582300</v>
+        <v>4293200</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="H51" t="n">
-        <v>28.08</v>
-      </c>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.46</v>
+      </c>
+      <c r="I51" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.479</v>
+        <v>0.225</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.589</v>
+        <v>0.272</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>2.4</v>
+        <v>5.24</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>-0.004099999999999999</v>
+        <v>-0.0095</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>3534000</v>
+        <v>4273700</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.31</v>
+        <v>0.33</v>
       </c>
       <c r="H52" t="n">
-        <v>45.1</v>
+        <v>40.48</v>
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>2.439</v>
+        <v>5.436</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>2.408</v>
+        <v>5.506</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0457</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PENTECH</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>0.315</v>
-      </c>
-      <c r="E53" s="17" t="n">
-        <v>0</v>
+        <v>4.72</v>
+      </c>
+      <c r="E53" s="10" t="n">
+        <v>0.0021</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>3464300</v>
+        <v>4244100</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.34</v>
+        <v>0.2</v>
       </c>
       <c r="H53" t="n">
-        <v>41.29</v>
-      </c>
-      <c r="I53" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.8</v>
+      </c>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>0.338</v>
+        <v>4.726</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>0.336</v>
+        <v>4.818</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2882,28 +2882,28 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0181</t>
+          <t>5183</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AEMULUS</t>
+          <t>PCHEM</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="E54" s="15" t="n">
-        <v>-0.0227</v>
+        <v>4.65</v>
+      </c>
+      <c r="E54" s="10" t="n">
+        <v>0.0356</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>3450600</v>
+        <v>4216300</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.51</v>
+        <v>0.86</v>
       </c>
       <c r="H54" t="n">
-        <v>51.27</v>
+        <v>59.24</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>0.428</v>
+        <v>4.408</v>
       </c>
       <c r="K54" s="9" t="n">
-        <v>0.418</v>
+        <v>4.439</v>
       </c>
       <c r="L54" t="inlineStr"/>
       <c r="M54" s="14" t="inlineStr"/>
@@ -2927,39 +2927,39 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="E55" s="17" t="n">
-        <v>0</v>
+        <v>0.555</v>
+      </c>
+      <c r="E55" s="10" t="n">
+        <v>0.0183</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>3435900</v>
+        <v>4164000</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.16</v>
+        <v>0.2</v>
       </c>
       <c r="H55" t="n">
-        <v>46.79</v>
-      </c>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.37</v>
+      </c>
+      <c r="I55" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>4.725</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>4.818</v>
+        <v>0.545</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2972,28 +2972,28 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0457</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>PENTECH</t>
         </is>
       </c>
       <c r="D56" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E56" s="15" t="n">
-        <v>-0.0755</v>
+        <v>0.32</v>
+      </c>
+      <c r="E56" s="10" t="n">
+        <v>0.0159</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3425800</v>
+        <v>3802800</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.73</v>
+        <v>0.37</v>
       </c>
       <c r="H56" t="n">
-        <v>46.56</v>
+        <v>43.38</v>
       </c>
       <c r="I56" s="16" t="inlineStr">
         <is>
@@ -3001,10 +3001,10 @@
         </is>
       </c>
       <c r="J56" s="9" t="n">
-        <v>0.834</v>
+        <v>0.339</v>
       </c>
       <c r="K56" s="9" t="n">
-        <v>0.618</v>
+        <v>0.336</v>
       </c>
       <c r="L56" t="inlineStr"/>
       <c r="M56" s="14" t="inlineStr"/>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E57" s="15" t="n">
-        <v>-0.019</v>
+        <v>0.735</v>
+      </c>
+      <c r="E57" s="10" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3423800</v>
+        <v>3713400</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="H57" t="n">
-        <v>34.71</v>
+        <v>49.92</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.887</v>
+        <v>0.736</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.856</v>
+        <v>0.724</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="E58" s="17" t="n">
-        <v>0</v>
+        <v>7.11</v>
+      </c>
+      <c r="E58" s="15" t="n">
+        <v>-0.005600000000000001</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3412900</v>
+        <v>3666000</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.74</v>
+        <v>0.22</v>
       </c>
       <c r="H58" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.89</v>
+      </c>
+      <c r="I58" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>0.098</v>
+        <v>7.383</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>0.083</v>
+        <v>7.636</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,39 +3107,39 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>0312</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>OFB</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E59" s="10" t="n">
-        <v>0.0417</v>
+        <v>0.16</v>
+      </c>
+      <c r="E59" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3356700</v>
+        <v>3664200</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0.32</v>
+        <v>58.4</v>
       </c>
       <c r="H59" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="I59" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>76.15000000000001</v>
+      </c>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J59" s="9" t="n">
-        <v>0.125</v>
+        <v>0.136</v>
       </c>
       <c r="K59" s="9" t="n">
-        <v>0.104</v>
+        <v>0.138</v>
       </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
@@ -3152,39 +3152,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>7.12</v>
+        <v>0.17</v>
       </c>
       <c r="E60" s="15" t="n">
-        <v>-0.0042</v>
+        <v>-0.0286</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3333000</v>
+        <v>3639200</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="H60" t="n">
-        <v>32.22</v>
-      </c>
-      <c r="I60" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.21</v>
+      </c>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>7.384</v>
+        <v>0.163</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>7.636</v>
+        <v>0.165</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3197,28 +3197,28 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0181</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>AEMULUS</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E61" s="17" t="n">
-        <v>0</v>
+        <v>0.43</v>
+      </c>
+      <c r="E61" s="15" t="n">
+        <v>-0.0227</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3268100</v>
+        <v>3605500</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.73</v>
+        <v>0.53</v>
       </c>
       <c r="H61" t="n">
-        <v>52.95</v>
+        <v>51.27</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,10 +3226,10 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.336</v>
+        <v>0.428</v>
       </c>
       <c r="K61" s="9" t="n">
-        <v>0.343</v>
+        <v>0.418</v>
       </c>
       <c r="L61" t="inlineStr"/>
       <c r="M61" s="14" t="inlineStr"/>
@@ -3242,28 +3242,28 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E62" s="15" t="n">
-        <v>-0.0417</v>
+        <v>1.19</v>
+      </c>
+      <c r="E62" s="10" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3248400</v>
+        <v>3533500</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1.21</v>
+        <v>0.55</v>
       </c>
       <c r="H62" t="n">
-        <v>14.67</v>
+        <v>53.45</v>
       </c>
       <c r="I62" s="16" t="inlineStr">
         <is>
@@ -3271,9 +3271,11 @@
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K62" s="9" t="n"/>
+        <v>1.173</v>
+      </c>
+      <c r="K62" s="9" t="n">
+        <v>1.147</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
     </row>
@@ -3285,39 +3287,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E63" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.74</v>
+      </c>
+      <c r="E63" s="15" t="n">
+        <v>-0.0692</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3116500</v>
+        <v>3520300</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.49</v>
+        <v>0.75</v>
       </c>
       <c r="H63" t="n">
-        <v>38.77</v>
-      </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.84</v>
+      </c>
+      <c r="I63" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.317</v>
+        <v>0.835</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.361</v>
+        <v>0.619</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3330,39 +3332,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E64" s="10" t="n">
-        <v>0.0204</v>
+        <v>0.105</v>
+      </c>
+      <c r="E64" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3080200</v>
+        <v>3412900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.51</v>
+        <v>0.74</v>
       </c>
       <c r="H64" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="I64" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>62.33</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.266</v>
+        <v>0.098</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.286</v>
+        <v>0.083</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3375,39 +3377,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E65" s="10" t="n">
-        <v>0.0259</v>
+        <v>0.34</v>
+      </c>
+      <c r="E65" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3006100</v>
+        <v>3381500</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.47</v>
+        <v>0.76</v>
       </c>
       <c r="H65" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="I65" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>52.95</v>
+      </c>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>1.173</v>
+        <v>0.336</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>1.147</v>
+        <v>0.343</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3420,33 +3422,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="E66" s="15" t="n">
-        <v>-0.0139</v>
+        <v>0.125</v>
+      </c>
+      <c r="E66" s="10" t="n">
+        <v>0.0417</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>2967000</v>
+        <v>3356900</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.08</v>
+        <v>0.32</v>
+      </c>
+      <c r="H66" t="n">
+        <v>52.38</v>
       </c>
       <c r="I66" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J66" s="9" t="n"/>
-      <c r="K66" s="9" t="n"/>
+      <c r="J66" s="9" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="K66" s="9" t="n">
+        <v>0.104</v>
+      </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
     </row>
@@ -3458,28 +3467,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>7.49</v>
+        <v>6.89</v>
       </c>
       <c r="E67" s="15" t="n">
-        <v>-0.0013</v>
+        <v>-0.0185</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>2966900</v>
+        <v>3345700</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>1.1</v>
+        <v>0.71</v>
       </c>
       <c r="H67" t="n">
-        <v>45.65</v>
+        <v>56.38</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3487,10 +3496,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>7.551</v>
+        <v>6.792</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>7.72</v>
+        <v>6.822</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3518,10 +3527,10 @@
         <v>-0.007800000000000001</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>2933200</v>
+        <v>3305400</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="H68" t="n">
         <v>45.87</v>
@@ -3548,28 +3557,28 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>5.24</v>
+        <v>0.23</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>-0.0095</v>
+        <v>-0.0417</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>2875800</v>
+        <v>3258400</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0.22</v>
+        <v>1.22</v>
       </c>
       <c r="H69" t="n">
-        <v>40.48</v>
+        <v>14.67</v>
       </c>
       <c r="I69" s="16" t="inlineStr">
         <is>
@@ -3577,11 +3586,9 @@
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>5.436</v>
-      </c>
-      <c r="K69" s="9" t="n">
-        <v>5.506</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="K69" s="9" t="n"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
     </row>
@@ -3593,28 +3600,28 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E70" s="17" t="n">
-        <v>0</v>
+        <v>0.295</v>
+      </c>
+      <c r="E70" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>2859300</v>
+        <v>3184200</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="H70" t="n">
-        <v>68.73</v>
+        <v>36.34</v>
       </c>
       <c r="I70" s="13" t="inlineStr">
         <is>
@@ -3622,10 +3629,10 @@
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.803</v>
+        <v>0.316</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.777</v>
+        <v>0.361</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3638,38 +3645,40 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>0.335</v>
+        <v>6.9</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.0429</v>
+        <v>-0.0058</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>2777400</v>
+        <v>3152500</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.5</v>
+        <v>0.29</v>
       </c>
       <c r="H71" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.13</v>
+      </c>
+      <c r="I71" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="K71" s="9" t="n"/>
+        <v>7.097</v>
+      </c>
+      <c r="K71" s="9" t="n">
+        <v>7.521</v>
+      </c>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
@@ -3681,28 +3690,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="E72" s="10" t="n">
-        <v>0.004699999999999999</v>
+        <v>7.49</v>
+      </c>
+      <c r="E72" s="15" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>2776800</v>
+        <v>3120600</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0.25</v>
+        <v>1.15</v>
       </c>
       <c r="H72" t="n">
-        <v>54.88</v>
+        <v>45.65</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3710,10 +3719,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>2.108</v>
+        <v>7.551</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>2.107</v>
+        <v>7.72</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3726,28 +3735,28 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>6.89</v>
+        <v>0.335</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.0185</v>
+        <v>-0.0429</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>2759300</v>
+        <v>3099000</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="H73" t="n">
-        <v>56.38</v>
+        <v>51.7</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -3755,11 +3764,9 @@
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>6.792</v>
-      </c>
-      <c r="K73" s="9" t="n">
-        <v>6.822</v>
-      </c>
+        <v>0.332</v>
+      </c>
+      <c r="K73" s="9" t="n"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3771,39 +3778,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E74" s="15" t="n">
-        <v>-0.0522</v>
+        <v>0.25</v>
+      </c>
+      <c r="E74" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>2614000</v>
+        <v>3081400</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.74</v>
+        <v>0.51</v>
       </c>
       <c r="H74" t="n">
-        <v>54.58</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.23</v>
+      </c>
+      <c r="I74" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>1.243</v>
+        <v>0.266</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>1.107</v>
+        <v>0.286</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3816,40 +3823,33 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E75" s="10" t="n">
-        <v>0.005</v>
+        <v>0.71</v>
+      </c>
+      <c r="E75" s="15" t="n">
+        <v>-0.0139</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>2583600</v>
+        <v>3081000</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="H75" t="n">
-        <v>46.51</v>
+        <v>0.08</v>
       </c>
       <c r="I75" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J75" s="9" t="n">
-        <v>2.039</v>
-      </c>
-      <c r="K75" s="9" t="n">
-        <v>2.065</v>
-      </c>
+      <c r="J75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
     </row>
@@ -3861,28 +3861,28 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>5285</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>SDG</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E76" s="15" t="n">
-        <v>-0.008</v>
+        <v>5.76</v>
+      </c>
+      <c r="E76" s="10" t="n">
+        <v>0.0052</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2541200</v>
+        <v>2904400</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.73</v>
+        <v>0.38</v>
       </c>
       <c r="H76" t="n">
-        <v>54.69</v>
+        <v>41.12</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -3890,10 +3890,10 @@
         </is>
       </c>
       <c r="J76" s="9" t="n">
-        <v>0.619</v>
+        <v>5.838</v>
       </c>
       <c r="K76" s="9" t="n">
-        <v>0.609</v>
+        <v>6.106</v>
       </c>
       <c r="L76" t="inlineStr"/>
       <c r="M76" s="14" t="inlineStr"/>
@@ -3906,28 +3906,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>4.47</v>
-      </c>
-      <c r="E77" s="15" t="n">
-        <v>-0.0022</v>
+        <v>0.825</v>
+      </c>
+      <c r="E77" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2531800</v>
+        <v>2903400</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.29</v>
+        <v>0.55</v>
       </c>
       <c r="H77" t="n">
-        <v>38.22</v>
+        <v>68.73</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>4.568</v>
+        <v>0.803</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>4.641</v>
+        <v>0.777</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,28 +3951,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>5327</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>MEGAFB</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="E78" s="10" t="n">
-        <v>0.003</v>
+        <v>4.48</v>
+      </c>
+      <c r="E78" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2486800</v>
+        <v>2878600</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.78</v>
+        <v>0.33</v>
       </c>
       <c r="H78" t="n">
-        <v>88.61</v>
+        <v>38.96</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>3.003</v>
+        <v>4.569</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2.546</v>
+        <v>4.641</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -4005,19 +4005,19 @@
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="E79" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>0.555</v>
+      </c>
+      <c r="E79" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2429500</v>
+        <v>2766000</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="H79" t="n">
-        <v>48.93</v>
+        <v>45.19</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -4041,39 +4041,39 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>0.495</v>
-      </c>
-      <c r="E80" s="15" t="n">
-        <v>-0.0198</v>
+        <v>2.03</v>
+      </c>
+      <c r="E80" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2381300</v>
+        <v>2729000</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="H80" t="n">
-        <v>72.58</v>
-      </c>
-      <c r="I80" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I80" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>0.442</v>
+        <v>2.039</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>0.436</v>
+        <v>2.065</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,39 +4086,39 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>0.54</v>
+        <v>1.28</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>-0.0182</v>
+        <v>-0.04480000000000001</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2278600</v>
+        <v>2701000</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.26</v>
+        <v>0.77</v>
       </c>
       <c r="H81" t="n">
-        <v>36.41</v>
-      </c>
-      <c r="I81" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.46</v>
+      </c>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>0.614</v>
+        <v>1.244</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>0.617</v>
+        <v>1.107</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,39 +4131,39 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E82" s="17" t="n">
-        <v>0</v>
+        <v>7.34</v>
+      </c>
+      <c r="E82" s="15" t="n">
+        <v>-0.0068</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2211600</v>
+        <v>2684100</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.26</v>
+        <v>0.24</v>
       </c>
       <c r="H82" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I82" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>40.97</v>
+      </c>
+      <c r="I82" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>0.652</v>
+        <v>7.42</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>7.843</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,39 +4176,39 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MYTECH</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E83" s="15" t="n">
-        <v>-0.0208</v>
+        <v>1.07</v>
+      </c>
+      <c r="E83" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2199100</v>
+        <v>2661600</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>19.44</v>
+        <v>0.79</v>
       </c>
       <c r="H83" t="n">
-        <v>46.35</v>
-      </c>
-      <c r="I83" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.27</v>
+      </c>
+      <c r="I83" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>0.236</v>
+        <v>1.131</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>0.25</v>
+        <v>1.11</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4221,39 +4221,39 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>5327</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>MEGAFB</t>
         </is>
       </c>
       <c r="D84" s="9" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="E84" s="15" t="n">
-        <v>-0.0058</v>
+        <v>3.4</v>
+      </c>
+      <c r="E84" s="10" t="n">
+        <v>0.0059</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2187000</v>
+        <v>2551100</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="H84" t="n">
-        <v>39.13</v>
-      </c>
-      <c r="I84" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>88.77</v>
+      </c>
+      <c r="I84" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J84" s="9" t="n">
-        <v>7.097</v>
+        <v>3.004</v>
       </c>
       <c r="K84" s="9" t="n">
-        <v>7.521</v>
+        <v>2.546</v>
       </c>
       <c r="L84" t="inlineStr"/>
       <c r="M84" s="14" t="inlineStr"/>
@@ -4266,39 +4266,39 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.755</v>
+        <v>0.62</v>
       </c>
       <c r="E85" s="15" t="n">
-        <v>-0.0131</v>
+        <v>-0.008</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2168700</v>
+        <v>2541200</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.28</v>
+        <v>0.73</v>
       </c>
       <c r="H85" t="n">
-        <v>45.88</v>
-      </c>
-      <c r="I85" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>54.69</v>
+      </c>
+      <c r="I85" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.768</v>
+        <v>0.619</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.771</v>
+        <v>0.609</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,28 +4311,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>0.31</v>
+        <v>2.07</v>
       </c>
       <c r="E86" s="10" t="n">
-        <v>0.0508</v>
+        <v>0.0049</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2157900</v>
+        <v>2521500</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="H86" t="n">
-        <v>53.89</v>
+        <v>65.72</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>0.295</v>
+        <v>1.952</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>0.329</v>
+        <v>1.958</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4371,10 +4371,10 @@
         <v>0.0124</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2153500</v>
+        <v>2426100</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.27</v>
+        <v>0.31</v>
       </c>
       <c r="H87" t="n">
         <v>49.3</v>
@@ -4401,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>5285</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>SDG</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="E88" s="10" t="n">
-        <v>0.0035</v>
+        <v>0.5</v>
+      </c>
+      <c r="E88" s="15" t="n">
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2100200</v>
+        <v>2383300</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.28</v>
+        <v>0.78</v>
       </c>
       <c r="H88" t="n">
-        <v>40.39</v>
+        <v>75.41</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>5.837</v>
+        <v>0.443</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>6.105</v>
+        <v>0.436</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,28 +4446,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>MYTECH</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>7.34</v>
+        <v>0.235</v>
       </c>
       <c r="E89" s="15" t="n">
-        <v>-0.0068</v>
+        <v>-0.0208</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2064000</v>
+        <v>2357300</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>0.19</v>
+        <v>20.84</v>
       </c>
       <c r="H89" t="n">
-        <v>40.97</v>
+        <v>46.35</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>7.42</v>
+        <v>0.236</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>7.843</v>
+        <v>0.25</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,28 +4491,28 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0024</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>JAG</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="E90" s="15" t="n">
-        <v>-0.0132</v>
+        <v>0.305</v>
+      </c>
+      <c r="E90" s="10" t="n">
+        <v>0.0339</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2062500</v>
+        <v>2334400</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0.29</v>
+        <v>2.05</v>
       </c>
       <c r="H90" t="n">
-        <v>54.17</v>
+        <v>51.87</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -4520,10 +4520,10 @@
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.373</v>
+        <v>0.295</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.37</v>
+        <v>0.329</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,28 +4536,28 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.27</v>
+        <v>0.535</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>-0.0182</v>
+        <v>-0.0273</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2007500</v>
+        <v>2295500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="H91" t="n">
-        <v>43.03</v>
+        <v>35.83</v>
       </c>
       <c r="I91" s="16" t="inlineStr">
         <is>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.285</v>
+        <v>0.613</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.283</v>
+        <v>0.617</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,28 +4581,28 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="E92" s="15" t="n">
-        <v>-0.0187</v>
+        <v>0.585</v>
+      </c>
+      <c r="E92" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2006000</v>
+        <v>2277700</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.59</v>
+        <v>0.27</v>
       </c>
       <c r="H92" t="n">
-        <v>39.04</v>
+        <v>35.4</v>
       </c>
       <c r="I92" s="16" t="inlineStr">
         <is>
@@ -4610,10 +4610,10 @@
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>1.129</v>
+        <v>0.652</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>1.11</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="E93" s="15" t="n">
-        <v>-0.0049</v>
+        <v>1.55</v>
+      </c>
+      <c r="E93" s="10" t="n">
+        <v>0.006500000000000001</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>1937800</v>
+        <v>2208200</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="H93" t="n">
-        <v>63.29</v>
-      </c>
-      <c r="I93" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.77</v>
+      </c>
+      <c r="I93" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.95</v>
+        <v>1.667</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.957</v>
+        <v>1.747</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="E94" s="15" t="n">
-        <v>-0.013</v>
+        <v>2.33</v>
+      </c>
+      <c r="E94" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>1932900</v>
+        <v>2191800</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.32</v>
+        <v>0.38</v>
       </c>
       <c r="H94" t="n">
-        <v>30.88</v>
+        <v>31.89</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>1.664</v>
+        <v>2.654</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>1.746</v>
+        <v>2.84</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4716,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="E95" s="10" t="n">
-        <v>0.0043</v>
+        <v>0.755</v>
+      </c>
+      <c r="E95" s="15" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>1872600</v>
+        <v>2168700</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.33</v>
+        <v>0.28</v>
       </c>
       <c r="H95" t="n">
-        <v>32.5</v>
+        <v>45.88</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>2.655</v>
+        <v>0.768</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>2.84</v>
+        <v>0.771</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,39 +4761,39 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>0.96</v>
-      </c>
-      <c r="E96" s="15" t="n">
-        <v>-0.0103</v>
+        <v>2.7</v>
+      </c>
+      <c r="E96" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>1807800</v>
+        <v>2111400</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.34</v>
+        <v>0.18</v>
       </c>
       <c r="H96" t="n">
-        <v>60.66</v>
-      </c>
-      <c r="I96" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.45</v>
+      </c>
+      <c r="I96" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>0.9399999999999999</v>
+        <v>2.741</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>0.889</v>
+        <v>2.747</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E97" s="10" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.27</v>
+      </c>
+      <c r="E97" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>1730100</v>
+        <v>2109900</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.47</v>
+        <v>0.26</v>
       </c>
       <c r="H97" t="n">
-        <v>39.27</v>
+        <v>43.03</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.556</v>
+        <v>0.285</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.592</v>
+        <v>0.283</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4851,39 +4851,39 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>0024</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>JAG</t>
         </is>
       </c>
       <c r="D98" s="9" t="n">
-        <v>1.15</v>
+        <v>0.37</v>
       </c>
       <c r="E98" s="15" t="n">
-        <v>-0.0086</v>
+        <v>-0.0263</v>
       </c>
       <c r="F98" s="11" t="n">
-        <v>1685000</v>
+        <v>2107600</v>
       </c>
       <c r="G98" s="12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="H98" t="n">
-        <v>33.76</v>
-      </c>
-      <c r="I98" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.52</v>
+      </c>
+      <c r="I98" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J98" s="9" t="n">
-        <v>1.21</v>
+        <v>0.372</v>
       </c>
       <c r="K98" s="9" t="n">
-        <v>1.297</v>
+        <v>0.37</v>
       </c>
       <c r="L98" t="inlineStr"/>
       <c r="M98" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0239</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ECOMATE</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.865</v>
-      </c>
-      <c r="E99" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.97</v>
+      </c>
+      <c r="E99" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1678100</v>
+        <v>1912300</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.57</v>
+        <v>0.36</v>
       </c>
       <c r="H99" t="n">
-        <v>50.82</v>
-      </c>
-      <c r="I99" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.89</v>
+      </c>
+      <c r="I99" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.865</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.86</v>
+        <v>0.889</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.265</v>
-      </c>
-      <c r="E100" s="17" t="n">
-        <v>0</v>
+        <v>0.525</v>
+      </c>
+      <c r="E100" s="10" t="n">
+        <v>0.06059999999999999</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1662100</v>
+        <v>1840100</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="H100" t="n">
-        <v>33.64</v>
+        <v>39.27</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.3</v>
+        <v>0.556</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.326</v>
+        <v>0.592</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,28 +4986,28 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="E101" s="10" t="n">
-        <v>0.0155</v>
+        <v>0.915</v>
+      </c>
+      <c r="E101" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1660600</v>
+        <v>1826100</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.91</v>
+        <v>0.42</v>
       </c>
       <c r="H101" t="n">
-        <v>36.37</v>
+        <v>25.71</v>
       </c>
       <c r="I101" s="16" t="inlineStr">
         <is>
@@ -5015,10 +5015,10 @@
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>1.363</v>
+        <v>0.952</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.443</v>
+        <v>1.036</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,28 +5031,28 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E102" s="10" t="n">
-        <v>0.008100000000000001</v>
+        <v>0.26</v>
+      </c>
+      <c r="E102" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1610600</v>
+        <v>1771400</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.48</v>
+        <v>0.27</v>
       </c>
       <c r="H102" t="n">
-        <v>47.24</v>
+        <v>32.41</v>
       </c>
       <c r="I102" s="16" t="inlineStr">
         <is>
@@ -5060,10 +5060,10 @@
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.635</v>
+        <v>0.299</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.621</v>
+        <v>0.326</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,39 +5076,39 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="E103" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1602600</v>
+        <v>1766200</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>1.18</v>
+        <v>0.53</v>
       </c>
       <c r="H103" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I103" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.21</v>
+      </c>
+      <c r="I103" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.23</v>
+        <v>0.634</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.238</v>
+        <v>0.621</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>0.825</v>
+        <v>1.3</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.0061</v>
+        <v>0.007800000000000001</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1591300</v>
+        <v>1715500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.41</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H104" t="n">
-        <v>51.41</v>
+        <v>34.14</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>0.825</v>
+        <v>1.362</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>0.796</v>
+        <v>1.443</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="E105" s="15" t="n">
-        <v>-0.0074</v>
+        <v>0.23</v>
+      </c>
+      <c r="E105" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1557400</v>
+        <v>1709900</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>0.14</v>
+        <v>1.26</v>
       </c>
       <c r="H105" t="n">
-        <v>45</v>
-      </c>
-      <c r="I105" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I105" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>2.739</v>
+        <v>0.23</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>2.747</v>
+        <v>0.238</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E106" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>1.16</v>
+      </c>
+      <c r="E106" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1497600</v>
+        <v>1705900</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.35</v>
+        <v>0.22</v>
       </c>
       <c r="H106" t="n">
-        <v>28.81</v>
+        <v>35.09</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>0.953</v>
+        <v>1.211</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.036</v>
+        <v>1.297</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5256,28 +5256,28 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>0239</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>ECOMATE</t>
         </is>
       </c>
       <c r="D107" s="9" t="n">
-        <v>2.05</v>
+        <v>0.865</v>
       </c>
       <c r="E107" s="15" t="n">
-        <v>-0.0049</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F107" s="11" t="n">
-        <v>1480000</v>
+        <v>1678100</v>
       </c>
       <c r="G107" s="12" t="n">
-        <v>4.43</v>
+        <v>0.57</v>
       </c>
       <c r="H107" t="n">
-        <v>40.07</v>
+        <v>50.82</v>
       </c>
       <c r="I107" s="16" t="inlineStr">
         <is>
@@ -5285,10 +5285,10 @@
         </is>
       </c>
       <c r="J107" s="9" t="n">
-        <v>2.076</v>
+        <v>0.865</v>
       </c>
       <c r="K107" s="9" t="n">
-        <v>2.082</v>
+        <v>0.86</v>
       </c>
       <c r="L107" t="inlineStr"/>
       <c r="M107" s="14" t="inlineStr"/>
@@ -5301,28 +5301,28 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="E108" s="17" t="n">
-        <v>0</v>
+        <v>0.83</v>
+      </c>
+      <c r="E108" s="10" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1473800</v>
+        <v>1613000</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.31</v>
+        <v>0.42</v>
       </c>
       <c r="H108" t="n">
-        <v>61.45</v>
+        <v>52.32</v>
       </c>
       <c r="I108" s="16" t="inlineStr">
         <is>
@@ -5330,10 +5330,10 @@
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.536</v>
+        <v>0.825</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.482</v>
+        <v>0.796</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>0310</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>UUE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.725</v>
-      </c>
-      <c r="E109" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.795</v>
+      </c>
+      <c r="E109" s="15" t="n">
+        <v>-0.0185</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1461800</v>
+        <v>1586500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.24</v>
+        <v>0.71</v>
       </c>
       <c r="H109" t="n">
-        <v>49.36</v>
-      </c>
-      <c r="I109" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>24.06</v>
+      </c>
+      <c r="I109" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.738</v>
+        <v>0.89</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>0.6870000000000001</v>
+        <v>1.048</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5406,10 +5406,10 @@
         <v>-0.0135</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1413600</v>
+        <v>1586400</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.43</v>
+        <v>0.48</v>
       </c>
       <c r="H110" t="n">
         <v>43.89</v>
@@ -5451,10 +5451,10 @@
         <v>-0.0123</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1401300</v>
+        <v>1581100</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>2.59</v>
+        <v>2.92</v>
       </c>
       <c r="H111" t="n">
         <v>14.63</v>
@@ -5481,28 +5481,28 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>0240</t>
+          <t>0310</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CORAZA</t>
+          <t>UUE</t>
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>1.27</v>
+        <v>0.725</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.016</v>
+        <v>0.0069</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1354500</v>
+        <v>1520900</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.53</v>
+        <v>0.25</v>
       </c>
       <c r="H112" t="n">
-        <v>52.13</v>
+        <v>49.36</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5510,10 +5510,10 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>1.266</v>
+        <v>0.738</v>
       </c>
       <c r="K112" s="9" t="n">
-        <v>1.184</v>
+        <v>0.6870000000000001</v>
       </c>
       <c r="L112" t="inlineStr"/>
       <c r="M112" s="14" t="inlineStr"/>
@@ -5526,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>0.785</v>
+        <v>7.72</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>-0.0309</v>
+        <v>-0.0077</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1349700</v>
+        <v>1509000</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.6</v>
+        <v>0.48</v>
       </c>
       <c r="H113" t="n">
-        <v>23.21</v>
+        <v>42.32</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>0.889</v>
+        <v>7.814</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>1.048</v>
+        <v>7.856</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>HUMEIND</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>0.345</v>
-      </c>
-      <c r="E114" s="10" t="n">
-        <v>0.0147</v>
+        <v>2.54</v>
+      </c>
+      <c r="E114" s="15" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1341600</v>
+        <v>1508500</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>2.18</v>
+        <v>6.67</v>
       </c>
       <c r="H114" t="n">
-        <v>59.5</v>
+        <v>37.18</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>0.335</v>
+        <v>2.61</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>0.326</v>
+        <v>2.743</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,28 +5616,28 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E115" s="15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.76</v>
+      </c>
+      <c r="E115" s="10" t="n">
+        <v>0.0066</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1333600</v>
+        <v>1496800</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>2.51</v>
+        <v>1.21</v>
       </c>
       <c r="H115" t="n">
-        <v>37.8</v>
+        <v>57.65</v>
       </c>
       <c r="I115" s="16" t="inlineStr">
         <is>
@@ -5645,10 +5645,10 @@
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>1.182</v>
+        <v>0.75</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>1.205</v>
+        <v>0.722</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,28 +5661,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E116" s="15" t="n">
-        <v>-0.0189</v>
+        <v>0.585</v>
+      </c>
+      <c r="E116" s="10" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1202300</v>
+        <v>1494200</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.64</v>
+        <v>0.31</v>
       </c>
       <c r="H116" t="n">
-        <v>49.74</v>
+        <v>62.13</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.263</v>
+        <v>0.536</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.243</v>
+        <v>0.482</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,39 +5706,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>5288</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SIMEPROP</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E117" s="17" t="n">
-        <v>0</v>
+        <v>0.355</v>
+      </c>
+      <c r="E117" s="10" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1195200</v>
+        <v>1491600</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>0.31</v>
+        <v>2.42</v>
       </c>
       <c r="H117" t="n">
-        <v>51.39</v>
-      </c>
-      <c r="I117" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>65.06999999999999</v>
+      </c>
+      <c r="I117" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>1.264</v>
+        <v>0.336</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>1.272</v>
+        <v>0.326</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,39 +5751,39 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>0.28</v>
+        <v>2.04</v>
       </c>
       <c r="E118" s="15" t="n">
-        <v>-0.0175</v>
+        <v>-0.0097</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1194700</v>
+        <v>1486400</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>0.53</v>
+        <v>4.45</v>
       </c>
       <c r="H118" t="n">
-        <v>58.99</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>37.52</v>
+      </c>
+      <c r="I118" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>0.271</v>
+        <v>2.075</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>0.258</v>
+        <v>2.082</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,28 +5796,28 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.235</v>
+        <v>0.86</v>
       </c>
       <c r="E119" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1185200</v>
+        <v>1463100</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="H119" t="n">
-        <v>46.77</v>
+        <v>30.9</v>
       </c>
       <c r="I119" s="13" t="inlineStr">
         <is>
@@ -5825,10 +5825,10 @@
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.239</v>
+        <v>0.895</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.241</v>
+        <v>0.96</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5841,39 +5841,39 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>5288</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>SIMEPROP</t>
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>0.275</v>
+        <v>1.27</v>
       </c>
       <c r="E120" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1153500</v>
+        <v>1452100</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>1.31</v>
+        <v>0.37</v>
       </c>
       <c r="H120" t="n">
-        <v>50.42</v>
-      </c>
-      <c r="I120" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.39</v>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>0.276</v>
+        <v>1.264</v>
       </c>
       <c r="K120" s="9" t="n">
-        <v>0.268</v>
+        <v>1.272</v>
       </c>
       <c r="L120" t="inlineStr"/>
       <c r="M120" s="14" t="inlineStr"/>
@@ -5886,28 +5886,28 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0240</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>CORAZA</t>
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E121" s="10" t="n">
-        <v>0.006</v>
+        <v>1.25</v>
+      </c>
+      <c r="E121" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1150500</v>
+        <v>1420800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.38</v>
+        <v>0.55</v>
       </c>
       <c r="H121" t="n">
-        <v>34.08</v>
+        <v>50.44</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5915,10 +5915,10 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>0.874</v>
+        <v>1.264</v>
       </c>
       <c r="K121" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>1.183</v>
       </c>
       <c r="L121" t="inlineStr"/>
       <c r="M121" s="14" t="inlineStr"/>
@@ -5931,39 +5931,39 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E122" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>1.39</v>
+      </c>
+      <c r="E122" s="10" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1145000</v>
+        <v>1349100</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="H122" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="I122" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.88</v>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>0.905</v>
+        <v>1.366</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>0.888</v>
+        <v>1.345</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5976,28 +5976,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="E123" s="10" t="n">
-        <v>0.018</v>
+        <v>1.17</v>
+      </c>
+      <c r="E123" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1140800</v>
+        <v>1335300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>0.24</v>
+        <v>2.51</v>
       </c>
       <c r="H123" t="n">
-        <v>58.14</v>
+        <v>41.3</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.08</v>
+        <v>1.183</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>0.952</v>
+        <v>1.205</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6021,28 +6021,28 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.985</v>
+        <v>0.705</v>
       </c>
       <c r="E124" s="15" t="n">
-        <v>-0.015</v>
+        <v>-0.0473</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1120700</v>
+        <v>1310000</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.3</v>
+        <v>0.57</v>
       </c>
       <c r="H124" t="n">
-        <v>44.99</v>
+        <v>38.47</v>
       </c>
       <c r="I124" s="16" t="inlineStr">
         <is>
@@ -6050,10 +6050,10 @@
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>1.027</v>
+        <v>0.762</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.968</v>
+        <v>0.771</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,28 +6066,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E125" s="15" t="n">
-        <v>-0.0473</v>
+        <v>1.12</v>
+      </c>
+      <c r="E125" s="10" t="n">
+        <v>0.009000000000000001</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1097000</v>
+        <v>1234000</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.48</v>
+        <v>0.26</v>
       </c>
       <c r="H125" t="n">
-        <v>38.47</v>
+        <v>57.31</v>
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>0.762</v>
+        <v>1.08</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.771</v>
+        <v>0.952</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,28 +6111,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0328</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>3REN</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E126" s="17" t="n">
-        <v>0</v>
+        <v>0.99</v>
+      </c>
+      <c r="E126" s="15" t="n">
+        <v>-0.01</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1094300</v>
+        <v>1208700</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.44</v>
+        <v>0.32</v>
       </c>
       <c r="H126" t="n">
-        <v>42.72</v>
+        <v>45.69</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>0.384</v>
+        <v>1.027</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.389</v>
+        <v>0.968</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,28 +6156,28 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E127" s="17" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E127" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1081700</v>
+        <v>1202300</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.21</v>
+        <v>0.64</v>
       </c>
       <c r="H127" t="n">
-        <v>37.29</v>
+        <v>49.74</v>
       </c>
       <c r="I127" s="16" t="inlineStr">
         <is>
@@ -6185,10 +6185,10 @@
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.721</v>
+        <v>0.263</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.243</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,39 +6201,39 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E128" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E128" s="15" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1064500</v>
+        <v>1194800</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>6.52</v>
+        <v>0.53</v>
       </c>
       <c r="H128" t="n">
-        <v>39.25</v>
-      </c>
-      <c r="I128" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.99</v>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>2.682</v>
+        <v>0.271</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>2.787</v>
+        <v>0.258</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,28 +6246,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.735</v>
+        <v>0.625</v>
       </c>
       <c r="E129" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1034200</v>
+        <v>1191600</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.35</v>
+        <v>0.23</v>
       </c>
       <c r="H129" t="n">
-        <v>50.4</v>
+        <v>37.29</v>
       </c>
       <c r="I129" s="16" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.742</v>
+        <v>0.721</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.707</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6291,28 +6291,28 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.455</v>
+        <v>0.235</v>
       </c>
       <c r="E130" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1023500</v>
+        <v>1190200</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.14</v>
+        <v>0.57</v>
       </c>
       <c r="H130" t="n">
-        <v>33.01</v>
+        <v>46.77</v>
       </c>
       <c r="I130" s="13" t="inlineStr">
         <is>
@@ -6320,10 +6320,10 @@
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.484</v>
+        <v>0.239</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.542</v>
+        <v>0.241</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6336,28 +6336,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>0.515</v>
+        <v>2.43</v>
       </c>
       <c r="E131" s="15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>-0.028</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>984000</v>
+        <v>1175800</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.19</v>
+        <v>0.41</v>
       </c>
       <c r="H131" t="n">
-        <v>43.43</v>
+        <v>34.66</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>0.548</v>
+        <v>2.53</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>0.523</v>
+        <v>2.653</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6381,39 +6381,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>1.38</v>
+        <v>2.72</v>
       </c>
       <c r="E132" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>981500</v>
+        <v>1171600</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.47</v>
+        <v>0.13</v>
       </c>
       <c r="H132" t="n">
-        <v>56.08</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.29</v>
+      </c>
+      <c r="I132" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>1.366</v>
+        <v>2.781</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>1.344</v>
+        <v>2.684</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6426,39 +6426,39 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="E133" s="17" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="E133" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>947500</v>
+        <v>1161900</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.27</v>
+        <v>0.12</v>
       </c>
       <c r="H133" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.86</v>
+      </c>
+      <c r="I133" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>0.895</v>
+        <v>3.96</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>0.96</v>
+        <v>3.623</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6471,28 +6471,28 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="E134" s="15" t="n">
-        <v>-0.0246</v>
+        <v>0.83</v>
+      </c>
+      <c r="E134" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>938500</v>
+        <v>1160000</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.26</v>
+        <v>0.38</v>
       </c>
       <c r="H134" t="n">
-        <v>50.28</v>
+        <v>32.09</v>
       </c>
       <c r="I134" s="16" t="inlineStr">
         <is>
@@ -6500,10 +6500,10 @@
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>10.433</v>
+        <v>0.874</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>9.846</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6516,28 +6516,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>5292</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>UWC</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>7.08</v>
-      </c>
-      <c r="E135" s="15" t="n">
-        <v>-0.0167</v>
+        <v>0.275</v>
+      </c>
+      <c r="E135" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>933400</v>
+        <v>1153500</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>0.2</v>
+        <v>1.31</v>
       </c>
       <c r="H135" t="n">
-        <v>47.02</v>
+        <v>50.42</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>7.281</v>
+        <v>0.276</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>6.934</v>
+        <v>0.268</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6561,39 +6561,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v>-0.032</v>
+        <v>0.455</v>
+      </c>
+      <c r="E136" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>904100</v>
+        <v>1149200</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.32</v>
+        <v>0.16</v>
       </c>
       <c r="H136" t="n">
-        <v>33.89</v>
-      </c>
-      <c r="I136" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.01</v>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>2.53</v>
+        <v>0.484</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>2.653</v>
+        <v>0.542</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6606,28 +6606,28 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0328</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>3REN</t>
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>2.7</v>
+        <v>0.365</v>
       </c>
       <c r="E137" s="15" t="n">
-        <v>-0.0074</v>
+        <v>-0.0135</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>881600</v>
+        <v>1148900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.1</v>
+        <v>0.46</v>
       </c>
       <c r="H137" t="n">
-        <v>46.18</v>
+        <v>40.86</v>
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
@@ -6635,10 +6635,10 @@
         </is>
       </c>
       <c r="J137" s="9" t="n">
-        <v>2.779</v>
+        <v>0.384</v>
       </c>
       <c r="K137" s="9" t="n">
-        <v>2.684</v>
+        <v>0.389</v>
       </c>
       <c r="L137" t="inlineStr"/>
       <c r="M137" s="14" t="inlineStr"/>
@@ -6651,28 +6651,28 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>3.1</v>
+        <v>0.875</v>
       </c>
       <c r="E138" s="15" t="n">
-        <v>-0.0159</v>
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>860200</v>
+        <v>1145000</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="H138" t="n">
-        <v>48.89</v>
+        <v>44.95</v>
       </c>
       <c r="I138" s="16" t="inlineStr">
         <is>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>3.154</v>
+        <v>0.905</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>2.942</v>
+        <v>0.888</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6696,28 +6696,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="E139" s="17" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E139" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>859900</v>
+        <v>1104100</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.14</v>
+        <v>0.21</v>
       </c>
       <c r="H139" t="n">
-        <v>53.68</v>
+        <v>46.74</v>
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>6.263</v>
+        <v>0.55</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>5.98</v>
+        <v>0.524</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6741,28 +6741,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="E140" s="10" t="n">
-        <v>0.0025</v>
+        <v>0.41</v>
+      </c>
+      <c r="E140" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>855200</v>
+        <v>1076200</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.09</v>
+        <v>0.41</v>
       </c>
       <c r="H140" t="n">
-        <v>52.42</v>
+        <v>38.76</v>
       </c>
       <c r="I140" s="16" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>3.956</v>
+        <v>0.435</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>3.622</v>
+        <v>0.431</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6786,28 +6786,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="E141" s="10" t="n">
-        <v>0.0254</v>
+        <v>2.6</v>
+      </c>
+      <c r="E141" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>825400</v>
+        <v>1064500</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>0.3</v>
+        <v>6.52</v>
       </c>
       <c r="H141" t="n">
-        <v>47.83</v>
+        <v>39.25</v>
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.066</v>
+        <v>2.682</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>1.993</v>
+        <v>2.787</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6831,39 +6831,39 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>7.72</v>
+        <v>10.38</v>
       </c>
       <c r="E142" s="15" t="n">
-        <v>-0.0077</v>
+        <v>-0.0189</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>822600</v>
+        <v>1047700</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="H142" t="n">
-        <v>42.32</v>
-      </c>
-      <c r="I142" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>51.37</v>
+      </c>
+      <c r="I142" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>7.814</v>
+        <v>10.438</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>7.856</v>
+        <v>9.847</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6876,28 +6876,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>2.38</v>
+        <v>0.735</v>
       </c>
       <c r="E143" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>822100</v>
+        <v>1047200</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="H143" t="n">
-        <v>33.86</v>
+        <v>50.4</v>
       </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>2.491</v>
+        <v>0.742</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>2.659</v>
+        <v>0.707</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6921,39 +6921,39 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5292</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>UWC</t>
         </is>
       </c>
       <c r="D144" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E144" s="17" t="n">
-        <v>0</v>
+        <v>7.09</v>
+      </c>
+      <c r="E144" s="15" t="n">
+        <v>-0.0153</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>812300</v>
+        <v>1033800</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.39</v>
+        <v>0.22</v>
       </c>
       <c r="H144" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="I144" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.22</v>
+      </c>
+      <c r="I144" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J144" s="9" t="n">
-        <v>2.112</v>
+        <v>7.282</v>
       </c>
       <c r="K144" s="9" t="n">
-        <v>2.075</v>
+        <v>6.934</v>
       </c>
       <c r="L144" t="inlineStr"/>
       <c r="M144" s="14" t="inlineStr"/>
@@ -6966,28 +6966,28 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E145" s="17" t="n">
-        <v>0</v>
+        <v>1.78</v>
+      </c>
+      <c r="E145" s="15" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>797200</v>
+        <v>958600</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.06</v>
+        <v>0.31</v>
       </c>
       <c r="H145" t="n">
-        <v>46.44</v>
+        <v>42.1</v>
       </c>
       <c r="I145" s="13" t="inlineStr">
         <is>
@@ -6995,10 +6995,10 @@
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>9.988</v>
+        <v>1.808</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>10.116</v>
+        <v>1.93</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7011,28 +7011,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="E146" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>3.09</v>
+      </c>
+      <c r="E146" s="15" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>775100</v>
+        <v>945900</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.26</v>
+        <v>0.63</v>
       </c>
       <c r="H146" t="n">
-        <v>33.54</v>
+        <v>48.16</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>0.532</v>
+        <v>3.153</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>2.942</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7065,19 +7065,19 @@
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>5.24</v>
+        <v>5.25</v>
       </c>
       <c r="E147" s="15" t="n">
-        <v>-0.0095</v>
+        <v>-0.0076</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>762800</v>
+        <v>939400</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.34</v>
+        <v>0.42</v>
       </c>
       <c r="H147" t="n">
-        <v>30.31</v>
+        <v>30.67</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>5.482</v>
+        <v>5.483</v>
       </c>
       <c r="K147" s="9" t="n">
         <v>5.752</v>
@@ -7101,28 +7101,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>4.13</v>
-      </c>
-      <c r="E148" s="15" t="n">
-        <v>-0.012</v>
+        <v>6.4</v>
+      </c>
+      <c r="E148" s="10" t="n">
+        <v>0.0031</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>734200</v>
+        <v>936500</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="H148" t="n">
-        <v>31.35</v>
+        <v>53.99</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>4.333</v>
+        <v>6.265</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>4.641</v>
+        <v>5.981</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7146,39 +7146,39 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>5.02</v>
-      </c>
-      <c r="E149" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>2.38</v>
+      </c>
+      <c r="E149" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>720200</v>
+        <v>922900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="H149" t="n">
-        <v>48.19</v>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.86</v>
+      </c>
+      <c r="I149" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>5.058</v>
+        <v>2.491</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>5.041</v>
+        <v>2.659</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7191,28 +7191,28 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="E150" s="15" t="n">
-        <v>-0.0058</v>
+        <v>5.53</v>
+      </c>
+      <c r="E150" s="10" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>711800</v>
+        <v>907300</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="H150" t="n">
-        <v>39.48</v>
+        <v>51.85</v>
       </c>
       <c r="I150" s="16" t="inlineStr">
         <is>
@@ -7220,10 +7220,10 @@
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>1.754</v>
+        <v>5.488</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>1.86</v>
+        <v>5.379</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7236,39 +7236,39 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>13.24</v>
-      </c>
-      <c r="E151" s="17" t="n">
-        <v>0</v>
+        <v>4.14</v>
+      </c>
+      <c r="E151" s="15" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>703600</v>
+        <v>904100</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.11</v>
+        <v>0.22</v>
       </c>
       <c r="H151" t="n">
-        <v>57.19</v>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>31.76</v>
+      </c>
+      <c r="I151" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>13.056</v>
+        <v>4.334</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>13.335</v>
+        <v>4.641</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7281,39 +7281,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="E152" s="15" t="n">
-        <v>-0.024</v>
+        <v>2.11</v>
+      </c>
+      <c r="E152" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>703300</v>
+        <v>898700</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.09</v>
+        <v>0.43</v>
       </c>
       <c r="H152" t="n">
-        <v>39.04</v>
-      </c>
-      <c r="I152" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.3</v>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>1.277</v>
+        <v>2.112</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>1.316</v>
+        <v>2.075</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7326,39 +7326,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E153" s="17" t="n">
-        <v>0</v>
+        <v>3.22</v>
+      </c>
+      <c r="E153" s="15" t="n">
+        <v>-0.0242</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>679000</v>
+        <v>891300</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="H153" t="n">
-        <v>52.91</v>
-      </c>
-      <c r="I153" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>37.01</v>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>0.574</v>
+        <v>3.328</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>0.482</v>
+        <v>3.56</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7371,39 +7371,39 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="E154" s="15" t="n">
-        <v>-0.0152</v>
+        <v>1.32</v>
+      </c>
+      <c r="E154" s="10" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>676000</v>
+        <v>886200</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.12</v>
+        <v>0.31</v>
       </c>
       <c r="H154" t="n">
-        <v>38.86</v>
-      </c>
-      <c r="I154" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.61</v>
+      </c>
+      <c r="I154" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>3.331</v>
+        <v>1.285</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>3.56</v>
+        <v>1.238</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7416,39 +7416,39 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E155" s="15" t="n">
-        <v>-0.0034</v>
+        <v>2.01</v>
+      </c>
+      <c r="E155" s="10" t="n">
+        <v>0.0203</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>669900</v>
+        <v>882200</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.59</v>
+        <v>0.32</v>
       </c>
       <c r="H155" t="n">
-        <v>56.78</v>
-      </c>
-      <c r="I155" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.22</v>
+      </c>
+      <c r="I155" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.792</v>
+        <v>2.065</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>2.839</v>
+        <v>1.993</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7461,39 +7461,39 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>2.86</v>
+        <v>5.03</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>-0.0138</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>655000</v>
+        <v>856800</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.24</v>
+        <v>0.21</v>
       </c>
       <c r="H156" t="n">
-        <v>44.83</v>
-      </c>
-      <c r="I156" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.7</v>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>2.986</v>
+        <v>5.059</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>2.859</v>
+        <v>5.041</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7506,28 +7506,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E157" s="17" t="n">
-        <v>0</v>
+        <v>9.960000000000001</v>
+      </c>
+      <c r="E157" s="15" t="n">
+        <v>-0.001</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>625100</v>
+        <v>856800</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.59</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="H157" t="n">
-        <v>55</v>
+        <v>45.78</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>0.633</v>
+        <v>9.987</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>0.632</v>
+        <v>10.116</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7551,28 +7551,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>0.695</v>
-      </c>
-      <c r="E158" s="10" t="n">
-        <v>0.0072</v>
+        <v>13.2</v>
+      </c>
+      <c r="E158" s="15" t="n">
+        <v>-0.003</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>616000</v>
+        <v>843400</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H158" t="n">
-        <v>40.67</v>
+        <v>55.14</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>0.714</v>
+        <v>13.053</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>0.773</v>
+        <v>13.334</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7596,28 +7596,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="E159" s="10" t="n">
-        <v>0.0236</v>
+        <v>0.505</v>
+      </c>
+      <c r="E159" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>614700</v>
+        <v>823200</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.21</v>
+        <v>0.28</v>
       </c>
       <c r="H159" t="n">
-        <v>52.17</v>
+        <v>29.82</v>
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>1.283</v>
+        <v>0.531</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>1.238</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7641,28 +7641,28 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>0.92</v>
+        <v>1.23</v>
       </c>
       <c r="E160" s="15" t="n">
-        <v>-0.0213</v>
+        <v>-0.016</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>609300</v>
+        <v>813800</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>1.73</v>
+        <v>0.1</v>
       </c>
       <c r="H160" t="n">
-        <v>29.15</v>
+        <v>40.29</v>
       </c>
       <c r="I160" s="16" t="inlineStr">
         <is>
@@ -7670,10 +7670,10 @@
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>0.958</v>
+        <v>1.278</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>0.993</v>
+        <v>1.316</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7695,19 +7695,19 @@
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>0.0182</v>
+        <v>0.0212</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>565800</v>
+        <v>776300</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="H161" t="n">
-        <v>50.52</v>
+        <v>51.17</v>
       </c>
       <c r="I161" s="13" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>3.374</v>
+        <v>3.375</v>
       </c>
       <c r="K161" s="9" t="n">
         <v>3.229</v>
@@ -7731,39 +7731,39 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>0.835</v>
-      </c>
-      <c r="E162" s="10" t="n">
-        <v>0.0245</v>
+        <v>2.88</v>
+      </c>
+      <c r="E162" s="15" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>562700</v>
+        <v>757700</v>
       </c>
       <c r="G162" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.28</v>
       </c>
       <c r="H162" t="n">
-        <v>35.3</v>
-      </c>
-      <c r="I162" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.68</v>
+      </c>
+      <c r="I162" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>0.863</v>
+        <v>2.988</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>0.924</v>
+        <v>2.859</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7776,39 +7776,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="E163" s="15" t="n">
-        <v>-0.0138</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E163" s="10" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>552500</v>
+        <v>749600</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.29</v>
+        <v>0.41</v>
       </c>
       <c r="H163" t="n">
-        <v>32.78</v>
-      </c>
-      <c r="I163" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.34</v>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>1.567</v>
+        <v>8.102</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>1.644</v>
+        <v>7.955</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7821,39 +7821,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E164" s="15" t="n">
-        <v>-0.0111</v>
+        <v>1.73</v>
+      </c>
+      <c r="E164" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>545200</v>
+        <v>732300</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="H164" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="I164" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.91</v>
+      </c>
+      <c r="I164" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.808</v>
+        <v>1.755</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>1.93</v>
+        <v>1.86</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7866,28 +7866,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="E165" s="10" t="n">
-        <v>0.008</v>
+        <v>0.575</v>
+      </c>
+      <c r="E165" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>523100</v>
+        <v>699000</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="H165" t="n">
-        <v>44.15</v>
+        <v>52.91</v>
       </c>
       <c r="I165" s="16" t="inlineStr">
         <is>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>6.342</v>
+        <v>0.574</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>6.667</v>
+        <v>0.482</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7911,39 +7911,39 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="E166" s="17" t="n">
-        <v>0</v>
+        <v>2.9</v>
+      </c>
+      <c r="E166" s="15" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>514400</v>
+        <v>683200</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.19</v>
+        <v>0.6</v>
       </c>
       <c r="H166" t="n">
-        <v>53.58</v>
-      </c>
-      <c r="I166" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.78</v>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>0.649</v>
+        <v>2.792</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>0.573</v>
+        <v>2.839</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7956,28 +7956,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>5.51</v>
-      </c>
-      <c r="E167" s="10" t="n">
-        <v>0.005500000000000001</v>
+        <v>1.18</v>
+      </c>
+      <c r="E167" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>509100</v>
+        <v>659000</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.13</v>
+        <v>0.67</v>
       </c>
       <c r="H167" t="n">
-        <v>51.35</v>
+        <v>48.65</v>
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>5.486</v>
+        <v>1.184</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>5.379</v>
+        <v>1.188</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8001,28 +8001,28 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>8.31</v>
+        <v>0.7</v>
       </c>
       <c r="E168" s="10" t="n">
-        <v>0.0073</v>
+        <v>0.0145</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>506300</v>
+        <v>648500</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.28</v>
+        <v>0.1</v>
       </c>
       <c r="H168" t="n">
-        <v>56.55</v>
+        <v>42.21</v>
       </c>
       <c r="I168" s="13" t="inlineStr">
         <is>
@@ -8030,16 +8030,466 @@
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>8.103</v>
+        <v>0.714</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>7.955</v>
+        <v>0.774</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>1619</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>DRBHCOM</t>
+        </is>
+      </c>
+      <c r="D169" s="9" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="E169" s="10" t="n">
+        <v>0.0184</v>
+      </c>
+      <c r="F169" s="11" t="n">
+        <v>645100</v>
+      </c>
+      <c r="G169" s="12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="H169" t="n">
+        <v>33.16</v>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J169" s="9" t="n">
+        <v>0.862</v>
+      </c>
+      <c r="K169" s="9" t="n">
+        <v>0.924</v>
+      </c>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" s="14" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>9296</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>RCECAP</t>
+        </is>
+      </c>
+      <c r="D170" s="9" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="E170" s="15" t="n">
+        <v>-0.0213</v>
+      </c>
+      <c r="F170" s="11" t="n">
+        <v>634500</v>
+      </c>
+      <c r="G170" s="12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H170" t="n">
+        <v>29.15</v>
+      </c>
+      <c r="I170" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J170" s="9" t="n">
+        <v>0.958</v>
+      </c>
+      <c r="K170" s="9" t="n">
+        <v>0.993</v>
+      </c>
+      <c r="L170" t="inlineStr"/>
+      <c r="M170" s="14" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>9792</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>SEG</t>
+        </is>
+      </c>
+      <c r="D171" s="9" t="n">
+        <v>0.635</v>
+      </c>
+      <c r="E171" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F171" s="11" t="n">
+        <v>625100</v>
+      </c>
+      <c r="G171" s="12" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="H171" t="n">
+        <v>55</v>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J171" s="9" t="n">
+        <v>0.633</v>
+      </c>
+      <c r="K171" s="9" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="L171" t="inlineStr"/>
+      <c r="M171" s="14" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>5162</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>VSTECS</t>
+        </is>
+      </c>
+      <c r="D172" s="9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="E172" s="15" t="n">
+        <v>-0.0069</v>
+      </c>
+      <c r="F172" s="11" t="n">
+        <v>609200</v>
+      </c>
+      <c r="G172" s="12" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H172" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="I172" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J172" s="9" t="n">
+        <v>1.568</v>
+      </c>
+      <c r="K172" s="9" t="n">
+        <v>1.644</v>
+      </c>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" s="14" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1015</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>AMBANK</t>
+        </is>
+      </c>
+      <c r="D173" s="9" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="E173" s="10" t="n">
+        <v>0.0064</v>
+      </c>
+      <c r="F173" s="11" t="n">
+        <v>605800</v>
+      </c>
+      <c r="G173" s="12" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="H173" t="n">
+        <v>43.52</v>
+      </c>
+      <c r="I173" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J173" s="9" t="n">
+        <v>6.341</v>
+      </c>
+      <c r="K173" s="9" t="n">
+        <v>6.667</v>
+      </c>
+      <c r="L173" t="inlineStr"/>
+      <c r="M173" s="14" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>5005</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>UNISEM</t>
+        </is>
+      </c>
+      <c r="D174" s="9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="E174" s="10" t="n">
+        <v>0.009899999999999999</v>
+      </c>
+      <c r="F174" s="11" t="n">
+        <v>569600</v>
+      </c>
+      <c r="G174" s="12" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="H174" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="I174" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J174" s="9" t="n">
+        <v>4.213</v>
+      </c>
+      <c r="K174" s="9" t="n">
+        <v>4.296</v>
+      </c>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" s="14" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>5357</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>SKYECHIP</t>
+        </is>
+      </c>
+      <c r="D175" s="9" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="E175" s="15" t="n">
+        <v>-0.0109</v>
+      </c>
+      <c r="F175" s="11" t="n">
+        <v>565500</v>
+      </c>
+      <c r="G175" s="12" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="H175" t="n">
+        <v>38.75</v>
+      </c>
+      <c r="I175" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J175" s="9" t="n">
+        <v>2.848</v>
+      </c>
+      <c r="K175" s="9" t="n">
+        <v>2.982</v>
+      </c>
+      <c r="L175" t="inlineStr"/>
+      <c r="M175" s="14" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>5328</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>LWSABAH</t>
+        </is>
+      </c>
+      <c r="D176" s="9" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="E176" s="10" t="n">
+        <v>0.0068</v>
+      </c>
+      <c r="F176" s="11" t="n">
+        <v>553900</v>
+      </c>
+      <c r="G176" s="12" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="H176" t="n">
+        <v>33.87</v>
+      </c>
+      <c r="I176" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J176" s="9" t="n">
+        <v>1.573</v>
+      </c>
+      <c r="K176" s="9" t="n">
+        <v>1.626</v>
+      </c>
+      <c r="L176" t="inlineStr"/>
+      <c r="M176" s="14" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>KEYFIELD</t>
+        </is>
+      </c>
+      <c r="D177" s="9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E177" s="15" t="n">
+        <v>-0.0357</v>
+      </c>
+      <c r="F177" s="11" t="n">
+        <v>538200</v>
+      </c>
+      <c r="G177" s="12" t="n">
+        <v>4.63</v>
+      </c>
+      <c r="H177" t="n">
+        <v>43.54</v>
+      </c>
+      <c r="I177" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J177" s="9" t="n">
+        <v>1.384</v>
+      </c>
+      <c r="K177" s="9" t="n">
+        <v>1.371</v>
+      </c>
+      <c r="L177" t="inlineStr"/>
+      <c r="M177" s="14" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D178" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E178" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="F178" s="11" t="n">
+        <v>530200</v>
+      </c>
+      <c r="G178" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H178" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="I178" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J178" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K178" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="L178" t="inlineStr"/>
+      <c r="M178" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M168"/>
+  <autoFilter ref="A1:M178"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
+++ b/docs/downloads/2026-10-23/bursa-report-2026-10-23.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2026-10-23" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$178</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'2026-10-23'!$A$1:$M$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -464,7 +464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M178"/>
+  <dimension ref="A1:M183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>4.12</v>
+        <v>4.11</v>
       </c>
       <c r="E2" s="4" t="n">
-        <v>0.0173</v>
+        <v>0.0148</v>
       </c>
       <c r="F2" s="5" t="n">
-        <v>4459800</v>
+        <v>4575000</v>
       </c>
       <c r="G2" s="6" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>64.12</v>
+        <v>63.92</v>
       </c>
       <c r="I2" s="7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="J2" s="3" t="n">
-        <v>3.759</v>
+        <v>3.758</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>3.203</v>
+        <v>3.202</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
@@ -598,7 +598,7 @@
       </c>
       <c r="M2" s="8" t="inlineStr">
         <is>
-          <t>SAR转多信号可靠，RSI 64.12偏高但未超买，现价4.12高于50日均线3.203约29%，多头动能较强。</t>
+          <t>SAR转多信号，RSI 63.92未超买，现价高于50日均线约28%，技术面信号偏可靠。</t>
         </is>
       </c>
     </row>
@@ -625,10 +625,10 @@
         <v>0.3</v>
       </c>
       <c r="F3" s="11" t="n">
-        <v>127358900</v>
+        <v>131740200</v>
       </c>
       <c r="G3" s="12" t="n">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="H3" t="n">
         <v>29.97</v>
@@ -670,7 +670,7 @@
         <v>-0.0303</v>
       </c>
       <c r="F4" s="11" t="n">
-        <v>56081400</v>
+        <v>56525700</v>
       </c>
       <c r="G4" s="12" t="n">
         <v>0.68</v>
@@ -715,10 +715,10 @@
         <v>-0.0313</v>
       </c>
       <c r="F5" s="11" t="n">
-        <v>26311500</v>
+        <v>26388600</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="H5" t="n">
         <v>48.33</v>
@@ -745,28 +745,28 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7215</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NIHSIN</t>
+          <t>TANCO</t>
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>0.485</v>
-      </c>
-      <c r="E6" s="10" t="n">
-        <v>0.05429999999999999</v>
+        <v>0.15</v>
+      </c>
+      <c r="E6" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F6" s="11" t="n">
-        <v>22420400</v>
+        <v>24215900</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0.62</v>
+        <v>1.69</v>
       </c>
       <c r="H6" t="n">
-        <v>78.45</v>
+        <v>37.79</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -774,10 +774,10 @@
         </is>
       </c>
       <c r="J6" s="9" t="n">
-        <v>0.414</v>
+        <v>0.154</v>
       </c>
       <c r="K6" s="9" t="n">
-        <v>0.31</v>
+        <v>0.18</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" s="14" t="inlineStr"/>
@@ -790,28 +790,28 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2429</t>
+          <t>7113</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TANCO</t>
+          <t>TOPGLOV</t>
         </is>
       </c>
       <c r="D7" s="9" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>-0.0333</v>
+        <v>0.915</v>
+      </c>
+      <c r="E7" s="10" t="n">
+        <v>0.0398</v>
       </c>
       <c r="F7" s="11" t="n">
-        <v>20915900</v>
+        <v>22578600</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>1.46</v>
+        <v>0.3</v>
       </c>
       <c r="H7" t="n">
-        <v>34.01</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="I7" s="13" t="inlineStr">
         <is>
@@ -819,10 +819,10 @@
         </is>
       </c>
       <c r="J7" s="9" t="n">
-        <v>0.153</v>
+        <v>0.852</v>
       </c>
       <c r="K7" s="9" t="n">
-        <v>0.18</v>
+        <v>0.758</v>
       </c>
       <c r="L7" t="inlineStr"/>
       <c r="M7" s="14" t="inlineStr"/>
@@ -835,39 +835,39 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0193</t>
+          <t>7215</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KINERGY</t>
+          <t>NIHSIN</t>
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0133</v>
+        <v>0.485</v>
+      </c>
+      <c r="E8" s="10" t="n">
+        <v>0.05429999999999999</v>
       </c>
       <c r="F8" s="11" t="n">
-        <v>20817300</v>
+        <v>22443900</v>
       </c>
       <c r="G8" s="12" t="n">
-        <v>2.35</v>
+        <v>0.62</v>
       </c>
       <c r="H8" t="n">
-        <v>18.34</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>78.45</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J8" s="9" t="n">
-        <v>0.39</v>
+        <v>0.414</v>
       </c>
       <c r="K8" s="9" t="n">
-        <v>0.404</v>
+        <v>0.31</v>
       </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" s="14" t="inlineStr"/>
@@ -880,39 +880,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>0193</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TOPGLOV</t>
+          <t>KINERGY</t>
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="E9" s="10" t="n">
-        <v>0.0341</v>
+        <v>0.37</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0133</v>
       </c>
       <c r="F9" s="11" t="n">
-        <v>20464700</v>
+        <v>20817300</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>0.28</v>
+        <v>2.35</v>
       </c>
       <c r="H9" t="n">
-        <v>63.71</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>18.34</v>
+      </c>
+      <c r="I9" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J9" s="9" t="n">
-        <v>0.852</v>
+        <v>0.39</v>
       </c>
       <c r="K9" s="9" t="n">
-        <v>0.758</v>
+        <v>0.404</v>
       </c>
       <c r="L9" t="inlineStr"/>
       <c r="M9" s="14" t="inlineStr"/>
@@ -940,10 +940,10 @@
         <v>-0.03700000000000001</v>
       </c>
       <c r="F10" s="11" t="n">
-        <v>17083400</v>
+        <v>17259800</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
         <v>36.24</v>
@@ -970,39 +970,39 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>0270</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>M&amp;G</t>
+          <t>NATGATE</t>
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0244</v>
       </c>
       <c r="F11" s="11" t="n">
-        <v>15474000</v>
+        <v>15623700</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="H11" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.32</v>
+      </c>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J11" s="9" t="n">
-        <v>0.307</v>
+        <v>1.963</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>0.302</v>
+        <v>1.786</v>
       </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" s="14" t="inlineStr"/>
@@ -1015,39 +1015,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0270</t>
+          <t>5078</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NATGATE</t>
+          <t>M&amp;G</t>
         </is>
       </c>
       <c r="D12" s="9" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0293</v>
+        <v>0.305</v>
+      </c>
+      <c r="E12" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F12" s="11" t="n">
-        <v>15273200</v>
+        <v>15574000</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>0.54</v>
+        <v>0.8</v>
       </c>
       <c r="H12" t="n">
-        <v>54.66</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.4</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J12" s="9" t="n">
-        <v>1.962</v>
+        <v>0.307</v>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1.786</v>
+        <v>0.302</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" s="14" t="inlineStr"/>
@@ -1069,19 +1069,19 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>0.415</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <v>0</v>
+        <v>0.42</v>
+      </c>
+      <c r="E13" s="10" t="n">
+        <v>0.012</v>
       </c>
       <c r="F13" s="11" t="n">
-        <v>14102400</v>
+        <v>14785900</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="H13" t="n">
-        <v>34.84</v>
+        <v>36.72</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -1105,39 +1105,39 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>7192</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>GIIB</t>
+          <t>SUPERMX</t>
         </is>
       </c>
       <c r="D14" s="9" t="n">
-        <v>0.745</v>
+        <v>0.455</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>0.042</v>
+        <v>0.046</v>
       </c>
       <c r="F14" s="11" t="n">
-        <v>13480800</v>
+        <v>14335000</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>0.54</v>
+        <v>0.72</v>
       </c>
       <c r="H14" t="n">
-        <v>84.38</v>
-      </c>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>59.71</v>
+      </c>
+      <c r="I14" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J14" s="9" t="n">
-        <v>0.652</v>
+        <v>0.43</v>
       </c>
       <c r="K14" s="9" t="n">
-        <v>0.555</v>
+        <v>0.381</v>
       </c>
       <c r="L14" t="inlineStr"/>
       <c r="M14" s="14" t="inlineStr"/>
@@ -1150,40 +1150,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>0479</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>SUPERMX</t>
+          <t>RPLANET</t>
         </is>
       </c>
       <c r="D15" s="9" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="E15" s="10" t="n">
-        <v>0.0345</v>
+        <v>0.255</v>
+      </c>
+      <c r="E15" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F15" s="11" t="n">
-        <v>13360500</v>
-      </c>
-      <c r="G15" s="12" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="H15" t="n">
-        <v>58.64</v>
-      </c>
+        <v>14153000</v>
+      </c>
+      <c r="G15" s="12" t="n"/>
       <c r="I15" s="16" t="inlineStr">
         <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J15" s="9" t="n">
-        <v>0.429</v>
-      </c>
-      <c r="K15" s="9" t="n">
-        <v>0.381</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="n"/>
+      <c r="K15" s="9" t="n"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" s="14" t="inlineStr"/>
     </row>
@@ -1195,31 +1186,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0479</t>
+          <t>4715</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>RPLANET</t>
+          <t>GENM</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E16" s="17" t="n">
-        <v>0</v>
+        <v>1.11</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>-0.0431</v>
       </c>
       <c r="F16" s="11" t="n">
-        <v>13202500</v>
-      </c>
-      <c r="G16" s="12" t="n"/>
+        <v>14108700</v>
+      </c>
+      <c r="G16" s="12" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="H16" t="n">
+        <v>17.85</v>
+      </c>
       <c r="I16" s="16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="9" t="n"/>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>1.316</v>
+      </c>
+      <c r="K16" s="9" t="n">
+        <v>1.515</v>
+      </c>
       <c r="L16" t="inlineStr"/>
       <c r="M16" s="14" t="inlineStr"/>
     </row>
@@ -1231,39 +1231,39 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4715</t>
+          <t>7192</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>GENM</t>
+          <t>GIIB</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0345</v>
+        <v>0.745</v>
+      </c>
+      <c r="E17" s="10" t="n">
+        <v>0.042</v>
       </c>
       <c r="F17" s="11" t="n">
-        <v>12936200</v>
+        <v>13486100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>2.61</v>
+        <v>0.54</v>
       </c>
       <c r="H17" t="n">
-        <v>18.28</v>
-      </c>
-      <c r="I17" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>84.38</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J17" s="9" t="n">
-        <v>1.317</v>
+        <v>0.652</v>
       </c>
       <c r="K17" s="9" t="n">
-        <v>1.515</v>
+        <v>0.555</v>
       </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" s="14" t="inlineStr"/>
@@ -1276,39 +1276,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>0187</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>XL</t>
+          <t>BCMALL</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="E18" s="15" t="n">
-        <v>-0.0061</v>
+        <v>0.005</v>
+      </c>
+      <c r="E18" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F18" s="11" t="n">
-        <v>11181200</v>
+        <v>12367400</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>0.7</v>
+        <v>33.99</v>
       </c>
       <c r="H18" t="n">
-        <v>54.27</v>
-      </c>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.02</v>
+      </c>
+      <c r="I18" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J18" s="9" t="n">
-        <v>0.8169999999999999</v>
+        <v>0.005</v>
       </c>
       <c r="K18" s="9" t="n">
-        <v>0.8139999999999999</v>
+        <v>0.006</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" s="14" t="inlineStr"/>
@@ -1336,10 +1336,10 @@
         <v>0.0833</v>
       </c>
       <c r="F19" s="11" t="n">
-        <v>11139400</v>
+        <v>11311400</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>13.87</v>
+        <v>14.09</v>
       </c>
       <c r="H19" t="n">
         <v>55.37</v>
@@ -1375,19 +1375,19 @@
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>0.865</v>
+        <v>0.86</v>
       </c>
       <c r="E20" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>-0.0115</v>
       </c>
       <c r="F20" s="11" t="n">
-        <v>11038000</v>
+        <v>11263400</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="H20" t="n">
-        <v>46.51</v>
+        <v>42.11</v>
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
@@ -1395,7 +1395,7 @@
         </is>
       </c>
       <c r="J20" s="9" t="n">
-        <v>0.868</v>
+        <v>0.867</v>
       </c>
       <c r="K20" s="9" t="n">
         <v>0.869</v>
@@ -1411,28 +1411,28 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HEXTAR</t>
+          <t>XL</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>0.775</v>
-      </c>
-      <c r="E21" s="17" t="n">
-        <v>0</v>
+        <v>0.8149999999999999</v>
+      </c>
+      <c r="E21" s="15" t="n">
+        <v>-0.0121</v>
       </c>
       <c r="F21" s="11" t="n">
-        <v>10558600</v>
+        <v>11181700</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="H21" t="n">
-        <v>50.42</v>
+        <v>49.72</v>
       </c>
       <c r="I21" s="13" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="J21" s="9" t="n">
-        <v>0.774</v>
+        <v>0.8169999999999999</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>0.776</v>
+        <v>0.8139999999999999</v>
       </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" s="14" t="inlineStr"/>
@@ -1456,33 +1456,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0472</t>
+          <t>5151</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ECOGRP</t>
+          <t>HEXTAR</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="E22" s="15" t="n">
-        <v>-0.0526</v>
+        <v>0.775</v>
+      </c>
+      <c r="E22" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F22" s="11" t="n">
-        <v>10557400</v>
+        <v>10898600</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="I22" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="9" t="n"/>
+        <v>0.7</v>
+      </c>
+      <c r="H22" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0.774</v>
+      </c>
+      <c r="K22" s="9" t="n">
+        <v>0.776</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" s="14" t="inlineStr"/>
     </row>
@@ -1494,39 +1501,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3174</t>
+          <t>4723</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>L&amp;G</t>
+          <t>JAKS</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="E23" s="17" t="n">
-        <v>0</v>
+        <v>0.165</v>
+      </c>
+      <c r="E23" s="15" t="n">
+        <v>-0.0294</v>
       </c>
       <c r="F23" s="11" t="n">
-        <v>10503900</v>
+        <v>10674000</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H23" t="n">
-        <v>44.11</v>
-      </c>
-      <c r="I23" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>53.64</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J23" s="9" t="n">
-        <v>0.186</v>
+        <v>0.16</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>0.186</v>
+        <v>0.146</v>
       </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" s="14" t="inlineStr"/>
@@ -1539,40 +1546,33 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>0472</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>JAKS</t>
+          <t>ECOGRP</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="E24" s="15" t="n">
-        <v>-0.0294</v>
+        <v>0.095</v>
+      </c>
+      <c r="E24" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F24" s="11" t="n">
-        <v>10416700</v>
+        <v>10567700</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="H24" t="n">
-        <v>53.64</v>
-      </c>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J24" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="K24" s="9" t="n">
-        <v>0.146</v>
-      </c>
+        <v>0.41</v>
+      </c>
+      <c r="I24" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" s="14" t="inlineStr"/>
     </row>
@@ -1584,28 +1584,28 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0187</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>BCMALL</t>
+          <t>L&amp;G</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>0.005</v>
+        <v>0.18</v>
       </c>
       <c r="E25" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F25" s="11" t="n">
-        <v>10304000</v>
+        <v>10543800</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>28.32</v>
+        <v>0.5</v>
       </c>
       <c r="H25" t="n">
-        <v>47.02</v>
+        <v>44.11</v>
       </c>
       <c r="I25" s="16" t="inlineStr">
         <is>
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="J25" s="9" t="n">
-        <v>0.005</v>
+        <v>0.186</v>
       </c>
       <c r="K25" s="9" t="n">
-        <v>0.006</v>
+        <v>0.186</v>
       </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" s="14" t="inlineStr"/>
@@ -1644,7 +1644,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="11" t="n">
-        <v>9304900</v>
+        <v>9334900</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>0.44</v>
@@ -1683,19 +1683,19 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="E27" s="15" t="n">
-        <v>-0.0048</v>
+        <v>-0.0097</v>
       </c>
       <c r="F27" s="11" t="n">
-        <v>9057800</v>
+        <v>9057900</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>0.82</v>
       </c>
       <c r="H27" t="n">
-        <v>39.55</v>
+        <v>38.59</v>
       </c>
       <c r="I27" s="13" t="inlineStr">
         <is>
@@ -1703,7 +1703,7 @@
         </is>
       </c>
       <c r="J27" s="9" t="n">
-        <v>2.118</v>
+        <v>2.117</v>
       </c>
       <c r="K27" s="9" t="n">
         <v>2.234</v>
@@ -1719,28 +1719,28 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0362</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>HARTA</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>0.135</v>
+        <v>1.16</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>0.08</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="F28" s="11" t="n">
-        <v>8806900</v>
+        <v>8886200</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>17.5</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>64.23</v>
+        <v>60.05</v>
       </c>
       <c r="I28" s="13" t="inlineStr">
         <is>
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="J28" s="9" t="n">
-        <v>0.127</v>
+        <v>1.088</v>
       </c>
       <c r="K28" s="9" t="n">
-        <v>0.129</v>
+        <v>1.054</v>
       </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" s="14" t="inlineStr"/>
@@ -1764,39 +1764,39 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>5398</t>
+          <t>0362</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>GAMUDA</t>
+          <t>ASM</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>4.79</v>
-      </c>
-      <c r="E29" s="15" t="n">
-        <v>-0.0083</v>
+        <v>0.13</v>
+      </c>
+      <c r="E29" s="10" t="n">
+        <v>0.04</v>
       </c>
       <c r="F29" s="11" t="n">
-        <v>8198000</v>
+        <v>8879300</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>0.34</v>
+        <v>17.64</v>
       </c>
       <c r="H29" t="n">
-        <v>46.13</v>
-      </c>
-      <c r="I29" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.19</v>
+      </c>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J29" s="9" t="n">
-        <v>4.87</v>
+        <v>0.127</v>
       </c>
       <c r="K29" s="9" t="n">
-        <v>4.756</v>
+        <v>0.129</v>
       </c>
       <c r="L29" t="inlineStr"/>
       <c r="M29" s="14" t="inlineStr"/>
@@ -1809,39 +1809,39 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0248</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>YEWLEE</t>
+          <t>AAGB</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E30" s="17" t="n">
-        <v>0</v>
+        <v>0.425</v>
+      </c>
+      <c r="E30" s="15" t="n">
+        <v>-0.023</v>
       </c>
       <c r="F30" s="11" t="n">
-        <v>7607100</v>
+        <v>8502900</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>0.72</v>
+        <v>0.51</v>
       </c>
       <c r="H30" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>24.81</v>
+      </c>
+      <c r="I30" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J30" s="9" t="n">
-        <v>0.623</v>
+        <v>0.484</v>
       </c>
       <c r="K30" s="9" t="n">
-        <v>0.617</v>
+        <v>0.63</v>
       </c>
       <c r="L30" t="inlineStr"/>
       <c r="M30" s="14" t="inlineStr"/>
@@ -1854,28 +1854,28 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5398</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>AAGB</t>
+          <t>GAMUDA</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>0.425</v>
+        <v>4.79</v>
       </c>
       <c r="E31" s="15" t="n">
-        <v>-0.023</v>
+        <v>-0.0083</v>
       </c>
       <c r="F31" s="11" t="n">
-        <v>7489900</v>
+        <v>8400400</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>0.45</v>
+        <v>0.34</v>
       </c>
       <c r="H31" t="n">
-        <v>24.81</v>
+        <v>46.13</v>
       </c>
       <c r="I31" s="16" t="inlineStr">
         <is>
@@ -1883,10 +1883,10 @@
         </is>
       </c>
       <c r="J31" s="9" t="n">
-        <v>0.484</v>
+        <v>4.87</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>0.63</v>
+        <v>4.756</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" s="14" t="inlineStr"/>
@@ -1899,28 +1899,28 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>0248</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HARTA</t>
+          <t>YEWLEE</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="E32" s="10" t="n">
-        <v>0.0755</v>
+        <v>0.635</v>
+      </c>
+      <c r="E32" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F32" s="11" t="n">
-        <v>7274000</v>
+        <v>7607100</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>0.82</v>
+        <v>0.72</v>
       </c>
       <c r="H32" t="n">
-        <v>58.03</v>
+        <v>60.81</v>
       </c>
       <c r="I32" s="13" t="inlineStr">
         <is>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.086</v>
+        <v>0.623</v>
       </c>
       <c r="K32" s="9" t="n">
-        <v>1.053</v>
+        <v>0.617</v>
       </c>
       <c r="L32" t="inlineStr"/>
       <c r="M32" s="14" t="inlineStr"/>
@@ -1959,7 +1959,7 @@
         <v>-0.0294</v>
       </c>
       <c r="F33" s="11" t="n">
-        <v>7217300</v>
+        <v>7247300</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>0.92</v>
@@ -2004,7 +2004,7 @@
         <v>-0.0238</v>
       </c>
       <c r="F34" s="11" t="n">
-        <v>6937100</v>
+        <v>6964100</v>
       </c>
       <c r="G34" s="12" t="n">
         <v>0.57</v>
@@ -2034,39 +2034,39 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0096</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>NEXGRAM</t>
+          <t>GENTING</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>0.055</v>
+        <v>1.37</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>0.1</v>
+        <v>0.0148</v>
       </c>
       <c r="F35" s="11" t="n">
-        <v>6804800</v>
+        <v>6951100</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>0.88</v>
+        <v>0.52</v>
       </c>
       <c r="H35" t="n">
-        <v>58.62</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>21.65</v>
+      </c>
+      <c r="I35" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J35" s="9" t="n">
-        <v>0.049</v>
+        <v>1.593</v>
       </c>
       <c r="K35" s="9" t="n">
-        <v>0.047</v>
+        <v>1.885</v>
       </c>
       <c r="L35" t="inlineStr"/>
       <c r="M35" s="14" t="inlineStr"/>
@@ -2079,39 +2079,39 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>0096</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>GENTING</t>
+          <t>NEXGRAM</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>1.37</v>
+        <v>0.055</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>0.0148</v>
+        <v>0.1</v>
       </c>
       <c r="F36" s="11" t="n">
-        <v>6775400</v>
+        <v>6814800</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>0.51</v>
+        <v>0.88</v>
       </c>
       <c r="H36" t="n">
-        <v>21.65</v>
-      </c>
-      <c r="I36" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.62</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J36" s="9" t="n">
-        <v>1.593</v>
+        <v>0.049</v>
       </c>
       <c r="K36" s="9" t="n">
-        <v>1.885</v>
+        <v>0.047</v>
       </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" s="14" t="inlineStr"/>
@@ -2139,7 +2139,7 @@
         <v>0.0435</v>
       </c>
       <c r="F37" s="11" t="n">
-        <v>6336900</v>
+        <v>6346900</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>0.33</v>
@@ -2169,39 +2169,39 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>7204</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>D&amp;O</t>
+          <t>MTTSL</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <v>0.0233</v>
+        <v>1.27</v>
+      </c>
+      <c r="E38" s="15" t="n">
+        <v>-0.007800000000000001</v>
       </c>
       <c r="F38" s="11" t="n">
-        <v>5746300</v>
+        <v>5841200</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>0.59</v>
+        <v>0.84</v>
       </c>
       <c r="H38" t="n">
-        <v>40.39</v>
-      </c>
-      <c r="I38" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.78</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J38" s="9" t="n">
-        <v>0.496</v>
+        <v>1.225</v>
       </c>
       <c r="K38" s="9" t="n">
-        <v>0.468</v>
+        <v>1.204</v>
       </c>
       <c r="L38" t="inlineStr"/>
       <c r="M38" s="14" t="inlineStr"/>
@@ -2214,39 +2214,39 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>5352</t>
+          <t>7204</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MTTSL</t>
+          <t>D&amp;O</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E39" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.445</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <v>0.0349</v>
       </c>
       <c r="F39" s="11" t="n">
-        <v>5582100</v>
+        <v>5753500</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="H39" t="n">
-        <v>58.78</v>
-      </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>41.38</v>
+      </c>
+      <c r="I39" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J39" s="9" t="n">
-        <v>1.225</v>
+        <v>0.496</v>
       </c>
       <c r="K39" s="9" t="n">
-        <v>1.204</v>
+        <v>0.468</v>
       </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" s="14" t="inlineStr"/>
@@ -2259,39 +2259,39 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5311</t>
+          <t>5555</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CEB</t>
+          <t>SUNMED</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E40" s="17" t="n">
-        <v>0</v>
+        <v>2.14</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <v>0.009399999999999999</v>
       </c>
       <c r="F40" s="11" t="n">
-        <v>5080600</v>
+        <v>5140200</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="H40" t="n">
-        <v>38.24</v>
-      </c>
-      <c r="I40" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.48</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J40" s="9" t="n">
-        <v>0.287</v>
+        <v>2.109</v>
       </c>
       <c r="K40" s="9" t="n">
-        <v>0.279</v>
+        <v>2.107</v>
       </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" s="14" t="inlineStr"/>
@@ -2304,39 +2304,39 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>5099</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>SUNMED</t>
+          <t>CAPITALA</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <v>0.009399999999999999</v>
+        <v>0.205</v>
+      </c>
+      <c r="E41" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F41" s="11" t="n">
-        <v>4986600</v>
+        <v>5100300</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>0.44</v>
+        <v>0.46</v>
       </c>
       <c r="H41" t="n">
-        <v>56.48</v>
-      </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>28.46</v>
+      </c>
+      <c r="I41" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J41" s="9" t="n">
-        <v>2.109</v>
+        <v>0.225</v>
       </c>
       <c r="K41" s="9" t="n">
-        <v>2.107</v>
+        <v>0.272</v>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" s="14" t="inlineStr"/>
@@ -2349,28 +2349,28 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>MRCB</t>
+          <t>CEB</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>0.255</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <v>0.02</v>
+        <v>0.26</v>
+      </c>
+      <c r="E42" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F42" s="11" t="n">
-        <v>4878200</v>
+        <v>5080600</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0.59</v>
+        <v>0.48</v>
       </c>
       <c r="H42" t="n">
-        <v>34.07</v>
+        <v>38.24</v>
       </c>
       <c r="I42" s="16" t="inlineStr">
         <is>
@@ -2378,10 +2378,10 @@
         </is>
       </c>
       <c r="J42" s="9" t="n">
-        <v>0.269</v>
+        <v>0.287</v>
       </c>
       <c r="K42" s="9" t="n">
-        <v>0.294</v>
+        <v>0.279</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" s="14" t="inlineStr"/>
@@ -2394,39 +2394,39 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5199</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HIBISCS</t>
+          <t>MRCB</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E43" s="15" t="n">
-        <v>-0.0165</v>
+        <v>0.255</v>
+      </c>
+      <c r="E43" s="10" t="n">
+        <v>0.02</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>4795000</v>
+        <v>4878400</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>1.36</v>
+        <v>0.59</v>
       </c>
       <c r="H43" t="n">
-        <v>61.04</v>
-      </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>34.07</v>
+      </c>
+      <c r="I43" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J43" s="9" t="n">
-        <v>2.275</v>
+        <v>0.269</v>
       </c>
       <c r="K43" s="9" t="n">
-        <v>2.2</v>
+        <v>0.294</v>
       </c>
       <c r="L43" t="inlineStr"/>
       <c r="M43" s="14" t="inlineStr"/>
@@ -2439,33 +2439,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0476</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SLG</t>
+          <t>HIBISCS</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="E44" s="10" t="n">
-        <v>0.0222</v>
+        <v>2.4</v>
+      </c>
+      <c r="E44" s="15" t="n">
+        <v>-0.0123</v>
       </c>
       <c r="F44" s="11" t="n">
-        <v>4671000</v>
+        <v>4835100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="I44" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J44" s="9" t="n"/>
-      <c r="K44" s="9" t="n"/>
+        <v>1.37</v>
+      </c>
+      <c r="H44" t="n">
+        <v>61.98</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J44" s="9" t="n">
+        <v>2.276</v>
+      </c>
+      <c r="K44" s="9" t="n">
+        <v>2.2</v>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="M44" s="14" t="inlineStr"/>
     </row>
@@ -2477,39 +2484,39 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0280</t>
+          <t>0166</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MBN</t>
+          <t>INARI</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>0.17</v>
+        <v>2.51</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>0.0625</v>
+        <v>0.0203</v>
       </c>
       <c r="F45" s="11" t="n">
-        <v>4622400</v>
+        <v>4740000</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>1.49</v>
+        <v>0.25</v>
       </c>
       <c r="H45" t="n">
-        <v>60.81</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>44.53</v>
+      </c>
+      <c r="I45" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J45" s="9" t="n">
-        <v>0.159</v>
+        <v>2.604</v>
       </c>
       <c r="K45" s="9" t="n">
-        <v>0.157</v>
+        <v>2.559</v>
       </c>
       <c r="L45" t="inlineStr"/>
       <c r="M45" s="14" t="inlineStr"/>
@@ -2522,40 +2529,33 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0166</t>
+          <t>0476</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INARI</t>
+          <t>SLG</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>2.51</v>
+        <v>0.23</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>0.0203</v>
+        <v>0.0222</v>
       </c>
       <c r="F46" s="11" t="n">
-        <v>4615400</v>
+        <v>4671000</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0.24</v>
-      </c>
-      <c r="H46" t="n">
-        <v>44.53</v>
+        <v>0.22</v>
       </c>
       <c r="I46" s="16" t="inlineStr">
         <is>
           <t>空头</t>
         </is>
       </c>
-      <c r="J46" s="9" t="n">
-        <v>2.604</v>
-      </c>
-      <c r="K46" s="9" t="n">
-        <v>2.559</v>
-      </c>
+      <c r="J46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" s="14" t="inlineStr"/>
     </row>
@@ -2567,39 +2567,39 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0323</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CREST</t>
+          <t>YTLPOWR</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>0.205</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <v>0.1389</v>
+        <v>5.25</v>
+      </c>
+      <c r="E47" s="15" t="n">
+        <v>-0.0076</v>
       </c>
       <c r="F47" s="11" t="n">
-        <v>4563100</v>
+        <v>4628800</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>5.69</v>
+        <v>0.35</v>
       </c>
       <c r="H47" t="n">
-        <v>67.34</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.82</v>
+      </c>
+      <c r="I47" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J47" s="9" t="n">
-        <v>0.173</v>
+        <v>5.437</v>
       </c>
       <c r="K47" s="9" t="n">
-        <v>0.177</v>
+        <v>5.507</v>
       </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" s="14" t="inlineStr"/>
@@ -2627,10 +2627,10 @@
         <v>-0.0132</v>
       </c>
       <c r="F48" s="11" t="n">
-        <v>4548300</v>
+        <v>4627800</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="H48" t="n">
         <v>27.63</v>
@@ -2657,39 +2657,39 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>0280</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>SIME</t>
+          <t>MBN</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <v>-0.0083</v>
+        <v>0.17</v>
+      </c>
+      <c r="E49" s="10" t="n">
+        <v>0.0625</v>
       </c>
       <c r="F49" s="11" t="n">
-        <v>4360300</v>
+        <v>4622400</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>0.38</v>
+        <v>1.49</v>
       </c>
       <c r="H49" t="n">
-        <v>43.89</v>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>60.81</v>
+      </c>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J49" s="9" t="n">
-        <v>2.438</v>
+        <v>0.159</v>
       </c>
       <c r="K49" s="9" t="n">
-        <v>2.408</v>
+        <v>0.157</v>
       </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" s="14" t="inlineStr"/>
@@ -2702,39 +2702,39 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0453</t>
+          <t>0323</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>EIPOWER</t>
+          <t>CREST</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>0.795</v>
+        <v>0.195</v>
       </c>
       <c r="E50" s="10" t="n">
-        <v>0.0063</v>
+        <v>0.0833</v>
       </c>
       <c r="F50" s="11" t="n">
-        <v>4307800</v>
+        <v>4598000</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>0.67</v>
+        <v>5.73</v>
       </c>
       <c r="H50" t="n">
-        <v>36.9</v>
-      </c>
-      <c r="I50" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>63.68</v>
+      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J50" s="9" t="n">
-        <v>0.889</v>
+        <v>0.172</v>
       </c>
       <c r="K50" s="9" t="n">
-        <v>0.856</v>
+        <v>0.177</v>
       </c>
       <c r="L50" t="inlineStr"/>
       <c r="M50" s="14" t="inlineStr"/>
@@ -2747,39 +2747,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>5099</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CAPITALA</t>
+          <t>PBBANK</t>
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>0.205</v>
+        <v>4.71</v>
       </c>
       <c r="E51" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="11" t="n">
-        <v>4293200</v>
+        <v>4529000</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>0.38</v>
+        <v>0.21</v>
       </c>
       <c r="H51" t="n">
-        <v>28.46</v>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.79</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J51" s="9" t="n">
-        <v>0.225</v>
+        <v>4.725</v>
       </c>
       <c r="K51" s="9" t="n">
-        <v>0.272</v>
+        <v>4.818</v>
       </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" s="14" t="inlineStr"/>
@@ -2792,28 +2792,28 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>6742</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>YTLPOWR</t>
+          <t>SIME</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>5.24</v>
+        <v>2.4</v>
       </c>
       <c r="E52" s="15" t="n">
-        <v>-0.0095</v>
+        <v>-0.004099999999999999</v>
       </c>
       <c r="F52" s="11" t="n">
-        <v>4273700</v>
+        <v>4412500</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>0.33</v>
+        <v>0.39</v>
       </c>
       <c r="H52" t="n">
-        <v>40.48</v>
+        <v>45.1</v>
       </c>
       <c r="I52" s="16" t="inlineStr">
         <is>
@@ -2821,10 +2821,10 @@
         </is>
       </c>
       <c r="J52" s="9" t="n">
-        <v>5.436</v>
+        <v>2.439</v>
       </c>
       <c r="K52" s="9" t="n">
-        <v>5.506</v>
+        <v>2.408</v>
       </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" s="14" t="inlineStr"/>
@@ -2837,39 +2837,39 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>5161</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>PBBANK</t>
+          <t>JCY</t>
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>4.72</v>
+        <v>0.555</v>
       </c>
       <c r="E53" s="10" t="n">
-        <v>0.0021</v>
+        <v>0.0183</v>
       </c>
       <c r="F53" s="11" t="n">
-        <v>4244100</v>
+        <v>4384200</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="H53" t="n">
-        <v>47.8</v>
-      </c>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.37</v>
+      </c>
+      <c r="I53" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J53" s="9" t="n">
-        <v>4.726</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="K53" s="9" t="n">
-        <v>4.818</v>
+        <v>0.545</v>
       </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" s="14" t="inlineStr"/>
@@ -2891,19 +2891,19 @@
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>4.65</v>
+        <v>4.66</v>
       </c>
       <c r="E54" s="10" t="n">
-        <v>0.0356</v>
+        <v>0.0379</v>
       </c>
       <c r="F54" s="11" t="n">
-        <v>4216300</v>
+        <v>4349100</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="H54" t="n">
-        <v>59.24</v>
+        <v>59.54</v>
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         </is>
       </c>
       <c r="J54" s="9" t="n">
-        <v>4.408</v>
+        <v>4.409</v>
       </c>
       <c r="K54" s="9" t="n">
         <v>4.439</v>
@@ -2927,28 +2927,28 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>0453</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>JCY</t>
+          <t>EIPOWER</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>0.555</v>
+        <v>0.795</v>
       </c>
       <c r="E55" s="10" t="n">
-        <v>0.0183</v>
+        <v>0.0063</v>
       </c>
       <c r="F55" s="11" t="n">
-        <v>4164000</v>
+        <v>4330600</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0.2</v>
+        <v>0.67</v>
       </c>
       <c r="H55" t="n">
-        <v>48.37</v>
+        <v>36.9</v>
       </c>
       <c r="I55" s="16" t="inlineStr">
         <is>
@@ -2956,10 +2956,10 @@
         </is>
       </c>
       <c r="J55" s="9" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="K55" s="9" t="n">
-        <v>0.545</v>
+        <v>0.856</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" s="14" t="inlineStr"/>
@@ -2987,10 +2987,10 @@
         <v>0.0159</v>
       </c>
       <c r="F56" s="11" t="n">
-        <v>3802800</v>
+        <v>3869500</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H56" t="n">
         <v>43.38</v>
@@ -3017,28 +3017,28 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>5184</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CYPARK</t>
+          <t>CIMB</t>
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E57" s="10" t="n">
-        <v>0.0068</v>
+        <v>7.12</v>
+      </c>
+      <c r="E57" s="15" t="n">
+        <v>-0.0042</v>
       </c>
       <c r="F57" s="11" t="n">
-        <v>3713400</v>
+        <v>3749600</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>0.28</v>
+        <v>0.23</v>
       </c>
       <c r="H57" t="n">
-        <v>49.92</v>
+        <v>32.22</v>
       </c>
       <c r="I57" s="16" t="inlineStr">
         <is>
@@ -3046,10 +3046,10 @@
         </is>
       </c>
       <c r="J57" s="9" t="n">
-        <v>0.736</v>
+        <v>7.384</v>
       </c>
       <c r="K57" s="9" t="n">
-        <v>0.724</v>
+        <v>7.636</v>
       </c>
       <c r="L57" t="inlineStr"/>
       <c r="M57" s="14" t="inlineStr"/>
@@ -3062,28 +3062,28 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>5184</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CIMB</t>
+          <t>CYPARK</t>
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>7.11</v>
-      </c>
-      <c r="E58" s="15" t="n">
-        <v>-0.005600000000000001</v>
+        <v>0.735</v>
+      </c>
+      <c r="E58" s="10" t="n">
+        <v>0.0068</v>
       </c>
       <c r="F58" s="11" t="n">
-        <v>3666000</v>
+        <v>3713800</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>0.22</v>
+        <v>0.28</v>
       </c>
       <c r="H58" t="n">
-        <v>31.89</v>
+        <v>49.92</v>
       </c>
       <c r="I58" s="16" t="inlineStr">
         <is>
@@ -3091,10 +3091,10 @@
         </is>
       </c>
       <c r="J58" s="9" t="n">
-        <v>7.383</v>
+        <v>0.736</v>
       </c>
       <c r="K58" s="9" t="n">
-        <v>7.636</v>
+        <v>0.724</v>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="M58" s="14" t="inlineStr"/>
@@ -3107,40 +3107,33 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0312</t>
+          <t>0477</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>OFB</t>
+          <t>ECOSYS</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="E59" s="17" t="n">
-        <v>0</v>
+        <v>0.715</v>
+      </c>
+      <c r="E59" s="15" t="n">
+        <v>-0.0069</v>
       </c>
       <c r="F59" s="11" t="n">
-        <v>3664200</v>
+        <v>3709500</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="H59" t="n">
-        <v>76.15000000000001</v>
-      </c>
-      <c r="I59" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
-        </is>
-      </c>
-      <c r="J59" s="9" t="n">
-        <v>0.136</v>
-      </c>
-      <c r="K59" s="9" t="n">
-        <v>0.138</v>
-      </c>
+        <v>0.1</v>
+      </c>
+      <c r="I59" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" s="14" t="inlineStr"/>
     </row>
@@ -3152,39 +3145,39 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0050</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WTS</t>
+          <t>KOSSAN</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="E60" s="15" t="n">
-        <v>-0.0286</v>
+        <v>1.19</v>
+      </c>
+      <c r="E60" s="10" t="n">
+        <v>0.0259</v>
       </c>
       <c r="F60" s="11" t="n">
-        <v>3639200</v>
+        <v>3706300</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="H60" t="n">
-        <v>56.21</v>
-      </c>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>53.45</v>
+      </c>
+      <c r="I60" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J60" s="9" t="n">
-        <v>0.163</v>
+        <v>1.173</v>
       </c>
       <c r="K60" s="9" t="n">
-        <v>0.165</v>
+        <v>1.147</v>
       </c>
       <c r="L60" t="inlineStr"/>
       <c r="M60" s="14" t="inlineStr"/>
@@ -3206,19 +3199,19 @@
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>0.43</v>
+        <v>0.435</v>
       </c>
       <c r="E61" s="15" t="n">
-        <v>-0.0227</v>
+        <v>-0.0114</v>
       </c>
       <c r="F61" s="11" t="n">
-        <v>3605500</v>
+        <v>3695400</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="H61" t="n">
-        <v>51.27</v>
+        <v>52.42</v>
       </c>
       <c r="I61" s="13" t="inlineStr">
         <is>
@@ -3226,7 +3219,7 @@
         </is>
       </c>
       <c r="J61" s="9" t="n">
-        <v>0.428</v>
+        <v>0.429</v>
       </c>
       <c r="K61" s="9" t="n">
         <v>0.418</v>
@@ -3242,39 +3235,39 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>7153</t>
+          <t>0312</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>KOSSAN</t>
+          <t>OFB</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="E62" s="10" t="n">
-        <v>0.0259</v>
+        <v>0.155</v>
+      </c>
+      <c r="E62" s="15" t="n">
+        <v>-0.0313</v>
       </c>
       <c r="F62" s="11" t="n">
-        <v>3533500</v>
+        <v>3675000</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0.55</v>
+        <v>58.58</v>
       </c>
       <c r="H62" t="n">
-        <v>53.45</v>
-      </c>
-      <c r="I62" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>69.20999999999999</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J62" s="9" t="n">
-        <v>1.173</v>
+        <v>0.136</v>
       </c>
       <c r="K62" s="9" t="n">
-        <v>1.147</v>
+        <v>0.138</v>
       </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" s="14" t="inlineStr"/>
@@ -3287,39 +3280,39 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>0455</t>
+          <t>0050</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>BUSCAP</t>
+          <t>WTS</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>0.74</v>
+        <v>0.17</v>
       </c>
       <c r="E63" s="15" t="n">
-        <v>-0.0692</v>
+        <v>-0.0286</v>
       </c>
       <c r="F63" s="11" t="n">
-        <v>3520300</v>
+        <v>3672600</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0.75</v>
+        <v>0.68</v>
       </c>
       <c r="H63" t="n">
-        <v>46.84</v>
-      </c>
-      <c r="I63" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>56.21</v>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J63" s="9" t="n">
-        <v>0.835</v>
+        <v>0.163</v>
       </c>
       <c r="K63" s="9" t="n">
-        <v>0.619</v>
+        <v>0.165</v>
       </c>
       <c r="L63" t="inlineStr"/>
       <c r="M63" s="14" t="inlineStr"/>
@@ -3332,39 +3325,39 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>9113</t>
+          <t>0208</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ICONIC</t>
+          <t>GREATEC</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>0.105</v>
+        <v>2.57</v>
       </c>
       <c r="E64" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="11" t="n">
-        <v>3412900</v>
+        <v>3607900</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H64" t="n">
-        <v>62.33</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.43</v>
+      </c>
+      <c r="I64" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J64" s="9" t="n">
-        <v>0.098</v>
+        <v>2.6</v>
       </c>
       <c r="K64" s="9" t="n">
-        <v>0.083</v>
+        <v>2.607</v>
       </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" s="14" t="inlineStr"/>
@@ -3377,39 +3370,39 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>5210</t>
+          <t>0455</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ARMADA</t>
+          <t>BUSCAP</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="E65" s="17" t="n">
-        <v>0</v>
+        <v>0.74</v>
+      </c>
+      <c r="E65" s="15" t="n">
+        <v>-0.0692</v>
       </c>
       <c r="F65" s="11" t="n">
-        <v>3381500</v>
+        <v>3523600</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="H65" t="n">
-        <v>52.95</v>
-      </c>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.84</v>
+      </c>
+      <c r="I65" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J65" s="9" t="n">
-        <v>0.336</v>
+        <v>0.835</v>
       </c>
       <c r="K65" s="9" t="n">
-        <v>0.343</v>
+        <v>0.619</v>
       </c>
       <c r="L65" t="inlineStr"/>
       <c r="M65" s="14" t="inlineStr"/>
@@ -3422,39 +3415,39 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>0131</t>
+          <t>5246</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>DFX</t>
+          <t>WPRTS</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="E66" s="10" t="n">
-        <v>0.0417</v>
+        <v>6.9</v>
+      </c>
+      <c r="E66" s="15" t="n">
+        <v>-0.0171</v>
       </c>
       <c r="F66" s="11" t="n">
-        <v>3356900</v>
+        <v>3490600</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0.32</v>
+        <v>0.74</v>
       </c>
       <c r="H66" t="n">
-        <v>52.38</v>
-      </c>
-      <c r="I66" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>57.02</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J66" s="9" t="n">
-        <v>0.125</v>
+        <v>6.793</v>
       </c>
       <c r="K66" s="9" t="n">
-        <v>0.104</v>
+        <v>6.822</v>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" s="14" t="inlineStr"/>
@@ -3467,28 +3460,28 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>5246</t>
+          <t>9113</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>WPRTS</t>
+          <t>ICONIC</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="E67" s="15" t="n">
-        <v>-0.0185</v>
+        <v>0.105</v>
+      </c>
+      <c r="E67" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F67" s="11" t="n">
-        <v>3345700</v>
+        <v>3412900</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="H67" t="n">
-        <v>56.38</v>
+        <v>62.33</v>
       </c>
       <c r="I67" s="13" t="inlineStr">
         <is>
@@ -3496,10 +3489,10 @@
         </is>
       </c>
       <c r="J67" s="9" t="n">
-        <v>6.792</v>
+        <v>0.098</v>
       </c>
       <c r="K67" s="9" t="n">
-        <v>6.822</v>
+        <v>0.083</v>
       </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" s="14" t="inlineStr"/>
@@ -3512,28 +3505,28 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>0208</t>
+          <t>0251</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>GREATEC</t>
+          <t>SFPTECH</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="E68" s="15" t="n">
-        <v>-0.007800000000000001</v>
+        <v>0.25</v>
+      </c>
+      <c r="E68" s="10" t="n">
+        <v>0.0204</v>
       </c>
       <c r="F68" s="11" t="n">
-        <v>3305400</v>
+        <v>3396900</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H68" t="n">
-        <v>45.87</v>
+        <v>41.23</v>
       </c>
       <c r="I68" s="16" t="inlineStr">
         <is>
@@ -3541,10 +3534,10 @@
         </is>
       </c>
       <c r="J68" s="9" t="n">
-        <v>2.598</v>
+        <v>0.266</v>
       </c>
       <c r="K68" s="9" t="n">
-        <v>2.607</v>
+        <v>0.286</v>
       </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" s="14" t="inlineStr"/>
@@ -3557,38 +3550,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>0469</t>
+          <t>5210</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>GTA</t>
+          <t>ARMADA</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>0.23</v>
+        <v>0.335</v>
       </c>
       <c r="E69" s="15" t="n">
-        <v>-0.0417</v>
+        <v>-0.0147</v>
       </c>
       <c r="F69" s="11" t="n">
-        <v>3258400</v>
+        <v>3384500</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1.22</v>
+        <v>0.76</v>
       </c>
       <c r="H69" t="n">
-        <v>14.67</v>
-      </c>
-      <c r="I69" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>47.96</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J69" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="K69" s="9" t="n"/>
+        <v>0.335</v>
+      </c>
+      <c r="K69" s="9" t="n">
+        <v>0.343</v>
+      </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" s="14" t="inlineStr"/>
     </row>
@@ -3600,39 +3595,39 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>9679</t>
+          <t>0131</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WCT</t>
+          <t>DFX</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>0.295</v>
+        <v>0.125</v>
       </c>
       <c r="E70" s="10" t="n">
-        <v>0.0172</v>
+        <v>0.0417</v>
       </c>
       <c r="F70" s="11" t="n">
-        <v>3184200</v>
+        <v>3356900</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0.5</v>
+        <v>0.32</v>
       </c>
       <c r="H70" t="n">
-        <v>36.34</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.38</v>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J70" s="9" t="n">
-        <v>0.316</v>
+        <v>0.125</v>
       </c>
       <c r="K70" s="9" t="n">
-        <v>0.361</v>
+        <v>0.104</v>
       </c>
       <c r="L70" t="inlineStr"/>
       <c r="M70" s="14" t="inlineStr"/>
@@ -3645,28 +3640,28 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>8869</t>
+          <t>0469</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>PMETAL</t>
+          <t>GTA</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>6.9</v>
+        <v>0.23</v>
       </c>
       <c r="E71" s="15" t="n">
-        <v>-0.0058</v>
+        <v>-0.0417</v>
       </c>
       <c r="F71" s="11" t="n">
-        <v>3152500</v>
+        <v>3258400</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>0.29</v>
+        <v>1.22</v>
       </c>
       <c r="H71" t="n">
-        <v>39.13</v>
+        <v>14.67</v>
       </c>
       <c r="I71" s="16" t="inlineStr">
         <is>
@@ -3674,11 +3669,9 @@
         </is>
       </c>
       <c r="J71" s="9" t="n">
-        <v>7.097</v>
-      </c>
-      <c r="K71" s="9" t="n">
-        <v>7.521</v>
-      </c>
+        <v>0.26</v>
+      </c>
+      <c r="K71" s="9" t="n"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" s="14" t="inlineStr"/>
     </row>
@@ -3690,28 +3683,28 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>5263</t>
+          <t>9679</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>SUNCON</t>
+          <t>WCT</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="E72" s="15" t="n">
-        <v>-0.0013</v>
+        <v>0.295</v>
+      </c>
+      <c r="E72" s="10" t="n">
+        <v>0.0172</v>
       </c>
       <c r="F72" s="11" t="n">
-        <v>3120600</v>
+        <v>3234200</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>1.15</v>
+        <v>0.51</v>
       </c>
       <c r="H72" t="n">
-        <v>45.65</v>
+        <v>36.34</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -3719,10 +3712,10 @@
         </is>
       </c>
       <c r="J72" s="9" t="n">
-        <v>7.551</v>
+        <v>0.316</v>
       </c>
       <c r="K72" s="9" t="n">
-        <v>7.72</v>
+        <v>0.361</v>
       </c>
       <c r="L72" t="inlineStr"/>
       <c r="M72" s="14" t="inlineStr"/>
@@ -3735,38 +3728,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0471</t>
+          <t>8869</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PIONEER</t>
+          <t>PMETAL</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>0.335</v>
+        <v>6.9</v>
       </c>
       <c r="E73" s="15" t="n">
-        <v>-0.0429</v>
+        <v>-0.0058</v>
       </c>
       <c r="F73" s="11" t="n">
-        <v>3099000</v>
+        <v>3199600</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0.55</v>
+        <v>0.29</v>
       </c>
       <c r="H73" t="n">
-        <v>51.7</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>39.13</v>
+      </c>
+      <c r="I73" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J73" s="9" t="n">
-        <v>0.332</v>
-      </c>
-      <c r="K73" s="9" t="n"/>
+        <v>7.097</v>
+      </c>
+      <c r="K73" s="9" t="n">
+        <v>7.521</v>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="M73" s="14" t="inlineStr"/>
     </row>
@@ -3778,39 +3773,39 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>0251</t>
+          <t>5263</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>SFPTECH</t>
+          <t>SUNCON</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="E74" s="10" t="n">
-        <v>0.0204</v>
+        <v>7.49</v>
+      </c>
+      <c r="E74" s="15" t="n">
+        <v>-0.0013</v>
       </c>
       <c r="F74" s="11" t="n">
-        <v>3081400</v>
+        <v>3154200</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0.51</v>
+        <v>1.16</v>
       </c>
       <c r="H74" t="n">
-        <v>41.23</v>
-      </c>
-      <c r="I74" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.65</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J74" s="9" t="n">
-        <v>0.266</v>
+        <v>7.551</v>
       </c>
       <c r="K74" s="9" t="n">
-        <v>0.286</v>
+        <v>7.72</v>
       </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" s="14" t="inlineStr"/>
@@ -3823,32 +3818,37 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0477</t>
+          <t>0471</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>ECOSYS</t>
+          <t>PIONEER</t>
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>0.71</v>
+        <v>0.335</v>
       </c>
       <c r="E75" s="15" t="n">
-        <v>-0.0139</v>
+        <v>-0.0429</v>
       </c>
       <c r="F75" s="11" t="n">
-        <v>3081000</v>
+        <v>3109400</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I75" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
-        </is>
-      </c>
-      <c r="J75" s="9" t="n"/>
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="H75" t="n">
+        <v>51.7</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
+        </is>
+      </c>
+      <c r="J75" s="9" t="n">
+        <v>0.332</v>
+      </c>
       <c r="K75" s="9" t="n"/>
       <c r="L75" t="inlineStr"/>
       <c r="M75" s="14" t="inlineStr"/>
@@ -3876,10 +3876,10 @@
         <v>0.0052</v>
       </c>
       <c r="F76" s="11" t="n">
-        <v>2904400</v>
+        <v>3015100</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="H76" t="n">
         <v>41.12</v>
@@ -3906,28 +3906,28 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>0321</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>SDCG</t>
+          <t>IOICORP</t>
         </is>
       </c>
       <c r="D77" s="9" t="n">
-        <v>0.825</v>
-      </c>
-      <c r="E77" s="17" t="n">
-        <v>0</v>
+        <v>4.49</v>
+      </c>
+      <c r="E77" s="10" t="n">
+        <v>0.0022</v>
       </c>
       <c r="F77" s="11" t="n">
-        <v>2903400</v>
+        <v>2939200</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>0.55</v>
+        <v>0.34</v>
       </c>
       <c r="H77" t="n">
-        <v>68.73</v>
+        <v>40.1</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="J77" s="9" t="n">
-        <v>0.803</v>
+        <v>4.57</v>
       </c>
       <c r="K77" s="9" t="n">
-        <v>0.777</v>
+        <v>4.641</v>
       </c>
       <c r="L77" t="inlineStr"/>
       <c r="M77" s="14" t="inlineStr"/>
@@ -3951,28 +3951,28 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1961</t>
+          <t>0321</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>IOICORP</t>
+          <t>SDCG</t>
         </is>
       </c>
       <c r="D78" s="9" t="n">
-        <v>4.48</v>
+        <v>0.825</v>
       </c>
       <c r="E78" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F78" s="11" t="n">
-        <v>2878600</v>
+        <v>2919300</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0.33</v>
+        <v>0.55</v>
       </c>
       <c r="H78" t="n">
-        <v>38.96</v>
+        <v>68.73</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -3980,10 +3980,10 @@
         </is>
       </c>
       <c r="J78" s="9" t="n">
-        <v>4.569</v>
+        <v>0.803</v>
       </c>
       <c r="K78" s="9" t="n">
-        <v>4.641</v>
+        <v>0.777</v>
       </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" s="14" t="inlineStr"/>
@@ -3996,39 +3996,39 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>0056</t>
+          <t>5176</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>NCT</t>
+          <t>SUNREIT</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="E79" s="17" t="n">
-        <v>0</v>
+        <v>2.03</v>
+      </c>
+      <c r="E79" s="10" t="n">
+        <v>0.005</v>
       </c>
       <c r="F79" s="11" t="n">
-        <v>2766000</v>
+        <v>2812200</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1.51</v>
+        <v>0.76</v>
       </c>
       <c r="H79" t="n">
-        <v>45.19</v>
-      </c>
-      <c r="I79" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>46.51</v>
+      </c>
+      <c r="I79" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J79" s="9" t="n">
-        <v>0.5610000000000001</v>
+        <v>2.039</v>
       </c>
       <c r="K79" s="9" t="n">
-        <v>0.5620000000000001</v>
+        <v>2.065</v>
       </c>
       <c r="L79" t="inlineStr"/>
       <c r="M79" s="14" t="inlineStr"/>
@@ -4041,28 +4041,28 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>5176</t>
+          <t>0217</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>SUNREIT</t>
+          <t>PWRWELL</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="E80" s="10" t="n">
-        <v>0.005</v>
+        <v>1.06</v>
+      </c>
+      <c r="E80" s="15" t="n">
+        <v>-0.009300000000000001</v>
       </c>
       <c r="F80" s="11" t="n">
-        <v>2729000</v>
+        <v>2769100</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0.74</v>
+        <v>0.82</v>
       </c>
       <c r="H80" t="n">
-        <v>46.51</v>
+        <v>40.12</v>
       </c>
       <c r="I80" s="16" t="inlineStr">
         <is>
@@ -4070,10 +4070,10 @@
         </is>
       </c>
       <c r="J80" s="9" t="n">
-        <v>2.039</v>
+        <v>1.13</v>
       </c>
       <c r="K80" s="9" t="n">
-        <v>2.065</v>
+        <v>1.11</v>
       </c>
       <c r="L80" t="inlineStr"/>
       <c r="M80" s="14" t="inlineStr"/>
@@ -4086,28 +4086,28 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>0292</t>
+          <t>1066</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>JTGROUP</t>
+          <t>RHBBANK</t>
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>1.28</v>
+        <v>7.34</v>
       </c>
       <c r="E81" s="15" t="n">
-        <v>-0.04480000000000001</v>
+        <v>-0.0068</v>
       </c>
       <c r="F81" s="11" t="n">
-        <v>2701000</v>
+        <v>2752700</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0.77</v>
+        <v>0.25</v>
       </c>
       <c r="H81" t="n">
-        <v>55.46</v>
+        <v>40.97</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -4115,10 +4115,10 @@
         </is>
       </c>
       <c r="J81" s="9" t="n">
-        <v>1.244</v>
+        <v>7.42</v>
       </c>
       <c r="K81" s="9" t="n">
-        <v>1.107</v>
+        <v>7.843</v>
       </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" s="14" t="inlineStr"/>
@@ -4131,28 +4131,28 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1066</t>
+          <t>0292</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>RHBBANK</t>
+          <t>JTGROUP</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>7.34</v>
+        <v>1.27</v>
       </c>
       <c r="E82" s="15" t="n">
-        <v>-0.0068</v>
+        <v>-0.0522</v>
       </c>
       <c r="F82" s="11" t="n">
-        <v>2684100</v>
+        <v>2722600</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0.24</v>
+        <v>0.77</v>
       </c>
       <c r="H82" t="n">
-        <v>40.97</v>
+        <v>54.58</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -4160,10 +4160,10 @@
         </is>
       </c>
       <c r="J82" s="9" t="n">
-        <v>7.42</v>
+        <v>1.243</v>
       </c>
       <c r="K82" s="9" t="n">
-        <v>7.843</v>
+        <v>1.107</v>
       </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" s="14" t="inlineStr"/>
@@ -4176,28 +4176,28 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>0217</t>
+          <t>0275</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>PWRWELL</t>
+          <t>OPPSTAR</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="E83" s="17" t="n">
-        <v>0</v>
+        <v>0.59</v>
+      </c>
+      <c r="E83" s="10" t="n">
+        <v>0.008500000000000001</v>
       </c>
       <c r="F83" s="11" t="n">
-        <v>2661600</v>
+        <v>2563800</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0.79</v>
+        <v>0.31</v>
       </c>
       <c r="H83" t="n">
-        <v>41.27</v>
+        <v>36.56</v>
       </c>
       <c r="I83" s="16" t="inlineStr">
         <is>
@@ -4205,10 +4205,10 @@
         </is>
       </c>
       <c r="J83" s="9" t="n">
-        <v>1.131</v>
+        <v>0.653</v>
       </c>
       <c r="K83" s="9" t="n">
-        <v>1.11</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="L83" t="inlineStr"/>
       <c r="M83" s="14" t="inlineStr"/>
@@ -4236,7 +4236,7 @@
         <v>0.0059</v>
       </c>
       <c r="F84" s="11" t="n">
-        <v>2551100</v>
+        <v>2559700</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0.8</v>
@@ -4266,28 +4266,28 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0388</t>
+          <t>7277</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SEMICO</t>
+          <t>DIALOG</t>
         </is>
       </c>
       <c r="D85" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E85" s="15" t="n">
-        <v>-0.008</v>
+        <v>2.07</v>
+      </c>
+      <c r="E85" s="10" t="n">
+        <v>0.0049</v>
       </c>
       <c r="F85" s="11" t="n">
-        <v>2541200</v>
+        <v>2550400</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0.73</v>
+        <v>0.4</v>
       </c>
       <c r="H85" t="n">
-        <v>54.69</v>
+        <v>65.72</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -4295,10 +4295,10 @@
         </is>
       </c>
       <c r="J85" s="9" t="n">
-        <v>0.619</v>
+        <v>1.952</v>
       </c>
       <c r="K85" s="9" t="n">
-        <v>0.609</v>
+        <v>1.958</v>
       </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" s="14" t="inlineStr"/>
@@ -4311,28 +4311,28 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>7277</t>
+          <t>0388</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>DIALOG</t>
+          <t>SEMICO</t>
         </is>
       </c>
       <c r="D86" s="9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="E86" s="10" t="n">
-        <v>0.0049</v>
+        <v>0.62</v>
+      </c>
+      <c r="E86" s="15" t="n">
+        <v>-0.008</v>
       </c>
       <c r="F86" s="11" t="n">
-        <v>2521500</v>
+        <v>2541200</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="H86" t="n">
-        <v>65.72</v>
+        <v>54.69</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -4340,10 +4340,10 @@
         </is>
       </c>
       <c r="J86" s="9" t="n">
-        <v>1.952</v>
+        <v>0.619</v>
       </c>
       <c r="K86" s="9" t="n">
-        <v>1.958</v>
+        <v>0.609</v>
       </c>
       <c r="L86" t="inlineStr"/>
       <c r="M86" s="14" t="inlineStr"/>
@@ -4356,39 +4356,39 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>6888</t>
+          <t>0083</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>AXIATA</t>
+          <t>NOTION</t>
         </is>
       </c>
       <c r="D87" s="9" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="E87" s="10" t="n">
-        <v>0.0124</v>
+        <v>0.54</v>
+      </c>
+      <c r="E87" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F87" s="11" t="n">
-        <v>2426100</v>
+        <v>2528200</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="H87" t="n">
-        <v>49.3</v>
-      </c>
-      <c r="I87" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>36.41</v>
+      </c>
+      <c r="I87" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J87" s="9" t="n">
-        <v>1.625</v>
+        <v>0.614</v>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1.678</v>
+        <v>0.617</v>
       </c>
       <c r="L87" t="inlineStr"/>
       <c r="M87" s="14" t="inlineStr"/>
@@ -4401,28 +4401,28 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>0198</t>
+          <t>0056</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>GDB</t>
+          <t>NCT</t>
         </is>
       </c>
       <c r="D88" s="9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E88" s="15" t="n">
-        <v>-0.009899999999999999</v>
+        <v>0.555</v>
+      </c>
+      <c r="E88" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F88" s="11" t="n">
-        <v>2383300</v>
+        <v>2507200</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0.78</v>
+        <v>1.37</v>
       </c>
       <c r="H88" t="n">
-        <v>75.41</v>
+        <v>45.19</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -4430,10 +4430,10 @@
         </is>
       </c>
       <c r="J88" s="9" t="n">
-        <v>0.443</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="K88" s="9" t="n">
-        <v>0.436</v>
+        <v>0.5620000000000001</v>
       </c>
       <c r="L88" t="inlineStr"/>
       <c r="M88" s="14" t="inlineStr"/>
@@ -4446,28 +4446,28 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>6888</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>MYTECH</t>
+          <t>AXIATA</t>
         </is>
       </c>
       <c r="D89" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E89" s="15" t="n">
-        <v>-0.0208</v>
+        <v>1.63</v>
+      </c>
+      <c r="E89" s="10" t="n">
+        <v>0.0124</v>
       </c>
       <c r="F89" s="11" t="n">
-        <v>2357300</v>
+        <v>2464100</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>20.84</v>
+        <v>0.31</v>
       </c>
       <c r="H89" t="n">
-        <v>46.35</v>
+        <v>49.3</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -4475,10 +4475,10 @@
         </is>
       </c>
       <c r="J89" s="9" t="n">
-        <v>0.236</v>
+        <v>1.625</v>
       </c>
       <c r="K89" s="9" t="n">
-        <v>0.25</v>
+        <v>1.678</v>
       </c>
       <c r="L89" t="inlineStr"/>
       <c r="M89" s="14" t="inlineStr"/>
@@ -4491,39 +4491,39 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>0382</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>FOODIE</t>
+          <t>DATASONIC</t>
         </is>
       </c>
       <c r="D90" s="9" t="n">
-        <v>0.305</v>
-      </c>
-      <c r="E90" s="10" t="n">
-        <v>0.0339</v>
+        <v>0.27</v>
+      </c>
+      <c r="E90" s="15" t="n">
+        <v>-0.0182</v>
       </c>
       <c r="F90" s="11" t="n">
-        <v>2334400</v>
+        <v>2451600</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>2.05</v>
+        <v>0.3</v>
       </c>
       <c r="H90" t="n">
-        <v>51.87</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43.03</v>
+      </c>
+      <c r="I90" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J90" s="9" t="n">
-        <v>0.295</v>
+        <v>0.285</v>
       </c>
       <c r="K90" s="9" t="n">
-        <v>0.329</v>
+        <v>0.283</v>
       </c>
       <c r="L90" t="inlineStr"/>
       <c r="M90" s="14" t="inlineStr"/>
@@ -4536,39 +4536,39 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>0083</t>
+          <t>0198</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>NOTION</t>
+          <t>GDB</t>
         </is>
       </c>
       <c r="D91" s="9" t="n">
-        <v>0.535</v>
+        <v>0.5</v>
       </c>
       <c r="E91" s="15" t="n">
-        <v>-0.0273</v>
+        <v>-0.009899999999999999</v>
       </c>
       <c r="F91" s="11" t="n">
-        <v>2295500</v>
+        <v>2439500</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0.26</v>
+        <v>0.8</v>
       </c>
       <c r="H91" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="I91" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>75.41</v>
+      </c>
+      <c r="I91" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J91" s="9" t="n">
-        <v>0.613</v>
+        <v>0.443</v>
       </c>
       <c r="K91" s="9" t="n">
-        <v>0.617</v>
+        <v>0.436</v>
       </c>
       <c r="L91" t="inlineStr"/>
       <c r="M91" s="14" t="inlineStr"/>
@@ -4581,39 +4581,39 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>0275</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>OPPSTAR</t>
+          <t>MYTECH</t>
         </is>
       </c>
       <c r="D92" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E92" s="17" t="n">
-        <v>0</v>
+        <v>0.235</v>
+      </c>
+      <c r="E92" s="15" t="n">
+        <v>-0.0208</v>
       </c>
       <c r="F92" s="11" t="n">
-        <v>2277700</v>
+        <v>2357300</v>
       </c>
       <c r="G92" s="12" t="n">
-        <v>0.27</v>
+        <v>20.84</v>
       </c>
       <c r="H92" t="n">
-        <v>35.4</v>
-      </c>
-      <c r="I92" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>46.35</v>
+      </c>
+      <c r="I92" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J92" s="9" t="n">
-        <v>0.652</v>
+        <v>0.236</v>
       </c>
       <c r="K92" s="9" t="n">
-        <v>0.6850000000000001</v>
+        <v>0.25</v>
       </c>
       <c r="L92" t="inlineStr"/>
       <c r="M92" s="14" t="inlineStr"/>
@@ -4626,39 +4626,39 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>8907</t>
+          <t>0382</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>EG</t>
+          <t>FOODIE</t>
         </is>
       </c>
       <c r="D93" s="9" t="n">
-        <v>1.55</v>
+        <v>0.305</v>
       </c>
       <c r="E93" s="10" t="n">
-        <v>0.006500000000000001</v>
+        <v>0.0339</v>
       </c>
       <c r="F93" s="11" t="n">
-        <v>2208200</v>
+        <v>2338300</v>
       </c>
       <c r="G93" s="12" t="n">
-        <v>0.36</v>
+        <v>2.06</v>
       </c>
       <c r="H93" t="n">
-        <v>33.77</v>
-      </c>
-      <c r="I93" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>51.87</v>
+      </c>
+      <c r="I93" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J93" s="9" t="n">
-        <v>1.667</v>
+        <v>0.295</v>
       </c>
       <c r="K93" s="9" t="n">
-        <v>1.747</v>
+        <v>0.329</v>
       </c>
       <c r="L93" t="inlineStr"/>
       <c r="M93" s="14" t="inlineStr"/>
@@ -4671,28 +4671,28 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>5356</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>STRATUS</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="D94" s="9" t="n">
-        <v>2.33</v>
+        <v>1.54</v>
       </c>
       <c r="E94" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F94" s="11" t="n">
-        <v>2191800</v>
+        <v>2260500</v>
       </c>
       <c r="G94" s="12" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="H94" t="n">
-        <v>31.89</v>
+        <v>32.27</v>
       </c>
       <c r="I94" s="16" t="inlineStr">
         <is>
@@ -4700,10 +4700,10 @@
         </is>
       </c>
       <c r="J94" s="9" t="n">
-        <v>2.654</v>
+        <v>1.666</v>
       </c>
       <c r="K94" s="9" t="n">
-        <v>2.84</v>
+        <v>1.746</v>
       </c>
       <c r="L94" t="inlineStr"/>
       <c r="M94" s="14" t="inlineStr"/>
@@ -4716,28 +4716,28 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>0236</t>
+          <t>5356</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>RAMSSOL</t>
+          <t>STRATUS</t>
         </is>
       </c>
       <c r="D95" s="9" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="E95" s="15" t="n">
-        <v>-0.0131</v>
+        <v>2.35</v>
+      </c>
+      <c r="E95" s="10" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F95" s="11" t="n">
-        <v>2168700</v>
+        <v>2216300</v>
       </c>
       <c r="G95" s="12" t="n">
-        <v>0.28</v>
+        <v>0.39</v>
       </c>
       <c r="H95" t="n">
-        <v>45.88</v>
+        <v>33.1</v>
       </c>
       <c r="I95" s="16" t="inlineStr">
         <is>
@@ -4745,10 +4745,10 @@
         </is>
       </c>
       <c r="J95" s="9" t="n">
-        <v>0.768</v>
+        <v>2.656</v>
       </c>
       <c r="K95" s="9" t="n">
-        <v>0.771</v>
+        <v>2.84</v>
       </c>
       <c r="L95" t="inlineStr"/>
       <c r="M95" s="14" t="inlineStr"/>
@@ -4761,28 +4761,28 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>3336</t>
+          <t>0236</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IJM</t>
+          <t>RAMSSOL</t>
         </is>
       </c>
       <c r="D96" s="9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="E96" s="17" t="n">
-        <v>0</v>
+        <v>0.755</v>
+      </c>
+      <c r="E96" s="15" t="n">
+        <v>-0.0131</v>
       </c>
       <c r="F96" s="11" t="n">
-        <v>2111400</v>
+        <v>2168700</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>0.18</v>
+        <v>0.28</v>
       </c>
       <c r="H96" t="n">
-        <v>46.45</v>
+        <v>45.88</v>
       </c>
       <c r="I96" s="16" t="inlineStr">
         <is>
@@ -4790,10 +4790,10 @@
         </is>
       </c>
       <c r="J96" s="9" t="n">
-        <v>2.741</v>
+        <v>0.768</v>
       </c>
       <c r="K96" s="9" t="n">
-        <v>2.747</v>
+        <v>0.771</v>
       </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" s="14" t="inlineStr"/>
@@ -4806,28 +4806,28 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>5216</t>
+          <t>3336</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>DATASONIC</t>
+          <t>IJM</t>
         </is>
       </c>
       <c r="D97" s="9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="E97" s="15" t="n">
-        <v>-0.0182</v>
+        <v>2.7</v>
+      </c>
+      <c r="E97" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F97" s="11" t="n">
-        <v>2109900</v>
+        <v>2114500</v>
       </c>
       <c r="G97" s="12" t="n">
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="H97" t="n">
-        <v>43.03</v>
+        <v>46.45</v>
       </c>
       <c r="I97" s="16" t="inlineStr">
         <is>
@@ -4835,10 +4835,10 @@
         </is>
       </c>
       <c r="J97" s="9" t="n">
-        <v>0.285</v>
+        <v>2.741</v>
       </c>
       <c r="K97" s="9" t="n">
-        <v>0.283</v>
+        <v>2.747</v>
       </c>
       <c r="L97" t="inlineStr"/>
       <c r="M97" s="14" t="inlineStr"/>
@@ -4896,39 +4896,39 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>0318</t>
+          <t>0104</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ELRIDGE</t>
+          <t>GENETEC</t>
         </is>
       </c>
       <c r="D99" s="9" t="n">
-        <v>0.97</v>
+        <v>0.265</v>
       </c>
       <c r="E99" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F99" s="11" t="n">
-        <v>1912300</v>
+        <v>1978600</v>
       </c>
       <c r="G99" s="12" t="n">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="H99" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="I99" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>33.64</v>
+      </c>
+      <c r="I99" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J99" s="9" t="n">
-        <v>0.9409999999999999</v>
+        <v>0.3</v>
       </c>
       <c r="K99" s="9" t="n">
-        <v>0.889</v>
+        <v>0.326</v>
       </c>
       <c r="L99" t="inlineStr"/>
       <c r="M99" s="14" t="inlineStr"/>
@@ -4941,28 +4941,28 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>0372</t>
+          <t>8583</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CHEEDING</t>
+          <t>MAHSING</t>
         </is>
       </c>
       <c r="D100" s="9" t="n">
-        <v>0.525</v>
-      </c>
-      <c r="E100" s="10" t="n">
-        <v>0.06059999999999999</v>
+        <v>0.91</v>
+      </c>
+      <c r="E100" s="15" t="n">
+        <v>-0.005500000000000001</v>
       </c>
       <c r="F100" s="11" t="n">
-        <v>1840100</v>
+        <v>1931900</v>
       </c>
       <c r="G100" s="12" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="H100" t="n">
-        <v>39.27</v>
+        <v>24.64</v>
       </c>
       <c r="I100" s="16" t="inlineStr">
         <is>
@@ -4970,10 +4970,10 @@
         </is>
       </c>
       <c r="J100" s="9" t="n">
-        <v>0.556</v>
+        <v>0.952</v>
       </c>
       <c r="K100" s="9" t="n">
-        <v>0.592</v>
+        <v>1.036</v>
       </c>
       <c r="L100" t="inlineStr"/>
       <c r="M100" s="14" t="inlineStr"/>
@@ -4986,39 +4986,39 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>0318</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>MAHSING</t>
+          <t>ELRIDGE</t>
         </is>
       </c>
       <c r="D101" s="9" t="n">
-        <v>0.915</v>
+        <v>0.97</v>
       </c>
       <c r="E101" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F101" s="11" t="n">
-        <v>1826100</v>
+        <v>1913800</v>
       </c>
       <c r="G101" s="12" t="n">
-        <v>0.42</v>
+        <v>0.36</v>
       </c>
       <c r="H101" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="I101" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>64.89</v>
+      </c>
+      <c r="I101" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J101" s="9" t="n">
-        <v>0.952</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="K101" s="9" t="n">
-        <v>1.036</v>
+        <v>0.889</v>
       </c>
       <c r="L101" t="inlineStr"/>
       <c r="M101" s="14" t="inlineStr"/>
@@ -5031,39 +5031,39 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>0104</t>
+          <t>0393</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>GENETEC</t>
+          <t>TEAMSTR</t>
         </is>
       </c>
       <c r="D102" s="9" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="E102" s="15" t="n">
-        <v>-0.0189</v>
+        <v>0.23</v>
+      </c>
+      <c r="E102" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F102" s="11" t="n">
-        <v>1771400</v>
+        <v>1884700</v>
       </c>
       <c r="G102" s="12" t="n">
-        <v>0.27</v>
+        <v>1.39</v>
       </c>
       <c r="H102" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="I102" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.11</v>
+      </c>
+      <c r="I102" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J102" s="9" t="n">
-        <v>0.299</v>
+        <v>0.23</v>
       </c>
       <c r="K102" s="9" t="n">
-        <v>0.326</v>
+        <v>0.238</v>
       </c>
       <c r="L102" t="inlineStr"/>
       <c r="M102" s="14" t="inlineStr"/>
@@ -5076,28 +5076,28 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>0045</t>
+          <t>5296</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>SSB8</t>
+          <t>MRDIY</t>
         </is>
       </c>
       <c r="D103" s="9" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="E103" s="17" t="n">
-        <v>0</v>
+        <v>1.15</v>
+      </c>
+      <c r="E103" s="15" t="n">
+        <v>-0.0086</v>
       </c>
       <c r="F103" s="11" t="n">
-        <v>1766200</v>
+        <v>1848600</v>
       </c>
       <c r="G103" s="12" t="n">
-        <v>0.53</v>
+        <v>0.24</v>
       </c>
       <c r="H103" t="n">
-        <v>45.21</v>
+        <v>33.76</v>
       </c>
       <c r="I103" s="16" t="inlineStr">
         <is>
@@ -5105,10 +5105,10 @@
         </is>
       </c>
       <c r="J103" s="9" t="n">
-        <v>0.634</v>
+        <v>1.21</v>
       </c>
       <c r="K103" s="9" t="n">
-        <v>0.621</v>
+        <v>1.297</v>
       </c>
       <c r="L103" t="inlineStr"/>
       <c r="M103" s="14" t="inlineStr"/>
@@ -5121,28 +5121,28 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>0372</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>DAYANG</t>
+          <t>CHEEDING</t>
         </is>
       </c>
       <c r="D104" s="9" t="n">
-        <v>1.3</v>
+        <v>0.525</v>
       </c>
       <c r="E104" s="10" t="n">
-        <v>0.007800000000000001</v>
+        <v>0.06059999999999999</v>
       </c>
       <c r="F104" s="11" t="n">
-        <v>1715500</v>
+        <v>1840500</v>
       </c>
       <c r="G104" s="12" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="H104" t="n">
-        <v>34.14</v>
+        <v>39.27</v>
       </c>
       <c r="I104" s="16" t="inlineStr">
         <is>
@@ -5150,10 +5150,10 @@
         </is>
       </c>
       <c r="J104" s="9" t="n">
-        <v>1.362</v>
+        <v>0.556</v>
       </c>
       <c r="K104" s="9" t="n">
-        <v>1.443</v>
+        <v>0.592</v>
       </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" s="14" t="inlineStr"/>
@@ -5166,39 +5166,39 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>0393</t>
+          <t>0045</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>TEAMSTR</t>
+          <t>SSB8</t>
         </is>
       </c>
       <c r="D105" s="9" t="n">
-        <v>0.23</v>
+        <v>0.62</v>
       </c>
       <c r="E105" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F105" s="11" t="n">
-        <v>1709900</v>
+        <v>1766500</v>
       </c>
       <c r="G105" s="12" t="n">
-        <v>1.26</v>
+        <v>0.53</v>
       </c>
       <c r="H105" t="n">
-        <v>48.11</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>45.21</v>
+      </c>
+      <c r="I105" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J105" s="9" t="n">
-        <v>0.23</v>
+        <v>0.634</v>
       </c>
       <c r="K105" s="9" t="n">
-        <v>0.238</v>
+        <v>0.621</v>
       </c>
       <c r="L105" t="inlineStr"/>
       <c r="M105" s="14" t="inlineStr"/>
@@ -5211,28 +5211,28 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>MRDIY</t>
+          <t>DAYANG</t>
         </is>
       </c>
       <c r="D106" s="9" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="E106" s="17" t="n">
-        <v>0</v>
+        <v>1.3</v>
+      </c>
+      <c r="E106" s="10" t="n">
+        <v>0.007800000000000001</v>
       </c>
       <c r="F106" s="11" t="n">
-        <v>1705900</v>
+        <v>1722700</v>
       </c>
       <c r="G106" s="12" t="n">
-        <v>0.22</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="H106" t="n">
-        <v>35.09</v>
+        <v>34.14</v>
       </c>
       <c r="I106" s="16" t="inlineStr">
         <is>
@@ -5240,10 +5240,10 @@
         </is>
       </c>
       <c r="J106" s="9" t="n">
-        <v>1.211</v>
+        <v>1.362</v>
       </c>
       <c r="K106" s="9" t="n">
-        <v>1.297</v>
+        <v>1.443</v>
       </c>
       <c r="L106" t="inlineStr"/>
       <c r="M106" s="14" t="inlineStr"/>
@@ -5301,39 +5301,39 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>0390</t>
+          <t>2852</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>ISF</t>
+          <t>CMSB</t>
         </is>
       </c>
       <c r="D108" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E108" s="10" t="n">
-        <v>0.0122</v>
+        <v>0.86</v>
+      </c>
+      <c r="E108" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F108" s="11" t="n">
-        <v>1613000</v>
+        <v>1663100</v>
       </c>
       <c r="G108" s="12" t="n">
-        <v>0.42</v>
+        <v>0.47</v>
       </c>
       <c r="H108" t="n">
-        <v>52.32</v>
-      </c>
-      <c r="I108" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>30.9</v>
+      </c>
+      <c r="I108" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J108" s="9" t="n">
-        <v>0.825</v>
+        <v>0.895</v>
       </c>
       <c r="K108" s="9" t="n">
-        <v>0.796</v>
+        <v>0.96</v>
       </c>
       <c r="L108" t="inlineStr"/>
       <c r="M108" s="14" t="inlineStr"/>
@@ -5346,39 +5346,39 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>0390</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>ISF</t>
         </is>
       </c>
       <c r="D109" s="9" t="n">
-        <v>0.795</v>
-      </c>
-      <c r="E109" s="15" t="n">
-        <v>-0.0185</v>
+        <v>0.83</v>
+      </c>
+      <c r="E109" s="10" t="n">
+        <v>0.0122</v>
       </c>
       <c r="F109" s="11" t="n">
-        <v>1586500</v>
+        <v>1642500</v>
       </c>
       <c r="G109" s="12" t="n">
-        <v>0.71</v>
+        <v>0.42</v>
       </c>
       <c r="H109" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="I109" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>52.32</v>
+      </c>
+      <c r="I109" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J109" s="9" t="n">
-        <v>0.89</v>
+        <v>0.825</v>
       </c>
       <c r="K109" s="9" t="n">
-        <v>1.048</v>
+        <v>0.796</v>
       </c>
       <c r="L109" t="inlineStr"/>
       <c r="M109" s="14" t="inlineStr"/>
@@ -5391,28 +5391,28 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>0245</t>
+          <t>0368</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MNHLDG</t>
+          <t>OXB</t>
         </is>
       </c>
       <c r="D110" s="9" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="E110" s="15" t="n">
-        <v>-0.0135</v>
+        <v>0.585</v>
+      </c>
+      <c r="E110" s="10" t="n">
+        <v>0.0086</v>
       </c>
       <c r="F110" s="11" t="n">
-        <v>1586400</v>
+        <v>1628500</v>
       </c>
       <c r="G110" s="12" t="n">
-        <v>0.48</v>
+        <v>0.34</v>
       </c>
       <c r="H110" t="n">
-        <v>43.89</v>
+        <v>62.13</v>
       </c>
       <c r="I110" s="16" t="inlineStr">
         <is>
@@ -5420,10 +5420,10 @@
         </is>
       </c>
       <c r="J110" s="9" t="n">
-        <v>3.799</v>
+        <v>0.536</v>
       </c>
       <c r="K110" s="9" t="n">
-        <v>3.731</v>
+        <v>0.482</v>
       </c>
       <c r="L110" t="inlineStr"/>
       <c r="M110" s="14" t="inlineStr"/>
@@ -5436,28 +5436,28 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>0245</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>MUHIBAH</t>
+          <t>MNHLDG</t>
         </is>
       </c>
       <c r="D111" s="9" t="n">
-        <v>0.4</v>
+        <v>3.67</v>
       </c>
       <c r="E111" s="15" t="n">
-        <v>-0.0123</v>
+        <v>-0.008100000000000001</v>
       </c>
       <c r="F111" s="11" t="n">
-        <v>1581100</v>
+        <v>1624700</v>
       </c>
       <c r="G111" s="12" t="n">
-        <v>2.92</v>
+        <v>0.49</v>
       </c>
       <c r="H111" t="n">
-        <v>14.63</v>
+        <v>44.65</v>
       </c>
       <c r="I111" s="16" t="inlineStr">
         <is>
@@ -5465,10 +5465,10 @@
         </is>
       </c>
       <c r="J111" s="9" t="n">
-        <v>0.428</v>
+        <v>3.801</v>
       </c>
       <c r="K111" s="9" t="n">
-        <v>0.449</v>
+        <v>3.732</v>
       </c>
       <c r="L111" t="inlineStr"/>
       <c r="M111" s="14" t="inlineStr"/>
@@ -5490,19 +5490,19 @@
         </is>
       </c>
       <c r="D112" s="9" t="n">
-        <v>0.725</v>
+        <v>0.73</v>
       </c>
       <c r="E112" s="10" t="n">
-        <v>0.0069</v>
+        <v>0.0139</v>
       </c>
       <c r="F112" s="11" t="n">
-        <v>1520900</v>
+        <v>1593600</v>
       </c>
       <c r="G112" s="12" t="n">
-        <v>0.25</v>
+        <v>0.27</v>
       </c>
       <c r="H112" t="n">
-        <v>49.36</v>
+        <v>50.16</v>
       </c>
       <c r="I112" s="16" t="inlineStr">
         <is>
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="J112" s="9" t="n">
-        <v>0.738</v>
+        <v>0.739</v>
       </c>
       <c r="K112" s="9" t="n">
         <v>0.6870000000000001</v>
@@ -5526,28 +5526,28 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>4863</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>TM</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D113" s="9" t="n">
-        <v>7.72</v>
+        <v>0.795</v>
       </c>
       <c r="E113" s="15" t="n">
-        <v>-0.0077</v>
+        <v>-0.0185</v>
       </c>
       <c r="F113" s="11" t="n">
-        <v>1509000</v>
+        <v>1586600</v>
       </c>
       <c r="G113" s="12" t="n">
-        <v>0.48</v>
+        <v>0.71</v>
       </c>
       <c r="H113" t="n">
-        <v>42.32</v>
+        <v>24.06</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -5555,10 +5555,10 @@
         </is>
       </c>
       <c r="J113" s="9" t="n">
-        <v>7.814</v>
+        <v>0.89</v>
       </c>
       <c r="K113" s="9" t="n">
-        <v>7.856</v>
+        <v>1.048</v>
       </c>
       <c r="L113" t="inlineStr"/>
       <c r="M113" s="14" t="inlineStr"/>
@@ -5571,28 +5571,28 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>5000</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HUMEIND</t>
+          <t>MUHIBAH</t>
         </is>
       </c>
       <c r="D114" s="9" t="n">
-        <v>2.54</v>
+        <v>0.4</v>
       </c>
       <c r="E114" s="15" t="n">
-        <v>-0.0155</v>
+        <v>-0.0123</v>
       </c>
       <c r="F114" s="11" t="n">
-        <v>1508500</v>
+        <v>1584000</v>
       </c>
       <c r="G114" s="12" t="n">
-        <v>6.67</v>
+        <v>2.92</v>
       </c>
       <c r="H114" t="n">
-        <v>37.18</v>
+        <v>14.63</v>
       </c>
       <c r="I114" s="16" t="inlineStr">
         <is>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="J114" s="9" t="n">
-        <v>2.61</v>
+        <v>0.428</v>
       </c>
       <c r="K114" s="9" t="n">
-        <v>2.743</v>
+        <v>0.449</v>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" s="14" t="inlineStr"/>
@@ -5616,39 +5616,39 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>7241</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>NGGB</t>
+          <t>TM</t>
         </is>
       </c>
       <c r="D115" s="9" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="E115" s="10" t="n">
-        <v>0.0066</v>
+        <v>7.72</v>
+      </c>
+      <c r="E115" s="15" t="n">
+        <v>-0.0077</v>
       </c>
       <c r="F115" s="11" t="n">
-        <v>1496800</v>
+        <v>1521300</v>
       </c>
       <c r="G115" s="12" t="n">
-        <v>1.21</v>
+        <v>0.49</v>
       </c>
       <c r="H115" t="n">
-        <v>57.65</v>
-      </c>
-      <c r="I115" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.32</v>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J115" s="9" t="n">
-        <v>0.75</v>
+        <v>7.814</v>
       </c>
       <c r="K115" s="9" t="n">
-        <v>0.722</v>
+        <v>7.856</v>
       </c>
       <c r="L115" t="inlineStr"/>
       <c r="M115" s="14" t="inlineStr"/>
@@ -5661,28 +5661,28 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>0368</t>
+          <t>5000</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>OXB</t>
+          <t>HUMEIND</t>
         </is>
       </c>
       <c r="D116" s="9" t="n">
-        <v>0.585</v>
-      </c>
-      <c r="E116" s="10" t="n">
-        <v>0.0086</v>
+        <v>2.54</v>
+      </c>
+      <c r="E116" s="15" t="n">
+        <v>-0.0155</v>
       </c>
       <c r="F116" s="11" t="n">
-        <v>1494200</v>
+        <v>1508900</v>
       </c>
       <c r="G116" s="12" t="n">
-        <v>0.31</v>
+        <v>6.67</v>
       </c>
       <c r="H116" t="n">
-        <v>62.13</v>
+        <v>37.18</v>
       </c>
       <c r="I116" s="16" t="inlineStr">
         <is>
@@ -5690,10 +5690,10 @@
         </is>
       </c>
       <c r="J116" s="9" t="n">
-        <v>0.536</v>
+        <v>2.61</v>
       </c>
       <c r="K116" s="9" t="n">
-        <v>0.482</v>
+        <v>2.743</v>
       </c>
       <c r="L116" t="inlineStr"/>
       <c r="M116" s="14" t="inlineStr"/>
@@ -5706,28 +5706,28 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>7247</t>
+          <t>7241</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>SCGM</t>
+          <t>NGGB</t>
         </is>
       </c>
       <c r="D117" s="9" t="n">
-        <v>0.355</v>
+        <v>0.76</v>
       </c>
       <c r="E117" s="10" t="n">
-        <v>0.0441</v>
+        <v>0.0066</v>
       </c>
       <c r="F117" s="11" t="n">
-        <v>1491600</v>
+        <v>1496800</v>
       </c>
       <c r="G117" s="12" t="n">
-        <v>2.42</v>
+        <v>1.21</v>
       </c>
       <c r="H117" t="n">
-        <v>65.06999999999999</v>
+        <v>57.65</v>
       </c>
       <c r="I117" s="16" t="inlineStr">
         <is>
@@ -5735,10 +5735,10 @@
         </is>
       </c>
       <c r="J117" s="9" t="n">
-        <v>0.336</v>
+        <v>0.75</v>
       </c>
       <c r="K117" s="9" t="n">
-        <v>0.326</v>
+        <v>0.722</v>
       </c>
       <c r="L117" t="inlineStr"/>
       <c r="M117" s="14" t="inlineStr"/>
@@ -5751,28 +5751,28 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>5273</t>
+          <t>7247</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CHINHIN</t>
+          <t>SCGM</t>
         </is>
       </c>
       <c r="D118" s="9" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="E118" s="15" t="n">
-        <v>-0.0097</v>
+        <v>0.355</v>
+      </c>
+      <c r="E118" s="10" t="n">
+        <v>0.0441</v>
       </c>
       <c r="F118" s="11" t="n">
-        <v>1486400</v>
+        <v>1491600</v>
       </c>
       <c r="G118" s="12" t="n">
-        <v>4.45</v>
+        <v>2.42</v>
       </c>
       <c r="H118" t="n">
-        <v>37.52</v>
+        <v>65.06999999999999</v>
       </c>
       <c r="I118" s="16" t="inlineStr">
         <is>
@@ -5780,10 +5780,10 @@
         </is>
       </c>
       <c r="J118" s="9" t="n">
-        <v>2.075</v>
+        <v>0.336</v>
       </c>
       <c r="K118" s="9" t="n">
-        <v>2.082</v>
+        <v>0.326</v>
       </c>
       <c r="L118" t="inlineStr"/>
       <c r="M118" s="14" t="inlineStr"/>
@@ -5796,39 +5796,39 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2852</t>
+          <t>5273</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CMSB</t>
+          <t>CHINHIN</t>
         </is>
       </c>
       <c r="D119" s="9" t="n">
-        <v>0.86</v>
+        <v>2.06</v>
       </c>
       <c r="E119" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F119" s="11" t="n">
-        <v>1463100</v>
+        <v>1486800</v>
       </c>
       <c r="G119" s="12" t="n">
-        <v>0.41</v>
+        <v>4.45</v>
       </c>
       <c r="H119" t="n">
-        <v>30.9</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>43</v>
+      </c>
+      <c r="I119" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J119" s="9" t="n">
-        <v>0.895</v>
+        <v>2.077</v>
       </c>
       <c r="K119" s="9" t="n">
-        <v>0.96</v>
+        <v>2.082</v>
       </c>
       <c r="L119" t="inlineStr"/>
       <c r="M119" s="14" t="inlineStr"/>
@@ -5850,19 +5850,19 @@
         </is>
       </c>
       <c r="D120" s="9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="E120" s="17" t="n">
-        <v>0</v>
+        <v>1.28</v>
+      </c>
+      <c r="E120" s="10" t="n">
+        <v>0.007900000000000001</v>
       </c>
       <c r="F120" s="11" t="n">
-        <v>1452100</v>
+        <v>1480200</v>
       </c>
       <c r="G120" s="12" t="n">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="H120" t="n">
-        <v>51.39</v>
+        <v>53.9</v>
       </c>
       <c r="I120" s="13" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         </is>
       </c>
       <c r="J120" s="9" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
       <c r="K120" s="9" t="n">
         <v>1.272</v>
@@ -5895,19 +5895,19 @@
         </is>
       </c>
       <c r="D121" s="9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="E121" s="17" t="n">
-        <v>0</v>
+        <v>1.26</v>
+      </c>
+      <c r="E121" s="10" t="n">
+        <v>0.008</v>
       </c>
       <c r="F121" s="11" t="n">
-        <v>1420800</v>
+        <v>1430800</v>
       </c>
       <c r="G121" s="12" t="n">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="H121" t="n">
-        <v>50.44</v>
+        <v>51.3</v>
       </c>
       <c r="I121" s="16" t="inlineStr">
         <is>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="J121" s="9" t="n">
-        <v>1.264</v>
+        <v>1.265</v>
       </c>
       <c r="K121" s="9" t="n">
         <v>1.183</v>
@@ -5931,28 +5931,28 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>5271</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PECCA</t>
+          <t>SPSETIA</t>
         </is>
       </c>
       <c r="D122" s="9" t="n">
-        <v>1.39</v>
+        <v>0.705</v>
       </c>
       <c r="E122" s="10" t="n">
-        <v>0.0072</v>
+        <v>0.0217</v>
       </c>
       <c r="F122" s="11" t="n">
-        <v>1349100</v>
+        <v>1391300</v>
       </c>
       <c r="G122" s="12" t="n">
-        <v>0.64</v>
+        <v>0.21</v>
       </c>
       <c r="H122" t="n">
-        <v>58.88</v>
+        <v>43.68</v>
       </c>
       <c r="I122" s="13" t="inlineStr">
         <is>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="J122" s="9" t="n">
-        <v>1.366</v>
+        <v>0.714</v>
       </c>
       <c r="K122" s="9" t="n">
-        <v>1.345</v>
+        <v>0.774</v>
       </c>
       <c r="L122" t="inlineStr"/>
       <c r="M122" s="14" t="inlineStr"/>
@@ -5976,28 +5976,28 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>3859</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>MAGNUM</t>
+          <t>ATECH</t>
         </is>
       </c>
       <c r="D123" s="9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="E123" s="17" t="n">
-        <v>0</v>
+        <v>0.7</v>
+      </c>
+      <c r="E123" s="15" t="n">
+        <v>-0.0541</v>
       </c>
       <c r="F123" s="11" t="n">
-        <v>1335300</v>
+        <v>1361300</v>
       </c>
       <c r="G123" s="12" t="n">
-        <v>2.51</v>
+        <v>0.59</v>
       </c>
       <c r="H123" t="n">
-        <v>41.3</v>
+        <v>37.78</v>
       </c>
       <c r="I123" s="16" t="inlineStr">
         <is>
@@ -6005,10 +6005,10 @@
         </is>
       </c>
       <c r="J123" s="9" t="n">
-        <v>1.183</v>
+        <v>0.761</v>
       </c>
       <c r="K123" s="9" t="n">
-        <v>1.205</v>
+        <v>0.771</v>
       </c>
       <c r="L123" t="inlineStr"/>
       <c r="M123" s="14" t="inlineStr"/>
@@ -6021,39 +6021,39 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>5271</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>ATECH</t>
+          <t>PECCA</t>
         </is>
       </c>
       <c r="D124" s="9" t="n">
-        <v>0.705</v>
-      </c>
-      <c r="E124" s="15" t="n">
-        <v>-0.0473</v>
+        <v>1.39</v>
+      </c>
+      <c r="E124" s="10" t="n">
+        <v>0.0072</v>
       </c>
       <c r="F124" s="11" t="n">
-        <v>1310000</v>
+        <v>1349100</v>
       </c>
       <c r="G124" s="12" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H124" t="n">
-        <v>38.47</v>
-      </c>
-      <c r="I124" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.88</v>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J124" s="9" t="n">
-        <v>0.762</v>
+        <v>1.366</v>
       </c>
       <c r="K124" s="9" t="n">
-        <v>0.771</v>
+        <v>1.345</v>
       </c>
       <c r="L124" t="inlineStr"/>
       <c r="M124" s="14" t="inlineStr"/>
@@ -6066,28 +6066,28 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>0246</t>
+          <t>3859</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CNERGEN</t>
+          <t>MAGNUM</t>
         </is>
       </c>
       <c r="D125" s="9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="E125" s="10" t="n">
-        <v>0.009000000000000001</v>
+        <v>1.17</v>
+      </c>
+      <c r="E125" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F125" s="11" t="n">
-        <v>1234000</v>
+        <v>1342800</v>
       </c>
       <c r="G125" s="12" t="n">
-        <v>0.26</v>
+        <v>2.53</v>
       </c>
       <c r="H125" t="n">
-        <v>57.31</v>
+        <v>41.3</v>
       </c>
       <c r="I125" s="16" t="inlineStr">
         <is>
@@ -6095,10 +6095,10 @@
         </is>
       </c>
       <c r="J125" s="9" t="n">
-        <v>1.08</v>
+        <v>1.183</v>
       </c>
       <c r="K125" s="9" t="n">
-        <v>0.952</v>
+        <v>1.205</v>
       </c>
       <c r="L125" t="inlineStr"/>
       <c r="M125" s="14" t="inlineStr"/>
@@ -6111,28 +6111,28 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>0296</t>
+          <t>0246</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>HEGROUP</t>
+          <t>CNERGEN</t>
         </is>
       </c>
       <c r="D126" s="9" t="n">
-        <v>0.99</v>
-      </c>
-      <c r="E126" s="15" t="n">
-        <v>-0.01</v>
+        <v>1.14</v>
+      </c>
+      <c r="E126" s="10" t="n">
+        <v>0.027</v>
       </c>
       <c r="F126" s="11" t="n">
-        <v>1208700</v>
+        <v>1247400</v>
       </c>
       <c r="G126" s="12" t="n">
-        <v>0.32</v>
+        <v>0.26</v>
       </c>
       <c r="H126" t="n">
-        <v>45.69</v>
+        <v>58.94</v>
       </c>
       <c r="I126" s="16" t="inlineStr">
         <is>
@@ -6140,10 +6140,10 @@
         </is>
       </c>
       <c r="J126" s="9" t="n">
-        <v>1.027</v>
+        <v>1.081</v>
       </c>
       <c r="K126" s="9" t="n">
-        <v>0.968</v>
+        <v>0.952</v>
       </c>
       <c r="L126" t="inlineStr"/>
       <c r="M126" s="14" t="inlineStr"/>
@@ -6156,39 +6156,39 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>0367</t>
+          <t>1155</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>ENPRO</t>
+          <t>MAYBANK</t>
         </is>
       </c>
       <c r="D127" s="9" t="n">
-        <v>0.26</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="E127" s="15" t="n">
-        <v>-0.0189</v>
+        <v>-0.001</v>
       </c>
       <c r="F127" s="11" t="n">
-        <v>1202300</v>
+        <v>1245400</v>
       </c>
       <c r="G127" s="12" t="n">
-        <v>0.64</v>
+        <v>0.1</v>
       </c>
       <c r="H127" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="I127" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>45.78</v>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J127" s="9" t="n">
-        <v>0.263</v>
+        <v>9.987</v>
       </c>
       <c r="K127" s="9" t="n">
-        <v>0.243</v>
+        <v>10.116</v>
       </c>
       <c r="L127" t="inlineStr"/>
       <c r="M127" s="14" t="inlineStr"/>
@@ -6201,28 +6201,28 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>0303</t>
+          <t>0337</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>ALPHA</t>
+          <t>SET</t>
         </is>
       </c>
       <c r="D128" s="9" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="E128" s="15" t="n">
-        <v>-0.0175</v>
+        <v>0.24</v>
+      </c>
+      <c r="E128" s="10" t="n">
+        <v>0.0213</v>
       </c>
       <c r="F128" s="11" t="n">
-        <v>1194800</v>
+        <v>1240200</v>
       </c>
       <c r="G128" s="12" t="n">
-        <v>0.53</v>
+        <v>0.59</v>
       </c>
       <c r="H128" t="n">
-        <v>58.99</v>
+        <v>50.35</v>
       </c>
       <c r="I128" s="13" t="inlineStr">
         <is>
@@ -6230,10 +6230,10 @@
         </is>
       </c>
       <c r="J128" s="9" t="n">
-        <v>0.271</v>
+        <v>0.24</v>
       </c>
       <c r="K128" s="9" t="n">
-        <v>0.258</v>
+        <v>0.241</v>
       </c>
       <c r="L128" t="inlineStr"/>
       <c r="M128" s="14" t="inlineStr"/>
@@ -6246,28 +6246,28 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>0459</t>
+          <t>0296</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>SUM</t>
+          <t>HEGROUP</t>
         </is>
       </c>
       <c r="D129" s="9" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="E129" s="17" t="n">
-        <v>0</v>
+        <v>0.995</v>
+      </c>
+      <c r="E129" s="15" t="n">
+        <v>-0.005</v>
       </c>
       <c r="F129" s="11" t="n">
-        <v>1191600</v>
+        <v>1219200</v>
       </c>
       <c r="G129" s="12" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H129" t="n">
-        <v>37.29</v>
+        <v>46.4</v>
       </c>
       <c r="I129" s="16" t="inlineStr">
         <is>
@@ -6275,10 +6275,10 @@
         </is>
       </c>
       <c r="J129" s="9" t="n">
-        <v>0.721</v>
+        <v>1.027</v>
       </c>
       <c r="K129" s="9" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.968</v>
       </c>
       <c r="L129" t="inlineStr"/>
       <c r="M129" s="14" t="inlineStr"/>
@@ -6291,39 +6291,39 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>0337</t>
+          <t>0367</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>SET</t>
+          <t>ENPRO</t>
         </is>
       </c>
       <c r="D130" s="9" t="n">
-        <v>0.235</v>
-      </c>
-      <c r="E130" s="17" t="n">
-        <v>0</v>
+        <v>0.26</v>
+      </c>
+      <c r="E130" s="15" t="n">
+        <v>-0.0189</v>
       </c>
       <c r="F130" s="11" t="n">
-        <v>1190200</v>
+        <v>1202300</v>
       </c>
       <c r="G130" s="12" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="H130" t="n">
-        <v>46.77</v>
-      </c>
-      <c r="I130" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>49.74</v>
+      </c>
+      <c r="I130" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J130" s="9" t="n">
-        <v>0.239</v>
+        <v>0.263</v>
       </c>
       <c r="K130" s="9" t="n">
-        <v>0.241</v>
+        <v>0.243</v>
       </c>
       <c r="L130" t="inlineStr"/>
       <c r="M130" s="14" t="inlineStr"/>
@@ -6336,28 +6336,28 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>6947</t>
+          <t>0215</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CDB</t>
+          <t>SLVEST</t>
         </is>
       </c>
       <c r="D131" s="9" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="E131" s="15" t="n">
-        <v>-0.028</v>
+        <v>4</v>
+      </c>
+      <c r="E131" s="10" t="n">
+        <v>0.0127</v>
       </c>
       <c r="F131" s="11" t="n">
-        <v>1175800</v>
+        <v>1202000</v>
       </c>
       <c r="G131" s="12" t="n">
-        <v>0.41</v>
+        <v>0.12</v>
       </c>
       <c r="H131" t="n">
-        <v>34.66</v>
+        <v>53.86</v>
       </c>
       <c r="I131" s="16" t="inlineStr">
         <is>
@@ -6365,10 +6365,10 @@
         </is>
       </c>
       <c r="J131" s="9" t="n">
-        <v>2.53</v>
+        <v>3.96</v>
       </c>
       <c r="K131" s="9" t="n">
-        <v>2.653</v>
+        <v>3.623</v>
       </c>
       <c r="L131" t="inlineStr"/>
       <c r="M131" s="14" t="inlineStr"/>
@@ -6381,28 +6381,28 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>0225</t>
+          <t>0459</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>SCGBHD</t>
+          <t>SUM</t>
         </is>
       </c>
       <c r="D132" s="9" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="E132" s="17" t="n">
-        <v>0</v>
+        <v>0.635</v>
+      </c>
+      <c r="E132" s="10" t="n">
+        <v>0.016</v>
       </c>
       <c r="F132" s="11" t="n">
-        <v>1171600</v>
+        <v>1200900</v>
       </c>
       <c r="G132" s="12" t="n">
-        <v>0.13</v>
+        <v>0.23</v>
       </c>
       <c r="H132" t="n">
-        <v>47.29</v>
+        <v>38.84</v>
       </c>
       <c r="I132" s="16" t="inlineStr">
         <is>
@@ -6410,10 +6410,10 @@
         </is>
       </c>
       <c r="J132" s="9" t="n">
-        <v>2.781</v>
+        <v>0.722</v>
       </c>
       <c r="K132" s="9" t="n">
-        <v>2.684</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L132" t="inlineStr"/>
       <c r="M132" s="14" t="inlineStr"/>
@@ -6426,28 +6426,28 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>0215</t>
+          <t>0225</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>SLVEST</t>
+          <t>SCGBHD</t>
         </is>
       </c>
       <c r="D133" s="9" t="n">
-        <v>4</v>
+        <v>2.73</v>
       </c>
       <c r="E133" s="10" t="n">
-        <v>0.0127</v>
+        <v>0.0037</v>
       </c>
       <c r="F133" s="11" t="n">
-        <v>1161900</v>
+        <v>1196700</v>
       </c>
       <c r="G133" s="12" t="n">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="H133" t="n">
-        <v>53.86</v>
+        <v>47.91</v>
       </c>
       <c r="I133" s="16" t="inlineStr">
         <is>
@@ -6455,10 +6455,10 @@
         </is>
       </c>
       <c r="J133" s="9" t="n">
-        <v>3.96</v>
+        <v>2.782</v>
       </c>
       <c r="K133" s="9" t="n">
-        <v>3.623</v>
+        <v>2.684</v>
       </c>
       <c r="L133" t="inlineStr"/>
       <c r="M133" s="14" t="inlineStr"/>
@@ -6471,39 +6471,39 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>0338</t>
+          <t>0303</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>KOPI</t>
+          <t>ALPHA</t>
         </is>
       </c>
       <c r="D134" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E134" s="17" t="n">
-        <v>0</v>
+        <v>0.28</v>
+      </c>
+      <c r="E134" s="15" t="n">
+        <v>-0.0175</v>
       </c>
       <c r="F134" s="11" t="n">
-        <v>1160000</v>
+        <v>1194900</v>
       </c>
       <c r="G134" s="12" t="n">
-        <v>0.38</v>
+        <v>0.53</v>
       </c>
       <c r="H134" t="n">
-        <v>32.09</v>
-      </c>
-      <c r="I134" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>58.99</v>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J134" s="9" t="n">
-        <v>0.874</v>
+        <v>0.271</v>
       </c>
       <c r="K134" s="9" t="n">
-        <v>0.9360000000000001</v>
+        <v>0.258</v>
       </c>
       <c r="L134" t="inlineStr"/>
       <c r="M134" s="14" t="inlineStr"/>
@@ -6516,28 +6516,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>0450</t>
+          <t>6947</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>MFGROUP</t>
+          <t>CDB</t>
         </is>
       </c>
       <c r="D135" s="9" t="n">
-        <v>0.275</v>
-      </c>
-      <c r="E135" s="17" t="n">
-        <v>0</v>
+        <v>2.43</v>
+      </c>
+      <c r="E135" s="15" t="n">
+        <v>-0.028</v>
       </c>
       <c r="F135" s="11" t="n">
-        <v>1153500</v>
+        <v>1193300</v>
       </c>
       <c r="G135" s="12" t="n">
-        <v>1.31</v>
+        <v>0.42</v>
       </c>
       <c r="H135" t="n">
-        <v>50.42</v>
+        <v>34.66</v>
       </c>
       <c r="I135" s="16" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
         </is>
       </c>
       <c r="J135" s="9" t="n">
-        <v>0.276</v>
+        <v>2.53</v>
       </c>
       <c r="K135" s="9" t="n">
-        <v>0.268</v>
+        <v>2.653</v>
       </c>
       <c r="L135" t="inlineStr"/>
       <c r="M135" s="14" t="inlineStr"/>
@@ -6561,39 +6561,39 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>5148</t>
+          <t>0338</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>UEMS</t>
+          <t>KOPI</t>
         </is>
       </c>
       <c r="D136" s="9" t="n">
-        <v>0.455</v>
+        <v>0.83</v>
       </c>
       <c r="E136" s="17" t="n">
         <v>0</v>
       </c>
       <c r="F136" s="11" t="n">
-        <v>1149200</v>
+        <v>1184700</v>
       </c>
       <c r="G136" s="12" t="n">
-        <v>0.16</v>
+        <v>0.39</v>
       </c>
       <c r="H136" t="n">
-        <v>33.01</v>
-      </c>
-      <c r="I136" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>32.09</v>
+      </c>
+      <c r="I136" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J136" s="9" t="n">
-        <v>0.484</v>
+        <v>0.874</v>
       </c>
       <c r="K136" s="9" t="n">
-        <v>0.542</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="M136" s="14" t="inlineStr"/>
@@ -6615,19 +6615,19 @@
         </is>
       </c>
       <c r="D137" s="9" t="n">
-        <v>0.365</v>
-      </c>
-      <c r="E137" s="15" t="n">
-        <v>-0.0135</v>
+        <v>0.37</v>
+      </c>
+      <c r="E137" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F137" s="11" t="n">
-        <v>1148900</v>
+        <v>1173900</v>
       </c>
       <c r="G137" s="12" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="H137" t="n">
-        <v>40.86</v>
+        <v>42.72</v>
       </c>
       <c r="I137" s="16" t="inlineStr">
         <is>
@@ -6651,39 +6651,39 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>0273</t>
+          <t>5148</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>VLB</t>
+          <t>UEMS</t>
         </is>
       </c>
       <c r="D138" s="9" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="E138" s="15" t="n">
-        <v>-0.005699999999999999</v>
+        <v>0.455</v>
+      </c>
+      <c r="E138" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F138" s="11" t="n">
-        <v>1145000</v>
+        <v>1153800</v>
       </c>
       <c r="G138" s="12" t="n">
-        <v>0.6</v>
+        <v>0.16</v>
       </c>
       <c r="H138" t="n">
-        <v>44.95</v>
-      </c>
-      <c r="I138" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.01</v>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J138" s="9" t="n">
-        <v>0.905</v>
+        <v>0.484</v>
       </c>
       <c r="K138" s="9" t="n">
-        <v>0.888</v>
+        <v>0.542</v>
       </c>
       <c r="L138" t="inlineStr"/>
       <c r="M138" s="14" t="inlineStr"/>
@@ -6696,28 +6696,28 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>0127</t>
+          <t>0450</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>JHM</t>
+          <t>MFGROUP</t>
         </is>
       </c>
       <c r="D139" s="9" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="E139" s="10" t="n">
-        <v>0.0192</v>
+        <v>0.275</v>
+      </c>
+      <c r="E139" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F139" s="11" t="n">
-        <v>1104100</v>
+        <v>1153500</v>
       </c>
       <c r="G139" s="12" t="n">
-        <v>0.21</v>
+        <v>1.31</v>
       </c>
       <c r="H139" t="n">
-        <v>46.74</v>
+        <v>50.42</v>
       </c>
       <c r="I139" s="16" t="inlineStr">
         <is>
@@ -6725,10 +6725,10 @@
         </is>
       </c>
       <c r="J139" s="9" t="n">
-        <v>0.55</v>
+        <v>0.276</v>
       </c>
       <c r="K139" s="9" t="n">
-        <v>0.524</v>
+        <v>0.268</v>
       </c>
       <c r="L139" t="inlineStr"/>
       <c r="M139" s="14" t="inlineStr"/>
@@ -6741,28 +6741,28 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>0172</t>
+          <t>0273</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>OCK</t>
+          <t>VLB</t>
         </is>
       </c>
       <c r="D140" s="9" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="E140" s="17" t="n">
-        <v>0</v>
+        <v>0.875</v>
+      </c>
+      <c r="E140" s="15" t="n">
+        <v>-0.005699999999999999</v>
       </c>
       <c r="F140" s="11" t="n">
-        <v>1076200</v>
+        <v>1145000</v>
       </c>
       <c r="G140" s="12" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="H140" t="n">
-        <v>38.76</v>
+        <v>44.95</v>
       </c>
       <c r="I140" s="16" t="inlineStr">
         <is>
@@ -6770,10 +6770,10 @@
         </is>
       </c>
       <c r="J140" s="9" t="n">
-        <v>0.435</v>
+        <v>0.905</v>
       </c>
       <c r="K140" s="9" t="n">
-        <v>0.431</v>
+        <v>0.888</v>
       </c>
       <c r="L140" t="inlineStr"/>
       <c r="M140" s="14" t="inlineStr"/>
@@ -6786,28 +6786,28 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>3905</t>
+          <t>0127</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>MULPHA</t>
+          <t>JHM</t>
         </is>
       </c>
       <c r="D141" s="9" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="E141" s="17" t="n">
-        <v>0</v>
+        <v>0.53</v>
+      </c>
+      <c r="E141" s="10" t="n">
+        <v>0.0192</v>
       </c>
       <c r="F141" s="11" t="n">
-        <v>1064500</v>
+        <v>1110800</v>
       </c>
       <c r="G141" s="12" t="n">
-        <v>6.52</v>
+        <v>0.21</v>
       </c>
       <c r="H141" t="n">
-        <v>39.25</v>
+        <v>46.74</v>
       </c>
       <c r="I141" s="16" t="inlineStr">
         <is>
@@ -6815,10 +6815,10 @@
         </is>
       </c>
       <c r="J141" s="9" t="n">
-        <v>2.682</v>
+        <v>0.55</v>
       </c>
       <c r="K141" s="9" t="n">
-        <v>2.787</v>
+        <v>0.524</v>
       </c>
       <c r="L141" t="inlineStr"/>
       <c r="M141" s="14" t="inlineStr"/>
@@ -6831,28 +6831,28 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>0097</t>
+          <t>0259</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>VITROX</t>
+          <t>SNS</t>
         </is>
       </c>
       <c r="D142" s="9" t="n">
-        <v>10.38</v>
-      </c>
-      <c r="E142" s="15" t="n">
-        <v>-0.0189</v>
+        <v>0.47</v>
+      </c>
+      <c r="E142" s="10" t="n">
+        <v>0.0108</v>
       </c>
       <c r="F142" s="11" t="n">
-        <v>1047700</v>
+        <v>1107600</v>
       </c>
       <c r="G142" s="12" t="n">
-        <v>0.29</v>
+        <v>0.14</v>
       </c>
       <c r="H142" t="n">
-        <v>51.37</v>
+        <v>38.8</v>
       </c>
       <c r="I142" s="16" t="inlineStr">
         <is>
@@ -6860,10 +6860,10 @@
         </is>
       </c>
       <c r="J142" s="9" t="n">
-        <v>10.438</v>
+        <v>0.495</v>
       </c>
       <c r="K142" s="9" t="n">
-        <v>9.847</v>
+        <v>0.518</v>
       </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" s="14" t="inlineStr"/>
@@ -6876,28 +6876,28 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>0146</t>
+          <t>0097</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>JFTECH</t>
+          <t>VITROX</t>
         </is>
       </c>
       <c r="D143" s="9" t="n">
-        <v>0.735</v>
-      </c>
-      <c r="E143" s="17" t="n">
-        <v>0</v>
+        <v>10.4</v>
+      </c>
+      <c r="E143" s="15" t="n">
+        <v>-0.017</v>
       </c>
       <c r="F143" s="11" t="n">
-        <v>1047200</v>
+        <v>1094800</v>
       </c>
       <c r="G143" s="12" t="n">
-        <v>0.35</v>
+        <v>0.31</v>
       </c>
       <c r="H143" t="n">
-        <v>50.4</v>
+        <v>51.74</v>
       </c>
       <c r="I143" s="16" t="inlineStr">
         <is>
@@ -6905,10 +6905,10 @@
         </is>
       </c>
       <c r="J143" s="9" t="n">
-        <v>0.742</v>
+        <v>10.44</v>
       </c>
       <c r="K143" s="9" t="n">
-        <v>0.707</v>
+        <v>9.847</v>
       </c>
       <c r="L143" t="inlineStr"/>
       <c r="M143" s="14" t="inlineStr"/>
@@ -6936,10 +6936,10 @@
         <v>-0.0153</v>
       </c>
       <c r="F144" s="11" t="n">
-        <v>1033800</v>
+        <v>1086600</v>
       </c>
       <c r="G144" s="12" t="n">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="H144" t="n">
         <v>47.22</v>
@@ -6966,39 +6966,39 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>5306</t>
+          <t>0172</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>FFB</t>
+          <t>OCK</t>
         </is>
       </c>
       <c r="D145" s="9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="E145" s="15" t="n">
-        <v>-0.0111</v>
+        <v>0.41</v>
+      </c>
+      <c r="E145" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F145" s="11" t="n">
-        <v>958600</v>
+        <v>1076200</v>
       </c>
       <c r="G145" s="12" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="H145" t="n">
-        <v>42.1</v>
-      </c>
-      <c r="I145" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>38.76</v>
+      </c>
+      <c r="I145" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J145" s="9" t="n">
-        <v>1.808</v>
+        <v>0.435</v>
       </c>
       <c r="K145" s="9" t="n">
-        <v>1.93</v>
+        <v>0.431</v>
       </c>
       <c r="L145" t="inlineStr"/>
       <c r="M145" s="14" t="inlineStr"/>
@@ -7011,28 +7011,28 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>5272</t>
+          <t>3905</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>RANHILL</t>
+          <t>MULPHA</t>
         </is>
       </c>
       <c r="D146" s="9" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="E146" s="15" t="n">
-        <v>-0.019</v>
+        <v>2.6</v>
+      </c>
+      <c r="E146" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F146" s="11" t="n">
-        <v>945900</v>
+        <v>1064500</v>
       </c>
       <c r="G146" s="12" t="n">
-        <v>0.63</v>
+        <v>6.52</v>
       </c>
       <c r="H146" t="n">
-        <v>48.16</v>
+        <v>39.25</v>
       </c>
       <c r="I146" s="16" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="J146" s="9" t="n">
-        <v>3.153</v>
+        <v>2.682</v>
       </c>
       <c r="K146" s="9" t="n">
-        <v>2.942</v>
+        <v>2.787</v>
       </c>
       <c r="L146" t="inlineStr"/>
       <c r="M146" s="14" t="inlineStr"/>
@@ -7056,28 +7056,28 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>5031</t>
+          <t>0146</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>TIMECOM</t>
+          <t>JFTECH</t>
         </is>
       </c>
       <c r="D147" s="9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="E147" s="15" t="n">
-        <v>-0.0076</v>
+        <v>0.735</v>
+      </c>
+      <c r="E147" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F147" s="11" t="n">
-        <v>939400</v>
+        <v>1050500</v>
       </c>
       <c r="G147" s="12" t="n">
-        <v>0.42</v>
+        <v>0.35</v>
       </c>
       <c r="H147" t="n">
-        <v>30.67</v>
+        <v>50.4</v>
       </c>
       <c r="I147" s="16" t="inlineStr">
         <is>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="J147" s="9" t="n">
-        <v>5.483</v>
+        <v>0.742</v>
       </c>
       <c r="K147" s="9" t="n">
-        <v>5.752</v>
+        <v>0.707</v>
       </c>
       <c r="L147" t="inlineStr"/>
       <c r="M147" s="14" t="inlineStr"/>
@@ -7101,28 +7101,28 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>5286</t>
+          <t>7160</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>PENTA</t>
         </is>
       </c>
       <c r="D148" s="9" t="n">
-        <v>6.4</v>
+        <v>5.54</v>
       </c>
       <c r="E148" s="10" t="n">
-        <v>0.0031</v>
+        <v>0.0109</v>
       </c>
       <c r="F148" s="11" t="n">
-        <v>936500</v>
+        <v>995000</v>
       </c>
       <c r="G148" s="12" t="n">
-        <v>0.15</v>
+        <v>0.25</v>
       </c>
       <c r="H148" t="n">
-        <v>53.99</v>
+        <v>52.09</v>
       </c>
       <c r="I148" s="16" t="inlineStr">
         <is>
@@ -7130,10 +7130,10 @@
         </is>
       </c>
       <c r="J148" s="9" t="n">
-        <v>6.265</v>
+        <v>5.489</v>
       </c>
       <c r="K148" s="9" t="n">
-        <v>5.981</v>
+        <v>5.379</v>
       </c>
       <c r="L148" t="inlineStr"/>
       <c r="M148" s="14" t="inlineStr"/>
@@ -7146,28 +7146,28 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>5878</t>
+          <t>5286</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>KPJ</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="D149" s="9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="E149" s="17" t="n">
-        <v>0</v>
+        <v>6.46</v>
+      </c>
+      <c r="E149" s="10" t="n">
+        <v>0.0125</v>
       </c>
       <c r="F149" s="11" t="n">
-        <v>922900</v>
+        <v>981900</v>
       </c>
       <c r="G149" s="12" t="n">
-        <v>0.22</v>
+        <v>0.16</v>
       </c>
       <c r="H149" t="n">
-        <v>33.86</v>
+        <v>54.89</v>
       </c>
       <c r="I149" s="16" t="inlineStr">
         <is>
@@ -7175,10 +7175,10 @@
         </is>
       </c>
       <c r="J149" s="9" t="n">
-        <v>2.491</v>
+        <v>6.271</v>
       </c>
       <c r="K149" s="9" t="n">
-        <v>2.659</v>
+        <v>5.982</v>
       </c>
       <c r="L149" t="inlineStr"/>
       <c r="M149" s="14" t="inlineStr"/>
@@ -7191,39 +7191,39 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>7160</t>
+          <t>5306</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>PENTA</t>
+          <t>FFB</t>
         </is>
       </c>
       <c r="D150" s="9" t="n">
-        <v>5.53</v>
-      </c>
-      <c r="E150" s="10" t="n">
-        <v>0.0091</v>
+        <v>1.78</v>
+      </c>
+      <c r="E150" s="15" t="n">
+        <v>-0.0111</v>
       </c>
       <c r="F150" s="11" t="n">
-        <v>907300</v>
+        <v>964700</v>
       </c>
       <c r="G150" s="12" t="n">
-        <v>0.23</v>
+        <v>0.32</v>
       </c>
       <c r="H150" t="n">
-        <v>51.85</v>
-      </c>
-      <c r="I150" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>42.1</v>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J150" s="9" t="n">
-        <v>5.488</v>
+        <v>1.808</v>
       </c>
       <c r="K150" s="9" t="n">
-        <v>5.379</v>
+        <v>1.93</v>
       </c>
       <c r="L150" t="inlineStr"/>
       <c r="M150" s="14" t="inlineStr"/>
@@ -7236,28 +7236,28 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>5211</t>
+          <t>5317</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>SUNWAY</t>
+          <t>CPETECH</t>
         </is>
       </c>
       <c r="D151" s="9" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="E151" s="15" t="n">
-        <v>-0.009599999999999999</v>
+        <v>1.32</v>
+      </c>
+      <c r="E151" s="10" t="n">
+        <v>0.0394</v>
       </c>
       <c r="F151" s="11" t="n">
-        <v>904100</v>
+        <v>954200</v>
       </c>
       <c r="G151" s="12" t="n">
-        <v>0.22</v>
+        <v>0.33</v>
       </c>
       <c r="H151" t="n">
-        <v>31.76</v>
+        <v>53.61</v>
       </c>
       <c r="I151" s="16" t="inlineStr">
         <is>
@@ -7265,10 +7265,10 @@
         </is>
       </c>
       <c r="J151" s="9" t="n">
-        <v>4.334</v>
+        <v>1.285</v>
       </c>
       <c r="K151" s="9" t="n">
-        <v>4.641</v>
+        <v>1.238</v>
       </c>
       <c r="L151" t="inlineStr"/>
       <c r="M151" s="14" t="inlineStr"/>
@@ -7281,39 +7281,39 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>7293</t>
+          <t>5272</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>YINSON</t>
+          <t>RANHILL</t>
         </is>
       </c>
       <c r="D152" s="9" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="E152" s="17" t="n">
-        <v>0</v>
+        <v>3.09</v>
+      </c>
+      <c r="E152" s="15" t="n">
+        <v>-0.019</v>
       </c>
       <c r="F152" s="11" t="n">
-        <v>898700</v>
+        <v>954100</v>
       </c>
       <c r="G152" s="12" t="n">
-        <v>0.43</v>
+        <v>0.64</v>
       </c>
       <c r="H152" t="n">
-        <v>51.3</v>
-      </c>
-      <c r="I152" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.16</v>
+      </c>
+      <c r="I152" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J152" s="9" t="n">
-        <v>2.112</v>
+        <v>3.153</v>
       </c>
       <c r="K152" s="9" t="n">
-        <v>2.075</v>
+        <v>2.942</v>
       </c>
       <c r="L152" t="inlineStr"/>
       <c r="M152" s="14" t="inlineStr"/>
@@ -7326,39 +7326,39 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>5249</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>IOIPG</t>
+          <t>TIMECOM</t>
         </is>
       </c>
       <c r="D153" s="9" t="n">
-        <v>3.22</v>
+        <v>5.25</v>
       </c>
       <c r="E153" s="15" t="n">
-        <v>-0.0242</v>
+        <v>-0.0076</v>
       </c>
       <c r="F153" s="11" t="n">
-        <v>891300</v>
+        <v>944300</v>
       </c>
       <c r="G153" s="12" t="n">
-        <v>0.16</v>
+        <v>0.42</v>
       </c>
       <c r="H153" t="n">
-        <v>37.01</v>
-      </c>
-      <c r="I153" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>30.67</v>
+      </c>
+      <c r="I153" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J153" s="9" t="n">
-        <v>3.328</v>
+        <v>5.483</v>
       </c>
       <c r="K153" s="9" t="n">
-        <v>3.56</v>
+        <v>5.752</v>
       </c>
       <c r="L153" t="inlineStr"/>
       <c r="M153" s="14" t="inlineStr"/>
@@ -7371,28 +7371,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5878</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>CPETECH</t>
+          <t>KPJ</t>
         </is>
       </c>
       <c r="D154" s="9" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="E154" s="10" t="n">
-        <v>0.0394</v>
+        <v>2.38</v>
+      </c>
+      <c r="E154" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F154" s="11" t="n">
-        <v>886200</v>
+        <v>942500</v>
       </c>
       <c r="G154" s="12" t="n">
-        <v>0.31</v>
+        <v>0.22</v>
       </c>
       <c r="H154" t="n">
-        <v>53.61</v>
+        <v>33.86</v>
       </c>
       <c r="I154" s="16" t="inlineStr">
         <is>
@@ -7400,10 +7400,10 @@
         </is>
       </c>
       <c r="J154" s="9" t="n">
-        <v>1.285</v>
+        <v>2.491</v>
       </c>
       <c r="K154" s="9" t="n">
-        <v>1.238</v>
+        <v>2.659</v>
       </c>
       <c r="L154" t="inlineStr"/>
       <c r="M154" s="14" t="inlineStr"/>
@@ -7416,28 +7416,28 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>0375</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>THMY</t>
+          <t>SUNWAY</t>
         </is>
       </c>
       <c r="D155" s="9" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="E155" s="10" t="n">
-        <v>0.0203</v>
+        <v>4.14</v>
+      </c>
+      <c r="E155" s="15" t="n">
+        <v>-0.009599999999999999</v>
       </c>
       <c r="F155" s="11" t="n">
-        <v>882200</v>
+        <v>920500</v>
       </c>
       <c r="G155" s="12" t="n">
-        <v>0.32</v>
+        <v>0.22</v>
       </c>
       <c r="H155" t="n">
-        <v>47.22</v>
+        <v>31.76</v>
       </c>
       <c r="I155" s="16" t="inlineStr">
         <is>
@@ -7445,10 +7445,10 @@
         </is>
       </c>
       <c r="J155" s="9" t="n">
-        <v>2.065</v>
+        <v>4.334</v>
       </c>
       <c r="K155" s="9" t="n">
-        <v>1.993</v>
+        <v>4.641</v>
       </c>
       <c r="L155" t="inlineStr"/>
       <c r="M155" s="14" t="inlineStr"/>
@@ -7461,28 +7461,28 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>0128</t>
+          <t>5249</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>FRONTKN</t>
+          <t>IOIPG</t>
         </is>
       </c>
       <c r="D156" s="9" t="n">
-        <v>5.03</v>
+        <v>3.22</v>
       </c>
       <c r="E156" s="15" t="n">
-        <v>-0.007900000000000001</v>
+        <v>-0.0242</v>
       </c>
       <c r="F156" s="11" t="n">
-        <v>856800</v>
+        <v>913000</v>
       </c>
       <c r="G156" s="12" t="n">
-        <v>0.21</v>
+        <v>0.17</v>
       </c>
       <c r="H156" t="n">
-        <v>48.7</v>
+        <v>37.01</v>
       </c>
       <c r="I156" s="13" t="inlineStr">
         <is>
@@ -7490,10 +7490,10 @@
         </is>
       </c>
       <c r="J156" s="9" t="n">
-        <v>5.059</v>
+        <v>3.328</v>
       </c>
       <c r="K156" s="9" t="n">
-        <v>5.041</v>
+        <v>3.56</v>
       </c>
       <c r="L156" t="inlineStr"/>
       <c r="M156" s="14" t="inlineStr"/>
@@ -7506,28 +7506,28 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>1155</t>
+          <t>0128</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>MAYBANK</t>
+          <t>FRONTKN</t>
         </is>
       </c>
       <c r="D157" s="9" t="n">
-        <v>9.960000000000001</v>
+        <v>5.03</v>
       </c>
       <c r="E157" s="15" t="n">
-        <v>-0.001</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="F157" s="11" t="n">
-        <v>856800</v>
+        <v>911900</v>
       </c>
       <c r="G157" s="12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="H157" t="n">
-        <v>45.78</v>
+        <v>48.7</v>
       </c>
       <c r="I157" s="13" t="inlineStr">
         <is>
@@ -7535,10 +7535,10 @@
         </is>
       </c>
       <c r="J157" s="9" t="n">
-        <v>9.987</v>
+        <v>5.059</v>
       </c>
       <c r="K157" s="9" t="n">
-        <v>10.116</v>
+        <v>5.041</v>
       </c>
       <c r="L157" t="inlineStr"/>
       <c r="M157" s="14" t="inlineStr"/>
@@ -7551,28 +7551,28 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>5347</t>
+          <t>7293</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>TENAGA</t>
+          <t>YINSON</t>
         </is>
       </c>
       <c r="D158" s="9" t="n">
-        <v>13.2</v>
+        <v>2.1</v>
       </c>
       <c r="E158" s="15" t="n">
-        <v>-0.003</v>
+        <v>-0.004699999999999999</v>
       </c>
       <c r="F158" s="11" t="n">
-        <v>843400</v>
+        <v>907900</v>
       </c>
       <c r="G158" s="12" t="n">
-        <v>0.13</v>
+        <v>0.43</v>
       </c>
       <c r="H158" t="n">
-        <v>55.14</v>
+        <v>49.72</v>
       </c>
       <c r="I158" s="13" t="inlineStr">
         <is>
@@ -7580,10 +7580,10 @@
         </is>
       </c>
       <c r="J158" s="9" t="n">
-        <v>13.053</v>
+        <v>2.111</v>
       </c>
       <c r="K158" s="9" t="n">
-        <v>13.334</v>
+        <v>2.075</v>
       </c>
       <c r="L158" t="inlineStr"/>
       <c r="M158" s="14" t="inlineStr"/>
@@ -7596,28 +7596,28 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>1171</t>
+          <t>0375</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>MBSB</t>
+          <t>THMY</t>
         </is>
       </c>
       <c r="D159" s="9" t="n">
-        <v>0.505</v>
-      </c>
-      <c r="E159" s="17" t="n">
-        <v>0</v>
+        <v>2.01</v>
+      </c>
+      <c r="E159" s="10" t="n">
+        <v>0.0203</v>
       </c>
       <c r="F159" s="11" t="n">
-        <v>823200</v>
+        <v>893500</v>
       </c>
       <c r="G159" s="12" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="H159" t="n">
-        <v>29.82</v>
+        <v>47.22</v>
       </c>
       <c r="I159" s="16" t="inlineStr">
         <is>
@@ -7625,10 +7625,10 @@
         </is>
       </c>
       <c r="J159" s="9" t="n">
-        <v>0.531</v>
+        <v>2.065</v>
       </c>
       <c r="K159" s="9" t="n">
-        <v>0.5629999999999999</v>
+        <v>1.993</v>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" s="14" t="inlineStr"/>
@@ -7641,39 +7641,39 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>5102</t>
+          <t>5347</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>GCB</t>
+          <t>TENAGA</t>
         </is>
       </c>
       <c r="D160" s="9" t="n">
-        <v>1.23</v>
+        <v>13.2</v>
       </c>
       <c r="E160" s="15" t="n">
-        <v>-0.016</v>
+        <v>-0.003</v>
       </c>
       <c r="F160" s="11" t="n">
-        <v>813800</v>
+        <v>862200</v>
       </c>
       <c r="G160" s="12" t="n">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="H160" t="n">
-        <v>40.29</v>
-      </c>
-      <c r="I160" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55.14</v>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J160" s="9" t="n">
-        <v>1.278</v>
+        <v>13.053</v>
       </c>
       <c r="K160" s="9" t="n">
-        <v>1.316</v>
+        <v>13.334</v>
       </c>
       <c r="L160" t="inlineStr"/>
       <c r="M160" s="14" t="inlineStr"/>
@@ -7686,39 +7686,39 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>KERJAYA</t>
+          <t>DUFU</t>
         </is>
       </c>
       <c r="D161" s="9" t="n">
-        <v>3.37</v>
+        <v>2.92</v>
       </c>
       <c r="E161" s="10" t="n">
-        <v>0.0212</v>
+        <v>0.0069</v>
       </c>
       <c r="F161" s="11" t="n">
-        <v>776300</v>
+        <v>831800</v>
       </c>
       <c r="G161" s="12" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="H161" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>47.56</v>
+      </c>
+      <c r="I161" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J161" s="9" t="n">
-        <v>3.375</v>
+        <v>2.992</v>
       </c>
       <c r="K161" s="9" t="n">
-        <v>3.229</v>
+        <v>2.86</v>
       </c>
       <c r="L161" t="inlineStr"/>
       <c r="M161" s="14" t="inlineStr"/>
@@ -7731,28 +7731,28 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>1171</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>DUFU</t>
+          <t>MBSB</t>
         </is>
       </c>
       <c r="D162" s="9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="E162" s="15" t="n">
-        <v>-0.0069</v>
+        <v>0.51</v>
+      </c>
+      <c r="E162" s="10" t="n">
+        <v>0.009899999999999999</v>
       </c>
       <c r="F162" s="11" t="n">
-        <v>757700</v>
+        <v>826000</v>
       </c>
       <c r="G162" s="12" t="n">
         <v>0.28</v>
       </c>
       <c r="H162" t="n">
-        <v>45.68</v>
+        <v>33.54</v>
       </c>
       <c r="I162" s="16" t="inlineStr">
         <is>
@@ -7760,10 +7760,10 @@
         </is>
       </c>
       <c r="J162" s="9" t="n">
-        <v>2.988</v>
+        <v>0.532</v>
       </c>
       <c r="K162" s="9" t="n">
-        <v>2.859</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="L162" t="inlineStr"/>
       <c r="M162" s="14" t="inlineStr"/>
@@ -7776,39 +7776,39 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>3816</t>
+          <t>5102</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>MISC</t>
+          <t>GCB</t>
         </is>
       </c>
       <c r="D163" s="9" t="n">
-        <v>8.300000000000001</v>
-      </c>
-      <c r="E163" s="10" t="n">
-        <v>0.0061</v>
+        <v>1.23</v>
+      </c>
+      <c r="E163" s="15" t="n">
+        <v>-0.016</v>
       </c>
       <c r="F163" s="11" t="n">
-        <v>749600</v>
+        <v>824900</v>
       </c>
       <c r="G163" s="12" t="n">
-        <v>0.41</v>
+        <v>0.1</v>
       </c>
       <c r="H163" t="n">
-        <v>56.34</v>
-      </c>
-      <c r="I163" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>40.29</v>
+      </c>
+      <c r="I163" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J163" s="9" t="n">
-        <v>8.102</v>
+        <v>1.278</v>
       </c>
       <c r="K163" s="9" t="n">
-        <v>7.955</v>
+        <v>1.316</v>
       </c>
       <c r="L163" t="inlineStr"/>
       <c r="M163" s="14" t="inlineStr"/>
@@ -7821,39 +7821,39 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>5323</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>JPG</t>
+          <t>KERJAYA</t>
         </is>
       </c>
       <c r="D164" s="9" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="E164" s="17" t="n">
-        <v>0</v>
+        <v>3.33</v>
+      </c>
+      <c r="E164" s="10" t="n">
+        <v>0.0091</v>
       </c>
       <c r="F164" s="11" t="n">
-        <v>732300</v>
+        <v>780100</v>
       </c>
       <c r="G164" s="12" t="n">
-        <v>0.17</v>
+        <v>0.55</v>
       </c>
       <c r="H164" t="n">
-        <v>40.91</v>
-      </c>
-      <c r="I164" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>48.46</v>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J164" s="9" t="n">
-        <v>1.755</v>
+        <v>3.371</v>
       </c>
       <c r="K164" s="9" t="n">
-        <v>1.86</v>
+        <v>3.228</v>
       </c>
       <c r="L164" t="inlineStr"/>
       <c r="M164" s="14" t="inlineStr"/>
@@ -7866,28 +7866,28 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>0120</t>
+          <t>5323</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>VIS</t>
+          <t>JPG</t>
         </is>
       </c>
       <c r="D165" s="9" t="n">
-        <v>0.575</v>
-      </c>
-      <c r="E165" s="17" t="n">
-        <v>0</v>
+        <v>1.72</v>
+      </c>
+      <c r="E165" s="15" t="n">
+        <v>-0.0058</v>
       </c>
       <c r="F165" s="11" t="n">
-        <v>699000</v>
+        <v>762200</v>
       </c>
       <c r="G165" s="12" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="H165" t="n">
-        <v>52.91</v>
+        <v>39.48</v>
       </c>
       <c r="I165" s="16" t="inlineStr">
         <is>
@@ -7895,10 +7895,10 @@
         </is>
       </c>
       <c r="J165" s="9" t="n">
-        <v>0.574</v>
+        <v>1.754</v>
       </c>
       <c r="K165" s="9" t="n">
-        <v>0.482</v>
+        <v>1.86</v>
       </c>
       <c r="L165" t="inlineStr"/>
       <c r="M165" s="14" t="inlineStr"/>
@@ -7911,28 +7911,28 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>5330</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>TMK</t>
+          <t>MISC</t>
         </is>
       </c>
       <c r="D166" s="9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="E166" s="15" t="n">
-        <v>-0.0034</v>
+        <v>8.300000000000001</v>
+      </c>
+      <c r="E166" s="10" t="n">
+        <v>0.0061</v>
       </c>
       <c r="F166" s="11" t="n">
-        <v>683200</v>
+        <v>752200</v>
       </c>
       <c r="G166" s="12" t="n">
-        <v>0.6</v>
+        <v>0.41</v>
       </c>
       <c r="H166" t="n">
-        <v>56.78</v>
+        <v>56.34</v>
       </c>
       <c r="I166" s="13" t="inlineStr">
         <is>
@@ -7940,10 +7940,10 @@
         </is>
       </c>
       <c r="J166" s="9" t="n">
-        <v>2.792</v>
+        <v>8.102</v>
       </c>
       <c r="K166" s="9" t="n">
-        <v>2.839</v>
+        <v>7.955</v>
       </c>
       <c r="L166" t="inlineStr"/>
       <c r="M166" s="14" t="inlineStr"/>
@@ -7956,28 +7956,28 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>0120</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>TROP</t>
+          <t>VIS</t>
         </is>
       </c>
       <c r="D167" s="9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="E167" s="17" t="n">
-        <v>0</v>
+        <v>0.58</v>
+      </c>
+      <c r="E167" s="10" t="n">
+        <v>0.008699999999999999</v>
       </c>
       <c r="F167" s="11" t="n">
-        <v>659000</v>
+        <v>709000</v>
       </c>
       <c r="G167" s="12" t="n">
-        <v>0.67</v>
+        <v>0.11</v>
       </c>
       <c r="H167" t="n">
-        <v>48.65</v>
+        <v>53.52</v>
       </c>
       <c r="I167" s="16" t="inlineStr">
         <is>
@@ -7985,10 +7985,10 @@
         </is>
       </c>
       <c r="J167" s="9" t="n">
-        <v>1.184</v>
+        <v>0.574</v>
       </c>
       <c r="K167" s="9" t="n">
-        <v>1.188</v>
+        <v>0.482</v>
       </c>
       <c r="L167" t="inlineStr"/>
       <c r="M167" s="14" t="inlineStr"/>
@@ -8001,39 +8001,39 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>8664</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>SPSETIA</t>
+          <t>TROP</t>
         </is>
       </c>
       <c r="D168" s="9" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="E168" s="10" t="n">
-        <v>0.0145</v>
+        <v>1.18</v>
+      </c>
+      <c r="E168" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F168" s="11" t="n">
-        <v>648500</v>
+        <v>709000</v>
       </c>
       <c r="G168" s="12" t="n">
-        <v>0.1</v>
+        <v>0.73</v>
       </c>
       <c r="H168" t="n">
-        <v>42.21</v>
-      </c>
-      <c r="I168" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>48.65</v>
+      </c>
+      <c r="I168" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J168" s="9" t="n">
-        <v>0.714</v>
+        <v>1.184</v>
       </c>
       <c r="K168" s="9" t="n">
-        <v>0.774</v>
+        <v>1.188</v>
       </c>
       <c r="L168" t="inlineStr"/>
       <c r="M168" s="14" t="inlineStr"/>
@@ -8046,28 +8046,28 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>DRBHCOM</t>
+          <t>TMK</t>
         </is>
       </c>
       <c r="D169" s="9" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="E169" s="10" t="n">
-        <v>0.0184</v>
+        <v>2.9</v>
+      </c>
+      <c r="E169" s="15" t="n">
+        <v>-0.0034</v>
       </c>
       <c r="F169" s="11" t="n">
-        <v>645100</v>
+        <v>687500</v>
       </c>
       <c r="G169" s="12" t="n">
-        <v>1.07</v>
+        <v>0.6</v>
       </c>
       <c r="H169" t="n">
-        <v>33.16</v>
+        <v>56.78</v>
       </c>
       <c r="I169" s="13" t="inlineStr">
         <is>
@@ -8075,10 +8075,10 @@
         </is>
       </c>
       <c r="J169" s="9" t="n">
-        <v>0.862</v>
+        <v>2.792</v>
       </c>
       <c r="K169" s="9" t="n">
-        <v>0.924</v>
+        <v>2.839</v>
       </c>
       <c r="L169" t="inlineStr"/>
       <c r="M169" s="14" t="inlineStr"/>
@@ -8091,39 +8091,39 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>9296</t>
+          <t>1619</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>RCECAP</t>
+          <t>DRBHCOM</t>
         </is>
       </c>
       <c r="D170" s="9" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="E170" s="15" t="n">
-        <v>-0.0213</v>
+        <v>0.83</v>
+      </c>
+      <c r="E170" s="10" t="n">
+        <v>0.0184</v>
       </c>
       <c r="F170" s="11" t="n">
-        <v>634500</v>
+        <v>662300</v>
       </c>
       <c r="G170" s="12" t="n">
-        <v>1.8</v>
+        <v>1.1</v>
       </c>
       <c r="H170" t="n">
-        <v>29.15</v>
-      </c>
-      <c r="I170" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>33.16</v>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J170" s="9" t="n">
-        <v>0.958</v>
+        <v>0.862</v>
       </c>
       <c r="K170" s="9" t="n">
-        <v>0.993</v>
+        <v>0.924</v>
       </c>
       <c r="L170" t="inlineStr"/>
       <c r="M170" s="14" t="inlineStr"/>
@@ -8136,39 +8136,39 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>9792</t>
+          <t>9296</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>SEG</t>
+          <t>RCECAP</t>
         </is>
       </c>
       <c r="D171" s="9" t="n">
-        <v>0.635</v>
-      </c>
-      <c r="E171" s="17" t="n">
-        <v>0</v>
+        <v>0.92</v>
+      </c>
+      <c r="E171" s="15" t="n">
+        <v>-0.0213</v>
       </c>
       <c r="F171" s="11" t="n">
-        <v>625100</v>
+        <v>656500</v>
       </c>
       <c r="G171" s="12" t="n">
-        <v>0.59</v>
+        <v>1.86</v>
       </c>
       <c r="H171" t="n">
-        <v>55</v>
-      </c>
-      <c r="I171" s="13" t="inlineStr">
-        <is>
-          <t>多头</t>
+        <v>29.15</v>
+      </c>
+      <c r="I171" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
         </is>
       </c>
       <c r="J171" s="9" t="n">
-        <v>0.633</v>
+        <v>0.958</v>
       </c>
       <c r="K171" s="9" t="n">
-        <v>0.632</v>
+        <v>0.993</v>
       </c>
       <c r="L171" t="inlineStr"/>
       <c r="M171" s="14" t="inlineStr"/>
@@ -8181,28 +8181,28 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>5162</t>
+          <t>0167</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>VSTECS</t>
+          <t>MCLEAN</t>
         </is>
       </c>
       <c r="D172" s="9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="E172" s="15" t="n">
-        <v>-0.0069</v>
+        <v>0.59</v>
+      </c>
+      <c r="E172" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F172" s="11" t="n">
-        <v>609200</v>
+        <v>653200</v>
       </c>
       <c r="G172" s="12" t="n">
-        <v>0.32</v>
+        <v>0.19</v>
       </c>
       <c r="H172" t="n">
-        <v>33.47</v>
+        <v>29.28</v>
       </c>
       <c r="I172" s="16" t="inlineStr">
         <is>
@@ -8210,10 +8210,10 @@
         </is>
       </c>
       <c r="J172" s="9" t="n">
-        <v>1.568</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="K172" s="9" t="n">
-        <v>1.644</v>
+        <v>0.736</v>
       </c>
       <c r="L172" t="inlineStr"/>
       <c r="M172" s="14" t="inlineStr"/>
@@ -8226,28 +8226,28 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>1015</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>AMBANK</t>
+          <t>VSTECS</t>
         </is>
       </c>
       <c r="D173" s="9" t="n">
-        <v>6.29</v>
-      </c>
-      <c r="E173" s="10" t="n">
-        <v>0.0064</v>
+        <v>1.45</v>
+      </c>
+      <c r="E173" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F173" s="11" t="n">
-        <v>605800</v>
+        <v>652000</v>
       </c>
       <c r="G173" s="12" t="n">
-        <v>0.09</v>
+        <v>0.35</v>
       </c>
       <c r="H173" t="n">
-        <v>43.52</v>
+        <v>34.18</v>
       </c>
       <c r="I173" s="16" t="inlineStr">
         <is>
@@ -8255,10 +8255,10 @@
         </is>
       </c>
       <c r="J173" s="9" t="n">
-        <v>6.341</v>
+        <v>1.569</v>
       </c>
       <c r="K173" s="9" t="n">
-        <v>6.667</v>
+        <v>1.645</v>
       </c>
       <c r="L173" t="inlineStr"/>
       <c r="M173" s="14" t="inlineStr"/>
@@ -8271,28 +8271,28 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>5005</t>
+          <t>1015</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>UNISEM</t>
+          <t>AMBANK</t>
         </is>
       </c>
       <c r="D174" s="9" t="n">
-        <v>4.1</v>
+        <v>6.3</v>
       </c>
       <c r="E174" s="10" t="n">
-        <v>0.009899999999999999</v>
+        <v>0.008</v>
       </c>
       <c r="F174" s="11" t="n">
-        <v>569600</v>
+        <v>633800</v>
       </c>
       <c r="G174" s="12" t="n">
-        <v>0.25</v>
+        <v>0.09</v>
       </c>
       <c r="H174" t="n">
-        <v>44.62</v>
+        <v>44.15</v>
       </c>
       <c r="I174" s="16" t="inlineStr">
         <is>
@@ -8300,10 +8300,10 @@
         </is>
       </c>
       <c r="J174" s="9" t="n">
-        <v>4.213</v>
+        <v>6.342</v>
       </c>
       <c r="K174" s="9" t="n">
-        <v>4.296</v>
+        <v>6.667</v>
       </c>
       <c r="L174" t="inlineStr"/>
       <c r="M174" s="14" t="inlineStr"/>
@@ -8316,39 +8316,39 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>5357</t>
+          <t>9792</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>SKYECHIP</t>
+          <t>SEG</t>
         </is>
       </c>
       <c r="D175" s="9" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="E175" s="15" t="n">
-        <v>-0.0109</v>
+        <v>0.635</v>
+      </c>
+      <c r="E175" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="F175" s="11" t="n">
-        <v>565500</v>
+        <v>625100</v>
       </c>
       <c r="G175" s="12" t="n">
-        <v>0.16</v>
+        <v>0.59</v>
       </c>
       <c r="H175" t="n">
-        <v>38.75</v>
-      </c>
-      <c r="I175" s="16" t="inlineStr">
-        <is>
-          <t>空头</t>
+        <v>55</v>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>多头</t>
         </is>
       </c>
       <c r="J175" s="9" t="n">
-        <v>2.848</v>
+        <v>0.633</v>
       </c>
       <c r="K175" s="9" t="n">
-        <v>2.982</v>
+        <v>0.632</v>
       </c>
       <c r="L175" t="inlineStr"/>
       <c r="M175" s="14" t="inlineStr"/>
@@ -8361,28 +8361,28 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>5328</t>
+          <t>5005</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>LWSABAH</t>
+          <t>UNISEM</t>
         </is>
       </c>
       <c r="D176" s="9" t="n">
-        <v>1.48</v>
+        <v>4.12</v>
       </c>
       <c r="E176" s="10" t="n">
-        <v>0.0068</v>
+        <v>0.0148</v>
       </c>
       <c r="F176" s="11" t="n">
-        <v>553900</v>
+        <v>610400</v>
       </c>
       <c r="G176" s="12" t="n">
-        <v>0.57</v>
+        <v>0.27</v>
       </c>
       <c r="H176" t="n">
-        <v>33.87</v>
+        <v>45.39</v>
       </c>
       <c r="I176" s="16" t="inlineStr">
         <is>
@@ -8390,10 +8390,10 @@
         </is>
       </c>
       <c r="J176" s="9" t="n">
-        <v>1.573</v>
+        <v>4.215</v>
       </c>
       <c r="K176" s="9" t="n">
-        <v>1.626</v>
+        <v>4.297</v>
       </c>
       <c r="L176" t="inlineStr"/>
       <c r="M176" s="14" t="inlineStr"/>
@@ -8406,28 +8406,28 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>5321</t>
+          <t>5357</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>KEYFIELD</t>
+          <t>SKYECHIP</t>
         </is>
       </c>
       <c r="D177" s="9" t="n">
-        <v>1.35</v>
+        <v>2.73</v>
       </c>
       <c r="E177" s="15" t="n">
-        <v>-0.0357</v>
+        <v>-0.0109</v>
       </c>
       <c r="F177" s="11" t="n">
-        <v>538200</v>
+        <v>601400</v>
       </c>
       <c r="G177" s="12" t="n">
-        <v>4.63</v>
+        <v>0.17</v>
       </c>
       <c r="H177" t="n">
-        <v>43.54</v>
+        <v>38.75</v>
       </c>
       <c r="I177" s="16" t="inlineStr">
         <is>
@@ -8435,10 +8435,10 @@
         </is>
       </c>
       <c r="J177" s="9" t="n">
-        <v>1.384</v>
+        <v>2.848</v>
       </c>
       <c r="K177" s="9" t="n">
-        <v>1.371</v>
+        <v>2.982</v>
       </c>
       <c r="L177" t="inlineStr"/>
       <c r="M177" s="14" t="inlineStr"/>
@@ -8451,28 +8451,28 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>7579</t>
+          <t>5328</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>AWC</t>
+          <t>LWSABAH</t>
         </is>
       </c>
       <c r="D178" s="9" t="n">
-        <v>0.655</v>
+        <v>1.48</v>
       </c>
       <c r="E178" s="10" t="n">
-        <v>0.0077</v>
+        <v>0.0068</v>
       </c>
       <c r="F178" s="11" t="n">
-        <v>530200</v>
+        <v>557100</v>
       </c>
       <c r="G178" s="12" t="n">
-        <v>0.2</v>
+        <v>0.57</v>
       </c>
       <c r="H178" t="n">
-        <v>54.65</v>
+        <v>33.87</v>
       </c>
       <c r="I178" s="16" t="inlineStr">
         <is>
@@ -8480,16 +8480,241 @@
         </is>
       </c>
       <c r="J178" s="9" t="n">
-        <v>0.65</v>
+        <v>1.573</v>
       </c>
       <c r="K178" s="9" t="n">
-        <v>0.573</v>
+        <v>1.626</v>
       </c>
       <c r="L178" t="inlineStr"/>
       <c r="M178" s="14" t="inlineStr"/>
     </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>5321</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>KEYFIELD</t>
+        </is>
+      </c>
+      <c r="D179" s="9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="E179" s="15" t="n">
+        <v>-0.0214</v>
+      </c>
+      <c r="F179" s="11" t="n">
+        <v>540200</v>
+      </c>
+      <c r="G179" s="12" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="H179" t="n">
+        <v>46.92</v>
+      </c>
+      <c r="I179" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J179" s="9" t="n">
+        <v>1.386</v>
+      </c>
+      <c r="K179" s="9" t="n">
+        <v>1.371</v>
+      </c>
+      <c r="L179" t="inlineStr"/>
+      <c r="M179" s="14" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>7579</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>AWC</t>
+        </is>
+      </c>
+      <c r="D180" s="9" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="E180" s="10" t="n">
+        <v>0.0077</v>
+      </c>
+      <c r="F180" s="11" t="n">
+        <v>530200</v>
+      </c>
+      <c r="G180" s="12" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="H180" t="n">
+        <v>54.65</v>
+      </c>
+      <c r="I180" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J180" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="K180" s="9" t="n">
+        <v>0.573</v>
+      </c>
+      <c r="L180" t="inlineStr"/>
+      <c r="M180" s="14" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>0223</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>SAMAIDEN</t>
+        </is>
+      </c>
+      <c r="D181" s="9" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E181" s="15" t="n">
+        <v>-0.0035</v>
+      </c>
+      <c r="F181" s="11" t="n">
+        <v>516400</v>
+      </c>
+      <c r="G181" s="12" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H181" t="n">
+        <v>56.34</v>
+      </c>
+      <c r="I181" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J181" s="9" t="n">
+        <v>2.808</v>
+      </c>
+      <c r="K181" s="9" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="L181" t="inlineStr"/>
+      <c r="M181" s="14" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>0196</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>QES</t>
+        </is>
+      </c>
+      <c r="D182" s="9" t="n">
+        <v>0.575</v>
+      </c>
+      <c r="E182" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F182" s="11" t="n">
+        <v>507600</v>
+      </c>
+      <c r="G182" s="12" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="H182" t="n">
+        <v>46.61</v>
+      </c>
+      <c r="I182" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J182" s="9" t="n">
+        <v>0.592</v>
+      </c>
+      <c r="K182" s="9" t="n">
+        <v>0.585</v>
+      </c>
+      <c r="L182" t="inlineStr"/>
+      <c r="M182" s="14" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>表格</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>5326</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>99SMART</t>
+        </is>
+      </c>
+      <c r="D183" s="9" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="E183" s="10" t="n">
+        <v>0.006500000000000001</v>
+      </c>
+      <c r="F183" s="11" t="n">
+        <v>505300</v>
+      </c>
+      <c r="G183" s="12" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H183" t="n">
+        <v>41.56</v>
+      </c>
+      <c r="I183" s="16" t="inlineStr">
+        <is>
+          <t>空头</t>
+        </is>
+      </c>
+      <c r="J183" s="9" t="n">
+        <v>3.126</v>
+      </c>
+      <c r="K183" s="9" t="n">
+        <v>3.278</v>
+      </c>
+      <c r="L183" t="inlineStr"/>
+      <c r="M183" s="14" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M178"/>
+  <autoFilter ref="A1:M183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>